--- a/data/uptrend_output.xlsx
+++ b/data/uptrend_output.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G241"/>
+  <dimension ref="A1:G234"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -522,22 +522,22 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1379.3</v>
+        <v>1444.97</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1312.77</v>
+        <v>1367.33</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1441.2</v>
+        <v>1447.8</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>1440.1</v>
+        <v>1457.9</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>3MINDIA</t>
+          <t>AAREYDRUGS</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -551,22 +551,22 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>34416.67</v>
+        <v>88.26000000000001</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>33663.33</v>
+        <v>84.26000000000001</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>34415</v>
+        <v>88.20999999999999</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>34500</v>
+        <v>87.89</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>A2ZINFRA</t>
+          <t>AARTIPHARM</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -580,22 +580,22 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>16.8</v>
+        <v>852.27</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>16.03</v>
+        <v>818.28</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>16.63</v>
+        <v>845.4</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>16.52</v>
+        <v>843.1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>AAREYDRUGS</t>
+          <t>ADL</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -609,22 +609,22 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>84.84999999999999</v>
+        <v>75.45</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>80.48999999999999</v>
+        <v>70.98999999999999</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>89.01000000000001</v>
+        <v>75.75</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>89.01000000000001</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>AARTECH</t>
+          <t>ADOR</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -638,22 +638,22 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>49.6</v>
+        <v>1665.8</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>47.63</v>
+        <v>1572.87</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>49.16</v>
+        <v>1705.2</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>48.7</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>ADANIENT</t>
+          <t>ADROITINFO</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -667,22 +667,22 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>3169.23</v>
+        <v>10.7</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>3117.03</v>
+        <v>10.12</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>3168.5</v>
+        <v>10.3</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>3168.5</v>
+        <v>10.25</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>ADROITINFO</t>
+          <t>ADVAIT</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -696,22 +696,22 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>10.59</v>
+        <v>2204.93</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>10.06</v>
+        <v>2124.9</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>10.44</v>
+        <v>2170.7</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>10.25</v>
+        <v>2162</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>AEROENTER</t>
+          <t>AEROPLANE</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -725,22 +725,22 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>146.47</v>
+        <v>176.37</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>141.49</v>
+        <v>171.1</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>146.29</v>
+        <v>174.33</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>146.1</v>
+        <v>174.88</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AETHER</t>
+          <t>ALBERTDAVD</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -754,22 +754,22 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1691.37</v>
+        <v>914.28</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1641.07</v>
+        <v>877.02</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1696.8</v>
+        <v>897.9</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>1700</v>
+        <v>907.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AHCL</t>
+          <t>ALMONDZ</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -783,22 +783,22 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>15.98</v>
+        <v>17.26</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>15.12</v>
+        <v>15.85</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>15.91</v>
+        <v>17.53</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>15.89</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>AHLADA</t>
+          <t>AMIRCHAND</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -812,22 +812,22 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>38.96</v>
+        <v>181.7</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>37.24</v>
+        <v>171.51</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>38.06</v>
+        <v>185.11</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>38.85</v>
+        <v>184.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>ALLTIME</t>
+          <t>ANDHRSUGAR</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -841,22 +841,22 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>208.48</v>
+        <v>100.85</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>201.44</v>
+        <v>96.12</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>203.79</v>
+        <v>99.64</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>202.7</v>
+        <v>100.3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>ALMONDZ</t>
+          <t>AONELIQUID</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -870,22 +870,22 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>16.63</v>
+        <v>1074.67</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>14.96</v>
+        <v>1074.65</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>16.96</v>
+        <v>1074.89</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>16.99</v>
+        <v>1074.89</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>AMBER</t>
+          <t>APCOTEXIND</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -899,22 +899,22 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>7717.5</v>
+        <v>635.67</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>7508.17</v>
+        <v>613.35</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>7675</v>
+        <v>646.3</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>7675</v>
+        <v>642</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>AMIRCHAND</t>
+          <t>APTECHT</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -928,22 +928,22 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>181.7</v>
+        <v>93.2</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>171.51</v>
+        <v>90.27</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>185.11</v>
+        <v>91.84</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>184.5</v>
+        <v>92.95</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>ANANDRATHI</t>
+          <t>ARFIN</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -957,22 +957,22 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>2206</v>
+        <v>86.83</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>2170.4</v>
+        <v>84.48999999999999</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>2213.4</v>
+        <v>87.23</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>2219.7</v>
+        <v>87.3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>ANDHRAPAP</t>
+          <t>ASHOKAMET</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -986,22 +986,22 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>61.13</v>
+        <v>13.8</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>59.86</v>
+        <v>13.19</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>61.07</v>
+        <v>13.78</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>61.37</v>
+        <v>13.83</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>ANUHPHR</t>
+          <t>ASIANTILES</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1015,22 +1015,22 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>83.3</v>
+        <v>48.85</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>79.23</v>
+        <v>47.33</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>83.56999999999999</v>
+        <v>49.61</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>83.75</v>
+        <v>49.63</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>AONELIQUID</t>
+          <t>ASKAUTOLTD</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1044,22 +1044,22 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1074.44</v>
+        <v>640.12</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1074.42</v>
+        <v>612.02</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1074.76</v>
+        <v>659.9</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>1074.75</v>
+        <v>660</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>ATHERENERG</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>2224.2</v>
+        <v>1620.23</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>2152.37</v>
+        <v>1540.8</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>2265.6</v>
+        <v>1717.7</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>2265.6</v>
+        <v>1717.7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>APOLLOTYRE</t>
+          <t>ATLANTAELE</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -1102,22 +1102,22 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>448.25</v>
+        <v>1773.63</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>440.22</v>
+        <v>1696.1</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>443.5</v>
+        <v>1830.4</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>443.5</v>
+        <v>1837</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>AROGRANITE</t>
+          <t>AUROPHARMA</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -1131,22 +1131,22 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>25.97</v>
+        <v>1670.07</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>24.77</v>
+        <v>1620.3</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>25.1</v>
+        <v>1717</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>25.05</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>ASIANENE</t>
+          <t>AVADHSUGAR</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1160,22 +1160,22 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>501.38</v>
+        <v>844.55</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>469.33</v>
+        <v>804.15</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>480.8</v>
+        <v>855.3</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>479</v>
+        <v>852.1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>ASIANTILES</t>
+          <t>AXISBNKETF</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -1189,22 +1189,22 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>47.71</v>
+        <v>599.1900000000001</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>46.77</v>
+        <v>593.95</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>47.88</v>
+        <v>597.15</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>48</v>
+        <v>597.09</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>ATHERENERG</t>
+          <t>AXISCETF</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -1218,22 +1218,22 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>1545.87</v>
+        <v>120.57</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>1479.63</v>
+        <v>118.88</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>1616.3</v>
+        <v>121.12</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>1616.3</v>
+        <v>120.8</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>AXISBNKETF</t>
+          <t>AZAD</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -1247,22 +1247,22 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>599.1900000000001</v>
+        <v>2887.4</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>593.95</v>
+        <v>2804.5</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>597.15</v>
+        <v>2861.8</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>597.09</v>
+        <v>2878</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>AXISCETF</t>
+          <t>BAFNAPH</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1276,22 +1276,22 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>120.57</v>
+        <v>292.67</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>118.88</v>
+        <v>278.53</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>121.12</v>
+        <v>304.25</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>120.8</v>
+        <v>305.65</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>BALPHARMA</t>
+          <t>BAJAJ-AUTO</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -1305,22 +1305,22 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>85.90000000000001</v>
+        <v>11975.33</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>83.20999999999999</v>
+        <v>11754.67</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>84.8</v>
+        <v>12130</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>84.56</v>
+        <v>12130</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>BALUFORGE</t>
+          <t>BAJAJCON</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -1334,22 +1334,22 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>648.02</v>
+        <v>476.17</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>628.83</v>
+        <v>455.82</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>638.8</v>
+        <v>474.05</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>638.7</v>
+        <v>475</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>BELLACASA</t>
+          <t>BANARISUG</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -1363,16 +1363,16 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>249.97</v>
+        <v>4003.83</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>233.66</v>
+        <v>3817.87</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>247.3</v>
+        <v>3925.7</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>251.99</v>
+        <v>3934</v>
       </c>
     </row>
     <row r="32">
@@ -1392,16 +1392,16 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>6282.33</v>
+        <v>6395.67</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>6171.33</v>
+        <v>6222.5</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>6339.5</v>
+        <v>6438</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>6339.5</v>
+        <v>6548</v>
       </c>
     </row>
     <row r="33">
@@ -1421,22 +1421,22 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>232.95</v>
+        <v>240.51</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>220.04</v>
+        <v>231.33</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>238.75</v>
+        <v>250.68</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>238.75</v>
+        <v>250.68</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>BIRLACABLE</t>
+          <t>BHARATSE</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -1450,22 +1450,22 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>283.52</v>
+        <v>227.18</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>274.4</v>
+        <v>220.39</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>295.11</v>
+        <v>224.25</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>295.11</v>
+        <v>225</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>BIRLAPREC</t>
+          <t>BLISSGVS</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -1479,22 +1479,22 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>47.33</v>
+        <v>593.87</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>43.57</v>
+        <v>564.4</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>47.64</v>
+        <v>616.75</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>47.25</v>
+        <v>617.35</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>BLISSGVS</t>
+          <t>BLSE</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -1508,22 +1508,22 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>579.6799999999999</v>
+        <v>327.33</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>556.0700000000001</v>
+        <v>311.93</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>588.1</v>
+        <v>327.9</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>588.1</v>
+        <v>328.9</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>BLKASHYAP</t>
+          <t>BLUECHIP</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -1537,22 +1537,22 @@
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>58.23</v>
+        <v>2.14</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>54.39</v>
+        <v>2.14</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>58.57</v>
+        <v>2.18</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>58.61</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>BLUECHIP</t>
+          <t>BODALCHEM</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -1566,22 +1566,22 @@
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>2.1</v>
+        <v>104.18</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>2.1</v>
+        <v>95.42</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>2.14</v>
+        <v>118.89</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>2.14</v>
+        <v>118.89</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>BODALCHEM</t>
+          <t>BROOKS</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -1595,22 +1595,22 @@
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>94.95</v>
+        <v>68.89</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>87.52</v>
+        <v>64.79000000000001</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>99.08</v>
+        <v>66.54000000000001</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>99.19</v>
+        <v>67.73999999999999</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>BROOKS</t>
+          <t>CARERATING</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -1624,22 +1624,22 @@
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>66.26000000000001</v>
+        <v>1711.33</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>63.21</v>
+        <v>1645.03</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>69.28</v>
+        <v>1729</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>69.28</v>
+        <v>1734.9</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>BSHSL</t>
+          <t>CARRARO</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -1653,22 +1653,22 @@
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>91.23999999999999</v>
+        <v>561.53</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>88.40000000000001</v>
+        <v>543.17</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>91.84999999999999</v>
+        <v>559.4</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>90.5</v>
+        <v>558</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>CALSOFT</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -1682,22 +1682,22 @@
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>33.84</v>
+        <v>1423.33</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>33.33</v>
+        <v>1406.8</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>35.5</v>
+        <v>1409.2</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>35.5</v>
+        <v>1409.2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>CAPLIPOINT</t>
+          <t>CMRGREEN</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -1711,22 +1711,22 @@
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>2560.5</v>
+        <v>227.1</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>2492.67</v>
+        <v>218.45</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>2517.2</v>
+        <v>230.78</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>2523.8</v>
+        <v>232</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>CARERATING</t>
+          <t>CNL</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -1740,22 +1740,22 @@
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>1674.67</v>
+        <v>1278.42</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>1626.67</v>
+        <v>1204.27</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>1682.1</v>
+        <v>1279.6</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>1685.2</v>
+        <v>1280.1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>CARRARO</t>
+          <t>COFORGE</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -1769,22 +1769,22 @@
         </is>
       </c>
       <c r="D45" s="3" t="n">
-        <v>550.97</v>
+        <v>1982.27</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>535.02</v>
+        <v>1921.2</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>557.8</v>
+        <v>1985.3</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>560</v>
+        <v>1985.3</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>CASHIETF</t>
+          <t>CRAFTSMAN</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -1798,22 +1798,22 @@
         </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>1077.89</v>
+        <v>11209.67</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>1077.1</v>
+        <v>10752</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>1077.45</v>
+        <v>11198.5</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>1077.46</v>
+        <v>11428.5</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>CCAVENUE</t>
+          <t>CRISIL</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -1827,22 +1827,22 @@
         </is>
       </c>
       <c r="D47" s="3" t="n">
-        <v>15.44</v>
+        <v>4785.97</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>15.14</v>
+        <v>4630.67</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>15.27</v>
+        <v>4821.8</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>15.27</v>
+        <v>4810</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>CCL</t>
+          <t>CSLFINANCE</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -1856,22 +1856,22 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1115.3</v>
+        <v>237.62</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1093.7</v>
+        <v>228.37</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1123.1</v>
+        <v>239.7</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>1125</v>
+        <v>240</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>CENTUM</t>
+          <t>CYIENT</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -1885,22 +1885,22 @@
         </is>
       </c>
       <c r="D49" s="3" t="n">
-        <v>3430.43</v>
+        <v>1121.83</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>3339.03</v>
+        <v>1049.52</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>3442.8</v>
+        <v>1174.8</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>3448.9</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>DALMIASUG</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -1914,22 +1914,22 @@
         </is>
       </c>
       <c r="D50" s="3" t="n">
-        <v>1421.1</v>
+        <v>496.82</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>1404.1</v>
+        <v>472.7</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>1423.5</v>
+        <v>484.15</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>1423.5</v>
+        <v>485</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>CMRGREEN</t>
+          <t>DBOL</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -1943,22 +1943,22 @@
         </is>
       </c>
       <c r="D51" s="3" t="n">
-        <v>222.98</v>
+        <v>130.96</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>216.68</v>
+        <v>123.42</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>225.11</v>
+        <v>127.24</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>225.02</v>
+        <v>127.5</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>CPPLUS</t>
+          <t>DGCONTENT</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -1972,22 +1972,22 @@
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>3620</v>
+        <v>26.06</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>3484.03</v>
+        <v>23.91</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>3576.6</v>
+        <v>25.2</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>3570.9</v>
+        <v>25.1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>CRAFTSMAN</t>
+          <t>DIFFNKG</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -2001,22 +2001,22 @@
         </is>
       </c>
       <c r="D53" s="3" t="n">
-        <v>10899.83</v>
+        <v>439.23</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>10566.33</v>
+        <v>401.82</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>11118</v>
+        <v>485.5</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>11097</v>
+        <v>493.2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>CRISIL</t>
+          <t>DIVISLAB</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -2030,22 +2030,22 @@
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>4681.83</v>
+        <v>9295.67</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>4547.6</v>
+        <v>9085.17</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>4732.7</v>
+        <v>9467</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>4740</v>
+        <v>9467</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>CYIENT</t>
+          <t>DODLA</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -2059,22 +2059,22 @@
         </is>
       </c>
       <c r="D55" s="3" t="n">
-        <v>1076.5</v>
+        <v>1116.07</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>1017.23</v>
+        <v>1074.93</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>1107.45</v>
+        <v>1080.6</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>1111.4</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>CYIENTDLM</t>
+          <t>DSKULKARNI</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -2088,22 +2088,22 @@
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>818.28</v>
+        <v>17.96</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>785.77</v>
+        <v>17.96</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>819.1</v>
+        <v>18.31</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>820</v>
+        <v>18.31</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>DALMIASUG</t>
+          <t>DYCL</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -2117,22 +2117,22 @@
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>489.03</v>
+        <v>485.23</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>470.02</v>
+        <v>458.7</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>477.95</v>
+        <v>493.2</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>482.55</v>
+        <v>490.9</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>DBSTOCKBRO</t>
+          <t>EBBETF0431</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -2146,22 +2146,22 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>29.25</v>
+        <v>1436.62</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>27.78</v>
+        <v>1430.64</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>29.48</v>
+        <v>1436.39</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>29.97</v>
+        <v>1436.15</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>DEEPINDS</t>
+          <t>ECLERX</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -2175,22 +2175,22 @@
         </is>
       </c>
       <c r="D59" s="3" t="n">
-        <v>677.38</v>
+        <v>2010.73</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>649.4</v>
+        <v>1927.67</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>674.45</v>
+        <v>1976.9</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>672</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>DELHIVERY</t>
+          <t>ELECTCAST</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -2204,22 +2204,22 @@
         </is>
       </c>
       <c r="D60" s="3" t="n">
-        <v>463.28</v>
+        <v>82.77</v>
       </c>
       <c r="E60" s="3" t="n">
-        <v>451.4</v>
+        <v>79.15000000000001</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>470.2</v>
+        <v>83.44</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>470.2</v>
+        <v>83.09999999999999</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>DIACABS</t>
+          <t>ELIQUID</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -2233,22 +2233,22 @@
         </is>
       </c>
       <c r="D61" s="3" t="n">
-        <v>345.13</v>
+        <v>1045.65</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>330.27</v>
+        <v>1043.4</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>349.4</v>
+        <v>1045.87</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>349.95</v>
+        <v>1045.87</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>DIFFNKG</t>
+          <t>EMKAY</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -2262,22 +2262,22 @@
         </is>
       </c>
       <c r="D62" s="3" t="n">
-        <v>408.03</v>
+        <v>254.86</v>
       </c>
       <c r="E62" s="3" t="n">
-        <v>392.45</v>
+        <v>241.94</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>411</v>
+        <v>257.18</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>412.2</v>
+        <v>254.48</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>DIVISLAB</t>
+          <t>ENGINERSIN</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -2291,22 +2291,22 @@
         </is>
       </c>
       <c r="D63" s="3" t="n">
-        <v>9154.33</v>
+        <v>256.87</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>8938.83</v>
+        <v>247.72</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>9239</v>
+        <v>261.87</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>9239</v>
+        <v>263</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>DSKULKARNI</t>
+          <t>EXICOM</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -2320,22 +2320,22 @@
         </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>17.96</v>
+        <v>167.22</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>17.96</v>
+        <v>158.72</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>18.31</v>
+        <v>165.99</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>18.31</v>
+        <v>166</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>DYCL</t>
+          <t>FEDDERSHOL</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -2349,22 +2349,22 @@
         </is>
       </c>
       <c r="D65" s="3" t="n">
-        <v>470.82</v>
+        <v>44.68</v>
       </c>
       <c r="E65" s="3" t="n">
-        <v>441.52</v>
+        <v>43.47</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>487.6</v>
+        <v>44.69</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>489</v>
+        <v>45</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>ECLERX</t>
+          <t>FINEORG</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -2378,22 +2378,22 @@
         </is>
       </c>
       <c r="D66" s="3" t="n">
-        <v>1977.57</v>
+        <v>5313.93</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>1912.23</v>
+        <v>5164.37</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>1955.5</v>
+        <v>5282.8</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>1945</v>
+        <v>5299.8</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>EIFFL</t>
+          <t>FMGOETZE</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -2407,22 +2407,22 @@
         </is>
       </c>
       <c r="D67" s="3" t="n">
-        <v>293.82</v>
+        <v>604.77</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>279.78</v>
+        <v>567.33</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>301.95</v>
+        <v>624.85</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>301.95</v>
+        <v>626.3</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>ELECTCAST</t>
+          <t>FRACTAL</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -2436,22 +2436,22 @@
         </is>
       </c>
       <c r="D68" s="3" t="n">
-        <v>81.11</v>
+        <v>854.85</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>77.59999999999999</v>
+        <v>833.75</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>81.5</v>
+        <v>852.15</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>81.3</v>
+        <v>844</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>EMUDHRA</t>
+          <t>GARFIBRES</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -2465,22 +2465,22 @@
         </is>
       </c>
       <c r="D69" s="3" t="n">
-        <v>562.52</v>
+        <v>809.2</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>544.85</v>
+        <v>786.3200000000001</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>559.65</v>
+        <v>813.85</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>555.15</v>
+        <v>818.8</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>ENTERO</t>
+          <t>GATECH</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -2494,22 +2494,22 @@
         </is>
       </c>
       <c r="D70" s="3" t="n">
-        <v>1763.1</v>
+        <v>1.07</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>1663.43</v>
+        <v>1.06</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>1808.6</v>
+        <v>1.1</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>1807</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>ESAFSFB</t>
+          <t>GEEKAYWIRE</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -2523,22 +2523,22 @@
         </is>
       </c>
       <c r="D71" s="3" t="n">
-        <v>44.83</v>
+        <v>26.06</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>43.47</v>
+        <v>23.29</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>44.71</v>
+        <v>26.7</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>44.76</v>
+        <v>26.8</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>EUREKAFORB</t>
+          <t>GHCLTEXTIL</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -2552,22 +2552,22 @@
         </is>
       </c>
       <c r="D72" s="3" t="n">
-        <v>434.55</v>
+        <v>132.33</v>
       </c>
       <c r="E72" s="3" t="n">
-        <v>419.52</v>
+        <v>126.92</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>427.75</v>
+        <v>134.77</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>428</v>
+        <v>133.6</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>FEDDERSHOL</t>
+          <t>GICL</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -2581,22 +2581,22 @@
         </is>
       </c>
       <c r="D73" s="3" t="n">
-        <v>43.81</v>
+        <v>23.9</v>
       </c>
       <c r="E73" s="3" t="n">
-        <v>42.69</v>
+        <v>22.96</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>43.99</v>
+        <v>23.84</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>44</v>
+        <v>23.9</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>FINEORG</t>
+          <t>GKSL</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -2610,22 +2610,22 @@
         </is>
       </c>
       <c r="D74" s="3" t="n">
-        <v>5274</v>
+        <v>161.11</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>5132.67</v>
+        <v>153.55</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>5282.5</v>
+        <v>158.14</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>5295</v>
+        <v>158.83</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>FIVESTAR</t>
+          <t>GOACARBON</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -2639,22 +2639,22 @@
         </is>
       </c>
       <c r="D75" s="3" t="n">
-        <v>536.22</v>
+        <v>365.78</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>514.63</v>
+        <v>352.15</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>537.85</v>
+        <v>369.55</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>539</v>
+        <v>370</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>FMNL</t>
+          <t>GRAPHITE</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -2668,22 +2668,22 @@
         </is>
       </c>
       <c r="D76" s="3" t="n">
-        <v>10.64</v>
+        <v>704.1799999999999</v>
       </c>
       <c r="E76" s="3" t="n">
-        <v>9.82</v>
+        <v>683.35</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>11</v>
+        <v>702.55</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>11</v>
+        <v>705.1</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>FOSECOIND</t>
+          <t>GRAUWEIL</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -2697,22 +2697,22 @@
         </is>
       </c>
       <c r="D77" s="3" t="n">
-        <v>6306.33</v>
+        <v>71.27</v>
       </c>
       <c r="E77" s="3" t="n">
-        <v>5882.5</v>
+        <v>68.23</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>6362</v>
+        <v>71.63</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>6300</v>
+        <v>71.5</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>FRACTAL</t>
+          <t>GVPTECH</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -2726,22 +2726,22 @@
         </is>
       </c>
       <c r="D78" s="3" t="n">
-        <v>849.85</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>828.37</v>
+        <v>7.74</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>844.3</v>
+        <v>8.59</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>845</v>
+        <v>8.359999999999999</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>GATECH</t>
+          <t>HALDYNGL</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -2755,22 +2755,22 @@
         </is>
       </c>
       <c r="D79" s="3" t="n">
-        <v>1.03</v>
+        <v>139.34</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>1.02</v>
+        <v>133.1</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>1.06</v>
+        <v>140.79</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>1.07</v>
+        <v>140</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>GEEKAYWIRE</t>
+          <t>HAPPYFORGE</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -2784,22 +2784,22 @@
         </is>
       </c>
       <c r="D80" s="3" t="n">
-        <v>24.02</v>
+        <v>2337.43</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>22.71</v>
+        <v>2243.3</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>24.69</v>
+        <v>2412</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>24.52</v>
+        <v>2419.1</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>GIPCL</t>
+          <t>HATSUN</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -2813,22 +2813,22 @@
         </is>
       </c>
       <c r="D81" s="3" t="n">
-        <v>205.02</v>
+        <v>1185.55</v>
       </c>
       <c r="E81" s="3" t="n">
-        <v>195.65</v>
+        <v>1127.85</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>205.91</v>
+        <v>1190.45</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>205.61</v>
+        <v>1189.55</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>GLAXO</t>
+          <t>HDFCLIQUID</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -2842,22 +2842,22 @@
         </is>
       </c>
       <c r="D82" s="3" t="n">
-        <v>3096.2</v>
+        <v>1075.78</v>
       </c>
       <c r="E82" s="3" t="n">
-        <v>3015.6</v>
+        <v>1075.75</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>3106.4</v>
+        <v>1076</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>3105</v>
+        <v>1076.01</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>GMMPFAUDLR</t>
+          <t>HDFCNIFIT</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -2871,22 +2871,22 @@
         </is>
       </c>
       <c r="D83" s="3" t="n">
-        <v>1039.13</v>
+        <v>33.23</v>
       </c>
       <c r="E83" s="3" t="n">
-        <v>1011.1</v>
+        <v>32.41</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>1026.7</v>
+        <v>32.97</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>1022.95</v>
+        <v>32.82</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>HAPPYFORGE</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -2900,22 +2900,22 @@
         </is>
       </c>
       <c r="D84" s="3" t="n">
-        <v>2282.87</v>
+        <v>253.08</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>2203</v>
+        <v>243.44</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>2307</v>
+        <v>249.09</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>2310</v>
+        <v>248.9</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>HATSUN</t>
+          <t>HITECHGEAR</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -2929,22 +2929,22 @@
         </is>
       </c>
       <c r="D85" s="3" t="n">
-        <v>1155.08</v>
+        <v>576.38</v>
       </c>
       <c r="E85" s="3" t="n">
-        <v>1075.45</v>
+        <v>547.47</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>1176.05</v>
+        <v>563.6</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>1177</v>
+        <v>560</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>HAWKINCOOK</t>
+          <t>IKIO</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -2958,22 +2958,22 @@
         </is>
       </c>
       <c r="D86" s="3" t="n">
-        <v>8262.67</v>
+        <v>211.43</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>8050.33</v>
+        <v>193.76</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>8230</v>
+        <v>215.48</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>8270</v>
+        <v>214.18</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>HDFCLIQUID</t>
+          <t>INDGN</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -2987,22 +2987,22 @@
         </is>
       </c>
       <c r="D87" s="3" t="n">
-        <v>1075.55</v>
+        <v>592.22</v>
       </c>
       <c r="E87" s="3" t="n">
-        <v>1075.52</v>
+        <v>569.08</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>1075.85</v>
+        <v>611.65</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>1075.87</v>
+        <v>608</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>HDFCPVTBAN</t>
+          <t>INDUSTOWER</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -3016,22 +3016,22 @@
         </is>
       </c>
       <c r="D88" s="3" t="n">
-        <v>28.86</v>
+        <v>386.23</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>28.13</v>
+        <v>377.35</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>28.32</v>
+        <v>388.8</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>28.38</v>
+        <v>388.8</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>HEADSUP</t>
+          <t>INFIBEAM</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -3045,22 +3045,22 @@
         </is>
       </c>
       <c r="D89" s="3" t="n">
-        <v>7.06</v>
+        <v>16.54</v>
       </c>
       <c r="E89" s="3" t="n">
-        <v>6.5</v>
+        <v>15.65</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>6.99</v>
+        <v>16.9</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>7</v>
+        <v>16.84</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>HEALTHADD</t>
+          <t>INGERRAND</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -3074,22 +3074,22 @@
         </is>
       </c>
       <c r="D90" s="3" t="n">
-        <v>16.93</v>
+        <v>4827.4</v>
       </c>
       <c r="E90" s="3" t="n">
-        <v>16.77</v>
+        <v>4652.1</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>16.91</v>
+        <v>4848.5</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>16.9</v>
+        <v>4850</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>INNOVACAP</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -3103,22 +3103,22 @@
         </is>
       </c>
       <c r="D91" s="3" t="n">
-        <v>22.14</v>
+        <v>1066.45</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>21.67</v>
+        <v>1028.07</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>21.89</v>
+        <v>1078.1</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>21.91</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>HEALTHY</t>
+          <t>INSECTICID</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -3132,22 +3132,22 @@
         </is>
       </c>
       <c r="D92" s="3" t="n">
-        <v>17.28</v>
+        <v>602.7</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>16.96</v>
+        <v>573.25</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>17.24</v>
+        <v>610.85</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>17.31</v>
+        <v>610</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>HEIDELBERG</t>
+          <t>INSPIRISYS</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -3161,22 +3161,22 @@
         </is>
       </c>
       <c r="D93" s="3" t="n">
-        <v>162.57</v>
+        <v>92.92</v>
       </c>
       <c r="E93" s="3" t="n">
-        <v>160.46</v>
+        <v>87.70999999999999</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>160.99</v>
+        <v>89.04000000000001</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>161</v>
+        <v>90.84999999999999</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>IOLCP</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -3190,22 +3190,22 @@
         </is>
       </c>
       <c r="D94" s="3" t="n">
-        <v>248.01</v>
+        <v>196.88</v>
       </c>
       <c r="E94" s="3" t="n">
-        <v>238.61</v>
+        <v>188.49</v>
       </c>
       <c r="F94" s="3" t="n">
-        <v>251.47</v>
+        <v>193.69</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>252.2</v>
+        <v>194</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>HSCL</t>
+          <t>IRIS</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -3219,22 +3219,22 @@
         </is>
       </c>
       <c r="D95" s="3" t="n">
-        <v>678.8</v>
+        <v>251.15</v>
       </c>
       <c r="E95" s="3" t="n">
-        <v>660.1</v>
+        <v>238.56</v>
       </c>
       <c r="F95" s="3" t="n">
-        <v>672.95</v>
+        <v>248.97</v>
       </c>
       <c r="G95" s="3" t="n">
-        <v>675.9</v>
+        <v>247.12</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>IFCI</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -3248,22 +3248,22 @@
         </is>
       </c>
       <c r="D96" s="3" t="n">
-        <v>89.27</v>
+        <v>34.61</v>
       </c>
       <c r="E96" s="3" t="n">
-        <v>83.36</v>
+        <v>33.76</v>
       </c>
       <c r="F96" s="3" t="n">
-        <v>89.95999999999999</v>
+        <v>34.32</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>90.2</v>
+        <v>34.47</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>IMAGICAA</t>
+          <t>ITAXIS</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -3277,22 +3277,22 @@
         </is>
       </c>
       <c r="D97" s="3" t="n">
-        <v>57.68</v>
+        <v>342.71</v>
       </c>
       <c r="E97" s="3" t="n">
-        <v>52.29</v>
+        <v>335.22</v>
       </c>
       <c r="F97" s="3" t="n">
-        <v>58.07</v>
+        <v>342.83</v>
       </c>
       <c r="G97" s="3" t="n">
-        <v>58.2</v>
+        <v>341.94</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>INDOCO</t>
+          <t>ITBEES</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -3306,22 +3306,22 @@
         </is>
       </c>
       <c r="D98" s="3" t="n">
-        <v>246.47</v>
+        <v>34.76</v>
       </c>
       <c r="E98" s="3" t="n">
-        <v>233.15</v>
+        <v>33.76</v>
       </c>
       <c r="F98" s="3" t="n">
-        <v>248.8</v>
+        <v>34.32</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>248</v>
+        <v>34.3</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>INFIBEAM</t>
+          <t>ITETF</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -3335,22 +3335,22 @@
         </is>
       </c>
       <c r="D99" s="3" t="n">
-        <v>16.54</v>
+        <v>33.31</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>15.65</v>
+        <v>32.18</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>16.9</v>
+        <v>32.74</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>16.84</v>
+        <v>32.9</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>INOXINDIA</t>
+          <t>ITIETF</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
@@ -3364,22 +3364,22 @@
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>2143.3</v>
+        <v>34.59</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>1976.07</v>
+        <v>33.84</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>2126.2</v>
+        <v>34.31</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>2118</v>
+        <v>34.25</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>IOLCP</t>
+          <t>IVC</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
@@ -3393,22 +3393,22 @@
         </is>
       </c>
       <c r="D101" s="3" t="n">
-        <v>193.42</v>
+        <v>8.74</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>182.54</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>194.95</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>193.9</v>
+        <v>9.08</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>IONEXCHANG</t>
+          <t>JINDWORLD</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
@@ -3422,22 +3422,22 @@
         </is>
       </c>
       <c r="D102" s="3" t="n">
-        <v>376.98</v>
+        <v>38.72</v>
       </c>
       <c r="E102" s="3" t="n">
-        <v>369.77</v>
+        <v>36.71</v>
       </c>
       <c r="F102" s="3" t="n">
-        <v>371.45</v>
+        <v>38.31</v>
       </c>
       <c r="G102" s="3" t="n">
-        <v>371.15</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>ITETF</t>
+          <t>JTLIND</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
@@ -3451,22 +3451,22 @@
         </is>
       </c>
       <c r="D103" s="3" t="n">
-        <v>32.97</v>
+        <v>89.67</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>32.01</v>
+        <v>84.33</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>33.08</v>
+        <v>89.93000000000001</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>33.17</v>
+        <v>89.33</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>JINDWORLD</t>
+          <t>JUSTDIAL</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
@@ -3480,22 +3480,22 @@
         </is>
       </c>
       <c r="D104" s="3" t="n">
-        <v>37.28</v>
+        <v>696.1799999999999</v>
       </c>
       <c r="E104" s="3" t="n">
-        <v>35.53</v>
+        <v>661.1799999999999</v>
       </c>
       <c r="F104" s="3" t="n">
-        <v>37.86</v>
+        <v>710.2</v>
       </c>
       <c r="G104" s="3" t="n">
-        <v>38</v>
+        <v>705.3</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>JMA</t>
+          <t>KALYANIFRG</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
@@ -3509,22 +3509,22 @@
         </is>
       </c>
       <c r="D105" s="3" t="n">
-        <v>96.31999999999999</v>
+        <v>799.27</v>
       </c>
       <c r="E105" s="3" t="n">
-        <v>90.04000000000001</v>
+        <v>693.2</v>
       </c>
       <c r="F105" s="3" t="n">
-        <v>95.09</v>
+        <v>914.3</v>
       </c>
       <c r="G105" s="3" t="n">
-        <v>95</v>
+        <v>914.3</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>JTLIND</t>
+          <t>KAMDHENU</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
@@ -3538,22 +3538,22 @@
         </is>
       </c>
       <c r="D106" s="3" t="n">
-        <v>86.23999999999999</v>
+        <v>36.62</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>80.87</v>
+        <v>34.79</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>89.87</v>
+        <v>36.58</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>89.59999999999999</v>
+        <v>36.8</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>JYOTICNC</t>
+          <t>KANANIIND</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
@@ -3567,22 +3567,22 @@
         </is>
       </c>
       <c r="D107" s="3" t="n">
-        <v>1036.27</v>
+        <v>1.54</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>1002.18</v>
+        <v>1.44</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>1039.4</v>
+        <v>1.52</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>1033.4</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>KAMATHOTEL</t>
+          <t>KAPSTON</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
@@ -3596,22 +3596,22 @@
         </is>
       </c>
       <c r="D108" s="3" t="n">
-        <v>238.05</v>
+        <v>556.23</v>
       </c>
       <c r="E108" s="3" t="n">
-        <v>225.19</v>
+        <v>521.3</v>
       </c>
       <c r="F108" s="3" t="n">
-        <v>228.3</v>
+        <v>586.8</v>
       </c>
       <c r="G108" s="3" t="n">
-        <v>229.84</v>
+        <v>590</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>KECL</t>
+          <t>KHADIM</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
@@ -3625,22 +3625,22 @@
         </is>
       </c>
       <c r="D109" s="3" t="n">
-        <v>134.58</v>
+        <v>117.47</v>
       </c>
       <c r="E109" s="3" t="n">
-        <v>128.95</v>
+        <v>111.74</v>
       </c>
       <c r="F109" s="3" t="n">
-        <v>134.83</v>
+        <v>116.16</v>
       </c>
       <c r="G109" s="3" t="n">
-        <v>134.7</v>
+        <v>116.16</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>KENNAMET</t>
+          <t>KLBRENG-B</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
@@ -3654,22 +3654,22 @@
         </is>
       </c>
       <c r="D110" s="3" t="n">
-        <v>4594.67</v>
+        <v>420.13</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>4288.87</v>
+        <v>400.45</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>4580.3</v>
+        <v>428.55</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>4620</v>
+        <v>428.75</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>KHADIM</t>
+          <t>KMSUGAR</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
@@ -3683,22 +3683,22 @@
         </is>
       </c>
       <c r="D111" s="3" t="n">
-        <v>114.64</v>
+        <v>33.22</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>108.02</v>
+        <v>30.97</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>117.63</v>
+        <v>32.49</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>116.15</v>
+        <v>32.64</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>KMEW</t>
+          <t>KOPRAN</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
@@ -3712,22 +3712,22 @@
         </is>
       </c>
       <c r="D112" s="3" t="n">
-        <v>2974.97</v>
+        <v>210.66</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>2817.37</v>
+        <v>194.3</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>3051.9</v>
+        <v>217.83</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>3052</v>
+        <v>217.9</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>KREBSBIO</t>
+          <t>KRISHIVAL</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
@@ -3741,22 +3741,22 @@
         </is>
       </c>
       <c r="D113" s="3" t="n">
-        <v>58.33</v>
+        <v>411.63</v>
       </c>
       <c r="E113" s="3" t="n">
-        <v>54.03</v>
+        <v>401.13</v>
       </c>
       <c r="F113" s="3" t="n">
-        <v>59.17</v>
+        <v>410.95</v>
       </c>
       <c r="G113" s="3" t="n">
-        <v>59</v>
+        <v>413</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>KRISHIVAL</t>
+          <t>LIQGRWBEES</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
@@ -3770,22 +3770,22 @@
         </is>
       </c>
       <c r="D114" s="3" t="n">
-        <v>410.2</v>
+        <v>1053.57</v>
       </c>
       <c r="E114" s="3" t="n">
-        <v>395.32</v>
+        <v>1053.51</v>
       </c>
       <c r="F114" s="3" t="n">
-        <v>410.25</v>
+        <v>1053.77</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>411.8</v>
+        <v>1053.78</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>LIQUIDBETA</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
@@ -3799,22 +3799,22 @@
         </is>
       </c>
       <c r="D115" s="3" t="n">
-        <v>1922.27</v>
+        <v>1005.95</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>1881.97</v>
+        <v>1005.94</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>1938.5</v>
+        <v>1006.32</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>1938.5</v>
+        <v>1006.32</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>LGEINDIA</t>
+          <t>LIQUIDBETF</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
@@ -3828,22 +3828,22 @@
         </is>
       </c>
       <c r="D116" s="3" t="n">
-        <v>1713.03</v>
+        <v>1096.66</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>1673.17</v>
+        <v>1096.64</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>1691.4</v>
+        <v>1096.88</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>1686</v>
+        <v>1096.87</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>LIQGRWBEES</t>
+          <t>LIQUIDCASE</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
@@ -3857,22 +3857,22 @@
         </is>
       </c>
       <c r="D117" s="3" t="n">
-        <v>1053.35</v>
+        <v>115.7</v>
       </c>
       <c r="E117" s="3" t="n">
-        <v>1053.33</v>
+        <v>115.68</v>
       </c>
       <c r="F117" s="3" t="n">
-        <v>1053.65</v>
+        <v>115.71</v>
       </c>
       <c r="G117" s="3" t="n">
-        <v>1053.66</v>
+        <v>115.72</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDADD</t>
+          <t>LIQUIDSHRI</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
@@ -3886,22 +3886,22 @@
         </is>
       </c>
       <c r="D118" s="3" t="n">
-        <v>1142.34</v>
+        <v>1119.35</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>1142.2</v>
+        <v>1119.33</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>1142.56</v>
+        <v>1119.57</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>1142.57</v>
+        <v>1119.58</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDBETA</t>
+          <t>LOKESHMACH</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
@@ -3915,22 +3915,22 @@
         </is>
       </c>
       <c r="D119" s="3" t="n">
-        <v>1005.64</v>
+        <v>332.38</v>
       </c>
       <c r="E119" s="3" t="n">
-        <v>1005.64</v>
+        <v>303.6</v>
       </c>
       <c r="F119" s="3" t="n">
-        <v>1005.78</v>
+        <v>345.25</v>
       </c>
       <c r="G119" s="3" t="n">
-        <v>1005.78</v>
+        <v>342.1</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDBETF</t>
+          <t>LUMAXTECH</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
@@ -3944,22 +3944,22 @@
         </is>
       </c>
       <c r="D120" s="3" t="n">
-        <v>1096.43</v>
+        <v>2018.47</v>
       </c>
       <c r="E120" s="3" t="n">
-        <v>1096.41</v>
+        <v>1933.97</v>
       </c>
       <c r="F120" s="3" t="n">
-        <v>1096.75</v>
+        <v>2078.5</v>
       </c>
       <c r="G120" s="3" t="n">
-        <v>1096.76</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDCASE</t>
+          <t>MAANALU</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
@@ -3973,22 +3973,22 @@
         </is>
       </c>
       <c r="D121" s="3" t="n">
-        <v>115.68</v>
+        <v>122.28</v>
       </c>
       <c r="E121" s="3" t="n">
-        <v>115.65</v>
+        <v>116.54</v>
       </c>
       <c r="F121" s="3" t="n">
-        <v>115.7</v>
+        <v>122.67</v>
       </c>
       <c r="G121" s="3" t="n">
-        <v>115.71</v>
+        <v>121.35</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDSHRI</t>
+          <t>MAFANG</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
@@ -4002,22 +4002,22 @@
         </is>
       </c>
       <c r="D122" s="3" t="n">
-        <v>1119.11</v>
+        <v>207.88</v>
       </c>
       <c r="E122" s="3" t="n">
-        <v>1119.09</v>
+        <v>207.88</v>
       </c>
       <c r="F122" s="3" t="n">
-        <v>1119.42</v>
+        <v>209.95</v>
       </c>
       <c r="G122" s="3" t="n">
-        <v>1119.42</v>
+        <v>209.95</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>MAFANG</t>
+          <t>MAFATIND</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
@@ -4031,22 +4031,22 @@
         </is>
       </c>
       <c r="D123" s="3" t="n">
-        <v>206.32</v>
+        <v>123.82</v>
       </c>
       <c r="E123" s="3" t="n">
-        <v>206.32</v>
+        <v>120.83</v>
       </c>
       <c r="F123" s="3" t="n">
-        <v>207.13</v>
+        <v>122.64</v>
       </c>
       <c r="G123" s="3" t="n">
-        <v>207.13</v>
+        <v>123.5</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>MAHSEAMLES</t>
+          <t>MAGADSUGAR</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
@@ -4060,22 +4060,22 @@
         </is>
       </c>
       <c r="D124" s="3" t="n">
-        <v>655.17</v>
+        <v>594.08</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>636.73</v>
+        <v>557.65</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>661.7</v>
+        <v>595</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>663.5</v>
+        <v>600</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>MANAKSTEEL</t>
+          <t>MAHASTEEL</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
@@ -4089,22 +4089,22 @@
         </is>
       </c>
       <c r="D125" s="3" t="n">
-        <v>91.39</v>
+        <v>1331.67</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>87.90000000000001</v>
+        <v>1236.27</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>94.79000000000001</v>
+        <v>1373</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>94.79000000000001</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>MANCREDIT</t>
+          <t>MAHSEAMLES</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
@@ -4118,22 +4118,22 @@
         </is>
       </c>
       <c r="D126" s="3" t="n">
-        <v>238.03</v>
+        <v>663.03</v>
       </c>
       <c r="E126" s="3" t="n">
-        <v>224.15</v>
+        <v>642.67</v>
       </c>
       <c r="F126" s="3" t="n">
-        <v>247.65</v>
+        <v>663.2</v>
       </c>
       <c r="G126" s="3" t="n">
-        <v>255.9</v>
+        <v>663.5</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>MANINFRA</t>
+          <t>MALLCOM</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
@@ -4147,22 +4147,22 @@
         </is>
       </c>
       <c r="D127" s="3" t="n">
-        <v>118.58</v>
+        <v>1011.3</v>
       </c>
       <c r="E127" s="3" t="n">
-        <v>114.71</v>
+        <v>968.05</v>
       </c>
       <c r="F127" s="3" t="n">
-        <v>122.81</v>
+        <v>974</v>
       </c>
       <c r="G127" s="3" t="n">
-        <v>122.8</v>
+        <v>979</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>MARKSANS</t>
+          <t>MANAKSIA</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
@@ -4176,22 +4176,22 @@
         </is>
       </c>
       <c r="D128" s="3" t="n">
-        <v>333.6</v>
+        <v>58.97</v>
       </c>
       <c r="E128" s="3" t="n">
-        <v>322.1</v>
+        <v>56.85</v>
       </c>
       <c r="F128" s="3" t="n">
-        <v>329.7</v>
+        <v>58.73</v>
       </c>
       <c r="G128" s="3" t="n">
-        <v>329.95</v>
+        <v>59</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>MARSONS</t>
+          <t>MANAKSTEEL</t>
         </is>
       </c>
       <c r="B129" s="3" t="inlineStr">
@@ -4205,22 +4205,22 @@
         </is>
       </c>
       <c r="D129" s="3" t="n">
-        <v>129.78</v>
+        <v>95.23</v>
       </c>
       <c r="E129" s="3" t="n">
-        <v>123.03</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="F129" s="3" t="n">
-        <v>133.17</v>
+        <v>99.52</v>
       </c>
       <c r="G129" s="3" t="n">
-        <v>136</v>
+        <v>99.52</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>MAZDA</t>
+          <t>MANCREDIT</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
@@ -4234,22 +4234,22 @@
         </is>
       </c>
       <c r="D130" s="3" t="n">
-        <v>246.98</v>
+        <v>249.67</v>
       </c>
       <c r="E130" s="3" t="n">
-        <v>239.02</v>
+        <v>230.73</v>
       </c>
       <c r="F130" s="3" t="n">
-        <v>247.82</v>
+        <v>242.74</v>
       </c>
       <c r="G130" s="3" t="n">
-        <v>247</v>
+        <v>240</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>MENNPIS</t>
+          <t>MANINFRA</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
@@ -4263,22 +4263,22 @@
         </is>
       </c>
       <c r="D131" s="3" t="n">
-        <v>74.81</v>
+        <v>121.42</v>
       </c>
       <c r="E131" s="3" t="n">
-        <v>70.81999999999999</v>
+        <v>117.24</v>
       </c>
       <c r="F131" s="3" t="n">
-        <v>73.97</v>
+        <v>122.62</v>
       </c>
       <c r="G131" s="3" t="n">
-        <v>73.75</v>
+        <v>122</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>MENONBE</t>
+          <t>MANORG</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
@@ -4292,22 +4292,22 @@
         </is>
       </c>
       <c r="D132" s="3" t="n">
-        <v>283.16</v>
+        <v>522.17</v>
       </c>
       <c r="E132" s="3" t="n">
-        <v>269.67</v>
+        <v>500.85</v>
       </c>
       <c r="F132" s="3" t="n">
-        <v>284.62</v>
+        <v>519.5</v>
       </c>
       <c r="G132" s="3" t="n">
-        <v>286.9</v>
+        <v>532.3</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>METROPOLIS</t>
+          <t>MAWANASUG</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
@@ -4321,22 +4321,22 @@
         </is>
       </c>
       <c r="D133" s="3" t="n">
-        <v>584.4</v>
+        <v>151.36</v>
       </c>
       <c r="E133" s="3" t="n">
-        <v>572.1</v>
+        <v>142.1</v>
       </c>
       <c r="F133" s="3" t="n">
-        <v>588.45</v>
+        <v>149.1</v>
       </c>
       <c r="G133" s="3" t="n">
-        <v>588.65</v>
+        <v>149.01</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>MICEL</t>
+          <t>MAZDA</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
@@ -4350,22 +4350,22 @@
         </is>
       </c>
       <c r="D134" s="3" t="n">
-        <v>39.6</v>
+        <v>251</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>38.29</v>
+        <v>242.61</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>41.54</v>
+        <v>251.82</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>41.54</v>
+        <v>251.1</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>MMP</t>
+          <t>MON100</t>
         </is>
       </c>
       <c r="B135" s="3" t="inlineStr">
@@ -4379,22 +4379,22 @@
         </is>
       </c>
       <c r="D135" s="3" t="n">
-        <v>410.08</v>
+        <v>328.75</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>395.93</v>
+        <v>328.75</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>404.4</v>
+        <v>332.2</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>407</v>
+        <v>332.2</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>MOMENTUM50</t>
+          <t>MOREPENLAB</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
@@ -4408,22 +4408,22 @@
         </is>
       </c>
       <c r="D136" s="3" t="n">
-        <v>55.36</v>
+        <v>105.5</v>
       </c>
       <c r="E136" s="3" t="n">
-        <v>54.88</v>
+        <v>97.69</v>
       </c>
       <c r="F136" s="3" t="n">
-        <v>55.46</v>
+        <v>107.16</v>
       </c>
       <c r="G136" s="3" t="n">
-        <v>55.5</v>
+        <v>107.38</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>MON100</t>
+          <t>MOTOGENFIN</t>
         </is>
       </c>
       <c r="B137" s="3" t="inlineStr">
@@ -4437,22 +4437,22 @@
         </is>
       </c>
       <c r="D137" s="3" t="n">
-        <v>326.68</v>
+        <v>27.85</v>
       </c>
       <c r="E137" s="3" t="n">
-        <v>326.68</v>
+        <v>26.92</v>
       </c>
       <c r="F137" s="3" t="n">
-        <v>327.1</v>
+        <v>28.04</v>
       </c>
       <c r="G137" s="3" t="n">
-        <v>327.1</v>
+        <v>28.1</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>MOREPENLAB</t>
+          <t>MVELECTRO</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
@@ -4466,22 +4466,22 @@
         </is>
       </c>
       <c r="D138" s="3" t="n">
-        <v>101.37</v>
+        <v>740.05</v>
       </c>
       <c r="E138" s="3" t="n">
-        <v>95.20999999999999</v>
+        <v>630.5</v>
       </c>
       <c r="F138" s="3" t="n">
-        <v>106.19</v>
+        <v>760.45</v>
       </c>
       <c r="G138" s="3" t="n">
-        <v>106.37</v>
+        <v>746</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>MOTOGENFIN</t>
+          <t>NATCAPSUQ</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
@@ -4495,22 +4495,22 @@
         </is>
       </c>
       <c r="D139" s="3" t="n">
-        <v>27.48</v>
+        <v>220.34</v>
       </c>
       <c r="E139" s="3" t="n">
-        <v>26.52</v>
+        <v>197.16</v>
       </c>
       <c r="F139" s="3" t="n">
-        <v>27</v>
+        <v>212.38</v>
       </c>
       <c r="G139" s="3" t="n">
-        <v>26.96</v>
+        <v>211</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>MSPL</t>
+          <t>NAVNETEDUL</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
@@ -4524,22 +4524,22 @@
         </is>
       </c>
       <c r="D140" s="3" t="n">
-        <v>35.62</v>
+        <v>135.96</v>
       </c>
       <c r="E140" s="3" t="n">
-        <v>34.27</v>
+        <v>133.36</v>
       </c>
       <c r="F140" s="3" t="n">
-        <v>36.39</v>
+        <v>134.61</v>
       </c>
       <c r="G140" s="3" t="n">
-        <v>36.49</v>
+        <v>134.08</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>MUKANDLTD</t>
+          <t>NEAGI</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
@@ -4553,22 +4553,22 @@
         </is>
       </c>
       <c r="D141" s="3" t="n">
-        <v>137.95</v>
+        <v>3490.43</v>
       </c>
       <c r="E141" s="3" t="n">
-        <v>134.72</v>
+        <v>3348.1</v>
       </c>
       <c r="F141" s="3" t="n">
-        <v>137.27</v>
+        <v>3496.7</v>
       </c>
       <c r="G141" s="3" t="n">
-        <v>137.64</v>
+        <v>3528</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>MVELECTRO</t>
+          <t>NEXTMEDIA</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
@@ -4582,22 +4582,22 @@
         </is>
       </c>
       <c r="D142" s="3" t="n">
-        <v>668.87</v>
+        <v>4.69</v>
       </c>
       <c r="E142" s="3" t="n">
-        <v>571.67</v>
+        <v>4.03</v>
       </c>
       <c r="F142" s="3" t="n">
-        <v>719.55</v>
+        <v>4.98</v>
       </c>
       <c r="G142" s="3" t="n">
-        <v>728</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>NATCAPSUQ</t>
+          <t>NIACL</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
@@ -4611,22 +4611,22 @@
         </is>
       </c>
       <c r="D143" s="3" t="n">
-        <v>207.51</v>
+        <v>193.3</v>
       </c>
       <c r="E143" s="3" t="n">
-        <v>183.49</v>
+        <v>185.39</v>
       </c>
       <c r="F143" s="3" t="n">
-        <v>204.96</v>
+        <v>191.23</v>
       </c>
       <c r="G143" s="3" t="n">
-        <v>209.3</v>
+        <v>191.9</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>NELCAST</t>
+          <t>NIFMID150</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
@@ -4640,22 +4640,22 @@
         </is>
       </c>
       <c r="D144" s="3" t="n">
-        <v>119.5</v>
+        <v>224.68</v>
       </c>
       <c r="E144" s="3" t="n">
-        <v>115.49</v>
+        <v>222.19</v>
       </c>
       <c r="F144" s="3" t="n">
-        <v>119.85</v>
+        <v>224.96</v>
       </c>
       <c r="G144" s="3" t="n">
-        <v>119.52</v>
+        <v>225.54</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>NIRAJISPAT</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
@@ -4669,22 +4669,22 @@
         </is>
       </c>
       <c r="D145" s="3" t="n">
-        <v>1923.87</v>
+        <v>302.66</v>
       </c>
       <c r="E145" s="3" t="n">
-        <v>1888.83</v>
+        <v>283.36</v>
       </c>
       <c r="F145" s="3" t="n">
-        <v>1932.1</v>
+        <v>355.08</v>
       </c>
       <c r="G145" s="3" t="n">
-        <v>1934.5</v>
+        <v>355.08</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>NIFMID150</t>
+          <t>NITTAGELA</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
@@ -4698,16 +4698,16 @@
         </is>
       </c>
       <c r="D146" s="3" t="n">
-        <v>224.68</v>
+        <v>1659.13</v>
       </c>
       <c r="E146" s="3" t="n">
-        <v>222.19</v>
+        <v>1579.2</v>
       </c>
       <c r="F146" s="3" t="n">
-        <v>224.96</v>
+        <v>1620.7</v>
       </c>
       <c r="G146" s="3" t="n">
-        <v>225.54</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="147">
@@ -4727,22 +4727,22 @@
         </is>
       </c>
       <c r="D147" s="3" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="E147" s="3" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="F147" s="3" t="n">
         <v>4.21</v>
       </c>
-      <c r="E147" s="3" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="F147" s="3" t="n">
+      <c r="G147" s="3" t="n">
         <v>4.2</v>
-      </c>
-      <c r="G147" s="3" t="n">
-        <v>4.22</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>NSLNISP</t>
+          <t>NURECA</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
@@ -4756,22 +4756,22 @@
         </is>
       </c>
       <c r="D148" s="3" t="n">
-        <v>45.49</v>
+        <v>331.73</v>
       </c>
       <c r="E148" s="3" t="n">
-        <v>42.01</v>
+        <v>315.37</v>
       </c>
       <c r="F148" s="3" t="n">
-        <v>49.02</v>
+        <v>331.8</v>
       </c>
       <c r="G148" s="3" t="n">
-        <v>48.75</v>
+        <v>334</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>NURECA</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
@@ -4785,22 +4785,22 @@
         </is>
       </c>
       <c r="D149" s="3" t="n">
-        <v>321.22</v>
+        <v>12243.67</v>
       </c>
       <c r="E149" s="3" t="n">
-        <v>306.03</v>
+        <v>11892</v>
       </c>
       <c r="F149" s="3" t="n">
-        <v>331.05</v>
+        <v>12540</v>
       </c>
       <c r="G149" s="3" t="n">
-        <v>333</v>
+        <v>12540</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>NUVAMA</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
@@ -4814,22 +4814,22 @@
         </is>
       </c>
       <c r="D150" s="3" t="n">
-        <v>1801.87</v>
+        <v>485.88</v>
       </c>
       <c r="E150" s="3" t="n">
-        <v>1761.67</v>
+        <v>472.03</v>
       </c>
       <c r="F150" s="3" t="n">
-        <v>1805</v>
+        <v>483.15</v>
       </c>
       <c r="G150" s="3" t="n">
-        <v>1800.1</v>
+        <v>483.15</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>OAL</t>
+          <t>OLAELEC</t>
         </is>
       </c>
       <c r="B151" s="3" t="inlineStr">
@@ -4843,22 +4843,22 @@
         </is>
       </c>
       <c r="D151" s="3" t="n">
-        <v>446.22</v>
+        <v>40.05</v>
       </c>
       <c r="E151" s="3" t="n">
-        <v>391.67</v>
+        <v>37.69</v>
       </c>
       <c r="F151" s="3" t="n">
-        <v>487.8</v>
+        <v>41.12</v>
       </c>
       <c r="G151" s="3" t="n">
-        <v>486</v>
+        <v>40.9</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>PARACABLES</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
@@ -4872,22 +4872,22 @@
         </is>
       </c>
       <c r="D152" s="3" t="n">
-        <v>476.42</v>
+        <v>64.23</v>
       </c>
       <c r="E152" s="3" t="n">
-        <v>465.18</v>
+        <v>59.63</v>
       </c>
       <c r="F152" s="3" t="n">
-        <v>482.85</v>
+        <v>65.34</v>
       </c>
       <c r="G152" s="3" t="n">
-        <v>482.85</v>
+        <v>65.54000000000001</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>OMAXE</t>
+          <t>PARSVNATH</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
@@ -4901,22 +4901,22 @@
         </is>
       </c>
       <c r="D153" s="3" t="n">
-        <v>120.7</v>
+        <v>1.45</v>
       </c>
       <c r="E153" s="3" t="n">
-        <v>106.24</v>
+        <v>1.44</v>
       </c>
       <c r="F153" s="3" t="n">
-        <v>131.74</v>
+        <v>1.47</v>
       </c>
       <c r="G153" s="3" t="n">
-        <v>132</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>OMINFRAL</t>
+          <t>PDMJEPAPER</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
@@ -4930,22 +4930,22 @@
         </is>
       </c>
       <c r="D154" s="3" t="n">
-        <v>84.18000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="E154" s="3" t="n">
-        <v>81.39</v>
+        <v>89.23</v>
       </c>
       <c r="F154" s="3" t="n">
-        <v>83.01000000000001</v>
+        <v>95.20999999999999</v>
       </c>
       <c r="G154" s="3" t="n">
-        <v>83.48</v>
+        <v>95.05</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>ORCHASP</t>
+          <t>PGIL</t>
         </is>
       </c>
       <c r="B155" s="3" t="inlineStr">
@@ -4959,22 +4959,22 @@
         </is>
       </c>
       <c r="D155" s="3" t="n">
-        <v>1.48</v>
+        <v>2381.1</v>
       </c>
       <c r="E155" s="3" t="n">
-        <v>1.37</v>
+        <v>2288.67</v>
       </c>
       <c r="F155" s="3" t="n">
-        <v>1.43</v>
+        <v>2463.8</v>
       </c>
       <c r="G155" s="3" t="n">
-        <v>1.44</v>
+        <v>2490</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>ORKLAINDIA</t>
+          <t>PIRAMALFIN</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
@@ -4988,22 +4988,22 @@
         </is>
       </c>
       <c r="D156" s="3" t="n">
-        <v>602.4</v>
+        <v>2288.37</v>
       </c>
       <c r="E156" s="3" t="n">
-        <v>576.75</v>
+        <v>2223.97</v>
       </c>
       <c r="F156" s="3" t="n">
-        <v>595.4</v>
+        <v>2300.4</v>
       </c>
       <c r="G156" s="3" t="n">
-        <v>601</v>
+        <v>2315</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>PARKHOSPS</t>
+          <t>POLYPLEX</t>
         </is>
       </c>
       <c r="B157" s="3" t="inlineStr">
@@ -5017,22 +5017,22 @@
         </is>
       </c>
       <c r="D157" s="3" t="n">
-        <v>292.38</v>
+        <v>1192.1</v>
       </c>
       <c r="E157" s="3" t="n">
-        <v>286.15</v>
+        <v>1157.37</v>
       </c>
       <c r="F157" s="3" t="n">
-        <v>290.55</v>
+        <v>1182.6</v>
       </c>
       <c r="G157" s="3" t="n">
-        <v>290</v>
+        <v>1183.7</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>PARSVNATH</t>
+          <t>PONNIERODE</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
@@ -5046,22 +5046,22 @@
         </is>
       </c>
       <c r="D158" s="3" t="n">
-        <v>1.43</v>
+        <v>404.42</v>
       </c>
       <c r="E158" s="3" t="n">
-        <v>1.42</v>
+        <v>387.6</v>
       </c>
       <c r="F158" s="3" t="n">
-        <v>1.45</v>
+        <v>403.3</v>
       </c>
       <c r="G158" s="3" t="n">
-        <v>1.45</v>
+        <v>404.6</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>PLATIND</t>
+          <t>PRAENG</t>
         </is>
       </c>
       <c r="B159" s="3" t="inlineStr">
@@ -5075,22 +5075,22 @@
         </is>
       </c>
       <c r="D159" s="3" t="n">
-        <v>228.8</v>
+        <v>20.8</v>
       </c>
       <c r="E159" s="3" t="n">
-        <v>217.47</v>
+        <v>19.71</v>
       </c>
       <c r="F159" s="3" t="n">
-        <v>230.58</v>
+        <v>21.49</v>
       </c>
       <c r="G159" s="3" t="n">
-        <v>230.4</v>
+        <v>20.91</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>POONAWALLA</t>
+          <t>PRECWIRE</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
@@ -5104,22 +5104,22 @@
         </is>
       </c>
       <c r="D160" s="3" t="n">
-        <v>483.65</v>
+        <v>489.6</v>
       </c>
       <c r="E160" s="3" t="n">
-        <v>472.58</v>
+        <v>444.88</v>
       </c>
       <c r="F160" s="3" t="n">
-        <v>479.05</v>
+        <v>505.6</v>
       </c>
       <c r="G160" s="3" t="n">
-        <v>477.85</v>
+        <v>506.5</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>POWERMECH</t>
+          <t>PTCIL</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
@@ -5133,22 +5133,22 @@
         </is>
       </c>
       <c r="D161" s="3" t="n">
-        <v>2563.63</v>
+        <v>21966</v>
       </c>
       <c r="E161" s="3" t="n">
-        <v>2518.6</v>
+        <v>20867</v>
       </c>
       <c r="F161" s="3" t="n">
-        <v>2580.6</v>
+        <v>22114</v>
       </c>
       <c r="G161" s="3" t="n">
-        <v>2579</v>
+        <v>21900</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>PPLPHARMA</t>
+          <t>QPOWER</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
@@ -5162,22 +5162,22 @@
         </is>
       </c>
       <c r="D162" s="3" t="n">
-        <v>217.65</v>
+        <v>1432.33</v>
       </c>
       <c r="E162" s="3" t="n">
-        <v>211.12</v>
+        <v>1363.73</v>
       </c>
       <c r="F162" s="3" t="n">
-        <v>218.68</v>
+        <v>1435.8</v>
       </c>
       <c r="G162" s="3" t="n">
-        <v>217.9</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>PRAENG</t>
+          <t>QUESS</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
@@ -5191,22 +5191,22 @@
         </is>
       </c>
       <c r="D163" s="3" t="n">
-        <v>20.15</v>
+        <v>379.15</v>
       </c>
       <c r="E163" s="3" t="n">
-        <v>19.26</v>
+        <v>359.17</v>
       </c>
       <c r="F163" s="3" t="n">
-        <v>20.63</v>
+        <v>381.75</v>
       </c>
       <c r="G163" s="3" t="n">
-        <v>20.64</v>
+        <v>383.3</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>PREMIER</t>
+          <t>RAMCOSYS</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
@@ -5220,22 +5220,22 @@
         </is>
       </c>
       <c r="D164" s="3" t="n">
-        <v>2.84</v>
+        <v>582.5</v>
       </c>
       <c r="E164" s="3" t="n">
-        <v>2.77</v>
+        <v>559.5</v>
       </c>
       <c r="F164" s="3" t="n">
-        <v>2.9</v>
+        <v>575.25</v>
       </c>
       <c r="G164" s="3" t="n">
-        <v>2.92</v>
+        <v>575</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>PVP</t>
+          <t>RATNAVEER</t>
         </is>
       </c>
       <c r="B165" s="3" t="inlineStr">
@@ -5249,22 +5249,22 @@
         </is>
       </c>
       <c r="D165" s="3" t="n">
-        <v>61.27</v>
+        <v>305.68</v>
       </c>
       <c r="E165" s="3" t="n">
-        <v>58.3</v>
+        <v>289.22</v>
       </c>
       <c r="F165" s="3" t="n">
-        <v>65.22</v>
+        <v>306.02</v>
       </c>
       <c r="G165" s="3" t="n">
-        <v>65.22</v>
+        <v>305.8</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>QPOWER</t>
+          <t>RAYMOND</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
@@ -5278,22 +5278,22 @@
         </is>
       </c>
       <c r="D166" s="3" t="n">
-        <v>1371.1</v>
+        <v>632.13</v>
       </c>
       <c r="E166" s="3" t="n">
-        <v>1309.5</v>
+        <v>614.4</v>
       </c>
       <c r="F166" s="3" t="n">
-        <v>1431.2</v>
+        <v>631.85</v>
       </c>
       <c r="G166" s="3" t="n">
-        <v>1431.2</v>
+        <v>630.25</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>QUADFUTURE</t>
+          <t>RELIGARE</t>
         </is>
       </c>
       <c r="B167" s="3" t="inlineStr">
@@ -5307,22 +5307,22 @@
         </is>
       </c>
       <c r="D167" s="3" t="n">
-        <v>434.22</v>
+        <v>239.92</v>
       </c>
       <c r="E167" s="3" t="n">
-        <v>415</v>
+        <v>229.55</v>
       </c>
       <c r="F167" s="3" t="n">
-        <v>429.2</v>
+        <v>242.8</v>
       </c>
       <c r="G167" s="3" t="n">
-        <v>425.5</v>
+        <v>244</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>RAMASTEEL</t>
+          <t>REMSONSIND</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
@@ -5336,22 +5336,22 @@
         </is>
       </c>
       <c r="D168" s="3" t="n">
-        <v>4.33</v>
+        <v>91.20999999999999</v>
       </c>
       <c r="E168" s="3" t="n">
-        <v>4.32</v>
+        <v>82.56999999999999</v>
       </c>
       <c r="F168" s="3" t="n">
-        <v>4.41</v>
+        <v>98.48</v>
       </c>
       <c r="G168" s="3" t="n">
-        <v>4.41</v>
+        <v>98.59999999999999</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>RAMRAT</t>
+          <t>RENUKA</t>
         </is>
       </c>
       <c r="B169" s="3" t="inlineStr">
@@ -5365,22 +5365,22 @@
         </is>
       </c>
       <c r="D169" s="3" t="n">
-        <v>570.05</v>
+        <v>24.96</v>
       </c>
       <c r="E169" s="3" t="n">
-        <v>525.88</v>
+        <v>23.54</v>
       </c>
       <c r="F169" s="3" t="n">
-        <v>591.9</v>
+        <v>24.9</v>
       </c>
       <c r="G169" s="3" t="n">
-        <v>586.2</v>
+        <v>24.95</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>RATNAVEER</t>
+          <t>RKFORGE</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
@@ -5394,22 +5394,22 @@
         </is>
       </c>
       <c r="D170" s="3" t="n">
-        <v>296.05</v>
+        <v>753.85</v>
       </c>
       <c r="E170" s="3" t="n">
-        <v>278.55</v>
+        <v>722.15</v>
       </c>
       <c r="F170" s="3" t="n">
-        <v>294.95</v>
+        <v>743.6</v>
       </c>
       <c r="G170" s="3" t="n">
-        <v>294</v>
+        <v>742.25</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>REDINGTON</t>
+          <t>RMDRIP</t>
         </is>
       </c>
       <c r="B171" s="3" t="inlineStr">
@@ -5423,22 +5423,22 @@
         </is>
       </c>
       <c r="D171" s="3" t="n">
-        <v>366.57</v>
+        <v>20.6</v>
       </c>
       <c r="E171" s="3" t="n">
-        <v>354.48</v>
+        <v>19.8</v>
       </c>
       <c r="F171" s="3" t="n">
-        <v>366</v>
+        <v>21.33</v>
       </c>
       <c r="G171" s="3" t="n">
-        <v>366.5</v>
+        <v>21.3</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>REDTAPE</t>
+          <t>RNBDENIMS</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
@@ -5452,22 +5452,22 @@
         </is>
       </c>
       <c r="D172" s="3" t="n">
-        <v>125.32</v>
+        <v>9.84</v>
       </c>
       <c r="E172" s="3" t="n">
-        <v>121.32</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F172" s="3" t="n">
-        <v>126.01</v>
+        <v>10.32</v>
       </c>
       <c r="G172" s="3" t="n">
-        <v>125.95</v>
+        <v>10.32</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>RNBDENIMS</t>
+          <t>ROML</t>
         </is>
       </c>
       <c r="B173" s="3" t="inlineStr">
@@ -5481,22 +5481,22 @@
         </is>
       </c>
       <c r="D173" s="3" t="n">
-        <v>9.380000000000001</v>
+        <v>43.02</v>
       </c>
       <c r="E173" s="3" t="n">
-        <v>9.24</v>
+        <v>40.86</v>
       </c>
       <c r="F173" s="3" t="n">
-        <v>9.83</v>
+        <v>42.62</v>
       </c>
       <c r="G173" s="3" t="n">
-        <v>9.83</v>
+        <v>42.56</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>ROLLT</t>
+          <t>RPEL</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
@@ -5510,22 +5510,22 @@
         </is>
       </c>
       <c r="D174" s="3" t="n">
-        <v>4.27</v>
+        <v>1791.3</v>
       </c>
       <c r="E174" s="3" t="n">
-        <v>3.9</v>
+        <v>1716.27</v>
       </c>
       <c r="F174" s="3" t="n">
-        <v>4.16</v>
+        <v>1771.2</v>
       </c>
       <c r="G174" s="3" t="n">
-        <v>4.22</v>
+        <v>1790.2</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>RPEL</t>
+          <t>RRKABEL</t>
         </is>
       </c>
       <c r="B175" s="3" t="inlineStr">
@@ -5539,16 +5539,16 @@
         </is>
       </c>
       <c r="D175" s="3" t="n">
-        <v>1770.97</v>
+        <v>2933.93</v>
       </c>
       <c r="E175" s="3" t="n">
-        <v>1675.47</v>
+        <v>2833.5</v>
       </c>
       <c r="F175" s="3" t="n">
-        <v>1748.4</v>
+        <v>2928.4</v>
       </c>
       <c r="G175" s="3" t="n">
-        <v>1745</v>
+        <v>2931.9</v>
       </c>
     </row>
     <row r="176">
@@ -5568,22 +5568,22 @@
         </is>
       </c>
       <c r="D176" s="3" t="n">
-        <v>174.23</v>
+        <v>177.82</v>
       </c>
       <c r="E176" s="3" t="n">
-        <v>166.7</v>
+        <v>170.77</v>
       </c>
       <c r="F176" s="3" t="n">
-        <v>177.49</v>
+        <v>177.66</v>
       </c>
       <c r="G176" s="3" t="n">
-        <v>177.1</v>
+        <v>175</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>RSSOFTWARE</t>
+          <t>SABEVENTS</t>
         </is>
       </c>
       <c r="B177" s="3" t="inlineStr">
@@ -5597,22 +5597,22 @@
         </is>
       </c>
       <c r="D177" s="3" t="n">
-        <v>32.75</v>
+        <v>6.4</v>
       </c>
       <c r="E177" s="3" t="n">
-        <v>30.73</v>
+        <v>6.2</v>
       </c>
       <c r="F177" s="3" t="n">
-        <v>31.29</v>
+        <v>6.63</v>
       </c>
       <c r="G177" s="3" t="n">
-        <v>31.29</v>
+        <v>6.63</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>RUBICON</t>
+          <t>SAGILITY</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
@@ -5626,22 +5626,22 @@
         </is>
       </c>
       <c r="D178" s="3" t="n">
-        <v>1866.67</v>
+        <v>46.37</v>
       </c>
       <c r="E178" s="3" t="n">
-        <v>1772.07</v>
+        <v>44.68</v>
       </c>
       <c r="F178" s="3" t="n">
-        <v>1804.4</v>
+        <v>47.05</v>
       </c>
       <c r="G178" s="3" t="n">
-        <v>1801.6</v>
+        <v>47.05</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>RUBYMILLS</t>
+          <t>SANGINITA</t>
         </is>
       </c>
       <c r="B179" s="3" t="inlineStr">
@@ -5655,22 +5655,22 @@
         </is>
       </c>
       <c r="D179" s="3" t="n">
-        <v>397.33</v>
+        <v>53.36</v>
       </c>
       <c r="E179" s="3" t="n">
-        <v>377.25</v>
+        <v>50.91</v>
       </c>
       <c r="F179" s="3" t="n">
-        <v>390.4</v>
+        <v>55.97</v>
       </c>
       <c r="G179" s="3" t="n">
-        <v>390</v>
+        <v>55.97</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>SABEVENTS</t>
+          <t>SASTASUNDR</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
@@ -5684,22 +5684,22 @@
         </is>
       </c>
       <c r="D180" s="3" t="n">
-        <v>6.4</v>
+        <v>283.13</v>
       </c>
       <c r="E180" s="3" t="n">
-        <v>6.2</v>
+        <v>269.72</v>
       </c>
       <c r="F180" s="3" t="n">
-        <v>6.63</v>
+        <v>282.6</v>
       </c>
       <c r="G180" s="3" t="n">
-        <v>6.63</v>
+        <v>284.65</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>SADBHIN</t>
+          <t>SBC</t>
         </is>
       </c>
       <c r="B181" s="3" t="inlineStr">
@@ -5713,22 +5713,22 @@
         </is>
       </c>
       <c r="D181" s="3" t="n">
-        <v>2.69</v>
+        <v>42.38</v>
       </c>
       <c r="E181" s="3" t="n">
-        <v>2.57</v>
+        <v>40.92</v>
       </c>
       <c r="F181" s="3" t="n">
-        <v>2.72</v>
+        <v>42.15</v>
       </c>
       <c r="G181" s="3" t="n">
-        <v>2.75</v>
+        <v>42</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>SAILIFE</t>
+          <t>SBILIQETF</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
@@ -5742,22 +5742,22 @@
         </is>
       </c>
       <c r="D182" s="3" t="n">
-        <v>1494.07</v>
+        <v>1053.83</v>
       </c>
       <c r="E182" s="3" t="n">
-        <v>1461.83</v>
+        <v>1053.81</v>
       </c>
       <c r="F182" s="3" t="n">
-        <v>1485</v>
+        <v>1054.05</v>
       </c>
       <c r="G182" s="3" t="n">
-        <v>1485</v>
+        <v>1054.06</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>SANGAMIND</t>
+          <t>SECMARK</t>
         </is>
       </c>
       <c r="B183" s="3" t="inlineStr">
@@ -5771,22 +5771,22 @@
         </is>
       </c>
       <c r="D183" s="3" t="n">
-        <v>590.52</v>
+        <v>153.75</v>
       </c>
       <c r="E183" s="3" t="n">
-        <v>566.33</v>
+        <v>136.58</v>
       </c>
       <c r="F183" s="3" t="n">
-        <v>603.15</v>
+        <v>163.27</v>
       </c>
       <c r="G183" s="3" t="n">
-        <v>596.1</v>
+        <v>164.4</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>SASTASUNDR</t>
+          <t>SETCO</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
@@ -5800,22 +5800,22 @@
         </is>
       </c>
       <c r="D184" s="3" t="n">
-        <v>283.13</v>
+        <v>18.18</v>
       </c>
       <c r="E184" s="3" t="n">
-        <v>269.72</v>
+        <v>17.04</v>
       </c>
       <c r="F184" s="3" t="n">
-        <v>282.6</v>
+        <v>17.7</v>
       </c>
       <c r="G184" s="3" t="n">
-        <v>284.65</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>SBCL</t>
+          <t>SETL</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">
@@ -5829,22 +5829,22 @@
         </is>
       </c>
       <c r="D185" s="3" t="n">
-        <v>1077.83</v>
+        <v>364.5</v>
       </c>
       <c r="E185" s="3" t="n">
-        <v>1024.3</v>
+        <v>347.72</v>
       </c>
       <c r="F185" s="3" t="n">
-        <v>1049.2</v>
+        <v>369.5</v>
       </c>
       <c r="G185" s="3" t="n">
-        <v>1045</v>
+        <v>368.5</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>SBILIQETF</t>
+          <t>SHAHALLOYS</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
@@ -5858,22 +5858,22 @@
         </is>
       </c>
       <c r="D186" s="3" t="n">
-        <v>1053.59</v>
+        <v>102.25</v>
       </c>
       <c r="E186" s="3" t="n">
-        <v>1053.57</v>
+        <v>90.34</v>
       </c>
       <c r="F186" s="3" t="n">
-        <v>1053.9</v>
+        <v>107.69</v>
       </c>
       <c r="G186" s="3" t="n">
-        <v>1053.92</v>
+        <v>107.1</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>SCHNEIDER</t>
+          <t>SHIVALIK</t>
         </is>
       </c>
       <c r="B187" s="3" t="inlineStr">
@@ -5887,22 +5887,22 @@
         </is>
       </c>
       <c r="D187" s="3" t="n">
-        <v>1205.13</v>
+        <v>308.6</v>
       </c>
       <c r="E187" s="3" t="n">
-        <v>1167.17</v>
+        <v>291.68</v>
       </c>
       <c r="F187" s="3" t="n">
-        <v>1201.9</v>
+        <v>322.19</v>
       </c>
       <c r="G187" s="3" t="n">
-        <v>1198.5</v>
+        <v>322.19</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>SCI</t>
+          <t>SHIVAMAUTO</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
@@ -5916,22 +5916,22 @@
         </is>
       </c>
       <c r="D188" s="3" t="n">
-        <v>299.25</v>
+        <v>17.73</v>
       </c>
       <c r="E188" s="3" t="n">
-        <v>290.3</v>
+        <v>16.3</v>
       </c>
       <c r="F188" s="3" t="n">
-        <v>299.05</v>
+        <v>17.63</v>
       </c>
       <c r="G188" s="3" t="n">
-        <v>299.5</v>
+        <v>17.37</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>SETL</t>
+          <t>SHIVATEX</t>
         </is>
       </c>
       <c r="B189" s="3" t="inlineStr">
@@ -5945,22 +5945,22 @@
         </is>
       </c>
       <c r="D189" s="3" t="n">
-        <v>347.18</v>
+        <v>181.1</v>
       </c>
       <c r="E189" s="3" t="n">
-        <v>333.35</v>
+        <v>167.37</v>
       </c>
       <c r="F189" s="3" t="n">
-        <v>364.2</v>
+        <v>181.17</v>
       </c>
       <c r="G189" s="3" t="n">
-        <v>364.2</v>
+        <v>182.46</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>SGIL</t>
+          <t>SILVERETF</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
@@ -5974,22 +5974,22 @@
         </is>
       </c>
       <c r="D190" s="3" t="n">
-        <v>599.97</v>
+        <v>201.81</v>
       </c>
       <c r="E190" s="3" t="n">
-        <v>582.72</v>
+        <v>198.28</v>
       </c>
       <c r="F190" s="3" t="n">
-        <v>607.7</v>
+        <v>203.98</v>
       </c>
       <c r="G190" s="3" t="n">
-        <v>603.5</v>
+        <v>204</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>SHAH</t>
+          <t>SIMPLEXINF</t>
         </is>
       </c>
       <c r="B191" s="3" t="inlineStr">
@@ -6003,22 +6003,22 @@
         </is>
       </c>
       <c r="D191" s="3" t="n">
-        <v>3.74</v>
+        <v>274.88</v>
       </c>
       <c r="E191" s="3" t="n">
-        <v>3.11</v>
+        <v>258.73</v>
       </c>
       <c r="F191" s="3" t="n">
-        <v>3.74</v>
+        <v>268.83</v>
       </c>
       <c r="G191" s="3" t="n">
-        <v>3.75</v>
+        <v>265.36</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>SHAHALLOYS</t>
+          <t>SINCLAIR</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
@@ -6032,22 +6032,22 @@
         </is>
       </c>
       <c r="D192" s="3" t="n">
-        <v>89.42</v>
+        <v>82.44</v>
       </c>
       <c r="E192" s="3" t="n">
-        <v>79.77</v>
+        <v>77.37</v>
       </c>
       <c r="F192" s="3" t="n">
-        <v>103.15</v>
+        <v>82.38</v>
       </c>
       <c r="G192" s="3" t="n">
-        <v>103.15</v>
+        <v>81.65000000000001</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>SHIVALIK</t>
+          <t>SOLARA</t>
         </is>
       </c>
       <c r="B193" s="3" t="inlineStr">
@@ -6061,22 +6061,22 @@
         </is>
       </c>
       <c r="D193" s="3" t="n">
-        <v>299.78</v>
+        <v>632.4299999999999</v>
       </c>
       <c r="E193" s="3" t="n">
-        <v>283.42</v>
+        <v>608.95</v>
       </c>
       <c r="F193" s="3" t="n">
-        <v>306.85</v>
+        <v>632.65</v>
       </c>
       <c r="G193" s="3" t="n">
-        <v>306.85</v>
+        <v>632</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>SHIVAMAUTO</t>
+          <t>SOMANYCERA</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
@@ -6090,22 +6090,22 @@
         </is>
       </c>
       <c r="D194" s="3" t="n">
-        <v>17.12</v>
+        <v>569.5700000000001</v>
       </c>
       <c r="E194" s="3" t="n">
-        <v>15.75</v>
+        <v>553.8200000000001</v>
       </c>
       <c r="F194" s="3" t="n">
-        <v>16.94</v>
+        <v>557.3</v>
       </c>
       <c r="G194" s="3" t="n">
-        <v>16.99</v>
+        <v>562.9</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>SHRENIK</t>
+          <t>SONAMLTD</t>
         </is>
       </c>
       <c r="B195" s="3" t="inlineStr">
@@ -6119,22 +6119,22 @@
         </is>
       </c>
       <c r="D195" s="3" t="n">
-        <v>0.3</v>
+        <v>73.43000000000001</v>
       </c>
       <c r="E195" s="3" t="n">
-        <v>0.29</v>
+        <v>66.68000000000001</v>
       </c>
       <c r="F195" s="3" t="n">
-        <v>0.3</v>
+        <v>77.81999999999999</v>
       </c>
       <c r="G195" s="3" t="n">
-        <v>0.31</v>
+        <v>77.5</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>SHYAMMETL</t>
+          <t>SONATSOFTW</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
@@ -6148,22 +6148,22 @@
         </is>
       </c>
       <c r="D196" s="3" t="n">
-        <v>1081.3</v>
+        <v>304.5</v>
       </c>
       <c r="E196" s="3" t="n">
-        <v>1025.23</v>
+        <v>289.42</v>
       </c>
       <c r="F196" s="3" t="n">
-        <v>1099.8</v>
+        <v>292.05</v>
       </c>
       <c r="G196" s="3" t="n">
-        <v>1104.4</v>
+        <v>292.55</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>SIGMAADV</t>
+          <t>SPAL</t>
         </is>
       </c>
       <c r="B197" s="3" t="inlineStr">
@@ -6177,22 +6177,22 @@
         </is>
       </c>
       <c r="D197" s="3" t="n">
-        <v>763.98</v>
+        <v>1029.15</v>
       </c>
       <c r="E197" s="3" t="n">
-        <v>729.13</v>
+        <v>978.67</v>
       </c>
       <c r="F197" s="3" t="n">
-        <v>777.1</v>
+        <v>1050.25</v>
       </c>
       <c r="G197" s="3" t="n">
-        <v>779</v>
+        <v>1044.55</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>SILGO</t>
+          <t>SPLPETRO</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
@@ -6206,22 +6206,22 @@
         </is>
       </c>
       <c r="D198" s="3" t="n">
-        <v>74.98999999999999</v>
+        <v>725.23</v>
       </c>
       <c r="E198" s="3" t="n">
-        <v>72.75</v>
+        <v>694.4</v>
       </c>
       <c r="F198" s="3" t="n">
-        <v>75.63</v>
+        <v>729.05</v>
       </c>
       <c r="G198" s="3" t="n">
-        <v>74.8</v>
+        <v>725.15</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>SILINV</t>
+          <t>SSWL</t>
         </is>
       </c>
       <c r="B199" s="3" t="inlineStr">
@@ -6235,22 +6235,22 @@
         </is>
       </c>
       <c r="D199" s="3" t="n">
-        <v>492.6</v>
+        <v>299.77</v>
       </c>
       <c r="E199" s="3" t="n">
-        <v>467</v>
+        <v>289.53</v>
       </c>
       <c r="F199" s="3" t="n">
-        <v>490.05</v>
+        <v>305.65</v>
       </c>
       <c r="G199" s="3" t="n">
-        <v>490</v>
+        <v>306.2</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>SILVERETF</t>
+          <t>STAR</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
@@ -6264,22 +6264,22 @@
         </is>
       </c>
       <c r="D200" s="3" t="n">
-        <v>201.81</v>
+        <v>1019.67</v>
       </c>
       <c r="E200" s="3" t="n">
-        <v>198.28</v>
+        <v>989.3</v>
       </c>
       <c r="F200" s="3" t="n">
-        <v>203.98</v>
+        <v>1025</v>
       </c>
       <c r="G200" s="3" t="n">
-        <v>204</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>SIMPLEXINF</t>
+          <t>STEL</t>
         </is>
       </c>
       <c r="B201" s="3" t="inlineStr">
@@ -6293,22 +6293,22 @@
         </is>
       </c>
       <c r="D201" s="3" t="n">
-        <v>267.54</v>
+        <v>655.63</v>
       </c>
       <c r="E201" s="3" t="n">
-        <v>252.08</v>
+        <v>618.08</v>
       </c>
       <c r="F201" s="3" t="n">
-        <v>277.59</v>
+        <v>661.2</v>
       </c>
       <c r="G201" s="3" t="n">
-        <v>278.8</v>
+        <v>658</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>SIS</t>
+          <t>STLNETWORK</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr">
@@ -6322,22 +6322,22 @@
         </is>
       </c>
       <c r="D202" s="3" t="n">
-        <v>429.98</v>
+        <v>27.46</v>
       </c>
       <c r="E202" s="3" t="n">
-        <v>418.22</v>
+        <v>26.29</v>
       </c>
       <c r="F202" s="3" t="n">
-        <v>431</v>
+        <v>28.15</v>
       </c>
       <c r="G202" s="3" t="n">
-        <v>432</v>
+        <v>28.12</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>SKFINDUS</t>
+          <t>STLTECH</t>
         </is>
       </c>
       <c r="B203" s="3" t="inlineStr">
@@ -6351,22 +6351,22 @@
         </is>
       </c>
       <c r="D203" s="3" t="n">
-        <v>2931.67</v>
+        <v>727.38</v>
       </c>
       <c r="E203" s="3" t="n">
-        <v>2817.8</v>
+        <v>698.73</v>
       </c>
       <c r="F203" s="3" t="n">
-        <v>2952.2</v>
+        <v>728.45</v>
       </c>
       <c r="G203" s="3" t="n">
-        <v>2959.6</v>
+        <v>730</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>SOLARINDS</t>
+          <t>SUDARSCHEM</t>
         </is>
       </c>
       <c r="B204" s="3" t="inlineStr">
@@ -6380,22 +6380,22 @@
         </is>
       </c>
       <c r="D204" s="3" t="n">
-        <v>20532.33</v>
+        <v>1266.37</v>
       </c>
       <c r="E204" s="3" t="n">
-        <v>20033</v>
+        <v>1230.13</v>
       </c>
       <c r="F204" s="3" t="n">
-        <v>20400</v>
+        <v>1266.8</v>
       </c>
       <c r="G204" s="3" t="n">
-        <v>20400</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>SOMANYCERA</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="B205" s="3" t="inlineStr">
@@ -6409,22 +6409,22 @@
         </is>
       </c>
       <c r="D205" s="3" t="n">
-        <v>566.1799999999999</v>
+        <v>1946.93</v>
       </c>
       <c r="E205" s="3" t="n">
-        <v>548.98</v>
+        <v>1902.27</v>
       </c>
       <c r="F205" s="3" t="n">
-        <v>564.5</v>
+        <v>1984.8</v>
       </c>
       <c r="G205" s="3" t="n">
-        <v>565.1</v>
+        <v>1984.8</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>STEL</t>
+          <t>SUPERSPIN</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr">
@@ -6438,22 +6438,22 @@
         </is>
       </c>
       <c r="D206" s="3" t="n">
-        <v>635.27</v>
+        <v>6.18</v>
       </c>
       <c r="E206" s="3" t="n">
-        <v>609.9299999999999</v>
+        <v>6.01</v>
       </c>
       <c r="F206" s="3" t="n">
-        <v>636.9</v>
+        <v>6.42</v>
       </c>
       <c r="G206" s="3" t="n">
-        <v>628.1</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>STLNETWORK</t>
+          <t>SUPRIYA</t>
         </is>
       </c>
       <c r="B207" s="3" t="inlineStr">
@@ -6467,22 +6467,22 @@
         </is>
       </c>
       <c r="D207" s="3" t="n">
-        <v>26.57</v>
+        <v>803.9299999999999</v>
       </c>
       <c r="E207" s="3" t="n">
-        <v>25.46</v>
+        <v>778.45</v>
       </c>
       <c r="F207" s="3" t="n">
-        <v>27.28</v>
+        <v>798.3</v>
       </c>
       <c r="G207" s="3" t="n">
-        <v>27.28</v>
+        <v>799.95</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>STLTECH</t>
+          <t>TAMBOLIIN</t>
         </is>
       </c>
       <c r="B208" s="3" t="inlineStr">
@@ -6496,22 +6496,22 @@
         </is>
       </c>
       <c r="D208" s="3" t="n">
-        <v>701.48</v>
+        <v>261.29</v>
       </c>
       <c r="E208" s="3" t="n">
-        <v>677.67</v>
+        <v>247.08</v>
       </c>
       <c r="F208" s="3" t="n">
-        <v>723.75</v>
+        <v>255</v>
       </c>
       <c r="G208" s="3" t="n">
-        <v>728.5</v>
+        <v>255</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>STYL</t>
+          <t>TATATECH</t>
         </is>
       </c>
       <c r="B209" s="3" t="inlineStr">
@@ -6525,22 +6525,22 @@
         </is>
       </c>
       <c r="D209" s="3" t="n">
-        <v>409.48</v>
+        <v>829.2</v>
       </c>
       <c r="E209" s="3" t="n">
-        <v>393.6</v>
+        <v>798.77</v>
       </c>
       <c r="F209" s="3" t="n">
-        <v>402.1</v>
+        <v>831.05</v>
       </c>
       <c r="G209" s="3" t="n">
-        <v>400</v>
+        <v>830.5</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>SUDARSCHEM</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="B210" s="3" t="inlineStr">
@@ -6554,22 +6554,22 @@
         </is>
       </c>
       <c r="D210" s="3" t="n">
-        <v>1260.63</v>
+        <v>2343.8</v>
       </c>
       <c r="E210" s="3" t="n">
-        <v>1225.07</v>
+        <v>2271.13</v>
       </c>
       <c r="F210" s="3" t="n">
-        <v>1256.9</v>
+        <v>2399.3</v>
       </c>
       <c r="G210" s="3" t="n">
-        <v>1260</v>
+        <v>2399.3</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>SUTLEJTEX</t>
+          <t>TEAMLEASE</t>
         </is>
       </c>
       <c r="B211" s="3" t="inlineStr">
@@ -6583,22 +6583,22 @@
         </is>
       </c>
       <c r="D211" s="3" t="n">
-        <v>39.61</v>
+        <v>1284.3</v>
       </c>
       <c r="E211" s="3" t="n">
-        <v>38.35</v>
+        <v>1243.8</v>
       </c>
       <c r="F211" s="3" t="n">
-        <v>39.3</v>
+        <v>1283.5</v>
       </c>
       <c r="G211" s="3" t="n">
-        <v>39.25</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>SYNCOMF</t>
+          <t>TECH</t>
         </is>
       </c>
       <c r="B212" s="3" t="inlineStr">
@@ -6612,22 +6612,22 @@
         </is>
       </c>
       <c r="D212" s="3" t="n">
-        <v>18.82</v>
+        <v>34.06</v>
       </c>
       <c r="E212" s="3" t="n">
-        <v>17.08</v>
+        <v>33.29</v>
       </c>
       <c r="F212" s="3" t="n">
-        <v>19.46</v>
+        <v>33.85</v>
       </c>
       <c r="G212" s="3" t="n">
-        <v>19.65</v>
+        <v>33.98</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>TECHNVISN</t>
         </is>
       </c>
       <c r="B213" s="3" t="inlineStr">
@@ -6641,22 +6641,22 @@
         </is>
       </c>
       <c r="D213" s="3" t="n">
-        <v>1495.67</v>
+        <v>5405.1</v>
       </c>
       <c r="E213" s="3" t="n">
-        <v>1464.97</v>
+        <v>5011.67</v>
       </c>
       <c r="F213" s="3" t="n">
-        <v>1474.3</v>
+        <v>5249.6</v>
       </c>
       <c r="G213" s="3" t="n">
-        <v>1474.5</v>
+        <v>5250</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>TAMBOLIIN</t>
+          <t>TFL</t>
         </is>
       </c>
       <c r="B214" s="3" t="inlineStr">
@@ -6670,22 +6670,22 @@
         </is>
       </c>
       <c r="D214" s="3" t="n">
-        <v>257.92</v>
+        <v>12.87</v>
       </c>
       <c r="E214" s="3" t="n">
-        <v>242.7</v>
+        <v>11.68</v>
       </c>
       <c r="F214" s="3" t="n">
-        <v>259.43</v>
+        <v>11.93</v>
       </c>
       <c r="G214" s="3" t="n">
-        <v>260.99</v>
+        <v>11.91</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>TATACHEM</t>
+          <t>TGBHOTELS</t>
         </is>
       </c>
       <c r="B215" s="3" t="inlineStr">
@@ -6699,22 +6699,22 @@
         </is>
       </c>
       <c r="D215" s="3" t="n">
-        <v>655.37</v>
+        <v>9.85</v>
       </c>
       <c r="E215" s="3" t="n">
-        <v>635.5</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="F215" s="3" t="n">
-        <v>655.75</v>
+        <v>9.84</v>
       </c>
       <c r="G215" s="3" t="n">
-        <v>655</v>
+        <v>9.84</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>TCIEXP</t>
+          <t>THELEELA</t>
         </is>
       </c>
       <c r="B216" s="3" t="inlineStr">
@@ -6728,22 +6728,22 @@
         </is>
       </c>
       <c r="D216" s="3" t="n">
-        <v>561.3200000000001</v>
+        <v>567.3</v>
       </c>
       <c r="E216" s="3" t="n">
-        <v>537.8200000000001</v>
+        <v>547.63</v>
       </c>
       <c r="F216" s="3" t="n">
-        <v>555.8</v>
+        <v>570.4</v>
       </c>
       <c r="G216" s="3" t="n">
-        <v>558</v>
+        <v>571.15</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>TEJASNET</t>
+          <t>TI</t>
         </is>
       </c>
       <c r="B217" s="3" t="inlineStr">
@@ -6757,22 +6757,22 @@
         </is>
       </c>
       <c r="D217" s="3" t="n">
-        <v>535.5</v>
+        <v>572.3</v>
       </c>
       <c r="E217" s="3" t="n">
-        <v>515.48</v>
+        <v>552</v>
       </c>
       <c r="F217" s="3" t="n">
-        <v>550.15</v>
+        <v>561.05</v>
       </c>
       <c r="G217" s="3" t="n">
-        <v>549</v>
+        <v>558.75</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>TEXRAIL</t>
+          <t>TIMEX</t>
         </is>
       </c>
       <c r="B218" s="3" t="inlineStr">
@@ -6786,22 +6786,22 @@
         </is>
       </c>
       <c r="D218" s="3" t="n">
-        <v>110.95</v>
+        <v>661.9299999999999</v>
       </c>
       <c r="E218" s="3" t="n">
-        <v>108.11</v>
+        <v>631.97</v>
       </c>
       <c r="F218" s="3" t="n">
-        <v>109.44</v>
+        <v>679.45</v>
       </c>
       <c r="G218" s="3" t="n">
-        <v>109.6</v>
+        <v>678.8</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>THEJO</t>
+          <t>TIRUMALCHM</t>
         </is>
       </c>
       <c r="B219" s="3" t="inlineStr">
@@ -6815,22 +6815,22 @@
         </is>
       </c>
       <c r="D219" s="3" t="n">
-        <v>2098.27</v>
+        <v>164.76</v>
       </c>
       <c r="E219" s="3" t="n">
-        <v>2035.77</v>
+        <v>158.42</v>
       </c>
       <c r="F219" s="3" t="n">
-        <v>2060.6</v>
+        <v>160.06</v>
       </c>
       <c r="G219" s="3" t="n">
-        <v>2056</v>
+        <v>159.91</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>TIMETECHNO</t>
+          <t>TTKHLTCARE</t>
         </is>
       </c>
       <c r="B220" s="3" t="inlineStr">
@@ -6844,22 +6844,22 @@
         </is>
       </c>
       <c r="D220" s="3" t="n">
-        <v>188.15</v>
+        <v>1148.63</v>
       </c>
       <c r="E220" s="3" t="n">
-        <v>184.21</v>
+        <v>1089.77</v>
       </c>
       <c r="F220" s="3" t="n">
-        <v>186.29</v>
+        <v>1159.7</v>
       </c>
       <c r="G220" s="3" t="n">
-        <v>186.01</v>
+        <v>1152.9</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>TURTLEMINT</t>
+          <t>TVSSRICHAK</t>
         </is>
       </c>
       <c r="B221" s="3" t="inlineStr">
@@ -6873,22 +6873,22 @@
         </is>
       </c>
       <c r="D221" s="3" t="n">
-        <v>154.67</v>
+        <v>5403.57</v>
       </c>
       <c r="E221" s="3" t="n">
-        <v>145.32</v>
+        <v>5183.47</v>
       </c>
       <c r="F221" s="3" t="n">
-        <v>152.65</v>
+        <v>5519.6</v>
       </c>
       <c r="G221" s="3" t="n">
-        <v>152.5</v>
+        <v>5480</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>UEL</t>
+          <t>UDS</t>
         </is>
       </c>
       <c r="B222" s="3" t="inlineStr">
@@ -6902,22 +6902,22 @@
         </is>
       </c>
       <c r="D222" s="3" t="n">
-        <v>180.46</v>
+        <v>225.23</v>
       </c>
       <c r="E222" s="3" t="n">
-        <v>175.58</v>
+        <v>220.06</v>
       </c>
       <c r="F222" s="3" t="n">
-        <v>189.33</v>
+        <v>224.73</v>
       </c>
       <c r="G222" s="3" t="n">
-        <v>189.33</v>
+        <v>222.25</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>UTISENSETF</t>
+          <t>UNICHEMLAB</t>
         </is>
       </c>
       <c r="B223" s="3" t="inlineStr">
@@ -6931,22 +6931,22 @@
         </is>
       </c>
       <c r="D223" s="3" t="n">
-        <v>941.63</v>
+        <v>568.12</v>
       </c>
       <c r="E223" s="3" t="n">
-        <v>933.52</v>
+        <v>535.87</v>
       </c>
       <c r="F223" s="3" t="n">
-        <v>939.25</v>
+        <v>556.55</v>
       </c>
       <c r="G223" s="3" t="n">
-        <v>938.3200000000001</v>
+        <v>554.05</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>VAISHALI</t>
+          <t>UNIECOM</t>
         </is>
       </c>
       <c r="B224" s="3" t="inlineStr">
@@ -6960,22 +6960,22 @@
         </is>
       </c>
       <c r="D224" s="3" t="n">
-        <v>8.369999999999999</v>
+        <v>88.77</v>
       </c>
       <c r="E224" s="3" t="n">
-        <v>7.94</v>
+        <v>84.38</v>
       </c>
       <c r="F224" s="3" t="n">
-        <v>8.31</v>
+        <v>89.36</v>
       </c>
       <c r="G224" s="3" t="n">
-        <v>8.24</v>
+        <v>89.5</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>VIJIFIN</t>
+          <t>UNIPARTS</t>
         </is>
       </c>
       <c r="B225" s="3" t="inlineStr">
@@ -6989,22 +6989,22 @@
         </is>
       </c>
       <c r="D225" s="3" t="n">
-        <v>14.75</v>
+        <v>867.87</v>
       </c>
       <c r="E225" s="3" t="n">
-        <v>14.75</v>
+        <v>824.02</v>
       </c>
       <c r="F225" s="3" t="n">
-        <v>15.04</v>
+        <v>893.45</v>
       </c>
       <c r="G225" s="3" t="n">
-        <v>15.04</v>
+        <v>898</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>VINCOFE</t>
+          <t>UNIVCABLES</t>
         </is>
       </c>
       <c r="B226" s="3" t="inlineStr">
@@ -7018,22 +7018,22 @@
         </is>
       </c>
       <c r="D226" s="3" t="n">
-        <v>175.89</v>
+        <v>1686.53</v>
       </c>
       <c r="E226" s="3" t="n">
-        <v>166.58</v>
+        <v>1602.23</v>
       </c>
       <c r="F226" s="3" t="n">
-        <v>177.97</v>
+        <v>1648.2</v>
       </c>
       <c r="G226" s="3" t="n">
-        <v>176.53</v>
+        <v>1654.9</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>VINDHYATEL</t>
+          <t>UTISENSETF</t>
         </is>
       </c>
       <c r="B227" s="3" t="inlineStr">
@@ -7047,22 +7047,22 @@
         </is>
       </c>
       <c r="D227" s="3" t="n">
-        <v>2542.17</v>
+        <v>941.63</v>
       </c>
       <c r="E227" s="3" t="n">
-        <v>2432.03</v>
+        <v>933.52</v>
       </c>
       <c r="F227" s="3" t="n">
-        <v>2585.5</v>
+        <v>939.25</v>
       </c>
       <c r="G227" s="3" t="n">
-        <v>2591</v>
+        <v>938.3200000000001</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>VINEETLAB</t>
+          <t>VIDYAWIRES</t>
         </is>
       </c>
       <c r="B228" s="3" t="inlineStr">
@@ -7076,22 +7076,22 @@
         </is>
       </c>
       <c r="D228" s="3" t="n">
-        <v>39.49</v>
+        <v>90.8</v>
       </c>
       <c r="E228" s="3" t="n">
-        <v>37.78</v>
+        <v>87.33</v>
       </c>
       <c r="F228" s="3" t="n">
-        <v>38.68</v>
+        <v>90.25</v>
       </c>
       <c r="G228" s="3" t="n">
-        <v>39.25</v>
+        <v>90.54000000000001</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>VITAL</t>
+          <t>VIJIFIN</t>
         </is>
       </c>
       <c r="B229" s="3" t="inlineStr">
@@ -7105,22 +7105,22 @@
         </is>
       </c>
       <c r="D229" s="3" t="n">
-        <v>55.3</v>
+        <v>15.04</v>
       </c>
       <c r="E229" s="3" t="n">
-        <v>51.51</v>
+        <v>15.04</v>
       </c>
       <c r="F229" s="3" t="n">
-        <v>55.48</v>
+        <v>15.34</v>
       </c>
       <c r="G229" s="3" t="n">
-        <v>55.5</v>
+        <v>15.34</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>VIVIMEDLAB</t>
+          <t>VINCOFE</t>
         </is>
       </c>
       <c r="B230" s="3" t="inlineStr">
@@ -7134,22 +7134,22 @@
         </is>
       </c>
       <c r="D230" s="3" t="n">
-        <v>6.94</v>
+        <v>183.35</v>
       </c>
       <c r="E230" s="3" t="n">
-        <v>6.94</v>
+        <v>171.67</v>
       </c>
       <c r="F230" s="3" t="n">
-        <v>7.07</v>
+        <v>185.77</v>
       </c>
       <c r="G230" s="3" t="n">
-        <v>7.07</v>
+        <v>185.94</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>VRAJ</t>
+          <t>VISACHROME</t>
         </is>
       </c>
       <c r="B231" s="3" t="inlineStr">
@@ -7163,16 +7163,16 @@
         </is>
       </c>
       <c r="D231" s="3" t="n">
-        <v>126.91</v>
+        <v>39.36</v>
       </c>
       <c r="E231" s="3" t="n">
-        <v>122.67</v>
+        <v>38.29</v>
       </c>
       <c r="F231" s="3" t="n">
-        <v>125.47</v>
+        <v>41.02</v>
       </c>
       <c r="G231" s="3" t="n">
-        <v>126</v>
+        <v>41.02</v>
       </c>
     </row>
     <row r="232">
@@ -7192,22 +7192,22 @@
         </is>
       </c>
       <c r="D232" s="3" t="n">
-        <v>295.62</v>
+        <v>300.1</v>
       </c>
       <c r="E232" s="3" t="n">
-        <v>287.53</v>
+        <v>290.48</v>
       </c>
       <c r="F232" s="3" t="n">
-        <v>295.95</v>
+        <v>303.15</v>
       </c>
       <c r="G232" s="3" t="n">
-        <v>297</v>
+        <v>303.5</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>WAKEFIT</t>
+          <t>XTRANET</t>
         </is>
       </c>
       <c r="B233" s="3" t="inlineStr">
@@ -7221,22 +7221,22 @@
         </is>
       </c>
       <c r="D233" s="3" t="n">
-        <v>149.57</v>
+        <v>191.13</v>
       </c>
       <c r="E233" s="3" t="n">
-        <v>143.04</v>
+        <v>169.11</v>
       </c>
       <c r="F233" s="3" t="n">
-        <v>144.71</v>
+        <v>194.82</v>
       </c>
       <c r="G233" s="3" t="n">
-        <v>144.6</v>
+        <v>196.8</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>WELCORP</t>
+          <t>YUKEN</t>
         </is>
       </c>
       <c r="B234" s="3" t="inlineStr">
@@ -7250,219 +7250,16 @@
         </is>
       </c>
       <c r="D234" s="3" t="n">
-        <v>2410.4</v>
+        <v>988.13</v>
       </c>
       <c r="E234" s="3" t="n">
-        <v>2289.47</v>
+        <v>943.28</v>
       </c>
       <c r="F234" s="3" t="n">
-        <v>2373.8</v>
+        <v>989.1</v>
       </c>
       <c r="G234" s="3" t="n">
-        <v>2365</v>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" s="2" t="inlineStr">
-        <is>
-          <t>WELSPUNLIV</t>
-        </is>
-      </c>
-      <c r="B235" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C235" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D235" s="3" t="n">
-        <v>193.38</v>
-      </c>
-      <c r="E235" s="3" t="n">
-        <v>188.03</v>
-      </c>
-      <c r="F235" s="3" t="n">
-        <v>190.46</v>
-      </c>
-      <c r="G235" s="3" t="n">
-        <v>189.55</v>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" s="2" t="inlineStr">
-        <is>
-          <t>WHEELS</t>
-        </is>
-      </c>
-      <c r="B236" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C236" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D236" s="3" t="n">
-        <v>1549.17</v>
-      </c>
-      <c r="E236" s="3" t="n">
-        <v>1489.27</v>
-      </c>
-      <c r="F236" s="3" t="n">
-        <v>1547.7</v>
-      </c>
-      <c r="G236" s="3" t="n">
-        <v>1546</v>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" s="2" t="inlineStr">
-        <is>
-          <t>WOCKPHARMA</t>
-        </is>
-      </c>
-      <c r="B237" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C237" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D237" s="3" t="n">
-        <v>1988.1</v>
-      </c>
-      <c r="E237" s="3" t="n">
-        <v>1903.57</v>
-      </c>
-      <c r="F237" s="3" t="n">
-        <v>1977.1</v>
-      </c>
-      <c r="G237" s="3" t="n">
-        <v>1975</v>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" s="2" t="inlineStr">
-        <is>
-          <t>WONDERLA</t>
-        </is>
-      </c>
-      <c r="B238" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C238" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D238" s="3" t="n">
-        <v>540.9</v>
-      </c>
-      <c r="E238" s="3" t="n">
-        <v>520.52</v>
-      </c>
-      <c r="F238" s="3" t="n">
-        <v>537.1</v>
-      </c>
-      <c r="G238" s="3" t="n">
-        <v>534.5</v>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" s="2" t="inlineStr">
-        <is>
-          <t>WORTHPERI</t>
-        </is>
-      </c>
-      <c r="B239" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C239" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D239" s="3" t="n">
-        <v>158.72</v>
-      </c>
-      <c r="E239" s="3" t="n">
-        <v>151.89</v>
-      </c>
-      <c r="F239" s="3" t="n">
-        <v>159.55</v>
-      </c>
-      <c r="G239" s="3" t="n">
-        <v>159.77</v>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" s="2" t="inlineStr">
-        <is>
-          <t>YATHARTH</t>
-        </is>
-      </c>
-      <c r="B240" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C240" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D240" s="3" t="n">
-        <v>992.95</v>
-      </c>
-      <c r="E240" s="3" t="n">
-        <v>939.02</v>
-      </c>
-      <c r="F240" s="3" t="n">
-        <v>967.4</v>
-      </c>
-      <c r="G240" s="3" t="n">
-        <v>969.5</v>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" s="2" t="inlineStr">
-        <is>
-          <t>ZYDUSLIFE</t>
-        </is>
-      </c>
-      <c r="B241" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C241" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D241" s="3" t="n">
-        <v>1181.6</v>
-      </c>
-      <c r="E241" s="3" t="n">
-        <v>1143.5</v>
-      </c>
-      <c r="F241" s="3" t="n">
-        <v>1191</v>
-      </c>
-      <c r="G241" s="3" t="n">
-        <v>1191</v>
+        <v>1000.85</v>
       </c>
     </row>
   </sheetData>

--- a/data/uptrend_output.xlsx
+++ b/data/uptrend_output.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G234"/>
+  <dimension ref="A1:G175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -522,22 +522,22 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1444.97</v>
+        <v>1506.6</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1367.33</v>
+        <v>1414.37</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1447.8</v>
+        <v>1523.5</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>1457.9</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>AAREYDRUGS</t>
+          <t>AARTIPHARM</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -551,22 +551,22 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>88.26000000000001</v>
+        <v>862.88</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>84.26000000000001</v>
+        <v>826.92</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>88.20999999999999</v>
+        <v>865.2</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>87.89</v>
+        <v>865</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>AARTIPHARM</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -580,22 +580,22 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>852.27</v>
+        <v>497.22</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>818.28</v>
+        <v>480.88</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>845.4</v>
+        <v>492.65</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>843.1</v>
+        <v>492</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>ADL</t>
+          <t>AHLEAST</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -609,22 +609,22 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>75.45</v>
+        <v>142.43</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>70.98999999999999</v>
+        <v>136.15</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>75.75</v>
+        <v>142.2</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>73</v>
+        <v>143</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>ADOR</t>
+          <t>AKSHARCHEM</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -638,22 +638,22 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1665.8</v>
+        <v>372.22</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1572.87</v>
+        <v>365.01</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1705.2</v>
+        <v>384.65</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>1699</v>
+        <v>384.65</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>ADROITINFO</t>
+          <t>AKUMS</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -667,22 +667,22 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>10.7</v>
+        <v>785.33</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>10.12</v>
+        <v>766.27</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>10.3</v>
+        <v>779.05</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>10.25</v>
+        <v>782</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>ADVAIT</t>
+          <t>ALMONDZ</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -696,22 +696,22 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>2204.93</v>
+        <v>17.71</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>2124.9</v>
+        <v>16.77</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>2170.7</v>
+        <v>17.49</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>2162</v>
+        <v>17.57</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>AEROPLANE</t>
+          <t>AMANTA</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -725,22 +725,22 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>176.37</v>
+        <v>188.3</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>171.1</v>
+        <v>186.49</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>174.33</v>
+        <v>190</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>174.88</v>
+        <v>190</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>ALBERTDAVD</t>
+          <t>AMBALALSA</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -754,22 +754,22 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>914.28</v>
+        <v>45.41</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>877.02</v>
+        <v>43.3</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>897.9</v>
+        <v>43.92</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>907.9</v>
+        <v>44.69</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>ALMONDZ</t>
+          <t>AMDIND</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -783,16 +783,16 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>17.26</v>
+        <v>57.63</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>15.85</v>
+        <v>53.16</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>17.53</v>
+        <v>57.02</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>17.5</v>
+        <v>57.12</v>
       </c>
     </row>
     <row r="12">
@@ -827,7 +827,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>ANDHRSUGAR</t>
+          <t>AONELIQUID</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -841,22 +841,22 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>100.85</v>
+        <v>1074.91</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>96.12</v>
+        <v>1074.89</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>99.64</v>
+        <v>1075.03</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>100.3</v>
+        <v>1075.04</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>AONELIQUID</t>
+          <t>APCOTEXIND</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -870,22 +870,22 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1074.67</v>
+        <v>648.33</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1074.65</v>
+        <v>619.27</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1074.89</v>
+        <v>639.2</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>1074.89</v>
+        <v>641</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>APCOTEXIND</t>
+          <t>ARVIND</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -899,22 +899,22 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>635.67</v>
+        <v>558.05</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>613.35</v>
+        <v>540.58</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>646.3</v>
+        <v>557.1</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>642</v>
+        <v>556.95</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>APTECHT</t>
+          <t>ASAHISONG</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -928,22 +928,22 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>93.2</v>
+        <v>380</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>90.27</v>
+        <v>359.48</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>91.84</v>
+        <v>374.55</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>92.95</v>
+        <v>375</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>ARFIN</t>
+          <t>ASIANHOTNR</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -957,22 +957,22 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>86.83</v>
+        <v>362.12</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>84.48999999999999</v>
+        <v>319.35</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>87.23</v>
+        <v>369.2</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>87.3</v>
+        <v>373</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>ASHOKAMET</t>
+          <t>ATHERENERG</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -986,22 +986,22 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>13.8</v>
+        <v>1697.23</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>13.19</v>
+        <v>1607.23</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>13.78</v>
+        <v>1725.6</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>13.83</v>
+        <v>1725.6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>ASIANTILES</t>
+          <t>ATLANTAA</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1015,22 +1015,22 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>48.85</v>
+        <v>39.89</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>47.33</v>
+        <v>37.49</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>49.61</v>
+        <v>40.68</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>49.63</v>
+        <v>40.8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>ASKAUTOLTD</t>
+          <t>ATLANTAELE</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1044,22 +1044,22 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>640.12</v>
+        <v>1823.17</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>612.02</v>
+        <v>1744.47</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>659.9</v>
+        <v>1823.6</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>660</v>
+        <v>1824.6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>ATHERENERG</t>
+          <t>AUSOMENT</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>1620.23</v>
+        <v>150.18</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>1540.8</v>
+        <v>145.77</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>1717.7</v>
+        <v>149.77</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>1717.7</v>
+        <v>148.1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>ATLANTAELE</t>
+          <t>AVL</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -1102,22 +1102,22 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>1773.63</v>
+        <v>601.9299999999999</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>1696.1</v>
+        <v>585.9</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>1830.4</v>
+        <v>604.1</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>1837</v>
+        <v>603.95</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>AUROPHARMA</t>
+          <t>AXISBNKETF</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -1131,22 +1131,22 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>1670.07</v>
+        <v>599.1900000000001</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>1620.3</v>
+        <v>593.95</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>1717</v>
+        <v>597.15</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>1717</v>
+        <v>597.09</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>AVADHSUGAR</t>
+          <t>AXISCADES</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1160,22 +1160,22 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>844.55</v>
+        <v>1669.2</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>804.15</v>
+        <v>1601.5</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>855.3</v>
+        <v>1644.2</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>852.1</v>
+        <v>1640.1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>AXISBNKETF</t>
+          <t>AXISCETF</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -1189,22 +1189,22 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>599.1900000000001</v>
+        <v>120.57</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>593.95</v>
+        <v>118.88</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>597.15</v>
+        <v>121.12</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>597.09</v>
+        <v>120.8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>AXISCETF</t>
+          <t>AYMSYNTEX</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -1218,22 +1218,22 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>120.57</v>
+        <v>286.05</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>118.88</v>
+        <v>253.97</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>121.12</v>
+        <v>294.2</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>120.8</v>
+        <v>291.8</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>AZAD</t>
+          <t>BAFNAPH</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -1247,22 +1247,22 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>2887.4</v>
+        <v>305.17</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>2804.5</v>
+        <v>290</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>2861.8</v>
+        <v>312.6</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>2878</v>
+        <v>313.8</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>BAFNAPH</t>
+          <t>BAJAJ-AUTO</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1276,22 +1276,22 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>292.67</v>
+        <v>12191.33</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>278.53</v>
+        <v>11912</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>304.25</v>
+        <v>12361</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>305.65</v>
+        <v>12361</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>BAJAJ-AUTO</t>
+          <t>BASML</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -1305,22 +1305,22 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>11975.33</v>
+        <v>25.82</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>11754.67</v>
+        <v>25.04</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>12130</v>
+        <v>25.57</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>12130</v>
+        <v>25.7</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>BAJAJCON</t>
+          <t>BENGALASM</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -1334,22 +1334,22 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>476.17</v>
+        <v>6535.67</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>455.82</v>
+        <v>6316.5</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>474.05</v>
+        <v>6661.5</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>475</v>
+        <v>6699.5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>BANARISUG</t>
+          <t>BHAGERIA</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -1363,22 +1363,22 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>4003.83</v>
+        <v>250.88</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>3817.87</v>
+        <v>246.29</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>3925.7</v>
+        <v>263.2</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>3934</v>
+        <v>263.2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>BENGALASM</t>
+          <t>BLISSGVS</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -1392,22 +1392,22 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>6395.67</v>
+        <v>613.53</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>6222.5</v>
+        <v>579.67</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>6438</v>
+        <v>630.4</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>6548</v>
+        <v>631</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>BHAGERIA</t>
+          <t>BODALCHEM</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -1421,22 +1421,22 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>240.51</v>
+        <v>116.44</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>231.33</v>
+        <v>106.19</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>250.68</v>
+        <v>126.76</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>250.68</v>
+        <v>128.1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>BHARATSE</t>
+          <t>BVCL</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -1450,22 +1450,22 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>227.18</v>
+        <v>45.53</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>220.39</v>
+        <v>42.45</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>224.25</v>
+        <v>43.5</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>225</v>
+        <v>43.7</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>BLISSGVS</t>
+          <t>CMRGREEN</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -1479,22 +1479,22 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>593.87</v>
+        <v>231.4</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>564.4</v>
+        <v>221.82</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>616.75</v>
+        <v>231.03</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>617.35</v>
+        <v>231.15</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>BLSE</t>
+          <t>COMSYN</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -1508,22 +1508,22 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>327.33</v>
+        <v>299.22</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>311.93</v>
+        <v>277.76</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>327.9</v>
+        <v>304.35</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>328.9</v>
+        <v>304.7</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>BLUECHIP</t>
+          <t>CORDSCABLE</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -1537,22 +1537,22 @@
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>2.14</v>
+        <v>289.3</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>2.14</v>
+        <v>259.83</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>2.18</v>
+        <v>312.95</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>2.18</v>
+        <v>310.25</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>BODALCHEM</t>
+          <t>CPCAP</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -1566,22 +1566,22 @@
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>104.18</v>
+        <v>118.9</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>95.42</v>
+        <v>113.24</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>118.89</v>
+        <v>117.72</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>118.89</v>
+        <v>118.9</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>BROOKS</t>
+          <t>CRISIL</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -1595,22 +1595,22 @@
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>68.89</v>
+        <v>4833.97</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>64.79000000000001</v>
+        <v>4717.37</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>66.54000000000001</v>
+        <v>4829.5</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>67.73999999999999</v>
+        <v>4761.5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>CARERATING</t>
+          <t>CSLFINANCE</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -1624,22 +1624,22 @@
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>1711.33</v>
+        <v>241.43</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>1645.03</v>
+        <v>232.03</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>1729</v>
+        <v>236.92</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>1734.9</v>
+        <v>237.5</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>CARRARO</t>
+          <t>CYBERMEDIA</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -1653,22 +1653,22 @@
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>561.53</v>
+        <v>19.38</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>543.17</v>
+        <v>17.98</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>559.4</v>
+        <v>18.66</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>558</v>
+        <v>18.78</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>CYIENT</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -1682,22 +1682,22 @@
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>1423.33</v>
+        <v>1175.17</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>1406.8</v>
+        <v>1088.68</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>1409.2</v>
+        <v>1164.6</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>1409.2</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>CMRGREEN</t>
+          <t>DRAGARWQ</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -1711,22 +1711,22 @@
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>227.1</v>
+        <v>5298.33</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>218.45</v>
+        <v>5225.33</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>230.78</v>
+        <v>5309.5</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>232</v>
+        <v>5321</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>CNL</t>
+          <t>DSKULKARNI</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -1740,22 +1740,22 @@
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>1278.42</v>
+        <v>18.31</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>1204.27</v>
+        <v>18.31</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>1279.6</v>
+        <v>18.67</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>1280.1</v>
+        <v>18.67</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>COFORGE</t>
+          <t>DYCL</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -1769,22 +1769,22 @@
         </is>
       </c>
       <c r="D45" s="3" t="n">
-        <v>1982.27</v>
+        <v>518.08</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>1921.2</v>
+        <v>471.17</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>1985.3</v>
+        <v>542.4</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>1985.3</v>
+        <v>543</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>CRAFTSMAN</t>
+          <t>EFCIL</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -1798,22 +1798,22 @@
         </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>11209.67</v>
+        <v>206.11</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>10752</v>
+        <v>198.33</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>11198.5</v>
+        <v>201.34</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>11428.5</v>
+        <v>202</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>CRISIL</t>
+          <t>ELECTCAST</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -1827,22 +1827,22 @@
         </is>
       </c>
       <c r="D47" s="3" t="n">
-        <v>4785.97</v>
+        <v>84.68000000000001</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>4630.67</v>
+        <v>81.16</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>4821.8</v>
+        <v>83.83</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>4810</v>
+        <v>83.8</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>CSLFINANCE</t>
+          <t>ELIQUID</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -1856,22 +1856,22 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>237.62</v>
+        <v>1045.88</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>228.37</v>
+        <v>1045.86</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>239.7</v>
+        <v>1045.99</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>240</v>
+        <v>1045.99</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>CYIENT</t>
+          <t>EMKAY</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -1885,22 +1885,22 @@
         </is>
       </c>
       <c r="D49" s="3" t="n">
-        <v>1121.83</v>
+        <v>262.93</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>1049.52</v>
+        <v>248.2</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>1174.8</v>
+        <v>264.1</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>1175</v>
+        <v>264.5</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>DALMIASUG</t>
+          <t>EMMBI</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -1914,22 +1914,22 @@
         </is>
       </c>
       <c r="D50" s="3" t="n">
-        <v>496.82</v>
+        <v>90.43000000000001</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>472.7</v>
+        <v>87.41</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>484.15</v>
+        <v>92.66</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>485</v>
+        <v>92.40000000000001</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>DBOL</t>
+          <t>ENGINERSIN</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -1943,22 +1943,22 @@
         </is>
       </c>
       <c r="D51" s="3" t="n">
-        <v>130.96</v>
+        <v>269.26</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>123.42</v>
+        <v>253.37</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>127.24</v>
+        <v>280.05</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>127.5</v>
+        <v>280.7</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>DGCONTENT</t>
+          <t>FEDDERSHOL</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -1972,22 +1972,22 @@
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>26.06</v>
+        <v>45.73</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>23.91</v>
+        <v>44.39</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>25.2</v>
+        <v>45.21</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>25.1</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>DIFFNKG</t>
+          <t>FINEORG</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -2001,22 +2001,22 @@
         </is>
       </c>
       <c r="D53" s="3" t="n">
-        <v>439.23</v>
+        <v>5345.6</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>401.82</v>
+        <v>5202.5</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>485.5</v>
+        <v>5255.5</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>493.2</v>
+        <v>5227</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>DIVISLAB</t>
+          <t>GABRIEL</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -2030,22 +2030,22 @@
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>9295.67</v>
+        <v>1434.57</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>9085.17</v>
+        <v>1351.63</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>9467</v>
+        <v>1426.3</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>9467</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>DODLA</t>
+          <t>GARFIBRES</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -2059,22 +2059,22 @@
         </is>
       </c>
       <c r="D55" s="3" t="n">
-        <v>1116.07</v>
+        <v>825.5700000000001</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>1074.93</v>
+        <v>794.4299999999999</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>1080.6</v>
+        <v>842.7</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>1076</v>
+        <v>850</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>DSKULKARNI</t>
+          <t>GEEKAYWIRE</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -2088,22 +2088,22 @@
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>17.96</v>
+        <v>28.18</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>17.96</v>
+        <v>24.72</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>18.31</v>
+        <v>29.09</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>18.31</v>
+        <v>29.11</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>DYCL</t>
+          <t>GHCLTEXTIL</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -2117,22 +2117,22 @@
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>485.23</v>
+        <v>137.68</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>458.7</v>
+        <v>130.34</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>493.2</v>
+        <v>140.45</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>490.9</v>
+        <v>141.14</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>EBBETF0431</t>
+          <t>GICRE</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -2146,22 +2146,22 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>1436.62</v>
+        <v>357.9</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>1430.64</v>
+        <v>352.83</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>1436.39</v>
+        <v>354.75</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>1436.15</v>
+        <v>354.6</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>ECLERX</t>
+          <t>GKSL</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -2175,22 +2175,22 @@
         </is>
       </c>
       <c r="D59" s="3" t="n">
-        <v>2010.73</v>
+        <v>165.48</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>1927.67</v>
+        <v>155.44</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>1976.9</v>
+        <v>162.45</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>1956</v>
+        <v>162.55</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>ELECTCAST</t>
+          <t>GLFL</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -2204,22 +2204,22 @@
         </is>
       </c>
       <c r="D60" s="3" t="n">
-        <v>82.77</v>
+        <v>5.96</v>
       </c>
       <c r="E60" s="3" t="n">
-        <v>79.15000000000001</v>
+        <v>5.44</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>83.44</v>
+        <v>5.93</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>83.09999999999999</v>
+        <v>5.66</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>ELIQUID</t>
+          <t>GOACARBON</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -2233,22 +2233,22 @@
         </is>
       </c>
       <c r="D61" s="3" t="n">
-        <v>1045.65</v>
+        <v>371.62</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>1043.4</v>
+        <v>357.75</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>1045.87</v>
+        <v>369.05</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>1045.87</v>
+        <v>368</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>EMKAY</t>
+          <t>GODREJAGRO</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -2262,22 +2262,22 @@
         </is>
       </c>
       <c r="D62" s="3" t="n">
-        <v>254.86</v>
+        <v>645.3200000000001</v>
       </c>
       <c r="E62" s="3" t="n">
-        <v>241.94</v>
+        <v>615.23</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>257.18</v>
+        <v>654.4</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>254.48</v>
+        <v>652</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>ENGINERSIN</t>
+          <t>GRAPHITE</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -2291,22 +2291,22 @@
         </is>
       </c>
       <c r="D63" s="3" t="n">
-        <v>256.87</v>
+        <v>723.03</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>247.72</v>
+        <v>692.78</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>261.87</v>
+        <v>732.9</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>263</v>
+        <v>733.8</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>EXICOM</t>
+          <t>GYFTR</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -2320,22 +2320,22 @@
         </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>167.22</v>
+        <v>177.69</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>158.72</v>
+        <v>166.79</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>165.99</v>
+        <v>182.15</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>166</v>
+        <v>183.85</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>FEDDERSHOL</t>
+          <t>HAPPYFORGE</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -2349,22 +2349,22 @@
         </is>
       </c>
       <c r="D65" s="3" t="n">
-        <v>44.68</v>
+        <v>2401.1</v>
       </c>
       <c r="E65" s="3" t="n">
-        <v>43.47</v>
+        <v>2295.33</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>44.69</v>
+        <v>2420.4</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>45</v>
+        <v>2424</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>FINEORG</t>
+          <t>HDFCLIQUID</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -2378,22 +2378,22 @@
         </is>
       </c>
       <c r="D66" s="3" t="n">
-        <v>5313.93</v>
+        <v>1076.01</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>5164.37</v>
+        <v>1075.99</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>5282.8</v>
+        <v>1076.13</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>5299.8</v>
+        <v>1076.12</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>FMGOETZE</t>
+          <t>HDFCNIFIT</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -2407,22 +2407,22 @@
         </is>
       </c>
       <c r="D67" s="3" t="n">
-        <v>604.77</v>
+        <v>33.56</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>567.33</v>
+        <v>32.68</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>624.85</v>
+        <v>33.43</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>626.3</v>
+        <v>33.35</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>FRACTAL</t>
+          <t>HINDCON</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -2436,22 +2436,22 @@
         </is>
       </c>
       <c r="D68" s="3" t="n">
-        <v>854.85</v>
+        <v>24.36</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>833.75</v>
+        <v>22.57</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>852.15</v>
+        <v>23.47</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>844</v>
+        <v>23.69</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>GARFIBRES</t>
+          <t>HINDOILEXP</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -2465,22 +2465,22 @@
         </is>
       </c>
       <c r="D69" s="3" t="n">
-        <v>809.2</v>
+        <v>168.31</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>786.3200000000001</v>
+        <v>161.34</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>813.85</v>
+        <v>169</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>818.8</v>
+        <v>167.9</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>GATECH</t>
+          <t>HNDFDS</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -2494,22 +2494,22 @@
         </is>
       </c>
       <c r="D70" s="3" t="n">
-        <v>1.07</v>
+        <v>658.25</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>1.06</v>
+        <v>635.15</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>1.1</v>
+        <v>644.1</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>1.11</v>
+        <v>647.5</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>GEEKAYWIRE</t>
+          <t>ICRA</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -2523,22 +2523,22 @@
         </is>
       </c>
       <c r="D71" s="3" t="n">
-        <v>26.06</v>
+        <v>4990.97</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>23.29</v>
+        <v>4855.23</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>26.7</v>
+        <v>5011.9</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>26.8</v>
+        <v>5017</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>GHCLTEXTIL</t>
+          <t>IGPL</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -2552,22 +2552,22 @@
         </is>
       </c>
       <c r="D72" s="3" t="n">
-        <v>132.33</v>
+        <v>544.6</v>
       </c>
       <c r="E72" s="3" t="n">
-        <v>126.92</v>
+        <v>526.12</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>134.77</v>
+        <v>548.35</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>133.6</v>
+        <v>549.9</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>GICL</t>
+          <t>IIFLCAPS</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -2581,22 +2581,22 @@
         </is>
       </c>
       <c r="D73" s="3" t="n">
-        <v>23.9</v>
+        <v>338.7</v>
       </c>
       <c r="E73" s="3" t="n">
-        <v>22.96</v>
+        <v>333.77</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>23.84</v>
+        <v>340.15</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>23.9</v>
+        <v>340</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>GKSL</t>
+          <t>INDORAMA</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -2610,22 +2610,22 @@
         </is>
       </c>
       <c r="D74" s="3" t="n">
-        <v>161.11</v>
+        <v>68.63</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>153.55</v>
+        <v>63.56</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>158.14</v>
+        <v>68.01000000000001</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>158.83</v>
+        <v>67.84999999999999</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>GOACARBON</t>
+          <t>INFIBEAM</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -2639,22 +2639,22 @@
         </is>
       </c>
       <c r="D75" s="3" t="n">
-        <v>365.78</v>
+        <v>16.54</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>352.15</v>
+        <v>15.65</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>369.55</v>
+        <v>16.9</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>370</v>
+        <v>16.84</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>GRAPHITE</t>
+          <t>INSECTICID</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -2668,22 +2668,22 @@
         </is>
       </c>
       <c r="D76" s="3" t="n">
-        <v>704.1799999999999</v>
+        <v>613</v>
       </c>
       <c r="E76" s="3" t="n">
-        <v>683.35</v>
+        <v>583.17</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>702.55</v>
+        <v>598.35</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>705.1</v>
+        <v>595.1</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>GRAUWEIL</t>
+          <t>IPCALAB</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -2697,22 +2697,22 @@
         </is>
       </c>
       <c r="D77" s="3" t="n">
-        <v>71.27</v>
+        <v>1986.33</v>
       </c>
       <c r="E77" s="3" t="n">
-        <v>68.23</v>
+        <v>1940.9</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>71.63</v>
+        <v>1987.6</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>71.5</v>
+        <v>1983.5</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>GVPTECH</t>
+          <t>ITAXIS</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -2726,22 +2726,22 @@
         </is>
       </c>
       <c r="D78" s="3" t="n">
-        <v>8.960000000000001</v>
+        <v>346.87</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>7.74</v>
+        <v>338.61</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>8.59</v>
+        <v>343.43</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>8.359999999999999</v>
+        <v>342.23</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>HALDYNGL</t>
+          <t>ITBEES</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -2755,22 +2755,22 @@
         </is>
       </c>
       <c r="D79" s="3" t="n">
-        <v>139.34</v>
+        <v>34.89</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>133.1</v>
+        <v>33.92</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>140.79</v>
+        <v>34.79</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>140</v>
+        <v>34.85</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>HAPPYFORGE</t>
+          <t>ITIETF</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -2784,22 +2784,22 @@
         </is>
       </c>
       <c r="D80" s="3" t="n">
-        <v>2337.43</v>
+        <v>34.91</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>2243.3</v>
+        <v>34.08</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>2412</v>
+        <v>34.8</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>2419.1</v>
+        <v>34.75</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>HATSUN</t>
+          <t>IVC</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -2813,22 +2813,22 @@
         </is>
       </c>
       <c r="D81" s="3" t="n">
-        <v>1185.55</v>
+        <v>9.06</v>
       </c>
       <c r="E81" s="3" t="n">
-        <v>1127.85</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>1190.45</v>
+        <v>9.32</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>1189.55</v>
+        <v>9.359999999999999</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>HDFCLIQUID</t>
+          <t>IVP</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -2842,22 +2842,22 @@
         </is>
       </c>
       <c r="D82" s="3" t="n">
-        <v>1075.78</v>
+        <v>200.96</v>
       </c>
       <c r="E82" s="3" t="n">
-        <v>1075.75</v>
+        <v>193.68</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>1076</v>
+        <v>205.84</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>1076.01</v>
+        <v>207.5</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>HDFCNIFIT</t>
+          <t>JAIBALAJI</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -2871,22 +2871,22 @@
         </is>
       </c>
       <c r="D83" s="3" t="n">
-        <v>33.23</v>
+        <v>72.56999999999999</v>
       </c>
       <c r="E83" s="3" t="n">
-        <v>32.41</v>
+        <v>69.02</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>32.97</v>
+        <v>70.44</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>32.82</v>
+        <v>71.09999999999999</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>JINDWORLD</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -2900,22 +2900,22 @@
         </is>
       </c>
       <c r="D84" s="3" t="n">
-        <v>253.08</v>
+        <v>40.85</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>243.44</v>
+        <v>38.15</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>249.09</v>
+        <v>42.08</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>248.9</v>
+        <v>41.98</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>HITECHGEAR</t>
+          <t>JNPR</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -2929,22 +2929,22 @@
         </is>
       </c>
       <c r="D85" s="3" t="n">
-        <v>576.38</v>
+        <v>264.48</v>
       </c>
       <c r="E85" s="3" t="n">
-        <v>547.47</v>
+        <v>252.47</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>563.6</v>
+        <v>262.35</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>560</v>
+        <v>261</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>IKIO</t>
+          <t>KALYANIFRG</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -2958,22 +2958,22 @@
         </is>
       </c>
       <c r="D86" s="3" t="n">
-        <v>211.43</v>
+        <v>931.98</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>193.76</v>
+        <v>796.08</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>215.48</v>
+        <v>1083.9</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>214.18</v>
+        <v>1097.15</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>INDGN</t>
+          <t>KAMDHENU</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -2987,22 +2987,22 @@
         </is>
       </c>
       <c r="D87" s="3" t="n">
-        <v>592.22</v>
+        <v>37.3</v>
       </c>
       <c r="E87" s="3" t="n">
-        <v>569.08</v>
+        <v>35.36</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>611.65</v>
+        <v>36.16</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>608</v>
+        <v>36</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>INDUSTOWER</t>
+          <t>KANANIIND</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -3016,22 +3016,22 @@
         </is>
       </c>
       <c r="D88" s="3" t="n">
-        <v>386.23</v>
+        <v>1.57</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>377.35</v>
+        <v>1.47</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>388.8</v>
+        <v>1.56</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>388.8</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>INFIBEAM</t>
+          <t>KAPSTON</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -3045,22 +3045,22 @@
         </is>
       </c>
       <c r="D89" s="3" t="n">
-        <v>16.54</v>
+        <v>583.8</v>
       </c>
       <c r="E89" s="3" t="n">
-        <v>15.65</v>
+        <v>541.48</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>16.9</v>
+        <v>572.3</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>16.84</v>
+        <v>579</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>INGERRAND</t>
+          <t>KARURVYSYA</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -3074,22 +3074,22 @@
         </is>
       </c>
       <c r="D90" s="3" t="n">
-        <v>4827.4</v>
+        <v>351.38</v>
       </c>
       <c r="E90" s="3" t="n">
-        <v>4652.1</v>
+        <v>344.62</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>4848.5</v>
+        <v>347.6</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>4850</v>
+        <v>347</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>INNOVACAP</t>
+          <t>KCPSUGIND</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -3103,22 +3103,22 @@
         </is>
       </c>
       <c r="D91" s="3" t="n">
-        <v>1066.45</v>
+        <v>33.33</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>1028.07</v>
+        <v>31.41</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>1078.1</v>
+        <v>32.25</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>1080</v>
+        <v>32.8</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>INSECTICID</t>
+          <t>LIQGRWBEES</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -3132,22 +3132,22 @@
         </is>
       </c>
       <c r="D92" s="3" t="n">
-        <v>602.7</v>
+        <v>1053.79</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>573.25</v>
+        <v>1053.73</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>610.85</v>
+        <v>1053.9</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>610</v>
+        <v>1053.91</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>INSPIRISYS</t>
+          <t>LIQUIDBETA</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -3161,22 +3161,22 @@
         </is>
       </c>
       <c r="D93" s="3" t="n">
-        <v>92.92</v>
+        <v>1006.2</v>
       </c>
       <c r="E93" s="3" t="n">
-        <v>87.70999999999999</v>
+        <v>1006.18</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>89.04000000000001</v>
+        <v>1006.46</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>90.84999999999999</v>
+        <v>1006.46</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>IOLCP</t>
+          <t>LIQUIDBETF</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -3190,22 +3190,22 @@
         </is>
       </c>
       <c r="D94" s="3" t="n">
-        <v>196.88</v>
+        <v>1096.89</v>
       </c>
       <c r="E94" s="3" t="n">
-        <v>188.49</v>
+        <v>1096.87</v>
       </c>
       <c r="F94" s="3" t="n">
-        <v>193.69</v>
+        <v>1097.02</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>194</v>
+        <v>1097.03</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>IRIS</t>
+          <t>LIQUIDCASE</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -3219,22 +3219,22 @@
         </is>
       </c>
       <c r="D95" s="3" t="n">
-        <v>251.15</v>
+        <v>115.73</v>
       </c>
       <c r="E95" s="3" t="n">
-        <v>238.56</v>
+        <v>115.71</v>
       </c>
       <c r="F95" s="3" t="n">
-        <v>248.97</v>
+        <v>115.73</v>
       </c>
       <c r="G95" s="3" t="n">
-        <v>247.12</v>
+        <v>115.73</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>LIQUIDPLUS</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -3248,22 +3248,22 @@
         </is>
       </c>
       <c r="D96" s="3" t="n">
-        <v>34.61</v>
+        <v>1101.25</v>
       </c>
       <c r="E96" s="3" t="n">
-        <v>33.76</v>
+        <v>1101.14</v>
       </c>
       <c r="F96" s="3" t="n">
-        <v>34.32</v>
+        <v>1101.37</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>34.47</v>
+        <v>1101.36</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>ITAXIS</t>
+          <t>LIQUIDSHRI</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -3277,22 +3277,22 @@
         </is>
       </c>
       <c r="D97" s="3" t="n">
-        <v>342.71</v>
+        <v>1119.58</v>
       </c>
       <c r="E97" s="3" t="n">
-        <v>335.22</v>
+        <v>1119.56</v>
       </c>
       <c r="F97" s="3" t="n">
-        <v>342.83</v>
+        <v>1119.72</v>
       </c>
       <c r="G97" s="3" t="n">
-        <v>341.94</v>
+        <v>1119.72</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>ITBEES</t>
+          <t>LUMAXTECH</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -3306,22 +3306,22 @@
         </is>
       </c>
       <c r="D98" s="3" t="n">
-        <v>34.76</v>
+        <v>2081.53</v>
       </c>
       <c r="E98" s="3" t="n">
-        <v>33.76</v>
+        <v>1979.4</v>
       </c>
       <c r="F98" s="3" t="n">
-        <v>34.32</v>
+        <v>2060</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>34.3</v>
+        <v>2045.1</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>ITETF</t>
+          <t>MAANALU</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -3335,22 +3335,22 @@
         </is>
       </c>
       <c r="D99" s="3" t="n">
-        <v>33.31</v>
+        <v>124.63</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>32.18</v>
+        <v>117.68</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>32.74</v>
+        <v>119.42</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>32.9</v>
+        <v>119.71</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>ITIETF</t>
+          <t>MAFANG</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
@@ -3364,22 +3364,22 @@
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>34.59</v>
+        <v>209.55</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>33.84</v>
+        <v>209.14</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>34.31</v>
+        <v>211.05</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>34.25</v>
+        <v>211</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>IVC</t>
+          <t>MALLCOM</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
@@ -3393,22 +3393,22 @@
         </is>
       </c>
       <c r="D101" s="3" t="n">
-        <v>8.74</v>
+        <v>1021.65</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>8.289999999999999</v>
+        <v>969.4299999999999</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>9.050000000000001</v>
+        <v>1004.45</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>9.08</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>JINDWORLD</t>
+          <t>MANALIPETC</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
@@ -3422,22 +3422,22 @@
         </is>
       </c>
       <c r="D102" s="3" t="n">
-        <v>38.72</v>
+        <v>82.31</v>
       </c>
       <c r="E102" s="3" t="n">
-        <v>36.71</v>
+        <v>75.54000000000001</v>
       </c>
       <c r="F102" s="3" t="n">
-        <v>38.31</v>
+        <v>84.04000000000001</v>
       </c>
       <c r="G102" s="3" t="n">
-        <v>38.5</v>
+        <v>84.89</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>JTLIND</t>
+          <t>MANGLMCEM</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
@@ -3451,22 +3451,22 @@
         </is>
       </c>
       <c r="D103" s="3" t="n">
-        <v>89.67</v>
+        <v>1100</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>84.33</v>
+        <v>1058.4</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>89.93000000000001</v>
+        <v>1084</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>89.33</v>
+        <v>1080.3</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>JUSTDIAL</t>
+          <t>MANINFRA</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
@@ -3480,22 +3480,22 @@
         </is>
       </c>
       <c r="D104" s="3" t="n">
-        <v>696.1799999999999</v>
+        <v>124.6</v>
       </c>
       <c r="E104" s="3" t="n">
-        <v>661.1799999999999</v>
+        <v>119.47</v>
       </c>
       <c r="F104" s="3" t="n">
-        <v>710.2</v>
+        <v>124.56</v>
       </c>
       <c r="G104" s="3" t="n">
-        <v>705.3</v>
+        <v>123.75</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>KALYANIFRG</t>
+          <t>MEDICAMEQ</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
@@ -3509,22 +3509,22 @@
         </is>
       </c>
       <c r="D105" s="3" t="n">
-        <v>799.27</v>
+        <v>265</v>
       </c>
       <c r="E105" s="3" t="n">
-        <v>693.2</v>
+        <v>241.68</v>
       </c>
       <c r="F105" s="3" t="n">
-        <v>914.3</v>
+        <v>267.4</v>
       </c>
       <c r="G105" s="3" t="n">
-        <v>914.3</v>
+        <v>266</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>KAMDHENU</t>
+          <t>MODISONLTD</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
@@ -3538,22 +3538,22 @@
         </is>
       </c>
       <c r="D106" s="3" t="n">
-        <v>36.62</v>
+        <v>456.4</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>34.79</v>
+        <v>425.92</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>36.58</v>
+        <v>499.45</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>36.8</v>
+        <v>499.45</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>KANANIIND</t>
+          <t>MOTOGENFIN</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
@@ -3567,22 +3567,22 @@
         </is>
       </c>
       <c r="D107" s="3" t="n">
-        <v>1.54</v>
+        <v>28.33</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>1.44</v>
+        <v>27.29</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>1.52</v>
+        <v>28.03</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>1.5</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>KAPSTON</t>
+          <t>MTEDUCARE</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
@@ -3596,22 +3596,22 @@
         </is>
       </c>
       <c r="D108" s="3" t="n">
-        <v>556.23</v>
+        <v>1.8</v>
       </c>
       <c r="E108" s="3" t="n">
-        <v>521.3</v>
+        <v>1.67</v>
       </c>
       <c r="F108" s="3" t="n">
-        <v>586.8</v>
+        <v>1.8</v>
       </c>
       <c r="G108" s="3" t="n">
-        <v>590</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>KHADIM</t>
+          <t>NATIONSTD</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
@@ -3625,22 +3625,22 @@
         </is>
       </c>
       <c r="D109" s="3" t="n">
-        <v>117.47</v>
+        <v>108.95</v>
       </c>
       <c r="E109" s="3" t="n">
-        <v>111.74</v>
+        <v>101.09</v>
       </c>
       <c r="F109" s="3" t="n">
-        <v>116.16</v>
+        <v>105.31</v>
       </c>
       <c r="G109" s="3" t="n">
-        <v>116.16</v>
+        <v>106.88</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>KLBRENG-B</t>
+          <t>NIFMID150</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
@@ -3654,22 +3654,22 @@
         </is>
       </c>
       <c r="D110" s="3" t="n">
-        <v>420.13</v>
+        <v>224.68</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>400.45</v>
+        <v>222.19</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>428.55</v>
+        <v>224.96</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>428.75</v>
+        <v>225.54</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>KMSUGAR</t>
+          <t>NIRAJISPAT</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
@@ -3683,22 +3683,22 @@
         </is>
       </c>
       <c r="D111" s="3" t="n">
-        <v>33.22</v>
+        <v>347.19</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>30.97</v>
+        <v>341.36</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>32.49</v>
+        <v>390.6</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>32.64</v>
+        <v>390.6</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>KOPRAN</t>
+          <t>NIRLON</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
@@ -3712,22 +3712,22 @@
         </is>
       </c>
       <c r="D112" s="3" t="n">
-        <v>210.66</v>
+        <v>650.28</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>194.3</v>
+        <v>641.17</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>217.83</v>
+        <v>649.45</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>217.9</v>
+        <v>650</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>KRISHIVAL</t>
+          <t>NITIRAJ</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
@@ -3741,22 +3741,22 @@
         </is>
       </c>
       <c r="D113" s="3" t="n">
-        <v>411.63</v>
+        <v>207.57</v>
       </c>
       <c r="E113" s="3" t="n">
-        <v>401.13</v>
+        <v>198.56</v>
       </c>
       <c r="F113" s="3" t="n">
-        <v>410.95</v>
+        <v>204.5</v>
       </c>
       <c r="G113" s="3" t="n">
-        <v>413</v>
+        <v>204.5</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>LIQGRWBEES</t>
+          <t>NOIDATOLL</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
@@ -3770,22 +3770,22 @@
         </is>
       </c>
       <c r="D114" s="3" t="n">
-        <v>1053.57</v>
+        <v>4.35</v>
       </c>
       <c r="E114" s="3" t="n">
-        <v>1053.51</v>
+        <v>4.12</v>
       </c>
       <c r="F114" s="3" t="n">
-        <v>1053.77</v>
+        <v>4.23</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>1053.78</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDBETA</t>
+          <t>NOVAAGRI</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
@@ -3799,22 +3799,22 @@
         </is>
       </c>
       <c r="D115" s="3" t="n">
-        <v>1005.95</v>
+        <v>25.52</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>1005.94</v>
+        <v>23.9</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>1006.32</v>
+        <v>24.22</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>1006.32</v>
+        <v>24.2</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDBETF</t>
+          <t>NOVARTIND</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
@@ -3828,22 +3828,22 @@
         </is>
       </c>
       <c r="D116" s="3" t="n">
-        <v>1096.66</v>
+        <v>1563.87</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>1096.64</v>
+        <v>1497.6</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>1096.88</v>
+        <v>1582.1</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>1096.87</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDCASE</t>
+          <t>NURECA</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
@@ -3857,22 +3857,22 @@
         </is>
       </c>
       <c r="D117" s="3" t="n">
-        <v>115.7</v>
+        <v>341.22</v>
       </c>
       <c r="E117" s="3" t="n">
-        <v>115.68</v>
+        <v>322.72</v>
       </c>
       <c r="F117" s="3" t="n">
-        <v>115.71</v>
+        <v>339</v>
       </c>
       <c r="G117" s="3" t="n">
-        <v>115.72</v>
+        <v>338.2</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDSHRI</t>
+          <t>OILCOUNTUB</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
@@ -3886,22 +3886,22 @@
         </is>
       </c>
       <c r="D118" s="3" t="n">
-        <v>1119.35</v>
+        <v>64.19</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>1119.33</v>
+        <v>62.14</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>1119.57</v>
+        <v>67.23</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>1119.58</v>
+        <v>67.23</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>LOKESHMACH</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
@@ -3915,22 +3915,22 @@
         </is>
       </c>
       <c r="D119" s="3" t="n">
-        <v>332.38</v>
+        <v>234.98</v>
       </c>
       <c r="E119" s="3" t="n">
-        <v>303.6</v>
+        <v>231.82</v>
       </c>
       <c r="F119" s="3" t="n">
-        <v>345.25</v>
+        <v>236.45</v>
       </c>
       <c r="G119" s="3" t="n">
-        <v>342.1</v>
+        <v>236.45</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>LUMAXTECH</t>
+          <t>PAR</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
@@ -3944,22 +3944,22 @@
         </is>
       </c>
       <c r="D120" s="3" t="n">
-        <v>2018.47</v>
+        <v>120.57</v>
       </c>
       <c r="E120" s="3" t="n">
-        <v>1933.97</v>
+        <v>105.93</v>
       </c>
       <c r="F120" s="3" t="n">
-        <v>2078.5</v>
+        <v>140.6</v>
       </c>
       <c r="G120" s="3" t="n">
-        <v>2083</v>
+        <v>140.82</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>MAANALU</t>
+          <t>PARAGMILK</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
@@ -3973,22 +3973,22 @@
         </is>
       </c>
       <c r="D121" s="3" t="n">
-        <v>122.28</v>
+        <v>253.88</v>
       </c>
       <c r="E121" s="3" t="n">
-        <v>116.54</v>
+        <v>241.82</v>
       </c>
       <c r="F121" s="3" t="n">
-        <v>122.67</v>
+        <v>259.1</v>
       </c>
       <c r="G121" s="3" t="n">
-        <v>121.35</v>
+        <v>258.9</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>MAFANG</t>
+          <t>PARSVNATH</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
@@ -4002,22 +4002,22 @@
         </is>
       </c>
       <c r="D122" s="3" t="n">
-        <v>207.88</v>
+        <v>1.47</v>
       </c>
       <c r="E122" s="3" t="n">
-        <v>207.88</v>
+        <v>1.47</v>
       </c>
       <c r="F122" s="3" t="n">
-        <v>209.95</v>
+        <v>1.49</v>
       </c>
       <c r="G122" s="3" t="n">
-        <v>209.95</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>MAFATIND</t>
+          <t>PENIND</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
@@ -4031,22 +4031,22 @@
         </is>
       </c>
       <c r="D123" s="3" t="n">
-        <v>123.82</v>
+        <v>167.47</v>
       </c>
       <c r="E123" s="3" t="n">
-        <v>120.83</v>
+        <v>161.54</v>
       </c>
       <c r="F123" s="3" t="n">
-        <v>122.64</v>
+        <v>165.66</v>
       </c>
       <c r="G123" s="3" t="n">
-        <v>123.5</v>
+        <v>165.89</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>MAGADSUGAR</t>
+          <t>PGHL</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
@@ -4060,22 +4060,22 @@
         </is>
       </c>
       <c r="D124" s="3" t="n">
-        <v>594.08</v>
+        <v>5791.67</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>557.65</v>
+        <v>5648.17</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>595</v>
+        <v>5776</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>600</v>
+        <v>5780</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>MAHASTEEL</t>
+          <t>PLAZACABLE</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
@@ -4089,22 +4089,22 @@
         </is>
       </c>
       <c r="D125" s="3" t="n">
-        <v>1331.67</v>
+        <v>56.59</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>1236.27</v>
+        <v>53.6</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>1373</v>
+        <v>58.92</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>1381</v>
+        <v>59.37</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>MAHSEAMLES</t>
+          <t>PRAENG</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
@@ -4118,22 +4118,22 @@
         </is>
       </c>
       <c r="D126" s="3" t="n">
-        <v>663.03</v>
+        <v>22.53</v>
       </c>
       <c r="E126" s="3" t="n">
-        <v>642.67</v>
+        <v>20.24</v>
       </c>
       <c r="F126" s="3" t="n">
-        <v>663.2</v>
+        <v>24.44</v>
       </c>
       <c r="G126" s="3" t="n">
-        <v>663.5</v>
+        <v>24.34</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>MALLCOM</t>
+          <t>PROZONER</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
@@ -4147,22 +4147,22 @@
         </is>
       </c>
       <c r="D127" s="3" t="n">
-        <v>1011.3</v>
+        <v>45.51</v>
       </c>
       <c r="E127" s="3" t="n">
-        <v>968.05</v>
+        <v>43.64</v>
       </c>
       <c r="F127" s="3" t="n">
-        <v>974</v>
+        <v>44.92</v>
       </c>
       <c r="G127" s="3" t="n">
-        <v>979</v>
+        <v>45.35</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>MANAKSIA</t>
+          <t>PTCIL</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
@@ -4176,22 +4176,22 @@
         </is>
       </c>
       <c r="D128" s="3" t="n">
-        <v>58.97</v>
+        <v>22651.67</v>
       </c>
       <c r="E128" s="3" t="n">
-        <v>56.85</v>
+        <v>21335.67</v>
       </c>
       <c r="F128" s="3" t="n">
-        <v>58.73</v>
+        <v>22755</v>
       </c>
       <c r="G128" s="3" t="n">
-        <v>59</v>
+        <v>22665</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>MANAKSTEEL</t>
+          <t>QMSMEDI</t>
         </is>
       </c>
       <c r="B129" s="3" t="inlineStr">
@@ -4205,22 +4205,22 @@
         </is>
       </c>
       <c r="D129" s="3" t="n">
-        <v>95.23</v>
+        <v>158.95</v>
       </c>
       <c r="E129" s="3" t="n">
-        <v>92.40000000000001</v>
+        <v>153.37</v>
       </c>
       <c r="F129" s="3" t="n">
-        <v>99.52</v>
+        <v>161.31</v>
       </c>
       <c r="G129" s="3" t="n">
-        <v>99.52</v>
+        <v>161.99</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>MANCREDIT</t>
+          <t>RAYMOND</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
@@ -4234,22 +4234,22 @@
         </is>
       </c>
       <c r="D130" s="3" t="n">
-        <v>249.67</v>
+        <v>638.25</v>
       </c>
       <c r="E130" s="3" t="n">
-        <v>230.73</v>
+        <v>619.48</v>
       </c>
       <c r="F130" s="3" t="n">
-        <v>242.74</v>
+        <v>635.3</v>
       </c>
       <c r="G130" s="3" t="n">
-        <v>240</v>
+        <v>636.05</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>MANINFRA</t>
+          <t>RELIGARE</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
@@ -4263,22 +4263,22 @@
         </is>
       </c>
       <c r="D131" s="3" t="n">
-        <v>121.42</v>
+        <v>246</v>
       </c>
       <c r="E131" s="3" t="n">
-        <v>117.24</v>
+        <v>235.43</v>
       </c>
       <c r="F131" s="3" t="n">
-        <v>122.62</v>
+        <v>249.78</v>
       </c>
       <c r="G131" s="3" t="n">
-        <v>122</v>
+        <v>251.01</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>MANORG</t>
+          <t>REMSONSIND</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
@@ -4292,22 +4292,22 @@
         </is>
       </c>
       <c r="D132" s="3" t="n">
-        <v>522.17</v>
+        <v>97.45</v>
       </c>
       <c r="E132" s="3" t="n">
-        <v>500.85</v>
+        <v>87.2</v>
       </c>
       <c r="F132" s="3" t="n">
-        <v>519.5</v>
+        <v>97.44</v>
       </c>
       <c r="G132" s="3" t="n">
-        <v>532.3</v>
+        <v>97.98</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>MAWANASUG</t>
+          <t>REPL</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
@@ -4321,22 +4321,22 @@
         </is>
       </c>
       <c r="D133" s="3" t="n">
-        <v>151.36</v>
+        <v>65.68000000000001</v>
       </c>
       <c r="E133" s="3" t="n">
-        <v>142.1</v>
+        <v>61.45</v>
       </c>
       <c r="F133" s="3" t="n">
-        <v>149.1</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="G133" s="3" t="n">
-        <v>149.01</v>
+        <v>64.98999999999999</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>MAZDA</t>
+          <t>RMDRIP</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
@@ -4350,22 +4350,22 @@
         </is>
       </c>
       <c r="D134" s="3" t="n">
-        <v>251</v>
+        <v>21.31</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>242.61</v>
+        <v>20.51</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>251.82</v>
+        <v>21.77</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>251.1</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>MON100</t>
+          <t>RNBDENIMS</t>
         </is>
       </c>
       <c r="B135" s="3" t="inlineStr">
@@ -4379,22 +4379,22 @@
         </is>
       </c>
       <c r="D135" s="3" t="n">
-        <v>328.75</v>
+        <v>10.33</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>328.75</v>
+        <v>10.28</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>332.2</v>
+        <v>10.83</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>332.2</v>
+        <v>10.83</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>MOREPENLAB</t>
+          <t>ROML</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
@@ -4408,22 +4408,22 @@
         </is>
       </c>
       <c r="D136" s="3" t="n">
-        <v>105.5</v>
+        <v>43.59</v>
       </c>
       <c r="E136" s="3" t="n">
-        <v>97.69</v>
+        <v>41.88</v>
       </c>
       <c r="F136" s="3" t="n">
-        <v>107.16</v>
+        <v>43.15</v>
       </c>
       <c r="G136" s="3" t="n">
-        <v>107.38</v>
+        <v>43.15</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>MOTOGENFIN</t>
+          <t>RSL</t>
         </is>
       </c>
       <c r="B137" s="3" t="inlineStr">
@@ -4437,22 +4437,22 @@
         </is>
       </c>
       <c r="D137" s="3" t="n">
-        <v>27.85</v>
+        <v>180.84</v>
       </c>
       <c r="E137" s="3" t="n">
-        <v>26.92</v>
+        <v>174.11</v>
       </c>
       <c r="F137" s="3" t="n">
-        <v>28.04</v>
+        <v>176.74</v>
       </c>
       <c r="G137" s="3" t="n">
-        <v>28.1</v>
+        <v>177.5</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>MVELECTRO</t>
+          <t>SABEVENTS</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
@@ -4466,22 +4466,22 @@
         </is>
       </c>
       <c r="D138" s="3" t="n">
-        <v>740.05</v>
+        <v>6.4</v>
       </c>
       <c r="E138" s="3" t="n">
-        <v>630.5</v>
+        <v>6.2</v>
       </c>
       <c r="F138" s="3" t="n">
-        <v>760.45</v>
+        <v>6.63</v>
       </c>
       <c r="G138" s="3" t="n">
-        <v>746</v>
+        <v>6.63</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>NATCAPSUQ</t>
+          <t>SAHLIBHFI</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
@@ -4495,22 +4495,22 @@
         </is>
       </c>
       <c r="D139" s="3" t="n">
-        <v>220.34</v>
+        <v>81.06</v>
       </c>
       <c r="E139" s="3" t="n">
-        <v>197.16</v>
+        <v>73.98999999999999</v>
       </c>
       <c r="F139" s="3" t="n">
-        <v>212.38</v>
+        <v>75.58</v>
       </c>
       <c r="G139" s="3" t="n">
-        <v>211</v>
+        <v>83.40000000000001</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>NAVNETEDUL</t>
+          <t>SALSTEEL</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
@@ -4524,22 +4524,22 @@
         </is>
       </c>
       <c r="D140" s="3" t="n">
-        <v>135.96</v>
+        <v>78.92</v>
       </c>
       <c r="E140" s="3" t="n">
-        <v>133.36</v>
+        <v>75.87</v>
       </c>
       <c r="F140" s="3" t="n">
-        <v>134.61</v>
+        <v>82.43000000000001</v>
       </c>
       <c r="G140" s="3" t="n">
-        <v>134.08</v>
+        <v>82.06</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>NEAGI</t>
+          <t>SANGINITA</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
@@ -4553,22 +4553,22 @@
         </is>
       </c>
       <c r="D141" s="3" t="n">
-        <v>3490.43</v>
+        <v>56.01</v>
       </c>
       <c r="E141" s="3" t="n">
-        <v>3348.1</v>
+        <v>55.17</v>
       </c>
       <c r="F141" s="3" t="n">
-        <v>3496.7</v>
+        <v>58.76</v>
       </c>
       <c r="G141" s="3" t="n">
-        <v>3528</v>
+        <v>58.76</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>NEXTMEDIA</t>
+          <t>SASTASUNDR</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
@@ -4582,22 +4582,22 @@
         </is>
       </c>
       <c r="D142" s="3" t="n">
-        <v>4.69</v>
+        <v>283.13</v>
       </c>
       <c r="E142" s="3" t="n">
-        <v>4.03</v>
+        <v>269.72</v>
       </c>
       <c r="F142" s="3" t="n">
-        <v>4.98</v>
+        <v>282.6</v>
       </c>
       <c r="G142" s="3" t="n">
-        <v>4.9</v>
+        <v>284.65</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>NIACL</t>
+          <t>SBILIQETF</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
@@ -4611,22 +4611,22 @@
         </is>
       </c>
       <c r="D143" s="3" t="n">
-        <v>193.3</v>
+        <v>1054.06</v>
       </c>
       <c r="E143" s="3" t="n">
-        <v>185.39</v>
+        <v>1054.04</v>
       </c>
       <c r="F143" s="3" t="n">
-        <v>191.23</v>
+        <v>1054.18</v>
       </c>
       <c r="G143" s="3" t="n">
-        <v>191.9</v>
+        <v>1054.17</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>NIFMID150</t>
+          <t>SETCO</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
@@ -4640,22 +4640,22 @@
         </is>
       </c>
       <c r="D144" s="3" t="n">
-        <v>224.68</v>
+        <v>18.39</v>
       </c>
       <c r="E144" s="3" t="n">
-        <v>222.19</v>
+        <v>17.26</v>
       </c>
       <c r="F144" s="3" t="n">
-        <v>224.96</v>
+        <v>17.67</v>
       </c>
       <c r="G144" s="3" t="n">
-        <v>225.54</v>
+        <v>17.9</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>NIRAJISPAT</t>
+          <t>SETL</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
@@ -4669,22 +4669,22 @@
         </is>
       </c>
       <c r="D145" s="3" t="n">
-        <v>302.66</v>
+        <v>378.18</v>
       </c>
       <c r="E145" s="3" t="n">
-        <v>283.36</v>
+        <v>361.85</v>
       </c>
       <c r="F145" s="3" t="n">
-        <v>355.08</v>
+        <v>387.05</v>
       </c>
       <c r="G145" s="3" t="n">
-        <v>355.08</v>
+        <v>387.95</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>NITTAGELA</t>
+          <t>SHADOWFAX</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
@@ -4698,22 +4698,22 @@
         </is>
       </c>
       <c r="D146" s="3" t="n">
-        <v>1659.13</v>
+        <v>256</v>
       </c>
       <c r="E146" s="3" t="n">
-        <v>1579.2</v>
+        <v>245.84</v>
       </c>
       <c r="F146" s="3" t="n">
-        <v>1620.7</v>
+        <v>257.2</v>
       </c>
       <c r="G146" s="3" t="n">
-        <v>1618</v>
+        <v>257.55</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>NOIDATOLL</t>
+          <t>SHIVALIK</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
@@ -4727,22 +4727,22 @@
         </is>
       </c>
       <c r="D147" s="3" t="n">
-        <v>4.28</v>
+        <v>322.45</v>
       </c>
       <c r="E147" s="3" t="n">
-        <v>4.09</v>
+        <v>305.53</v>
       </c>
       <c r="F147" s="3" t="n">
-        <v>4.21</v>
+        <v>338.05</v>
       </c>
       <c r="G147" s="3" t="n">
-        <v>4.2</v>
+        <v>336</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>NURECA</t>
+          <t>SHREYANIND</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
@@ -4756,22 +4756,22 @@
         </is>
       </c>
       <c r="D148" s="3" t="n">
-        <v>331.73</v>
+        <v>126.5</v>
       </c>
       <c r="E148" s="3" t="n">
-        <v>315.37</v>
+        <v>123.38</v>
       </c>
       <c r="F148" s="3" t="n">
-        <v>331.8</v>
+        <v>125.8</v>
       </c>
       <c r="G148" s="3" t="n">
-        <v>334</v>
+        <v>125.3</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>SHRIPISTON</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
@@ -4785,22 +4785,22 @@
         </is>
       </c>
       <c r="D149" s="3" t="n">
-        <v>12243.67</v>
+        <v>4628.23</v>
       </c>
       <c r="E149" s="3" t="n">
-        <v>11892</v>
+        <v>4484.6</v>
       </c>
       <c r="F149" s="3" t="n">
-        <v>12540</v>
+        <v>4598.2</v>
       </c>
       <c r="G149" s="3" t="n">
-        <v>12540</v>
+        <v>4600</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>SILVERETF</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
@@ -4814,22 +4814,22 @@
         </is>
       </c>
       <c r="D150" s="3" t="n">
-        <v>485.88</v>
+        <v>201.81</v>
       </c>
       <c r="E150" s="3" t="n">
-        <v>472.03</v>
+        <v>198.28</v>
       </c>
       <c r="F150" s="3" t="n">
-        <v>483.15</v>
+        <v>203.98</v>
       </c>
       <c r="G150" s="3" t="n">
-        <v>483.15</v>
+        <v>204</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>OLAELEC</t>
+          <t>SINCLAIR</t>
         </is>
       </c>
       <c r="B151" s="3" t="inlineStr">
@@ -4843,22 +4843,22 @@
         </is>
       </c>
       <c r="D151" s="3" t="n">
-        <v>40.05</v>
+        <v>84.04000000000001</v>
       </c>
       <c r="E151" s="3" t="n">
-        <v>37.69</v>
+        <v>79.41</v>
       </c>
       <c r="F151" s="3" t="n">
-        <v>41.12</v>
+        <v>82.91</v>
       </c>
       <c r="G151" s="3" t="n">
-        <v>40.9</v>
+        <v>83</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>PARACABLES</t>
+          <t>SMCGLOBAL</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
@@ -4872,22 +4872,22 @@
         </is>
       </c>
       <c r="D152" s="3" t="n">
-        <v>64.23</v>
+        <v>80.81999999999999</v>
       </c>
       <c r="E152" s="3" t="n">
-        <v>59.63</v>
+        <v>78.47</v>
       </c>
       <c r="F152" s="3" t="n">
-        <v>65.34</v>
+        <v>79.65000000000001</v>
       </c>
       <c r="G152" s="3" t="n">
-        <v>65.54000000000001</v>
+        <v>79.90000000000001</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>PARSVNATH</t>
+          <t>SOLARA</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
@@ -4901,22 +4901,22 @@
         </is>
       </c>
       <c r="D153" s="3" t="n">
-        <v>1.45</v>
+        <v>650.28</v>
       </c>
       <c r="E153" s="3" t="n">
-        <v>1.44</v>
+        <v>617.72</v>
       </c>
       <c r="F153" s="3" t="n">
-        <v>1.47</v>
+        <v>643.45</v>
       </c>
       <c r="G153" s="3" t="n">
-        <v>1.47</v>
+        <v>640.75</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>PDMJEPAPER</t>
+          <t>SRHHYPOLTD</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
@@ -4930,22 +4930,22 @@
         </is>
       </c>
       <c r="D154" s="3" t="n">
-        <v>95.8</v>
+        <v>497.27</v>
       </c>
       <c r="E154" s="3" t="n">
-        <v>89.23</v>
+        <v>477.63</v>
       </c>
       <c r="F154" s="3" t="n">
-        <v>95.20999999999999</v>
+        <v>494.45</v>
       </c>
       <c r="G154" s="3" t="n">
-        <v>95.05</v>
+        <v>494.1</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>PGIL</t>
+          <t>SSWL</t>
         </is>
       </c>
       <c r="B155" s="3" t="inlineStr">
@@ -4959,22 +4959,22 @@
         </is>
       </c>
       <c r="D155" s="3" t="n">
-        <v>2381.1</v>
+        <v>323.62</v>
       </c>
       <c r="E155" s="3" t="n">
-        <v>2288.67</v>
+        <v>294.78</v>
       </c>
       <c r="F155" s="3" t="n">
-        <v>2463.8</v>
+        <v>357.25</v>
       </c>
       <c r="G155" s="3" t="n">
-        <v>2490</v>
+        <v>351.3</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>PIRAMALFIN</t>
+          <t>SUDEEPPHRM</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
@@ -4988,22 +4988,22 @@
         </is>
       </c>
       <c r="D156" s="3" t="n">
-        <v>2288.37</v>
+        <v>1214.78</v>
       </c>
       <c r="E156" s="3" t="n">
-        <v>2223.97</v>
+        <v>1148.85</v>
       </c>
       <c r="F156" s="3" t="n">
-        <v>2300.4</v>
+        <v>1230.9</v>
       </c>
       <c r="G156" s="3" t="n">
-        <v>2315</v>
+        <v>1239.8</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>POLYPLEX</t>
+          <t>SUPERSPIN</t>
         </is>
       </c>
       <c r="B157" s="3" t="inlineStr">
@@ -5017,22 +5017,22 @@
         </is>
       </c>
       <c r="D157" s="3" t="n">
-        <v>1192.1</v>
+        <v>6.42</v>
       </c>
       <c r="E157" s="3" t="n">
-        <v>1157.37</v>
+        <v>6.12</v>
       </c>
       <c r="F157" s="3" t="n">
-        <v>1182.6</v>
+        <v>6.52</v>
       </c>
       <c r="G157" s="3" t="n">
-        <v>1183.7</v>
+        <v>6.39</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>PONNIERODE</t>
+          <t>SURYALAXMI</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
@@ -5046,22 +5046,22 @@
         </is>
       </c>
       <c r="D158" s="3" t="n">
-        <v>404.42</v>
+        <v>62.29</v>
       </c>
       <c r="E158" s="3" t="n">
-        <v>387.6</v>
+        <v>58.1</v>
       </c>
       <c r="F158" s="3" t="n">
-        <v>403.3</v>
+        <v>62.92</v>
       </c>
       <c r="G158" s="3" t="n">
-        <v>404.6</v>
+        <v>62.95</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>PRAENG</t>
+          <t>SUVEN</t>
         </is>
       </c>
       <c r="B159" s="3" t="inlineStr">
@@ -5075,22 +5075,22 @@
         </is>
       </c>
       <c r="D159" s="3" t="n">
-        <v>20.8</v>
+        <v>388.88</v>
       </c>
       <c r="E159" s="3" t="n">
-        <v>19.71</v>
+        <v>367.72</v>
       </c>
       <c r="F159" s="3" t="n">
-        <v>21.49</v>
+        <v>381.6</v>
       </c>
       <c r="G159" s="3" t="n">
-        <v>20.91</v>
+        <v>381.85</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>PRECWIRE</t>
+          <t>TATACOMM</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
@@ -5104,22 +5104,22 @@
         </is>
       </c>
       <c r="D160" s="3" t="n">
-        <v>489.6</v>
+        <v>1727.3</v>
       </c>
       <c r="E160" s="3" t="n">
-        <v>444.88</v>
+        <v>1692</v>
       </c>
       <c r="F160" s="3" t="n">
-        <v>505.6</v>
+        <v>1733.8</v>
       </c>
       <c r="G160" s="3" t="n">
-        <v>506.5</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>PTCIL</t>
+          <t>TECH</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
@@ -5133,22 +5133,22 @@
         </is>
       </c>
       <c r="D161" s="3" t="n">
-        <v>21966</v>
+        <v>34.37</v>
       </c>
       <c r="E161" s="3" t="n">
-        <v>20867</v>
+        <v>33.5</v>
       </c>
       <c r="F161" s="3" t="n">
-        <v>22114</v>
+        <v>34.24</v>
       </c>
       <c r="G161" s="3" t="n">
-        <v>21900</v>
+        <v>34.24</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>QPOWER</t>
+          <t>TNPETRO</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
@@ -5162,22 +5162,22 @@
         </is>
       </c>
       <c r="D162" s="3" t="n">
-        <v>1432.33</v>
+        <v>125.23</v>
       </c>
       <c r="E162" s="3" t="n">
-        <v>1363.73</v>
+        <v>113.77</v>
       </c>
       <c r="F162" s="3" t="n">
-        <v>1435.8</v>
+        <v>132.35</v>
       </c>
       <c r="G162" s="3" t="n">
-        <v>1445</v>
+        <v>133.1</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>QUESS</t>
+          <t>TRANSPEK</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
@@ -5191,22 +5191,22 @@
         </is>
       </c>
       <c r="D163" s="3" t="n">
-        <v>379.15</v>
+        <v>1430.83</v>
       </c>
       <c r="E163" s="3" t="n">
-        <v>359.17</v>
+        <v>1364.13</v>
       </c>
       <c r="F163" s="3" t="n">
-        <v>381.75</v>
+        <v>1422.8</v>
       </c>
       <c r="G163" s="3" t="n">
-        <v>383.3</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>RAMCOSYS</t>
+          <t>TVSSRICHAK</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
@@ -5220,22 +5220,22 @@
         </is>
       </c>
       <c r="D164" s="3" t="n">
-        <v>582.5</v>
+        <v>5553.27</v>
       </c>
       <c r="E164" s="3" t="n">
-        <v>559.5</v>
+        <v>5277.3</v>
       </c>
       <c r="F164" s="3" t="n">
-        <v>575.25</v>
+        <v>5525.5</v>
       </c>
       <c r="G164" s="3" t="n">
-        <v>575</v>
+        <v>5521</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>RATNAVEER</t>
+          <t>UDS</t>
         </is>
       </c>
       <c r="B165" s="3" t="inlineStr">
@@ -5249,22 +5249,22 @@
         </is>
       </c>
       <c r="D165" s="3" t="n">
-        <v>305.68</v>
+        <v>227.24</v>
       </c>
       <c r="E165" s="3" t="n">
-        <v>289.22</v>
+        <v>221.49</v>
       </c>
       <c r="F165" s="3" t="n">
-        <v>306.02</v>
+        <v>227.12</v>
       </c>
       <c r="G165" s="3" t="n">
-        <v>305.8</v>
+        <v>224.5</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>RAYMOND</t>
+          <t>UNIPARTS</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
@@ -5278,22 +5278,22 @@
         </is>
       </c>
       <c r="D166" s="3" t="n">
-        <v>632.13</v>
+        <v>898.52</v>
       </c>
       <c r="E166" s="3" t="n">
-        <v>614.4</v>
+        <v>849.73</v>
       </c>
       <c r="F166" s="3" t="n">
-        <v>631.85</v>
+        <v>901.15</v>
       </c>
       <c r="G166" s="3" t="n">
-        <v>630.25</v>
+        <v>904.5</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>RELIGARE</t>
+          <t>URAVIDEF</t>
         </is>
       </c>
       <c r="B167" s="3" t="inlineStr">
@@ -5307,22 +5307,22 @@
         </is>
       </c>
       <c r="D167" s="3" t="n">
-        <v>239.92</v>
+        <v>113.72</v>
       </c>
       <c r="E167" s="3" t="n">
-        <v>229.55</v>
+        <v>108.91</v>
       </c>
       <c r="F167" s="3" t="n">
-        <v>242.8</v>
+        <v>118.97</v>
       </c>
       <c r="G167" s="3" t="n">
-        <v>244</v>
+        <v>118.97</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>REMSONSIND</t>
+          <t>UTISENSETF</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
@@ -5336,22 +5336,22 @@
         </is>
       </c>
       <c r="D168" s="3" t="n">
-        <v>91.20999999999999</v>
+        <v>941.63</v>
       </c>
       <c r="E168" s="3" t="n">
-        <v>82.56999999999999</v>
+        <v>933.52</v>
       </c>
       <c r="F168" s="3" t="n">
-        <v>98.48</v>
+        <v>939.25</v>
       </c>
       <c r="G168" s="3" t="n">
-        <v>98.59999999999999</v>
+        <v>938.3200000000001</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>RENUKA</t>
+          <t>UTKARSHBNK</t>
         </is>
       </c>
       <c r="B169" s="3" t="inlineStr">
@@ -5365,22 +5365,22 @@
         </is>
       </c>
       <c r="D169" s="3" t="n">
-        <v>24.96</v>
+        <v>15.07</v>
       </c>
       <c r="E169" s="3" t="n">
-        <v>23.54</v>
+        <v>14.59</v>
       </c>
       <c r="F169" s="3" t="n">
-        <v>24.9</v>
+        <v>14.88</v>
       </c>
       <c r="G169" s="3" t="n">
-        <v>24.95</v>
+        <v>14.88</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>RKFORGE</t>
+          <t>VARROC</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
@@ -5394,22 +5394,22 @@
         </is>
       </c>
       <c r="D170" s="3" t="n">
-        <v>753.85</v>
+        <v>864.97</v>
       </c>
       <c r="E170" s="3" t="n">
-        <v>722.15</v>
+        <v>821.27</v>
       </c>
       <c r="F170" s="3" t="n">
-        <v>743.6</v>
+        <v>877</v>
       </c>
       <c r="G170" s="3" t="n">
-        <v>742.25</v>
+        <v>870</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>RMDRIP</t>
+          <t>VHL</t>
         </is>
       </c>
       <c r="B171" s="3" t="inlineStr">
@@ -5423,22 +5423,22 @@
         </is>
       </c>
       <c r="D171" s="3" t="n">
-        <v>20.6</v>
+        <v>3603.37</v>
       </c>
       <c r="E171" s="3" t="n">
-        <v>19.8</v>
+        <v>3418.03</v>
       </c>
       <c r="F171" s="3" t="n">
-        <v>21.33</v>
+        <v>3568.4</v>
       </c>
       <c r="G171" s="3" t="n">
-        <v>21.3</v>
+        <v>3598</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>RNBDENIMS</t>
+          <t>VIJIFIN</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
@@ -5452,22 +5452,22 @@
         </is>
       </c>
       <c r="D172" s="3" t="n">
-        <v>9.84</v>
+        <v>15.34</v>
       </c>
       <c r="E172" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>15.34</v>
       </c>
       <c r="F172" s="3" t="n">
-        <v>10.32</v>
+        <v>15.64</v>
       </c>
       <c r="G172" s="3" t="n">
-        <v>10.32</v>
+        <v>15.64</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>ROML</t>
+          <t>VIPIND</t>
         </is>
       </c>
       <c r="B173" s="3" t="inlineStr">
@@ -5481,22 +5481,22 @@
         </is>
       </c>
       <c r="D173" s="3" t="n">
-        <v>43.02</v>
+        <v>309.92</v>
       </c>
       <c r="E173" s="3" t="n">
-        <v>40.86</v>
+        <v>300.92</v>
       </c>
       <c r="F173" s="3" t="n">
-        <v>42.62</v>
+        <v>303.75</v>
       </c>
       <c r="G173" s="3" t="n">
-        <v>42.56</v>
+        <v>304.9</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>RPEL</t>
+          <t>WELENT</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
@@ -5510,22 +5510,22 @@
         </is>
       </c>
       <c r="D174" s="3" t="n">
-        <v>1791.3</v>
+        <v>698.08</v>
       </c>
       <c r="E174" s="3" t="n">
-        <v>1716.27</v>
+        <v>667.12</v>
       </c>
       <c r="F174" s="3" t="n">
-        <v>1771.2</v>
+        <v>705.55</v>
       </c>
       <c r="G174" s="3" t="n">
-        <v>1790.2</v>
+        <v>712</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>RRKABEL</t>
+          <t>WSTCSTPAPR</t>
         </is>
       </c>
       <c r="B175" s="3" t="inlineStr">
@@ -5539,1727 +5539,16 @@
         </is>
       </c>
       <c r="D175" s="3" t="n">
-        <v>2933.93</v>
+        <v>636.45</v>
       </c>
       <c r="E175" s="3" t="n">
-        <v>2833.5</v>
+        <v>608.53</v>
       </c>
       <c r="F175" s="3" t="n">
-        <v>2928.4</v>
+        <v>653.6</v>
       </c>
       <c r="G175" s="3" t="n">
-        <v>2931.9</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" s="2" t="inlineStr">
-        <is>
-          <t>RSL</t>
-        </is>
-      </c>
-      <c r="B176" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C176" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D176" s="3" t="n">
-        <v>177.82</v>
-      </c>
-      <c r="E176" s="3" t="n">
-        <v>170.77</v>
-      </c>
-      <c r="F176" s="3" t="n">
-        <v>177.66</v>
-      </c>
-      <c r="G176" s="3" t="n">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" s="2" t="inlineStr">
-        <is>
-          <t>SABEVENTS</t>
-        </is>
-      </c>
-      <c r="B177" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C177" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D177" s="3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="E177" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="F177" s="3" t="n">
-        <v>6.63</v>
-      </c>
-      <c r="G177" s="3" t="n">
-        <v>6.63</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="2" t="inlineStr">
-        <is>
-          <t>SAGILITY</t>
-        </is>
-      </c>
-      <c r="B178" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C178" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D178" s="3" t="n">
-        <v>46.37</v>
-      </c>
-      <c r="E178" s="3" t="n">
-        <v>44.68</v>
-      </c>
-      <c r="F178" s="3" t="n">
-        <v>47.05</v>
-      </c>
-      <c r="G178" s="3" t="n">
-        <v>47.05</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" s="2" t="inlineStr">
-        <is>
-          <t>SANGINITA</t>
-        </is>
-      </c>
-      <c r="B179" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C179" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D179" s="3" t="n">
-        <v>53.36</v>
-      </c>
-      <c r="E179" s="3" t="n">
-        <v>50.91</v>
-      </c>
-      <c r="F179" s="3" t="n">
-        <v>55.97</v>
-      </c>
-      <c r="G179" s="3" t="n">
-        <v>55.97</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" s="2" t="inlineStr">
-        <is>
-          <t>SASTASUNDR</t>
-        </is>
-      </c>
-      <c r="B180" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C180" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D180" s="3" t="n">
-        <v>283.13</v>
-      </c>
-      <c r="E180" s="3" t="n">
-        <v>269.72</v>
-      </c>
-      <c r="F180" s="3" t="n">
-        <v>282.6</v>
-      </c>
-      <c r="G180" s="3" t="n">
-        <v>284.65</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" s="2" t="inlineStr">
-        <is>
-          <t>SBC</t>
-        </is>
-      </c>
-      <c r="B181" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C181" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D181" s="3" t="n">
-        <v>42.38</v>
-      </c>
-      <c r="E181" s="3" t="n">
-        <v>40.92</v>
-      </c>
-      <c r="F181" s="3" t="n">
-        <v>42.15</v>
-      </c>
-      <c r="G181" s="3" t="n">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" s="2" t="inlineStr">
-        <is>
-          <t>SBILIQETF</t>
-        </is>
-      </c>
-      <c r="B182" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C182" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D182" s="3" t="n">
-        <v>1053.83</v>
-      </c>
-      <c r="E182" s="3" t="n">
-        <v>1053.81</v>
-      </c>
-      <c r="F182" s="3" t="n">
-        <v>1054.05</v>
-      </c>
-      <c r="G182" s="3" t="n">
-        <v>1054.06</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" s="2" t="inlineStr">
-        <is>
-          <t>SECMARK</t>
-        </is>
-      </c>
-      <c r="B183" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C183" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D183" s="3" t="n">
-        <v>153.75</v>
-      </c>
-      <c r="E183" s="3" t="n">
-        <v>136.58</v>
-      </c>
-      <c r="F183" s="3" t="n">
-        <v>163.27</v>
-      </c>
-      <c r="G183" s="3" t="n">
-        <v>164.4</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" s="2" t="inlineStr">
-        <is>
-          <t>SETCO</t>
-        </is>
-      </c>
-      <c r="B184" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C184" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D184" s="3" t="n">
-        <v>18.18</v>
-      </c>
-      <c r="E184" s="3" t="n">
-        <v>17.04</v>
-      </c>
-      <c r="F184" s="3" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="G184" s="3" t="n">
-        <v>18.2</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" s="2" t="inlineStr">
-        <is>
-          <t>SETL</t>
-        </is>
-      </c>
-      <c r="B185" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C185" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D185" s="3" t="n">
-        <v>364.5</v>
-      </c>
-      <c r="E185" s="3" t="n">
-        <v>347.72</v>
-      </c>
-      <c r="F185" s="3" t="n">
-        <v>369.5</v>
-      </c>
-      <c r="G185" s="3" t="n">
-        <v>368.5</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" s="2" t="inlineStr">
-        <is>
-          <t>SHAHALLOYS</t>
-        </is>
-      </c>
-      <c r="B186" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C186" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D186" s="3" t="n">
-        <v>102.25</v>
-      </c>
-      <c r="E186" s="3" t="n">
-        <v>90.34</v>
-      </c>
-      <c r="F186" s="3" t="n">
-        <v>107.69</v>
-      </c>
-      <c r="G186" s="3" t="n">
-        <v>107.1</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" s="2" t="inlineStr">
-        <is>
-          <t>SHIVALIK</t>
-        </is>
-      </c>
-      <c r="B187" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C187" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D187" s="3" t="n">
-        <v>308.6</v>
-      </c>
-      <c r="E187" s="3" t="n">
-        <v>291.68</v>
-      </c>
-      <c r="F187" s="3" t="n">
-        <v>322.19</v>
-      </c>
-      <c r="G187" s="3" t="n">
-        <v>322.19</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" s="2" t="inlineStr">
-        <is>
-          <t>SHIVAMAUTO</t>
-        </is>
-      </c>
-      <c r="B188" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C188" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D188" s="3" t="n">
-        <v>17.73</v>
-      </c>
-      <c r="E188" s="3" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="F188" s="3" t="n">
-        <v>17.63</v>
-      </c>
-      <c r="G188" s="3" t="n">
-        <v>17.37</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" s="2" t="inlineStr">
-        <is>
-          <t>SHIVATEX</t>
-        </is>
-      </c>
-      <c r="B189" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C189" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D189" s="3" t="n">
-        <v>181.1</v>
-      </c>
-      <c r="E189" s="3" t="n">
-        <v>167.37</v>
-      </c>
-      <c r="F189" s="3" t="n">
-        <v>181.17</v>
-      </c>
-      <c r="G189" s="3" t="n">
-        <v>182.46</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" s="2" t="inlineStr">
-        <is>
-          <t>SILVERETF</t>
-        </is>
-      </c>
-      <c r="B190" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C190" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D190" s="3" t="n">
-        <v>201.81</v>
-      </c>
-      <c r="E190" s="3" t="n">
-        <v>198.28</v>
-      </c>
-      <c r="F190" s="3" t="n">
-        <v>203.98</v>
-      </c>
-      <c r="G190" s="3" t="n">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" s="2" t="inlineStr">
-        <is>
-          <t>SIMPLEXINF</t>
-        </is>
-      </c>
-      <c r="B191" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C191" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D191" s="3" t="n">
-        <v>274.88</v>
-      </c>
-      <c r="E191" s="3" t="n">
-        <v>258.73</v>
-      </c>
-      <c r="F191" s="3" t="n">
-        <v>268.83</v>
-      </c>
-      <c r="G191" s="3" t="n">
-        <v>265.36</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" s="2" t="inlineStr">
-        <is>
-          <t>SINCLAIR</t>
-        </is>
-      </c>
-      <c r="B192" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C192" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D192" s="3" t="n">
-        <v>82.44</v>
-      </c>
-      <c r="E192" s="3" t="n">
-        <v>77.37</v>
-      </c>
-      <c r="F192" s="3" t="n">
-        <v>82.38</v>
-      </c>
-      <c r="G192" s="3" t="n">
-        <v>81.65000000000001</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" s="2" t="inlineStr">
-        <is>
-          <t>SOLARA</t>
-        </is>
-      </c>
-      <c r="B193" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C193" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D193" s="3" t="n">
-        <v>632.4299999999999</v>
-      </c>
-      <c r="E193" s="3" t="n">
-        <v>608.95</v>
-      </c>
-      <c r="F193" s="3" t="n">
-        <v>632.65</v>
-      </c>
-      <c r="G193" s="3" t="n">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" s="2" t="inlineStr">
-        <is>
-          <t>SOMANYCERA</t>
-        </is>
-      </c>
-      <c r="B194" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C194" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D194" s="3" t="n">
-        <v>569.5700000000001</v>
-      </c>
-      <c r="E194" s="3" t="n">
-        <v>553.8200000000001</v>
-      </c>
-      <c r="F194" s="3" t="n">
-        <v>557.3</v>
-      </c>
-      <c r="G194" s="3" t="n">
-        <v>562.9</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" s="2" t="inlineStr">
-        <is>
-          <t>SONAMLTD</t>
-        </is>
-      </c>
-      <c r="B195" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C195" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D195" s="3" t="n">
-        <v>73.43000000000001</v>
-      </c>
-      <c r="E195" s="3" t="n">
-        <v>66.68000000000001</v>
-      </c>
-      <c r="F195" s="3" t="n">
-        <v>77.81999999999999</v>
-      </c>
-      <c r="G195" s="3" t="n">
-        <v>77.5</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" s="2" t="inlineStr">
-        <is>
-          <t>SONATSOFTW</t>
-        </is>
-      </c>
-      <c r="B196" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C196" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D196" s="3" t="n">
-        <v>304.5</v>
-      </c>
-      <c r="E196" s="3" t="n">
-        <v>289.42</v>
-      </c>
-      <c r="F196" s="3" t="n">
-        <v>292.05</v>
-      </c>
-      <c r="G196" s="3" t="n">
-        <v>292.55</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" s="2" t="inlineStr">
-        <is>
-          <t>SPAL</t>
-        </is>
-      </c>
-      <c r="B197" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C197" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D197" s="3" t="n">
-        <v>1029.15</v>
-      </c>
-      <c r="E197" s="3" t="n">
-        <v>978.67</v>
-      </c>
-      <c r="F197" s="3" t="n">
-        <v>1050.25</v>
-      </c>
-      <c r="G197" s="3" t="n">
-        <v>1044.55</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" s="2" t="inlineStr">
-        <is>
-          <t>SPLPETRO</t>
-        </is>
-      </c>
-      <c r="B198" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C198" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D198" s="3" t="n">
-        <v>725.23</v>
-      </c>
-      <c r="E198" s="3" t="n">
-        <v>694.4</v>
-      </c>
-      <c r="F198" s="3" t="n">
-        <v>729.05</v>
-      </c>
-      <c r="G198" s="3" t="n">
-        <v>725.15</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" s="2" t="inlineStr">
-        <is>
-          <t>SSWL</t>
-        </is>
-      </c>
-      <c r="B199" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C199" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D199" s="3" t="n">
-        <v>299.77</v>
-      </c>
-      <c r="E199" s="3" t="n">
-        <v>289.53</v>
-      </c>
-      <c r="F199" s="3" t="n">
-        <v>305.65</v>
-      </c>
-      <c r="G199" s="3" t="n">
-        <v>306.2</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" s="2" t="inlineStr">
-        <is>
-          <t>STAR</t>
-        </is>
-      </c>
-      <c r="B200" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C200" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D200" s="3" t="n">
-        <v>1019.67</v>
-      </c>
-      <c r="E200" s="3" t="n">
-        <v>989.3</v>
-      </c>
-      <c r="F200" s="3" t="n">
-        <v>1025</v>
-      </c>
-      <c r="G200" s="3" t="n">
-        <v>1029</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" s="2" t="inlineStr">
-        <is>
-          <t>STEL</t>
-        </is>
-      </c>
-      <c r="B201" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C201" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D201" s="3" t="n">
-        <v>655.63</v>
-      </c>
-      <c r="E201" s="3" t="n">
-        <v>618.08</v>
-      </c>
-      <c r="F201" s="3" t="n">
-        <v>661.2</v>
-      </c>
-      <c r="G201" s="3" t="n">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" s="2" t="inlineStr">
-        <is>
-          <t>STLNETWORK</t>
-        </is>
-      </c>
-      <c r="B202" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C202" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D202" s="3" t="n">
-        <v>27.46</v>
-      </c>
-      <c r="E202" s="3" t="n">
-        <v>26.29</v>
-      </c>
-      <c r="F202" s="3" t="n">
-        <v>28.15</v>
-      </c>
-      <c r="G202" s="3" t="n">
-        <v>28.12</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" s="2" t="inlineStr">
-        <is>
-          <t>STLTECH</t>
-        </is>
-      </c>
-      <c r="B203" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C203" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D203" s="3" t="n">
-        <v>727.38</v>
-      </c>
-      <c r="E203" s="3" t="n">
-        <v>698.73</v>
-      </c>
-      <c r="F203" s="3" t="n">
-        <v>728.45</v>
-      </c>
-      <c r="G203" s="3" t="n">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" s="2" t="inlineStr">
-        <is>
-          <t>SUDARSCHEM</t>
-        </is>
-      </c>
-      <c r="B204" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C204" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D204" s="3" t="n">
-        <v>1266.37</v>
-      </c>
-      <c r="E204" s="3" t="n">
-        <v>1230.13</v>
-      </c>
-      <c r="F204" s="3" t="n">
-        <v>1266.8</v>
-      </c>
-      <c r="G204" s="3" t="n">
-        <v>1270</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" s="2" t="inlineStr">
-        <is>
-          <t>SUNPHARMA</t>
-        </is>
-      </c>
-      <c r="B205" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C205" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D205" s="3" t="n">
-        <v>1946.93</v>
-      </c>
-      <c r="E205" s="3" t="n">
-        <v>1902.27</v>
-      </c>
-      <c r="F205" s="3" t="n">
-        <v>1984.8</v>
-      </c>
-      <c r="G205" s="3" t="n">
-        <v>1984.8</v>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" s="2" t="inlineStr">
-        <is>
-          <t>SUPERSPIN</t>
-        </is>
-      </c>
-      <c r="B206" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C206" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D206" s="3" t="n">
-        <v>6.18</v>
-      </c>
-      <c r="E206" s="3" t="n">
-        <v>6.01</v>
-      </c>
-      <c r="F206" s="3" t="n">
-        <v>6.42</v>
-      </c>
-      <c r="G206" s="3" t="n">
-        <v>6.42</v>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" s="2" t="inlineStr">
-        <is>
-          <t>SUPRIYA</t>
-        </is>
-      </c>
-      <c r="B207" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C207" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D207" s="3" t="n">
-        <v>803.9299999999999</v>
-      </c>
-      <c r="E207" s="3" t="n">
-        <v>778.45</v>
-      </c>
-      <c r="F207" s="3" t="n">
-        <v>798.3</v>
-      </c>
-      <c r="G207" s="3" t="n">
-        <v>799.95</v>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" s="2" t="inlineStr">
-        <is>
-          <t>TAMBOLIIN</t>
-        </is>
-      </c>
-      <c r="B208" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C208" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D208" s="3" t="n">
-        <v>261.29</v>
-      </c>
-      <c r="E208" s="3" t="n">
-        <v>247.08</v>
-      </c>
-      <c r="F208" s="3" t="n">
-        <v>255</v>
-      </c>
-      <c r="G208" s="3" t="n">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" s="2" t="inlineStr">
-        <is>
-          <t>TATATECH</t>
-        </is>
-      </c>
-      <c r="B209" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C209" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D209" s="3" t="n">
-        <v>829.2</v>
-      </c>
-      <c r="E209" s="3" t="n">
-        <v>798.77</v>
-      </c>
-      <c r="F209" s="3" t="n">
-        <v>831.05</v>
-      </c>
-      <c r="G209" s="3" t="n">
-        <v>830.5</v>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" s="2" t="inlineStr">
-        <is>
-          <t>TCS</t>
-        </is>
-      </c>
-      <c r="B210" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C210" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D210" s="3" t="n">
-        <v>2343.8</v>
-      </c>
-      <c r="E210" s="3" t="n">
-        <v>2271.13</v>
-      </c>
-      <c r="F210" s="3" t="n">
-        <v>2399.3</v>
-      </c>
-      <c r="G210" s="3" t="n">
-        <v>2399.3</v>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" s="2" t="inlineStr">
-        <is>
-          <t>TEAMLEASE</t>
-        </is>
-      </c>
-      <c r="B211" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C211" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D211" s="3" t="n">
-        <v>1284.3</v>
-      </c>
-      <c r="E211" s="3" t="n">
-        <v>1243.8</v>
-      </c>
-      <c r="F211" s="3" t="n">
-        <v>1283.5</v>
-      </c>
-      <c r="G211" s="3" t="n">
-        <v>1280</v>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" s="2" t="inlineStr">
-        <is>
-          <t>TECH</t>
-        </is>
-      </c>
-      <c r="B212" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C212" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D212" s="3" t="n">
-        <v>34.06</v>
-      </c>
-      <c r="E212" s="3" t="n">
-        <v>33.29</v>
-      </c>
-      <c r="F212" s="3" t="n">
-        <v>33.85</v>
-      </c>
-      <c r="G212" s="3" t="n">
-        <v>33.98</v>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" s="2" t="inlineStr">
-        <is>
-          <t>TECHNVISN</t>
-        </is>
-      </c>
-      <c r="B213" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C213" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D213" s="3" t="n">
-        <v>5405.1</v>
-      </c>
-      <c r="E213" s="3" t="n">
-        <v>5011.67</v>
-      </c>
-      <c r="F213" s="3" t="n">
-        <v>5249.6</v>
-      </c>
-      <c r="G213" s="3" t="n">
-        <v>5250</v>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" s="2" t="inlineStr">
-        <is>
-          <t>TFL</t>
-        </is>
-      </c>
-      <c r="B214" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C214" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D214" s="3" t="n">
-        <v>12.87</v>
-      </c>
-      <c r="E214" s="3" t="n">
-        <v>11.68</v>
-      </c>
-      <c r="F214" s="3" t="n">
-        <v>11.93</v>
-      </c>
-      <c r="G214" s="3" t="n">
-        <v>11.91</v>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" s="2" t="inlineStr">
-        <is>
-          <t>TGBHOTELS</t>
-        </is>
-      </c>
-      <c r="B215" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C215" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D215" s="3" t="n">
-        <v>9.85</v>
-      </c>
-      <c r="E215" s="3" t="n">
-        <v>9.029999999999999</v>
-      </c>
-      <c r="F215" s="3" t="n">
-        <v>9.84</v>
-      </c>
-      <c r="G215" s="3" t="n">
-        <v>9.84</v>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" s="2" t="inlineStr">
-        <is>
-          <t>THELEELA</t>
-        </is>
-      </c>
-      <c r="B216" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C216" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D216" s="3" t="n">
-        <v>567.3</v>
-      </c>
-      <c r="E216" s="3" t="n">
-        <v>547.63</v>
-      </c>
-      <c r="F216" s="3" t="n">
-        <v>570.4</v>
-      </c>
-      <c r="G216" s="3" t="n">
-        <v>571.15</v>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" s="2" t="inlineStr">
-        <is>
-          <t>TI</t>
-        </is>
-      </c>
-      <c r="B217" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C217" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D217" s="3" t="n">
-        <v>572.3</v>
-      </c>
-      <c r="E217" s="3" t="n">
-        <v>552</v>
-      </c>
-      <c r="F217" s="3" t="n">
-        <v>561.05</v>
-      </c>
-      <c r="G217" s="3" t="n">
-        <v>558.75</v>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" s="2" t="inlineStr">
-        <is>
-          <t>TIMEX</t>
-        </is>
-      </c>
-      <c r="B218" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C218" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D218" s="3" t="n">
-        <v>661.9299999999999</v>
-      </c>
-      <c r="E218" s="3" t="n">
-        <v>631.97</v>
-      </c>
-      <c r="F218" s="3" t="n">
-        <v>679.45</v>
-      </c>
-      <c r="G218" s="3" t="n">
-        <v>678.8</v>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" s="2" t="inlineStr">
-        <is>
-          <t>TIRUMALCHM</t>
-        </is>
-      </c>
-      <c r="B219" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C219" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D219" s="3" t="n">
-        <v>164.76</v>
-      </c>
-      <c r="E219" s="3" t="n">
-        <v>158.42</v>
-      </c>
-      <c r="F219" s="3" t="n">
-        <v>160.06</v>
-      </c>
-      <c r="G219" s="3" t="n">
-        <v>159.91</v>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" s="2" t="inlineStr">
-        <is>
-          <t>TTKHLTCARE</t>
-        </is>
-      </c>
-      <c r="B220" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C220" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D220" s="3" t="n">
-        <v>1148.63</v>
-      </c>
-      <c r="E220" s="3" t="n">
-        <v>1089.77</v>
-      </c>
-      <c r="F220" s="3" t="n">
-        <v>1159.7</v>
-      </c>
-      <c r="G220" s="3" t="n">
-        <v>1152.9</v>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" s="2" t="inlineStr">
-        <is>
-          <t>TVSSRICHAK</t>
-        </is>
-      </c>
-      <c r="B221" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C221" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D221" s="3" t="n">
-        <v>5403.57</v>
-      </c>
-      <c r="E221" s="3" t="n">
-        <v>5183.47</v>
-      </c>
-      <c r="F221" s="3" t="n">
-        <v>5519.6</v>
-      </c>
-      <c r="G221" s="3" t="n">
-        <v>5480</v>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" s="2" t="inlineStr">
-        <is>
-          <t>UDS</t>
-        </is>
-      </c>
-      <c r="B222" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C222" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D222" s="3" t="n">
-        <v>225.23</v>
-      </c>
-      <c r="E222" s="3" t="n">
-        <v>220.06</v>
-      </c>
-      <c r="F222" s="3" t="n">
-        <v>224.73</v>
-      </c>
-      <c r="G222" s="3" t="n">
-        <v>222.25</v>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" s="2" t="inlineStr">
-        <is>
-          <t>UNICHEMLAB</t>
-        </is>
-      </c>
-      <c r="B223" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C223" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D223" s="3" t="n">
-        <v>568.12</v>
-      </c>
-      <c r="E223" s="3" t="n">
-        <v>535.87</v>
-      </c>
-      <c r="F223" s="3" t="n">
-        <v>556.55</v>
-      </c>
-      <c r="G223" s="3" t="n">
-        <v>554.05</v>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" s="2" t="inlineStr">
-        <is>
-          <t>UNIECOM</t>
-        </is>
-      </c>
-      <c r="B224" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C224" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D224" s="3" t="n">
-        <v>88.77</v>
-      </c>
-      <c r="E224" s="3" t="n">
-        <v>84.38</v>
-      </c>
-      <c r="F224" s="3" t="n">
-        <v>89.36</v>
-      </c>
-      <c r="G224" s="3" t="n">
-        <v>89.5</v>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" s="2" t="inlineStr">
-        <is>
-          <t>UNIPARTS</t>
-        </is>
-      </c>
-      <c r="B225" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C225" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D225" s="3" t="n">
-        <v>867.87</v>
-      </c>
-      <c r="E225" s="3" t="n">
-        <v>824.02</v>
-      </c>
-      <c r="F225" s="3" t="n">
-        <v>893.45</v>
-      </c>
-      <c r="G225" s="3" t="n">
-        <v>898</v>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" s="2" t="inlineStr">
-        <is>
-          <t>UNIVCABLES</t>
-        </is>
-      </c>
-      <c r="B226" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C226" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D226" s="3" t="n">
-        <v>1686.53</v>
-      </c>
-      <c r="E226" s="3" t="n">
-        <v>1602.23</v>
-      </c>
-      <c r="F226" s="3" t="n">
-        <v>1648.2</v>
-      </c>
-      <c r="G226" s="3" t="n">
-        <v>1654.9</v>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" s="2" t="inlineStr">
-        <is>
-          <t>UTISENSETF</t>
-        </is>
-      </c>
-      <c r="B227" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C227" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D227" s="3" t="n">
-        <v>941.63</v>
-      </c>
-      <c r="E227" s="3" t="n">
-        <v>933.52</v>
-      </c>
-      <c r="F227" s="3" t="n">
-        <v>939.25</v>
-      </c>
-      <c r="G227" s="3" t="n">
-        <v>938.3200000000001</v>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" s="2" t="inlineStr">
-        <is>
-          <t>VIDYAWIRES</t>
-        </is>
-      </c>
-      <c r="B228" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C228" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D228" s="3" t="n">
-        <v>90.8</v>
-      </c>
-      <c r="E228" s="3" t="n">
-        <v>87.33</v>
-      </c>
-      <c r="F228" s="3" t="n">
-        <v>90.25</v>
-      </c>
-      <c r="G228" s="3" t="n">
-        <v>90.54000000000001</v>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" s="2" t="inlineStr">
-        <is>
-          <t>VIJIFIN</t>
-        </is>
-      </c>
-      <c r="B229" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C229" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D229" s="3" t="n">
-        <v>15.04</v>
-      </c>
-      <c r="E229" s="3" t="n">
-        <v>15.04</v>
-      </c>
-      <c r="F229" s="3" t="n">
-        <v>15.34</v>
-      </c>
-      <c r="G229" s="3" t="n">
-        <v>15.34</v>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" s="2" t="inlineStr">
-        <is>
-          <t>VINCOFE</t>
-        </is>
-      </c>
-      <c r="B230" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C230" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D230" s="3" t="n">
-        <v>183.35</v>
-      </c>
-      <c r="E230" s="3" t="n">
-        <v>171.67</v>
-      </c>
-      <c r="F230" s="3" t="n">
-        <v>185.77</v>
-      </c>
-      <c r="G230" s="3" t="n">
-        <v>185.94</v>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" s="2" t="inlineStr">
-        <is>
-          <t>VISACHROME</t>
-        </is>
-      </c>
-      <c r="B231" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C231" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D231" s="3" t="n">
-        <v>39.36</v>
-      </c>
-      <c r="E231" s="3" t="n">
-        <v>38.29</v>
-      </c>
-      <c r="F231" s="3" t="n">
-        <v>41.02</v>
-      </c>
-      <c r="G231" s="3" t="n">
-        <v>41.02</v>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" s="2" t="inlineStr">
-        <is>
-          <t>VRLLOG</t>
-        </is>
-      </c>
-      <c r="B232" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C232" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D232" s="3" t="n">
-        <v>300.1</v>
-      </c>
-      <c r="E232" s="3" t="n">
-        <v>290.48</v>
-      </c>
-      <c r="F232" s="3" t="n">
-        <v>303.15</v>
-      </c>
-      <c r="G232" s="3" t="n">
-        <v>303.5</v>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" s="2" t="inlineStr">
-        <is>
-          <t>XTRANET</t>
-        </is>
-      </c>
-      <c r="B233" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C233" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D233" s="3" t="n">
-        <v>191.13</v>
-      </c>
-      <c r="E233" s="3" t="n">
-        <v>169.11</v>
-      </c>
-      <c r="F233" s="3" t="n">
-        <v>194.82</v>
-      </c>
-      <c r="G233" s="3" t="n">
-        <v>196.8</v>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" s="2" t="inlineStr">
-        <is>
-          <t>YUKEN</t>
-        </is>
-      </c>
-      <c r="B234" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C234" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D234" s="3" t="n">
-        <v>988.13</v>
-      </c>
-      <c r="E234" s="3" t="n">
-        <v>943.28</v>
-      </c>
-      <c r="F234" s="3" t="n">
-        <v>989.1</v>
-      </c>
-      <c r="G234" s="3" t="n">
-        <v>1000.85</v>
+        <v>651.5</v>
       </c>
     </row>
   </sheetData>

--- a/data/uptrend_output.xlsx
+++ b/data/uptrend_output.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G175"/>
+  <dimension ref="A1:G126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -522,16 +522,16 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1506.6</v>
+        <v>1548.57</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1414.37</v>
+        <v>1450.07</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1523.5</v>
+        <v>1478.6</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>1525</v>
+        <v>1478.9</v>
       </c>
     </row>
     <row r="3">
@@ -551,22 +551,22 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>862.88</v>
+        <v>873.05</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>826.92</v>
+        <v>841.5</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>865.2</v>
+        <v>867.25</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>865</v>
+        <v>864.45</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>AKI</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -580,22 +580,22 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>497.22</v>
+        <v>4.82</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>480.88</v>
+        <v>4.23</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>492.65</v>
+        <v>5.48</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>492</v>
+        <v>5.48</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>AHLEAST</t>
+          <t>ALKALI</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -609,22 +609,22 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>142.43</v>
+        <v>68.28</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>136.15</v>
+        <v>64.83</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>142.2</v>
+        <v>68.86</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>143</v>
+        <v>68.84999999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>AKSHARCHEM</t>
+          <t>AMIRCHAND</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -638,22 +638,22 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>372.22</v>
+        <v>181.7</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>365.01</v>
+        <v>171.51</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>384.65</v>
+        <v>185.11</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>384.65</v>
+        <v>184.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>AKUMS</t>
+          <t>ANTHEM</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -667,22 +667,22 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>785.33</v>
+        <v>933</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>766.27</v>
+        <v>898.95</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>779.05</v>
+        <v>934.5</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>782</v>
+        <v>938</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>ALMONDZ</t>
+          <t>AONELIQUID</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -696,22 +696,22 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>17.71</v>
+        <v>1075.05</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>16.77</v>
+        <v>1075.03</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>17.49</v>
+        <v>1075.16</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>17.57</v>
+        <v>1075.18</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>AMANTA</t>
+          <t>ARROWGREEN</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -725,22 +725,22 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>188.3</v>
+        <v>738.95</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>186.49</v>
+        <v>705.53</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>190</v>
+        <v>771.2</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>190</v>
+        <v>771.2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AMBALALSA</t>
+          <t>ARVINDFASN</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -754,22 +754,22 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>45.41</v>
+        <v>460.65</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>43.3</v>
+        <v>444.97</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>43.92</v>
+        <v>461.15</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>44.69</v>
+        <v>460.1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AMDIND</t>
+          <t>ASIANENE</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -783,22 +783,22 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>57.63</v>
+        <v>497.55</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>53.16</v>
+        <v>472.45</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>57.02</v>
+        <v>504.1</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>57.12</v>
+        <v>505</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>AMIRCHAND</t>
+          <t>ASTAR</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -812,22 +812,22 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>181.7</v>
+        <v>596.65</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>171.51</v>
+        <v>584.03</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>185.11</v>
+        <v>590</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>184.5</v>
+        <v>590</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>AONELIQUID</t>
+          <t>AUSOMENT</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -841,22 +841,22 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>1074.91</v>
+        <v>152.98</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>1074.89</v>
+        <v>146.58</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>1075.03</v>
+        <v>156.45</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>1075.04</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>APCOTEXIND</t>
+          <t>AVL</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -870,22 +870,22 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>648.33</v>
+        <v>605.85</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>619.27</v>
+        <v>589.53</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>639.2</v>
+        <v>599.85</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>641</v>
+        <v>598.1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>ARVIND</t>
+          <t>AXISBNKETF</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -899,22 +899,22 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>558.05</v>
+        <v>599.1900000000001</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>540.58</v>
+        <v>593.95</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>557.1</v>
+        <v>597.15</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>556.95</v>
+        <v>597.09</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>ASAHISONG</t>
+          <t>AXISCADES</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -928,22 +928,22 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>380</v>
+        <v>1695.2</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>359.48</v>
+        <v>1616.27</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>374.55</v>
+        <v>1689.7</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>375</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>ASIANHOTNR</t>
+          <t>AXISCETF</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -957,22 +957,22 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>362.12</v>
+        <v>120.57</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>319.35</v>
+        <v>118.88</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>369.2</v>
+        <v>121.12</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>373</v>
+        <v>120.8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>ATHERENERG</t>
+          <t>AYMSYNTEX</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -986,22 +986,22 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1697.23</v>
+        <v>306.8</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1607.23</v>
+        <v>269.45</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1725.6</v>
+        <v>312.5</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>1725.6</v>
+        <v>312</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>ATLANTAA</t>
+          <t>BALAXI</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1015,22 +1015,22 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>39.89</v>
+        <v>23.71</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>37.49</v>
+        <v>22.27</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>40.68</v>
+        <v>25.01</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>40.8</v>
+        <v>25.04</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>ATLANTAELE</t>
+          <t>BEPL</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1044,22 +1044,22 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1823.17</v>
+        <v>126.95</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1744.47</v>
+        <v>122.08</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1823.6</v>
+        <v>127.29</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>1824.6</v>
+        <v>127.5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>AUSOMENT</t>
+          <t>BFINVEST</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>150.18</v>
+        <v>449.9</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>145.77</v>
+        <v>436.03</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>149.77</v>
+        <v>452.95</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>148.1</v>
+        <v>454.5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>AVL</t>
+          <t>BIRLACABLE</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -1102,22 +1102,22 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>601.9299999999999</v>
+        <v>325.6</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>585.9</v>
+        <v>312.02</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>604.1</v>
+        <v>341.6</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>603.95</v>
+        <v>341.6</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>AXISBNKETF</t>
+          <t>BLISSGVS</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -1131,22 +1131,22 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>599.1900000000001</v>
+        <v>637.17</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>593.95</v>
+        <v>599</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>597.15</v>
+        <v>648.65</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>597.09</v>
+        <v>649.9</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>AXISCADES</t>
+          <t>BOROSCI</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1160,22 +1160,22 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>1669.2</v>
+        <v>129.98</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>1601.5</v>
+        <v>123.96</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>1644.2</v>
+        <v>131.31</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>1640.1</v>
+        <v>131.1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>AXISCETF</t>
+          <t>CALSOFT</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -1189,22 +1189,22 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>120.57</v>
+        <v>39.16</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>118.88</v>
+        <v>37.74</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>121.12</v>
+        <v>41.08</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>120.8</v>
+        <v>41.08</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>AYMSYNTEX</t>
+          <t>CENTENKA</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -1218,22 +1218,22 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>286.05</v>
+        <v>576.1799999999999</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>253.97</v>
+        <v>547.5</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>294.2</v>
+        <v>602.35</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>291.8</v>
+        <v>619</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>BAFNAPH</t>
+          <t>CMSINFO</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -1247,22 +1247,22 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>305.17</v>
+        <v>250.56</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>290</v>
+        <v>242.09</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>312.6</v>
+        <v>249.3</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>313.8</v>
+        <v>249</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>BAJAJ-AUTO</t>
+          <t>COMSYN</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1276,22 +1276,22 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>12191.33</v>
+        <v>308.58</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>11912</v>
+        <v>288.08</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>12361</v>
+        <v>302.65</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>12361</v>
+        <v>298.75</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>BASML</t>
+          <t>CORDSCABLE</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -1305,22 +1305,22 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>25.82</v>
+        <v>315.07</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>25.04</v>
+        <v>279.99</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>25.57</v>
+        <v>315.5</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>25.7</v>
+        <v>314.8</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>BENGALASM</t>
+          <t>CPPLUS</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -1334,22 +1334,22 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>6535.67</v>
+        <v>3710.2</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>6316.5</v>
+        <v>3538.83</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>6661.5</v>
+        <v>3721.4</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>6699.5</v>
+        <v>3712</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>BHAGERIA</t>
+          <t>CROWN</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -1363,22 +1363,22 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>250.88</v>
+        <v>110.8</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>246.29</v>
+        <v>103.84</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>263.2</v>
+        <v>108.27</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>263.2</v>
+        <v>108.2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>BLISSGVS</t>
+          <t>CYBERMEDIA</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -1392,22 +1392,22 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>613.53</v>
+        <v>19.74</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>579.67</v>
+        <v>18.07</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>630.4</v>
+        <v>19.9</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>631</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>BODALCHEM</t>
+          <t>DBSTOCKBRO</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -1421,22 +1421,22 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>116.44</v>
+        <v>30.69</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>106.19</v>
+        <v>28.91</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>126.76</v>
+        <v>30.3</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>128.1</v>
+        <v>30.5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>BVCL</t>
+          <t>DCMSHRIRAM</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -1450,22 +1450,22 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>45.53</v>
+        <v>1042.1</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>42.45</v>
+        <v>1012.87</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>43.5</v>
+        <v>1028</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>43.7</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>CMRGREEN</t>
+          <t>DEEDEV</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -1479,22 +1479,22 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>231.4</v>
+        <v>625.52</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>221.82</v>
+        <v>591.67</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>231.03</v>
+        <v>643.85</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>231.15</v>
+        <v>643</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>COMSYN</t>
+          <t>DRAGARWQ</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -1508,22 +1508,22 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>299.22</v>
+        <v>5369.83</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>277.76</v>
+        <v>5253.67</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>304.35</v>
+        <v>5420</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>304.7</v>
+        <v>5440</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>CORDSCABLE</t>
+          <t>DSKULKARNI</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -1537,22 +1537,22 @@
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>289.3</v>
+        <v>18.67</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>259.83</v>
+        <v>18.67</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>312.95</v>
+        <v>19.04</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>310.25</v>
+        <v>19.04</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>CPCAP</t>
+          <t>ELIQUID</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -1566,22 +1566,22 @@
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>118.9</v>
+        <v>1047.7</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>113.24</v>
+        <v>1045.99</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>117.72</v>
+        <v>1046.13</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>118.9</v>
+        <v>1046.12</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>CRISIL</t>
+          <t>GANGAFORGE</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -1595,22 +1595,22 @@
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>4833.97</v>
+        <v>1.77</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>4717.37</v>
+        <v>1.68</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>4829.5</v>
+        <v>1.85</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>4761.5</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>CSLFINANCE</t>
+          <t>GCSL</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -1624,22 +1624,22 @@
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>241.43</v>
+        <v>567.37</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>232.03</v>
+        <v>549.67</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>236.92</v>
+        <v>571.85</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>237.5</v>
+        <v>569</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>CYBERMEDIA</t>
+          <t>GEEKAYWIRE</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -1653,22 +1653,22 @@
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>19.38</v>
+        <v>30.17</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>17.98</v>
+        <v>26.26</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>18.66</v>
+        <v>27.86</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>18.78</v>
+        <v>28.2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>CYIENT</t>
+          <t>GHCLTEXTIL</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -1682,22 +1682,22 @@
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>1175.17</v>
+        <v>141.86</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>1088.68</v>
+        <v>134.67</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>1164.6</v>
+        <v>139.35</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>1153</v>
+        <v>139.94</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>DRAGARWQ</t>
+          <t>GILLETTE</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -1711,22 +1711,22 @@
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>5298.33</v>
+        <v>7415.83</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>5225.33</v>
+        <v>7269.67</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>5309.5</v>
+        <v>7346</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>5321</v>
+        <v>7353</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>DSKULKARNI</t>
+          <t>GKSL</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -1740,22 +1740,22 @@
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>18.31</v>
+        <v>168.3</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>18.31</v>
+        <v>158.27</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>18.67</v>
+        <v>168.3</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>18.67</v>
+        <v>168.05</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>DYCL</t>
+          <t>GLOBAL</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -1769,22 +1769,22 @@
         </is>
       </c>
       <c r="D45" s="3" t="n">
-        <v>518.08</v>
+        <v>113.43</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>471.17</v>
+        <v>106.58</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>542.4</v>
+        <v>117.31</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>543</v>
+        <v>118.5</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>EFCIL</t>
+          <t>GROWWLIQID</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -1798,22 +1798,22 @@
         </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>206.11</v>
+        <v>110.59</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>198.33</v>
+        <v>110.57</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>201.34</v>
+        <v>110.59</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>202</v>
+        <v>110.6</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>ELECTCAST</t>
+          <t>GUFICBIO</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -1827,22 +1827,22 @@
         </is>
       </c>
       <c r="D47" s="3" t="n">
-        <v>84.68000000000001</v>
+        <v>434.73</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>81.16</v>
+        <v>408.38</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>83.83</v>
+        <v>438.8</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>83.8</v>
+        <v>440</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>ELIQUID</t>
+          <t>GUJENERGY</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -1856,22 +1856,22 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1045.88</v>
+        <v>259.03</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1045.86</v>
+        <v>249.57</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1045.99</v>
+        <v>262.29</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>1045.99</v>
+        <v>262.22</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>EMKAY</t>
+          <t>GYFTR</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -1885,22 +1885,22 @@
         </is>
       </c>
       <c r="D49" s="3" t="n">
-        <v>262.93</v>
+        <v>184.56</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>248.2</v>
+        <v>169.67</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>264.1</v>
+        <v>183</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>264.5</v>
+        <v>182.6</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>EMMBI</t>
+          <t>HARSHA</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -1914,22 +1914,22 @@
         </is>
       </c>
       <c r="D50" s="3" t="n">
-        <v>90.43000000000001</v>
+        <v>460</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>87.41</v>
+        <v>441.1</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>92.66</v>
+        <v>450.75</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>92.40000000000001</v>
+        <v>448.5</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>ENGINERSIN</t>
+          <t>HITECHCORP</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -1943,22 +1943,22 @@
         </is>
       </c>
       <c r="D51" s="3" t="n">
-        <v>269.26</v>
+        <v>338.3</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>253.37</v>
+        <v>332.25</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>280.05</v>
+        <v>336.55</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>280.7</v>
+        <v>338</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>FEDDERSHOL</t>
+          <t>HPAL</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -1972,22 +1972,22 @@
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>45.73</v>
+        <v>35.47</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>44.39</v>
+        <v>34.22</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>45.21</v>
+        <v>35.01</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>45.15</v>
+        <v>35.2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>FINEORG</t>
+          <t>INFIBEAM</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -2001,22 +2001,22 @@
         </is>
       </c>
       <c r="D53" s="3" t="n">
-        <v>5345.6</v>
+        <v>16.54</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>5202.5</v>
+        <v>15.65</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>5255.5</v>
+        <v>16.9</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>5227</v>
+        <v>16.84</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>GABRIEL</t>
+          <t>ITADD</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -2030,22 +2030,22 @@
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>1434.57</v>
+        <v>33.41</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>1351.63</v>
+        <v>32.58</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>1426.3</v>
+        <v>32.9</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>1425</v>
+        <v>32.74</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>GARFIBRES</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -2059,22 +2059,22 @@
         </is>
       </c>
       <c r="D55" s="3" t="n">
-        <v>825.5700000000001</v>
+        <v>267.92</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>794.4299999999999</v>
+        <v>259.93</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>842.7</v>
+        <v>266.3</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>850</v>
+        <v>266.3</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>GEEKAYWIRE</t>
+          <t>IVP</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -2088,22 +2088,22 @@
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>28.18</v>
+        <v>206.96</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>24.72</v>
+        <v>199.08</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>29.09</v>
+        <v>209.8</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>29.11</v>
+        <v>209.75</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>GHCLTEXTIL</t>
+          <t>JAYKAY</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -2117,22 +2117,22 @@
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>137.68</v>
+        <v>164.16</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>130.34</v>
+        <v>150.99</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>140.45</v>
+        <v>169.4</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>141.14</v>
+        <v>169</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>GICRE</t>
+          <t>JSL</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -2146,22 +2146,22 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>357.9</v>
+        <v>731.65</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>352.83</v>
+        <v>704.15</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>354.75</v>
+        <v>734.9</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>354.6</v>
+        <v>735</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>GKSL</t>
+          <t>KALYANIFRG</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -2175,22 +2175,22 @@
         </is>
       </c>
       <c r="D59" s="3" t="n">
-        <v>165.48</v>
+        <v>1067.9</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>155.44</v>
+        <v>897.25</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>162.45</v>
+        <v>1113.65</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>162.55</v>
+        <v>1176.6</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>GLFL</t>
+          <t>KANANIIND</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -2204,22 +2204,22 @@
         </is>
       </c>
       <c r="D60" s="3" t="n">
-        <v>5.96</v>
+        <v>1.59</v>
       </c>
       <c r="E60" s="3" t="n">
-        <v>5.44</v>
+        <v>1.5</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>5.93</v>
+        <v>1.53</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>5.66</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>GOACARBON</t>
+          <t>KHAITANLTD</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -2233,22 +2233,22 @@
         </is>
       </c>
       <c r="D61" s="3" t="n">
-        <v>371.62</v>
+        <v>153</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>357.75</v>
+        <v>139.05</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>369.05</v>
+        <v>160.8</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>368</v>
+        <v>165</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>GODREJAGRO</t>
+          <t>KIRLOSENG</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -2262,22 +2262,22 @@
         </is>
       </c>
       <c r="D62" s="3" t="n">
-        <v>645.3200000000001</v>
+        <v>2148.33</v>
       </c>
       <c r="E62" s="3" t="n">
-        <v>615.23</v>
+        <v>2075.33</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>654.4</v>
+        <v>2160.9</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>652</v>
+        <v>2172</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>GRAPHITE</t>
+          <t>KRONOX</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -2291,22 +2291,22 @@
         </is>
       </c>
       <c r="D63" s="3" t="n">
-        <v>723.03</v>
+        <v>185.28</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>692.78</v>
+        <v>172.24</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>732.9</v>
+        <v>189.68</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>733.8</v>
+        <v>189.98</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>GYFTR</t>
+          <t>KRYSTAL</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -2320,22 +2320,22 @@
         </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>177.69</v>
+        <v>667.1799999999999</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>166.79</v>
+        <v>628.4299999999999</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>182.15</v>
+        <v>667</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>183.85</v>
+        <v>668.75</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>HAPPYFORGE</t>
+          <t>LAHOTIOV</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -2349,22 +2349,22 @@
         </is>
       </c>
       <c r="D65" s="3" t="n">
-        <v>2401.1</v>
+        <v>42.27</v>
       </c>
       <c r="E65" s="3" t="n">
-        <v>2295.33</v>
+        <v>40.39</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>2420.4</v>
+        <v>41.98</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>2424</v>
+        <v>41.99</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>HDFCLIQUID</t>
+          <t>LIQUIDADD</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -2378,22 +2378,22 @@
         </is>
       </c>
       <c r="D66" s="3" t="n">
-        <v>1076.01</v>
+        <v>1142.87</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>1075.99</v>
+        <v>1142.83</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>1076.13</v>
+        <v>1142.98</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>1076.12</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>HDFCNIFIT</t>
+          <t>LIQUIDBETA</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -2407,22 +2407,22 @@
         </is>
       </c>
       <c r="D67" s="3" t="n">
-        <v>33.56</v>
+        <v>1006.47</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>32.68</v>
+        <v>1006.45</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>33.43</v>
+        <v>1006.57</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>33.35</v>
+        <v>1006.57</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>HINDCON</t>
+          <t>LIQUIDBETF</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -2436,22 +2436,22 @@
         </is>
       </c>
       <c r="D68" s="3" t="n">
-        <v>24.36</v>
+        <v>1097.03</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>22.57</v>
+        <v>1097</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>23.47</v>
+        <v>1097.15</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>23.69</v>
+        <v>1097.15</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>HINDOILEXP</t>
+          <t>LIQUIDCASE</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -2465,22 +2465,22 @@
         </is>
       </c>
       <c r="D69" s="3" t="n">
-        <v>168.31</v>
+        <v>115.74</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>161.34</v>
+        <v>115.72</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>169</v>
+        <v>115.74</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>167.9</v>
+        <v>115.74</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>HNDFDS</t>
+          <t>LIQUIDPLUS</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -2494,22 +2494,22 @@
         </is>
       </c>
       <c r="D70" s="3" t="n">
-        <v>658.25</v>
+        <v>1101.38</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>635.15</v>
+        <v>1101.27</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>644.1</v>
+        <v>1101.5</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>647.5</v>
+        <v>1101.51</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>ICRA</t>
+          <t>LIQUIDSHRI</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -2523,22 +2523,22 @@
         </is>
       </c>
       <c r="D71" s="3" t="n">
-        <v>4990.97</v>
+        <v>1119.72</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>4855.23</v>
+        <v>1119.7</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>5011.9</v>
+        <v>1119.83</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>5017</v>
+        <v>1119.83</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>IGPL</t>
+          <t>MALLCOM</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -2552,22 +2552,22 @@
         </is>
       </c>
       <c r="D72" s="3" t="n">
-        <v>544.6</v>
+        <v>1033.33</v>
       </c>
       <c r="E72" s="3" t="n">
-        <v>526.12</v>
+        <v>974.23</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>548.35</v>
+        <v>1021.15</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>549.9</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>IIFLCAPS</t>
+          <t>MARINE</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -2581,22 +2581,22 @@
         </is>
       </c>
       <c r="D73" s="3" t="n">
-        <v>338.7</v>
+        <v>425.83</v>
       </c>
       <c r="E73" s="3" t="n">
-        <v>333.77</v>
+        <v>401.1</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>340.15</v>
+        <v>431.5</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>340</v>
+        <v>433.3</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>INDORAMA</t>
+          <t>MMFL</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -2610,22 +2610,22 @@
         </is>
       </c>
       <c r="D74" s="3" t="n">
-        <v>68.63</v>
+        <v>665.75</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>63.56</v>
+        <v>634.8200000000001</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>68.01000000000001</v>
+        <v>648.05</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>67.84999999999999</v>
+        <v>654</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>INFIBEAM</t>
+          <t>MODISONLTD</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -2639,22 +2639,22 @@
         </is>
       </c>
       <c r="D75" s="3" t="n">
-        <v>16.54</v>
+        <v>499.83</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>15.65</v>
+        <v>464.62</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>16.9</v>
+        <v>520.65</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>16.84</v>
+        <v>521</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>INSECTICID</t>
+          <t>MOOILGAS</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -2668,22 +2668,22 @@
         </is>
       </c>
       <c r="D76" s="3" t="n">
-        <v>613</v>
+        <v>11.36</v>
       </c>
       <c r="E76" s="3" t="n">
-        <v>583.17</v>
+        <v>11.05</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>598.35</v>
+        <v>11.18</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>595.1</v>
+        <v>11.18</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>IPCALAB</t>
+          <t>NIFMID150</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -2697,22 +2697,22 @@
         </is>
       </c>
       <c r="D77" s="3" t="n">
-        <v>1986.33</v>
+        <v>224.68</v>
       </c>
       <c r="E77" s="3" t="n">
-        <v>1940.9</v>
+        <v>222.19</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>1987.6</v>
+        <v>224.96</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>1983.5</v>
+        <v>225.54</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>ITAXIS</t>
+          <t>NIRAJISPAT</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -2726,22 +2726,22 @@
         </is>
       </c>
       <c r="D78" s="3" t="n">
-        <v>346.87</v>
+        <v>391.78</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>338.61</v>
+        <v>391.03</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>343.43</v>
+        <v>429.65</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>342.23</v>
+        <v>429.65</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>ITBEES</t>
+          <t>NLCINDIA</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -2755,22 +2755,22 @@
         </is>
       </c>
       <c r="D79" s="3" t="n">
-        <v>34.89</v>
+        <v>275.72</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>33.92</v>
+        <v>268.35</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>34.79</v>
+        <v>275.5</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>34.85</v>
+        <v>275.6</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>ITIETF</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -2784,22 +2784,22 @@
         </is>
       </c>
       <c r="D80" s="3" t="n">
-        <v>34.91</v>
+        <v>236.92</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>34.08</v>
+        <v>233.28</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>34.8</v>
+        <v>237.5</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>34.75</v>
+        <v>237.5</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>IVC</t>
+          <t>PANAMAPET</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -2813,22 +2813,22 @@
         </is>
       </c>
       <c r="D81" s="3" t="n">
-        <v>9.06</v>
+        <v>490.2</v>
       </c>
       <c r="E81" s="3" t="n">
-        <v>8.640000000000001</v>
+        <v>469.35</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>9.32</v>
+        <v>489.75</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>9.359999999999999</v>
+        <v>489.7</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>IVP</t>
+          <t>PAR</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -2842,22 +2842,22 @@
         </is>
       </c>
       <c r="D82" s="3" t="n">
-        <v>200.96</v>
+        <v>143.18</v>
       </c>
       <c r="E82" s="3" t="n">
-        <v>193.68</v>
+        <v>121.59</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>205.84</v>
+        <v>168.25</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>207.5</v>
+        <v>168.72</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>JAIBALAJI</t>
+          <t>PARSVNATH</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -2871,22 +2871,22 @@
         </is>
       </c>
       <c r="D83" s="3" t="n">
-        <v>72.56999999999999</v>
+        <v>1.49</v>
       </c>
       <c r="E83" s="3" t="n">
-        <v>69.02</v>
+        <v>1.49</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>70.44</v>
+        <v>1.51</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>71.09999999999999</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>JINDWORLD</t>
+          <t>PASUPTAC</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -2900,22 +2900,22 @@
         </is>
       </c>
       <c r="D84" s="3" t="n">
-        <v>40.85</v>
+        <v>63.65</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>38.15</v>
+        <v>60.85</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>42.08</v>
+        <v>64.64</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>41.98</v>
+        <v>64.8</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>JNPR</t>
+          <t>PATINTLOG</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -2929,22 +2929,22 @@
         </is>
       </c>
       <c r="D85" s="3" t="n">
-        <v>264.48</v>
+        <v>13.32</v>
       </c>
       <c r="E85" s="3" t="n">
-        <v>252.47</v>
+        <v>12.65</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>262.35</v>
+        <v>13.3</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>261</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>KALYANIFRG</t>
+          <t>PLAZACABLE</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -2958,22 +2958,22 @@
         </is>
       </c>
       <c r="D86" s="3" t="n">
-        <v>931.98</v>
+        <v>59.26</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>796.08</v>
+        <v>55.15</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>1083.9</v>
+        <v>61.8</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>1097.15</v>
+        <v>61.74</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>KAMDHENU</t>
+          <t>PRAENG</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -2987,22 +2987,22 @@
         </is>
       </c>
       <c r="D87" s="3" t="n">
-        <v>37.3</v>
+        <v>24.36</v>
       </c>
       <c r="E87" s="3" t="n">
-        <v>35.36</v>
+        <v>21.78</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>36.16</v>
+        <v>24.86</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>36</v>
+        <v>24.95</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>KANANIIND</t>
+          <t>PROZONER</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -3016,22 +3016,22 @@
         </is>
       </c>
       <c r="D88" s="3" t="n">
-        <v>1.57</v>
+        <v>46.25</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>1.47</v>
+        <v>43.97</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>1.56</v>
+        <v>46.49</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>1.55</v>
+        <v>46</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>KAPSTON</t>
+          <t>PTCIL</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -3045,22 +3045,22 @@
         </is>
       </c>
       <c r="D89" s="3" t="n">
-        <v>583.8</v>
+        <v>22906.67</v>
       </c>
       <c r="E89" s="3" t="n">
-        <v>541.48</v>
+        <v>21906.67</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>572.3</v>
+        <v>22715</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>579</v>
+        <v>22865</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>KARURVYSYA</t>
+          <t>RELIANCE</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -3074,22 +3074,22 @@
         </is>
       </c>
       <c r="D90" s="3" t="n">
-        <v>351.38</v>
+        <v>1310.43</v>
       </c>
       <c r="E90" s="3" t="n">
-        <v>344.62</v>
+        <v>1281.37</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>347.6</v>
+        <v>1313.1</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>347</v>
+        <v>1313.1</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>KCPSUGIND</t>
+          <t>REPL</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -3103,22 +3103,22 @@
         </is>
       </c>
       <c r="D91" s="3" t="n">
-        <v>33.33</v>
+        <v>67.2</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>31.41</v>
+        <v>61.98</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>32.25</v>
+        <v>64.3</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>32.8</v>
+        <v>64.3</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>LIQGRWBEES</t>
+          <t>RNBDENIMS</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -3132,22 +3132,22 @@
         </is>
       </c>
       <c r="D92" s="3" t="n">
-        <v>1053.79</v>
+        <v>10.84</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>1053.73</v>
+        <v>10.84</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>1053.9</v>
+        <v>11.37</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>1053.91</v>
+        <v>11.37</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDBETA</t>
+          <t>ROSSTECH</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -3161,22 +3161,22 @@
         </is>
       </c>
       <c r="D93" s="3" t="n">
-        <v>1006.2</v>
+        <v>1152.45</v>
       </c>
       <c r="E93" s="3" t="n">
-        <v>1006.18</v>
+        <v>1102.33</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>1006.46</v>
+        <v>1134</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>1006.46</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDBETF</t>
+          <t>RVHL</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -3190,22 +3190,22 @@
         </is>
       </c>
       <c r="D94" s="3" t="n">
-        <v>1096.89</v>
+        <v>40.52</v>
       </c>
       <c r="E94" s="3" t="n">
-        <v>1096.87</v>
+        <v>37.67</v>
       </c>
       <c r="F94" s="3" t="n">
-        <v>1097.02</v>
+        <v>39.28</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>1097.03</v>
+        <v>39</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDCASE</t>
+          <t>SABEVENTS</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -3219,22 +3219,22 @@
         </is>
       </c>
       <c r="D95" s="3" t="n">
-        <v>115.73</v>
+        <v>6.4</v>
       </c>
       <c r="E95" s="3" t="n">
-        <v>115.71</v>
+        <v>6.2</v>
       </c>
       <c r="F95" s="3" t="n">
-        <v>115.73</v>
+        <v>6.63</v>
       </c>
       <c r="G95" s="3" t="n">
-        <v>115.73</v>
+        <v>6.63</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDPLUS</t>
+          <t>SAHLIBHFI</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -3248,22 +3248,22 @@
         </is>
       </c>
       <c r="D96" s="3" t="n">
-        <v>1101.25</v>
+        <v>84.26000000000001</v>
       </c>
       <c r="E96" s="3" t="n">
-        <v>1101.14</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="F96" s="3" t="n">
-        <v>1101.37</v>
+        <v>86.36</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>1101.36</v>
+        <v>85.90000000000001</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDSHRI</t>
+          <t>SAILIFE</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -3277,22 +3277,22 @@
         </is>
       </c>
       <c r="D97" s="3" t="n">
-        <v>1119.58</v>
+        <v>1550.5</v>
       </c>
       <c r="E97" s="3" t="n">
-        <v>1119.56</v>
+        <v>1474.1</v>
       </c>
       <c r="F97" s="3" t="n">
-        <v>1119.72</v>
+        <v>1587</v>
       </c>
       <c r="G97" s="3" t="n">
-        <v>1119.72</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>LUMAXTECH</t>
+          <t>SAKAR</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -3306,22 +3306,22 @@
         </is>
       </c>
       <c r="D98" s="3" t="n">
-        <v>2081.53</v>
+        <v>968.8200000000001</v>
       </c>
       <c r="E98" s="3" t="n">
-        <v>1979.4</v>
+        <v>898.6</v>
       </c>
       <c r="F98" s="3" t="n">
-        <v>2060</v>
+        <v>985.8</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>2045.1</v>
+        <v>990</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>MAANALU</t>
+          <t>SASTASUNDR</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -3335,22 +3335,22 @@
         </is>
       </c>
       <c r="D99" s="3" t="n">
-        <v>124.63</v>
+        <v>283.13</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>117.68</v>
+        <v>269.72</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>119.42</v>
+        <v>282.6</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>119.71</v>
+        <v>284.65</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>MAFANG</t>
+          <t>SBILIQETF</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
@@ -3364,22 +3364,22 @@
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>209.55</v>
+        <v>1054.19</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>209.14</v>
+        <v>1054.17</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>211.05</v>
+        <v>1054.3</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>211</v>
+        <v>1054.32</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>MALLCOM</t>
+          <t>SFL</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
@@ -3393,22 +3393,22 @@
         </is>
       </c>
       <c r="D101" s="3" t="n">
-        <v>1021.65</v>
+        <v>651.8200000000001</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>969.4299999999999</v>
+        <v>631.53</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>1004.45</v>
+        <v>646.85</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>1030</v>
+        <v>645.45</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>MANALIPETC</t>
+          <t>SICAGEN</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
@@ -3422,22 +3422,22 @@
         </is>
       </c>
       <c r="D102" s="3" t="n">
-        <v>82.31</v>
+        <v>56.35</v>
       </c>
       <c r="E102" s="3" t="n">
-        <v>75.54000000000001</v>
+        <v>54.18</v>
       </c>
       <c r="F102" s="3" t="n">
-        <v>84.04000000000001</v>
+        <v>57.93</v>
       </c>
       <c r="G102" s="3" t="n">
-        <v>84.89</v>
+        <v>57.94</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>MANGLMCEM</t>
+          <t>SILVERETF</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
@@ -3451,22 +3451,22 @@
         </is>
       </c>
       <c r="D103" s="3" t="n">
-        <v>1100</v>
+        <v>201.81</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>1058.4</v>
+        <v>198.28</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>1084</v>
+        <v>203.98</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>1080.3</v>
+        <v>204</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>MANINFRA</t>
+          <t>SKFINDUS</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
@@ -3480,22 +3480,22 @@
         </is>
       </c>
       <c r="D104" s="3" t="n">
-        <v>124.6</v>
+        <v>3069.03</v>
       </c>
       <c r="E104" s="3" t="n">
-        <v>119.47</v>
+        <v>2906.4</v>
       </c>
       <c r="F104" s="3" t="n">
-        <v>124.56</v>
+        <v>3039.2</v>
       </c>
       <c r="G104" s="3" t="n">
-        <v>123.75</v>
+        <v>3020</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>MEDICAMEQ</t>
+          <t>SMLMAH</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
@@ -3509,22 +3509,22 @@
         </is>
       </c>
       <c r="D105" s="3" t="n">
-        <v>265</v>
+        <v>5447.67</v>
       </c>
       <c r="E105" s="3" t="n">
-        <v>241.68</v>
+        <v>5182.67</v>
       </c>
       <c r="F105" s="3" t="n">
-        <v>267.4</v>
+        <v>5318.5</v>
       </c>
       <c r="G105" s="3" t="n">
-        <v>266</v>
+        <v>5308</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>MODISONLTD</t>
+          <t>SOMATEX</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
@@ -3538,22 +3538,22 @@
         </is>
       </c>
       <c r="D106" s="3" t="n">
-        <v>456.4</v>
+        <v>84.45999999999999</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>425.92</v>
+        <v>82.67</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>499.45</v>
+        <v>88.34</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>499.45</v>
+        <v>88.34</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>MOTOGENFIN</t>
+          <t>SOTL</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
@@ -3567,22 +3567,22 @@
         </is>
       </c>
       <c r="D107" s="3" t="n">
-        <v>28.33</v>
+        <v>761.62</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>27.29</v>
+        <v>699.83</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>28.03</v>
+        <v>752.6</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>27.5</v>
+        <v>743</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>MTEDUCARE</t>
+          <t>SREEL</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
@@ -3596,22 +3596,22 @@
         </is>
       </c>
       <c r="D108" s="3" t="n">
-        <v>1.8</v>
+        <v>256.43</v>
       </c>
       <c r="E108" s="3" t="n">
-        <v>1.67</v>
+        <v>245.52</v>
       </c>
       <c r="F108" s="3" t="n">
-        <v>1.8</v>
+        <v>253.7</v>
       </c>
       <c r="G108" s="3" t="n">
-        <v>1.75</v>
+        <v>255.99</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>NATIONSTD</t>
+          <t>SUDEEPPHRM</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
@@ -3625,22 +3625,22 @@
         </is>
       </c>
       <c r="D109" s="3" t="n">
-        <v>108.95</v>
+        <v>1255.03</v>
       </c>
       <c r="E109" s="3" t="n">
-        <v>101.09</v>
+        <v>1187.25</v>
       </c>
       <c r="F109" s="3" t="n">
-        <v>105.31</v>
+        <v>1234</v>
       </c>
       <c r="G109" s="3" t="n">
-        <v>106.88</v>
+        <v>1239.6</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>NIFMID150</t>
+          <t>SUPERSPIN</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
@@ -3654,22 +3654,22 @@
         </is>
       </c>
       <c r="D110" s="3" t="n">
-        <v>224.68</v>
+        <v>6.66</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>222.19</v>
+        <v>6.27</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>224.96</v>
+        <v>6.51</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>225.54</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>NIRAJISPAT</t>
+          <t>TBZ</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
@@ -3683,22 +3683,22 @@
         </is>
       </c>
       <c r="D111" s="3" t="n">
-        <v>347.19</v>
+        <v>368.88</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>341.36</v>
+        <v>328.27</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>390.6</v>
+        <v>418.25</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>390.6</v>
+        <v>414</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>NIRLON</t>
+          <t>TCC</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
@@ -3712,22 +3712,22 @@
         </is>
       </c>
       <c r="D112" s="3" t="n">
-        <v>650.28</v>
+        <v>232.88</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>641.17</v>
+        <v>222.1</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>649.45</v>
+        <v>233.31</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>650</v>
+        <v>232.85</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>NITIRAJ</t>
+          <t>TECILCHEM</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
@@ -3741,22 +3741,22 @@
         </is>
       </c>
       <c r="D113" s="3" t="n">
-        <v>207.57</v>
+        <v>10.39</v>
       </c>
       <c r="E113" s="3" t="n">
-        <v>198.56</v>
+        <v>9.35</v>
       </c>
       <c r="F113" s="3" t="n">
-        <v>204.5</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="G113" s="3" t="n">
-        <v>204.5</v>
+        <v>9.85</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>NOIDATOLL</t>
+          <t>TIJARIA</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
@@ -3770,22 +3770,22 @@
         </is>
       </c>
       <c r="D114" s="3" t="n">
-        <v>4.35</v>
+        <v>7.24</v>
       </c>
       <c r="E114" s="3" t="n">
-        <v>4.12</v>
+        <v>6.13</v>
       </c>
       <c r="F114" s="3" t="n">
-        <v>4.23</v>
+        <v>7.58</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>4.25</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>NOVAAGRI</t>
+          <t>TNPETRO</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
@@ -3799,22 +3799,22 @@
         </is>
       </c>
       <c r="D115" s="3" t="n">
-        <v>25.52</v>
+        <v>133.77</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>23.9</v>
+        <v>121.48</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>24.22</v>
+        <v>133.73</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>24.2</v>
+        <v>135.5</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>NOVARTIND</t>
+          <t>TOP10ADD</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
@@ -3828,22 +3828,22 @@
         </is>
       </c>
       <c r="D116" s="3" t="n">
-        <v>1563.87</v>
+        <v>89.06999999999999</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>1497.6</v>
+        <v>87.02</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>1582.1</v>
+        <v>87.87</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>1595</v>
+        <v>87.98</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>NURECA</t>
+          <t>TPHQ</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
@@ -3857,22 +3857,22 @@
         </is>
       </c>
       <c r="D117" s="3" t="n">
-        <v>341.22</v>
+        <v>0.57</v>
       </c>
       <c r="E117" s="3" t="n">
-        <v>322.72</v>
+        <v>0.55</v>
       </c>
       <c r="F117" s="3" t="n">
-        <v>339</v>
+        <v>0.57</v>
       </c>
       <c r="G117" s="3" t="n">
-        <v>338.2</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>OILCOUNTUB</t>
+          <t>UDS</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
@@ -3886,22 +3886,22 @@
         </is>
       </c>
       <c r="D118" s="3" t="n">
-        <v>64.19</v>
+        <v>230.14</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>62.14</v>
+        <v>222.66</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>67.23</v>
+        <v>231.44</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>67.23</v>
+        <v>233.3</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>UFLEX</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
@@ -3915,22 +3915,22 @@
         </is>
       </c>
       <c r="D119" s="3" t="n">
-        <v>234.98</v>
+        <v>678.73</v>
       </c>
       <c r="E119" s="3" t="n">
-        <v>231.82</v>
+        <v>632.97</v>
       </c>
       <c r="F119" s="3" t="n">
-        <v>236.45</v>
+        <v>701.8</v>
       </c>
       <c r="G119" s="3" t="n">
-        <v>236.45</v>
+        <v>696.6</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>PAR</t>
+          <t>UNIDT</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
@@ -3944,22 +3944,22 @@
         </is>
       </c>
       <c r="D120" s="3" t="n">
-        <v>120.57</v>
+        <v>223.43</v>
       </c>
       <c r="E120" s="3" t="n">
-        <v>105.93</v>
+        <v>211.07</v>
       </c>
       <c r="F120" s="3" t="n">
-        <v>140.6</v>
+        <v>221.27</v>
       </c>
       <c r="G120" s="3" t="n">
-        <v>140.82</v>
+        <v>221.86</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>PARAGMILK</t>
+          <t>URAVIDEF</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
@@ -3973,22 +3973,22 @@
         </is>
       </c>
       <c r="D121" s="3" t="n">
-        <v>253.88</v>
+        <v>119.06</v>
       </c>
       <c r="E121" s="3" t="n">
-        <v>241.82</v>
+        <v>114.26</v>
       </c>
       <c r="F121" s="3" t="n">
-        <v>259.1</v>
+        <v>124.05</v>
       </c>
       <c r="G121" s="3" t="n">
-        <v>258.9</v>
+        <v>124</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>PARSVNATH</t>
+          <t>UTISENSETF</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
@@ -4002,22 +4002,22 @@
         </is>
       </c>
       <c r="D122" s="3" t="n">
-        <v>1.47</v>
+        <v>941.63</v>
       </c>
       <c r="E122" s="3" t="n">
-        <v>1.47</v>
+        <v>933.52</v>
       </c>
       <c r="F122" s="3" t="n">
-        <v>1.49</v>
+        <v>939.25</v>
       </c>
       <c r="G122" s="3" t="n">
-        <v>1.49</v>
+        <v>938.3200000000001</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>PENIND</t>
+          <t>VIJIFIN</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
@@ -4031,22 +4031,22 @@
         </is>
       </c>
       <c r="D123" s="3" t="n">
-        <v>167.47</v>
+        <v>15.64</v>
       </c>
       <c r="E123" s="3" t="n">
-        <v>161.54</v>
+        <v>15.64</v>
       </c>
       <c r="F123" s="3" t="n">
-        <v>165.66</v>
+        <v>15.95</v>
       </c>
       <c r="G123" s="3" t="n">
-        <v>165.89</v>
+        <v>15.95</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>PGHL</t>
+          <t>WAKEFIT</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
@@ -4060,22 +4060,22 @@
         </is>
       </c>
       <c r="D124" s="3" t="n">
-        <v>5791.67</v>
+        <v>153.87</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>5648.17</v>
+        <v>146.58</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>5776</v>
+        <v>152.47</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>5780</v>
+        <v>152.45</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>PLAZACABLE</t>
+          <t>WELCORP</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
@@ -4089,22 +4089,22 @@
         </is>
       </c>
       <c r="D125" s="3" t="n">
-        <v>56.59</v>
+        <v>2530.67</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>53.6</v>
+        <v>2407.67</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>58.92</v>
+        <v>2523.5</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>59.37</v>
+        <v>2524</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>PRAENG</t>
+          <t>WELENT</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
@@ -4118,1437 +4118,16 @@
         </is>
       </c>
       <c r="D126" s="3" t="n">
-        <v>22.53</v>
+        <v>717.83</v>
       </c>
       <c r="E126" s="3" t="n">
-        <v>20.24</v>
+        <v>679.3</v>
       </c>
       <c r="F126" s="3" t="n">
-        <v>24.44</v>
+        <v>741.7</v>
       </c>
       <c r="G126" s="3" t="n">
-        <v>24.34</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
-        <is>
-          <t>PROZONER</t>
-        </is>
-      </c>
-      <c r="B127" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C127" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D127" s="3" t="n">
-        <v>45.51</v>
-      </c>
-      <c r="E127" s="3" t="n">
-        <v>43.64</v>
-      </c>
-      <c r="F127" s="3" t="n">
-        <v>44.92</v>
-      </c>
-      <c r="G127" s="3" t="n">
-        <v>45.35</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
-        <is>
-          <t>PTCIL</t>
-        </is>
-      </c>
-      <c r="B128" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C128" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D128" s="3" t="n">
-        <v>22651.67</v>
-      </c>
-      <c r="E128" s="3" t="n">
-        <v>21335.67</v>
-      </c>
-      <c r="F128" s="3" t="n">
-        <v>22755</v>
-      </c>
-      <c r="G128" s="3" t="n">
-        <v>22665</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
-        <is>
-          <t>QMSMEDI</t>
-        </is>
-      </c>
-      <c r="B129" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C129" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D129" s="3" t="n">
-        <v>158.95</v>
-      </c>
-      <c r="E129" s="3" t="n">
-        <v>153.37</v>
-      </c>
-      <c r="F129" s="3" t="n">
-        <v>161.31</v>
-      </c>
-      <c r="G129" s="3" t="n">
-        <v>161.99</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
-        <is>
-          <t>RAYMOND</t>
-        </is>
-      </c>
-      <c r="B130" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C130" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D130" s="3" t="n">
-        <v>638.25</v>
-      </c>
-      <c r="E130" s="3" t="n">
-        <v>619.48</v>
-      </c>
-      <c r="F130" s="3" t="n">
-        <v>635.3</v>
-      </c>
-      <c r="G130" s="3" t="n">
-        <v>636.05</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
-        <is>
-          <t>RELIGARE</t>
-        </is>
-      </c>
-      <c r="B131" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C131" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D131" s="3" t="n">
-        <v>246</v>
-      </c>
-      <c r="E131" s="3" t="n">
-        <v>235.43</v>
-      </c>
-      <c r="F131" s="3" t="n">
-        <v>249.78</v>
-      </c>
-      <c r="G131" s="3" t="n">
-        <v>251.01</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
-        <is>
-          <t>REMSONSIND</t>
-        </is>
-      </c>
-      <c r="B132" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C132" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D132" s="3" t="n">
-        <v>97.45</v>
-      </c>
-      <c r="E132" s="3" t="n">
-        <v>87.2</v>
-      </c>
-      <c r="F132" s="3" t="n">
-        <v>97.44</v>
-      </c>
-      <c r="G132" s="3" t="n">
-        <v>97.98</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
-        <is>
-          <t>REPL</t>
-        </is>
-      </c>
-      <c r="B133" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C133" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D133" s="3" t="n">
-        <v>65.68000000000001</v>
-      </c>
-      <c r="E133" s="3" t="n">
-        <v>61.45</v>
-      </c>
-      <c r="F133" s="3" t="n">
-        <v>64.98999999999999</v>
-      </c>
-      <c r="G133" s="3" t="n">
-        <v>64.98999999999999</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
-        <is>
-          <t>RMDRIP</t>
-        </is>
-      </c>
-      <c r="B134" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C134" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D134" s="3" t="n">
-        <v>21.31</v>
-      </c>
-      <c r="E134" s="3" t="n">
-        <v>20.51</v>
-      </c>
-      <c r="F134" s="3" t="n">
-        <v>21.77</v>
-      </c>
-      <c r="G134" s="3" t="n">
-        <v>21.9</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
-        <is>
-          <t>RNBDENIMS</t>
-        </is>
-      </c>
-      <c r="B135" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C135" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D135" s="3" t="n">
-        <v>10.33</v>
-      </c>
-      <c r="E135" s="3" t="n">
-        <v>10.28</v>
-      </c>
-      <c r="F135" s="3" t="n">
-        <v>10.83</v>
-      </c>
-      <c r="G135" s="3" t="n">
-        <v>10.83</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
-        <is>
-          <t>ROML</t>
-        </is>
-      </c>
-      <c r="B136" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C136" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D136" s="3" t="n">
-        <v>43.59</v>
-      </c>
-      <c r="E136" s="3" t="n">
-        <v>41.88</v>
-      </c>
-      <c r="F136" s="3" t="n">
-        <v>43.15</v>
-      </c>
-      <c r="G136" s="3" t="n">
-        <v>43.15</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
-        <is>
-          <t>RSL</t>
-        </is>
-      </c>
-      <c r="B137" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C137" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D137" s="3" t="n">
-        <v>180.84</v>
-      </c>
-      <c r="E137" s="3" t="n">
-        <v>174.11</v>
-      </c>
-      <c r="F137" s="3" t="n">
-        <v>176.74</v>
-      </c>
-      <c r="G137" s="3" t="n">
-        <v>177.5</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
-        <is>
-          <t>SABEVENTS</t>
-        </is>
-      </c>
-      <c r="B138" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C138" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D138" s="3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="E138" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="F138" s="3" t="n">
-        <v>6.63</v>
-      </c>
-      <c r="G138" s="3" t="n">
-        <v>6.63</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
-        <is>
-          <t>SAHLIBHFI</t>
-        </is>
-      </c>
-      <c r="B139" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C139" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D139" s="3" t="n">
-        <v>81.06</v>
-      </c>
-      <c r="E139" s="3" t="n">
-        <v>73.98999999999999</v>
-      </c>
-      <c r="F139" s="3" t="n">
-        <v>75.58</v>
-      </c>
-      <c r="G139" s="3" t="n">
-        <v>83.40000000000001</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
-        <is>
-          <t>SALSTEEL</t>
-        </is>
-      </c>
-      <c r="B140" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C140" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D140" s="3" t="n">
-        <v>78.92</v>
-      </c>
-      <c r="E140" s="3" t="n">
-        <v>75.87</v>
-      </c>
-      <c r="F140" s="3" t="n">
-        <v>82.43000000000001</v>
-      </c>
-      <c r="G140" s="3" t="n">
-        <v>82.06</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
-        <is>
-          <t>SANGINITA</t>
-        </is>
-      </c>
-      <c r="B141" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C141" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D141" s="3" t="n">
-        <v>56.01</v>
-      </c>
-      <c r="E141" s="3" t="n">
-        <v>55.17</v>
-      </c>
-      <c r="F141" s="3" t="n">
-        <v>58.76</v>
-      </c>
-      <c r="G141" s="3" t="n">
-        <v>58.76</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
-        <is>
-          <t>SASTASUNDR</t>
-        </is>
-      </c>
-      <c r="B142" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C142" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D142" s="3" t="n">
-        <v>283.13</v>
-      </c>
-      <c r="E142" s="3" t="n">
-        <v>269.72</v>
-      </c>
-      <c r="F142" s="3" t="n">
-        <v>282.6</v>
-      </c>
-      <c r="G142" s="3" t="n">
-        <v>284.65</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
-        <is>
-          <t>SBILIQETF</t>
-        </is>
-      </c>
-      <c r="B143" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C143" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D143" s="3" t="n">
-        <v>1054.06</v>
-      </c>
-      <c r="E143" s="3" t="n">
-        <v>1054.04</v>
-      </c>
-      <c r="F143" s="3" t="n">
-        <v>1054.18</v>
-      </c>
-      <c r="G143" s="3" t="n">
-        <v>1054.17</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
-        <is>
-          <t>SETCO</t>
-        </is>
-      </c>
-      <c r="B144" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C144" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D144" s="3" t="n">
-        <v>18.39</v>
-      </c>
-      <c r="E144" s="3" t="n">
-        <v>17.26</v>
-      </c>
-      <c r="F144" s="3" t="n">
-        <v>17.67</v>
-      </c>
-      <c r="G144" s="3" t="n">
-        <v>17.9</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
-        <is>
-          <t>SETL</t>
-        </is>
-      </c>
-      <c r="B145" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C145" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D145" s="3" t="n">
-        <v>378.18</v>
-      </c>
-      <c r="E145" s="3" t="n">
-        <v>361.85</v>
-      </c>
-      <c r="F145" s="3" t="n">
-        <v>387.05</v>
-      </c>
-      <c r="G145" s="3" t="n">
-        <v>387.95</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
-        <is>
-          <t>SHADOWFAX</t>
-        </is>
-      </c>
-      <c r="B146" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C146" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D146" s="3" t="n">
-        <v>256</v>
-      </c>
-      <c r="E146" s="3" t="n">
-        <v>245.84</v>
-      </c>
-      <c r="F146" s="3" t="n">
-        <v>257.2</v>
-      </c>
-      <c r="G146" s="3" t="n">
-        <v>257.55</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
-        <is>
-          <t>SHIVALIK</t>
-        </is>
-      </c>
-      <c r="B147" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C147" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D147" s="3" t="n">
-        <v>322.45</v>
-      </c>
-      <c r="E147" s="3" t="n">
-        <v>305.53</v>
-      </c>
-      <c r="F147" s="3" t="n">
-        <v>338.05</v>
-      </c>
-      <c r="G147" s="3" t="n">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
-        <is>
-          <t>SHREYANIND</t>
-        </is>
-      </c>
-      <c r="B148" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C148" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D148" s="3" t="n">
-        <v>126.5</v>
-      </c>
-      <c r="E148" s="3" t="n">
-        <v>123.38</v>
-      </c>
-      <c r="F148" s="3" t="n">
-        <v>125.8</v>
-      </c>
-      <c r="G148" s="3" t="n">
-        <v>125.3</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
-        <is>
-          <t>SHRIPISTON</t>
-        </is>
-      </c>
-      <c r="B149" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C149" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D149" s="3" t="n">
-        <v>4628.23</v>
-      </c>
-      <c r="E149" s="3" t="n">
-        <v>4484.6</v>
-      </c>
-      <c r="F149" s="3" t="n">
-        <v>4598.2</v>
-      </c>
-      <c r="G149" s="3" t="n">
-        <v>4600</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
-        <is>
-          <t>SILVERETF</t>
-        </is>
-      </c>
-      <c r="B150" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C150" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D150" s="3" t="n">
-        <v>201.81</v>
-      </c>
-      <c r="E150" s="3" t="n">
-        <v>198.28</v>
-      </c>
-      <c r="F150" s="3" t="n">
-        <v>203.98</v>
-      </c>
-      <c r="G150" s="3" t="n">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
-        <is>
-          <t>SINCLAIR</t>
-        </is>
-      </c>
-      <c r="B151" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C151" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D151" s="3" t="n">
-        <v>84.04000000000001</v>
-      </c>
-      <c r="E151" s="3" t="n">
-        <v>79.41</v>
-      </c>
-      <c r="F151" s="3" t="n">
-        <v>82.91</v>
-      </c>
-      <c r="G151" s="3" t="n">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
-        <is>
-          <t>SMCGLOBAL</t>
-        </is>
-      </c>
-      <c r="B152" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C152" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D152" s="3" t="n">
-        <v>80.81999999999999</v>
-      </c>
-      <c r="E152" s="3" t="n">
-        <v>78.47</v>
-      </c>
-      <c r="F152" s="3" t="n">
-        <v>79.65000000000001</v>
-      </c>
-      <c r="G152" s="3" t="n">
-        <v>79.90000000000001</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
-        <is>
-          <t>SOLARA</t>
-        </is>
-      </c>
-      <c r="B153" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C153" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D153" s="3" t="n">
-        <v>650.28</v>
-      </c>
-      <c r="E153" s="3" t="n">
-        <v>617.72</v>
-      </c>
-      <c r="F153" s="3" t="n">
-        <v>643.45</v>
-      </c>
-      <c r="G153" s="3" t="n">
-        <v>640.75</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
-        <is>
-          <t>SRHHYPOLTD</t>
-        </is>
-      </c>
-      <c r="B154" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C154" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D154" s="3" t="n">
-        <v>497.27</v>
-      </c>
-      <c r="E154" s="3" t="n">
-        <v>477.63</v>
-      </c>
-      <c r="F154" s="3" t="n">
-        <v>494.45</v>
-      </c>
-      <c r="G154" s="3" t="n">
-        <v>494.1</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
-        <is>
-          <t>SSWL</t>
-        </is>
-      </c>
-      <c r="B155" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C155" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D155" s="3" t="n">
-        <v>323.62</v>
-      </c>
-      <c r="E155" s="3" t="n">
-        <v>294.78</v>
-      </c>
-      <c r="F155" s="3" t="n">
-        <v>357.25</v>
-      </c>
-      <c r="G155" s="3" t="n">
-        <v>351.3</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
-        <is>
-          <t>SUDEEPPHRM</t>
-        </is>
-      </c>
-      <c r="B156" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C156" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D156" s="3" t="n">
-        <v>1214.78</v>
-      </c>
-      <c r="E156" s="3" t="n">
-        <v>1148.85</v>
-      </c>
-      <c r="F156" s="3" t="n">
-        <v>1230.9</v>
-      </c>
-      <c r="G156" s="3" t="n">
-        <v>1239.8</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
-        <is>
-          <t>SUPERSPIN</t>
-        </is>
-      </c>
-      <c r="B157" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C157" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D157" s="3" t="n">
-        <v>6.42</v>
-      </c>
-      <c r="E157" s="3" t="n">
-        <v>6.12</v>
-      </c>
-      <c r="F157" s="3" t="n">
-        <v>6.52</v>
-      </c>
-      <c r="G157" s="3" t="n">
-        <v>6.39</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
-        <is>
-          <t>SURYALAXMI</t>
-        </is>
-      </c>
-      <c r="B158" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C158" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D158" s="3" t="n">
-        <v>62.29</v>
-      </c>
-      <c r="E158" s="3" t="n">
-        <v>58.1</v>
-      </c>
-      <c r="F158" s="3" t="n">
-        <v>62.92</v>
-      </c>
-      <c r="G158" s="3" t="n">
-        <v>62.95</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="2" t="inlineStr">
-        <is>
-          <t>SUVEN</t>
-        </is>
-      </c>
-      <c r="B159" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C159" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D159" s="3" t="n">
-        <v>388.88</v>
-      </c>
-      <c r="E159" s="3" t="n">
-        <v>367.72</v>
-      </c>
-      <c r="F159" s="3" t="n">
-        <v>381.6</v>
-      </c>
-      <c r="G159" s="3" t="n">
-        <v>381.85</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="2" t="inlineStr">
-        <is>
-          <t>TATACOMM</t>
-        </is>
-      </c>
-      <c r="B160" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C160" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D160" s="3" t="n">
-        <v>1727.3</v>
-      </c>
-      <c r="E160" s="3" t="n">
-        <v>1692</v>
-      </c>
-      <c r="F160" s="3" t="n">
-        <v>1733.8</v>
-      </c>
-      <c r="G160" s="3" t="n">
-        <v>1737</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="2" t="inlineStr">
-        <is>
-          <t>TECH</t>
-        </is>
-      </c>
-      <c r="B161" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C161" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D161" s="3" t="n">
-        <v>34.37</v>
-      </c>
-      <c r="E161" s="3" t="n">
-        <v>33.5</v>
-      </c>
-      <c r="F161" s="3" t="n">
-        <v>34.24</v>
-      </c>
-      <c r="G161" s="3" t="n">
-        <v>34.24</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="2" t="inlineStr">
-        <is>
-          <t>TNPETRO</t>
-        </is>
-      </c>
-      <c r="B162" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C162" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D162" s="3" t="n">
-        <v>125.23</v>
-      </c>
-      <c r="E162" s="3" t="n">
-        <v>113.77</v>
-      </c>
-      <c r="F162" s="3" t="n">
-        <v>132.35</v>
-      </c>
-      <c r="G162" s="3" t="n">
-        <v>133.1</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="2" t="inlineStr">
-        <is>
-          <t>TRANSPEK</t>
-        </is>
-      </c>
-      <c r="B163" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C163" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D163" s="3" t="n">
-        <v>1430.83</v>
-      </c>
-      <c r="E163" s="3" t="n">
-        <v>1364.13</v>
-      </c>
-      <c r="F163" s="3" t="n">
-        <v>1422.8</v>
-      </c>
-      <c r="G163" s="3" t="n">
-        <v>1421</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="2" t="inlineStr">
-        <is>
-          <t>TVSSRICHAK</t>
-        </is>
-      </c>
-      <c r="B164" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C164" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D164" s="3" t="n">
-        <v>5553.27</v>
-      </c>
-      <c r="E164" s="3" t="n">
-        <v>5277.3</v>
-      </c>
-      <c r="F164" s="3" t="n">
-        <v>5525.5</v>
-      </c>
-      <c r="G164" s="3" t="n">
-        <v>5521</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="2" t="inlineStr">
-        <is>
-          <t>UDS</t>
-        </is>
-      </c>
-      <c r="B165" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C165" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D165" s="3" t="n">
-        <v>227.24</v>
-      </c>
-      <c r="E165" s="3" t="n">
-        <v>221.49</v>
-      </c>
-      <c r="F165" s="3" t="n">
-        <v>227.12</v>
-      </c>
-      <c r="G165" s="3" t="n">
-        <v>224.5</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="2" t="inlineStr">
-        <is>
-          <t>UNIPARTS</t>
-        </is>
-      </c>
-      <c r="B166" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C166" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D166" s="3" t="n">
-        <v>898.52</v>
-      </c>
-      <c r="E166" s="3" t="n">
-        <v>849.73</v>
-      </c>
-      <c r="F166" s="3" t="n">
-        <v>901.15</v>
-      </c>
-      <c r="G166" s="3" t="n">
-        <v>904.5</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="2" t="inlineStr">
-        <is>
-          <t>URAVIDEF</t>
-        </is>
-      </c>
-      <c r="B167" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C167" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D167" s="3" t="n">
-        <v>113.72</v>
-      </c>
-      <c r="E167" s="3" t="n">
-        <v>108.91</v>
-      </c>
-      <c r="F167" s="3" t="n">
-        <v>118.97</v>
-      </c>
-      <c r="G167" s="3" t="n">
-        <v>118.97</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="2" t="inlineStr">
-        <is>
-          <t>UTISENSETF</t>
-        </is>
-      </c>
-      <c r="B168" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C168" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D168" s="3" t="n">
-        <v>941.63</v>
-      </c>
-      <c r="E168" s="3" t="n">
-        <v>933.52</v>
-      </c>
-      <c r="F168" s="3" t="n">
-        <v>939.25</v>
-      </c>
-      <c r="G168" s="3" t="n">
-        <v>938.3200000000001</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="2" t="inlineStr">
-        <is>
-          <t>UTKARSHBNK</t>
-        </is>
-      </c>
-      <c r="B169" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C169" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D169" s="3" t="n">
-        <v>15.07</v>
-      </c>
-      <c r="E169" s="3" t="n">
-        <v>14.59</v>
-      </c>
-      <c r="F169" s="3" t="n">
-        <v>14.88</v>
-      </c>
-      <c r="G169" s="3" t="n">
-        <v>14.88</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="2" t="inlineStr">
-        <is>
-          <t>VARROC</t>
-        </is>
-      </c>
-      <c r="B170" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C170" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D170" s="3" t="n">
-        <v>864.97</v>
-      </c>
-      <c r="E170" s="3" t="n">
-        <v>821.27</v>
-      </c>
-      <c r="F170" s="3" t="n">
-        <v>877</v>
-      </c>
-      <c r="G170" s="3" t="n">
-        <v>870</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" s="2" t="inlineStr">
-        <is>
-          <t>VHL</t>
-        </is>
-      </c>
-      <c r="B171" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C171" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D171" s="3" t="n">
-        <v>3603.37</v>
-      </c>
-      <c r="E171" s="3" t="n">
-        <v>3418.03</v>
-      </c>
-      <c r="F171" s="3" t="n">
-        <v>3568.4</v>
-      </c>
-      <c r="G171" s="3" t="n">
-        <v>3598</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" s="2" t="inlineStr">
-        <is>
-          <t>VIJIFIN</t>
-        </is>
-      </c>
-      <c r="B172" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C172" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D172" s="3" t="n">
-        <v>15.34</v>
-      </c>
-      <c r="E172" s="3" t="n">
-        <v>15.34</v>
-      </c>
-      <c r="F172" s="3" t="n">
-        <v>15.64</v>
-      </c>
-      <c r="G172" s="3" t="n">
-        <v>15.64</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" s="2" t="inlineStr">
-        <is>
-          <t>VIPIND</t>
-        </is>
-      </c>
-      <c r="B173" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C173" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D173" s="3" t="n">
-        <v>309.92</v>
-      </c>
-      <c r="E173" s="3" t="n">
-        <v>300.92</v>
-      </c>
-      <c r="F173" s="3" t="n">
-        <v>303.75</v>
-      </c>
-      <c r="G173" s="3" t="n">
-        <v>304.9</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" s="2" t="inlineStr">
-        <is>
-          <t>WELENT</t>
-        </is>
-      </c>
-      <c r="B174" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C174" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D174" s="3" t="n">
-        <v>698.08</v>
-      </c>
-      <c r="E174" s="3" t="n">
-        <v>667.12</v>
-      </c>
-      <c r="F174" s="3" t="n">
-        <v>705.55</v>
-      </c>
-      <c r="G174" s="3" t="n">
-        <v>712</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" s="2" t="inlineStr">
-        <is>
-          <t>WSTCSTPAPR</t>
-        </is>
-      </c>
-      <c r="B175" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C175" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D175" s="3" t="n">
-        <v>636.45</v>
-      </c>
-      <c r="E175" s="3" t="n">
-        <v>608.53</v>
-      </c>
-      <c r="F175" s="3" t="n">
-        <v>653.6</v>
-      </c>
-      <c r="G175" s="3" t="n">
-        <v>651.5</v>
+        <v>744</v>
       </c>
     </row>
   </sheetData>

--- a/data/uptrend_output.xlsx
+++ b/data/uptrend_output.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G126"/>
+  <dimension ref="A1:G187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -508,7 +508,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>3BBLACKBIO</t>
+          <t>63MOONS</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -522,22 +522,22 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1548.57</v>
+        <v>819.9299999999999</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1450.07</v>
+        <v>781.58</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1478.6</v>
+        <v>851.25</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>1478.9</v>
+        <v>848</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>AARTIPHARM</t>
+          <t>AAREYDRUGS</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -551,22 +551,22 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>873.05</v>
+        <v>93.87</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>841.5</v>
+        <v>89.77</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>867.25</v>
+        <v>94.44</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>864.45</v>
+        <v>94.79000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>AKI</t>
+          <t>AARTECH</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -580,22 +580,22 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>4.82</v>
+        <v>50.18</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>4.23</v>
+        <v>47.88</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>5.48</v>
+        <v>49.16</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>5.48</v>
+        <v>49.74</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>ALKALI</t>
+          <t>AARTISURF</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -609,22 +609,22 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>68.28</v>
+        <v>538.23</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>64.83</v>
+        <v>502.27</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>68.86</v>
+        <v>544.25</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>68.84999999999999</v>
+        <v>545</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>AMIRCHAND</t>
+          <t>ABMINTLLTD</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -638,22 +638,22 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>181.7</v>
+        <v>56.17</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>171.51</v>
+        <v>55.37</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>185.11</v>
+        <v>57</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>184.5</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>ANTHEM</t>
+          <t>ADANIGREEN</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -667,22 +667,22 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>933</v>
+        <v>1294.83</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>898.95</v>
+        <v>1244</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>934.5</v>
+        <v>1283.4</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>938</v>
+        <v>1283.4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>AONELIQUID</t>
+          <t>ADANIPORTS</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -696,22 +696,22 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1075.05</v>
+        <v>1681.03</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1075.03</v>
+        <v>1646.3</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1075.16</v>
+        <v>1706.5</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>1075.18</v>
+        <v>1706.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>ARROWGREEN</t>
+          <t>AEGISVOPAK</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -725,22 +725,22 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>738.95</v>
+        <v>286.33</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>705.53</v>
+        <v>270.05</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>771.2</v>
+        <v>286.85</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>771.2</v>
+        <v>286.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>ARVINDFASN</t>
+          <t>AEPL</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -754,22 +754,22 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>460.65</v>
+        <v>16.51</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>444.97</v>
+        <v>15</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>461.15</v>
+        <v>17.09</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>460.1</v>
+        <v>17.2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>ASIANENE</t>
+          <t>AEROPLANE</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -783,22 +783,22 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>497.55</v>
+        <v>182.84</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>472.45</v>
+        <v>173.9</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>504.1</v>
+        <v>188.07</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>505</v>
+        <v>188</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ASTAR</t>
+          <t>AKI</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -812,22 +812,22 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>596.65</v>
+        <v>5.6</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>584.03</v>
+        <v>5.11</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>590</v>
+        <v>6.57</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>590</v>
+        <v>6.57</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>AUSOMENT</t>
+          <t>ALPHAGEO</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -841,22 +841,22 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>152.98</v>
+        <v>302.88</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>146.58</v>
+        <v>287.85</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>156.45</v>
+        <v>315</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>155</v>
+        <v>315</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>AVL</t>
+          <t>AMBICAAGAR</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -870,22 +870,22 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>605.85</v>
+        <v>25.99</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>589.53</v>
+        <v>24.26</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>599.85</v>
+        <v>26.33</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>598.1</v>
+        <v>27.49</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>AXISBNKETF</t>
+          <t>AMIRCHAND</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -899,22 +899,22 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>599.1900000000001</v>
+        <v>181.7</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>593.95</v>
+        <v>171.51</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>597.15</v>
+        <v>185.11</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>597.09</v>
+        <v>184.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>AXISCADES</t>
+          <t>ANTELOPUS</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -928,22 +928,22 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1695.2</v>
+        <v>941.75</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1616.27</v>
+        <v>850.85</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1689.7</v>
+        <v>1013.3</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>1690</v>
+        <v>990.6</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>AXISCETF</t>
+          <t>ANTHEM</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -957,22 +957,22 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>120.57</v>
+        <v>948.9299999999999</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>118.88</v>
+        <v>913.62</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>121.12</v>
+        <v>950.7</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>120.8</v>
+        <v>950</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>AYMSYNTEX</t>
+          <t>AONELIQUID</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -986,22 +986,22 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>306.8</v>
+        <v>1075.18</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>269.45</v>
+        <v>1075.16</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>312.5</v>
+        <v>1075.29</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>312</v>
+        <v>1075.29</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>BALAXI</t>
+          <t>APTUS</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1015,22 +1015,22 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>23.71</v>
+        <v>256.96</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>22.27</v>
+        <v>249.98</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>25.01</v>
+        <v>257.31</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>25.04</v>
+        <v>256.98</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>BEPL</t>
+          <t>ARCHIDPLY</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1044,22 +1044,22 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>126.95</v>
+        <v>106.95</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>122.08</v>
+        <v>102.26</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>127.29</v>
+        <v>105.99</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>127.5</v>
+        <v>106</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>BFINVEST</t>
+          <t>ARFIN</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>449.9</v>
+        <v>88.7</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>436.03</v>
+        <v>85.84999999999999</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>452.95</v>
+        <v>89.09</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>454.5</v>
+        <v>89.17</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>BIRLACABLE</t>
+          <t>ARROWGREEN</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -1102,22 +1102,22 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>325.6</v>
+        <v>768.25</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>312.02</v>
+        <v>735.77</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>341.6</v>
+        <v>777.4</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>341.6</v>
+        <v>777</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>BLISSGVS</t>
+          <t>ASIANENE</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -1131,22 +1131,22 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>637.17</v>
+        <v>512.35</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>599</v>
+        <v>483.4</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>648.65</v>
+        <v>523</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>649.9</v>
+        <v>522.9</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>BOROSCI</t>
+          <t>AUSOMENT</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1160,22 +1160,22 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>129.98</v>
+        <v>156.98</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>123.96</v>
+        <v>149.09</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>131.31</v>
+        <v>159.95</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>131.1</v>
+        <v>160</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>CALSOFT</t>
+          <t>AVL</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -1189,22 +1189,22 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>39.16</v>
+        <v>610.9299999999999</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>37.74</v>
+        <v>594.02</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>41.08</v>
+        <v>600.4</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>41.08</v>
+        <v>599.55</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>CENTENKA</t>
+          <t>AXISBNKETF</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -1218,22 +1218,22 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>576.1799999999999</v>
+        <v>599.1900000000001</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>547.5</v>
+        <v>593.95</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>602.35</v>
+        <v>597.15</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>619</v>
+        <v>597.09</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>CMSINFO</t>
+          <t>AXISCADES</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -1247,22 +1247,22 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>250.56</v>
+        <v>1716.93</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>242.09</v>
+        <v>1639.57</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>249.3</v>
+        <v>1730.4</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>249</v>
+        <v>1727.2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>COMSYN</t>
+          <t>AXISCETF</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1276,22 +1276,22 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>308.58</v>
+        <v>120.57</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>288.08</v>
+        <v>118.88</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>302.65</v>
+        <v>121.12</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>298.75</v>
+        <v>120.8</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>CORDSCABLE</t>
+          <t>AYMSYNTEX</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -1305,22 +1305,22 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>315.07</v>
+        <v>316.9</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>279.99</v>
+        <v>289.27</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>315.5</v>
+        <v>317.25</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>314.8</v>
+        <v>317.9</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>CPPLUS</t>
+          <t>BALAXI</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -1334,22 +1334,22 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>3710.2</v>
+        <v>25.04</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>3538.83</v>
+        <v>23.07</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>3721.4</v>
+        <v>25.8</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>3712</v>
+        <v>25.42</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>CROWN</t>
+          <t>BANSWRAS</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -1363,22 +1363,22 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>110.8</v>
+        <v>120.06</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>103.84</v>
+        <v>115.02</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>108.27</v>
+        <v>117.78</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>108.2</v>
+        <v>117.17</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>CYBERMEDIA</t>
+          <t>BEML</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -1392,22 +1392,22 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>19.74</v>
+        <v>2038.93</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>18.07</v>
+        <v>1972.23</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>19.9</v>
+        <v>2079.4</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>20</v>
+        <v>2066.1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>DBSTOCKBRO</t>
+          <t>BEPL</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -1421,22 +1421,22 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>30.69</v>
+        <v>129.83</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>28.91</v>
+        <v>124.84</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>30.3</v>
+        <v>129.74</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>30.5</v>
+        <v>129.6</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>DCMSHRIRAM</t>
+          <t>BESTAGRO</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -1450,22 +1450,22 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>1042.1</v>
+        <v>18.97</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>1012.87</v>
+        <v>18.22</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>1028</v>
+        <v>20.34</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>1028</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>DEEDEV</t>
+          <t>BFINVEST</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -1479,22 +1479,22 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>625.52</v>
+        <v>463.58</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>591.67</v>
+        <v>442.65</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>643.85</v>
+        <v>469.45</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>643</v>
+        <v>472.6</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>DRAGARWQ</t>
+          <t>BIRLACABLE</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -1508,22 +1508,22 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>5369.83</v>
+        <v>341.87</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>5253.67</v>
+        <v>330.42</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>5420</v>
+        <v>358.65</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>5440</v>
+        <v>358.65</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>DSKULKARNI</t>
+          <t>BLISSGVS</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -1537,22 +1537,22 @@
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>18.67</v>
+        <v>653</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>18.67</v>
+        <v>617.33</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>19.04</v>
+        <v>639.35</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>19.04</v>
+        <v>637</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>ELIQUID</t>
+          <t>BLUESTONE</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -1566,22 +1566,22 @@
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>1047.7</v>
+        <v>821</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>1045.99</v>
+        <v>793.12</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>1046.13</v>
+        <v>804.9</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>1046.12</v>
+        <v>802</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>GANGAFORGE</t>
+          <t>BLUSPRING</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -1595,22 +1595,22 @@
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>1.77</v>
+        <v>133.06</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>1.68</v>
+        <v>123.48</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>1.85</v>
+        <v>134.25</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>1.85</v>
+        <v>134.4</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>GCSL</t>
+          <t>BOROSCI</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -1624,22 +1624,22 @@
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>567.37</v>
+        <v>134.02</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>549.67</v>
+        <v>127.13</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>571.85</v>
+        <v>134.93</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>569</v>
+        <v>137.99</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>GEEKAYWIRE</t>
+          <t>CALSOFT</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -1653,22 +1653,22 @@
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>30.17</v>
+        <v>41.11</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>26.26</v>
+        <v>39.91</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>27.86</v>
+        <v>43.13</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>28.2</v>
+        <v>43.13</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>GHCLTEXTIL</t>
+          <t>CAPTRUST</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -1682,22 +1682,22 @@
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>141.86</v>
+        <v>19.81</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>134.67</v>
+        <v>18.75</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>139.35</v>
+        <v>19.76</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>139.94</v>
+        <v>19.99</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>GILLETTE</t>
+          <t>CENTENKA</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -1711,22 +1711,22 @@
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>7415.83</v>
+        <v>604.75</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>7269.67</v>
+        <v>570.3200000000001</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>7346</v>
+        <v>616.65</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>7353</v>
+        <v>612</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>GKSL</t>
+          <t>CENTRUM</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -1740,22 +1740,22 @@
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>168.3</v>
+        <v>23.23</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>158.27</v>
+        <v>22.05</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>168.3</v>
+        <v>22.45</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>168.05</v>
+        <v>22.4</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>GLOBAL</t>
+          <t>CENTUM</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -1769,22 +1769,22 @@
         </is>
       </c>
       <c r="D45" s="3" t="n">
-        <v>113.43</v>
+        <v>3629.6</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>106.58</v>
+        <v>3476.07</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>117.31</v>
+        <v>3776.1</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>118.5</v>
+        <v>3770.9</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>GROWWLIQID</t>
+          <t>CGCL</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -1798,22 +1798,22 @@
         </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>110.59</v>
+        <v>263.25</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>110.57</v>
+        <v>248.53</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>110.59</v>
+        <v>271.7</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>110.6</v>
+        <v>272.1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>GUFICBIO</t>
+          <t>CHAMBLFERT</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -1827,22 +1827,22 @@
         </is>
       </c>
       <c r="D47" s="3" t="n">
-        <v>434.73</v>
+        <v>417.37</v>
       </c>
       <c r="E47" s="3" t="n">
         <v>408.38</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>438.8</v>
+        <v>418.3</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>440</v>
+        <v>419</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>GUJENERGY</t>
+          <t>CLEANMAX</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -1856,22 +1856,22 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>259.03</v>
+        <v>1294.33</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>249.57</v>
+        <v>1234.17</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>262.29</v>
+        <v>1298.7</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>262.22</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>GYFTR</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -1885,22 +1885,22 @@
         </is>
       </c>
       <c r="D49" s="3" t="n">
-        <v>184.56</v>
+        <v>419.37</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>169.67</v>
+        <v>407.57</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>183</v>
+        <v>420.05</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>182.6</v>
+        <v>420.05</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>HARSHA</t>
+          <t>CONFIPET</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -1914,22 +1914,22 @@
         </is>
       </c>
       <c r="D50" s="3" t="n">
-        <v>460</v>
+        <v>84.86</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>441.1</v>
+        <v>79.81999999999999</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>450.75</v>
+        <v>84.28</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>448.5</v>
+        <v>83.98999999999999</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>HITECHCORP</t>
+          <t>CROWN</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -1943,22 +1943,22 @@
         </is>
       </c>
       <c r="D51" s="3" t="n">
-        <v>338.3</v>
+        <v>112.47</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>332.25</v>
+        <v>106.85</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>336.55</v>
+        <v>111.8</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>338</v>
+        <v>111.95</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>HPAL</t>
+          <t>CYBERMEDIA</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -1972,22 +1972,22 @@
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>35.47</v>
+        <v>21.31</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>34.22</v>
+        <v>19</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>35.01</v>
+        <v>23.88</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>35.2</v>
+        <v>23.88</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>INFIBEAM</t>
+          <t>DANGEE</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -2001,22 +2001,22 @@
         </is>
       </c>
       <c r="D53" s="3" t="n">
-        <v>16.54</v>
+        <v>3</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>15.65</v>
+        <v>2.68</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>16.9</v>
+        <v>2.94</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>16.84</v>
+        <v>2.93</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>ITADD</t>
+          <t>DATAPATTNS</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -2030,22 +2030,22 @@
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>33.41</v>
+        <v>4576.87</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>32.58</v>
+        <v>4466.67</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>32.9</v>
+        <v>4587.3</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>32.74</v>
+        <v>4595</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>DEEDEV</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -2059,22 +2059,22 @@
         </is>
       </c>
       <c r="D55" s="3" t="n">
-        <v>267.92</v>
+        <v>643.08</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>259.93</v>
+        <v>610.03</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>266.3</v>
+        <v>645.9</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>266.3</v>
+        <v>643.8</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>IVP</t>
+          <t>DHANUKA</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -2088,22 +2088,22 @@
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>206.96</v>
+        <v>1003.6</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>199.08</v>
+        <v>973.53</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>209.8</v>
+        <v>1010.15</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>209.75</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>JAYKAY</t>
+          <t>DHUNINV</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -2117,22 +2117,22 @@
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>164.16</v>
+        <v>1024.17</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>150.99</v>
+        <v>990.7</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>169.4</v>
+        <v>1046.25</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>169</v>
+        <v>1048.5</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>JSL</t>
+          <t>DMCC</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -2146,22 +2146,22 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>731.65</v>
+        <v>297.72</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>704.15</v>
+        <v>286.98</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>734.9</v>
+        <v>295.5</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>735</v>
+        <v>295.5</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>KALYANIFRG</t>
+          <t>DRAGARWQ</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -2175,22 +2175,22 @@
         </is>
       </c>
       <c r="D59" s="3" t="n">
-        <v>1067.9</v>
+        <v>5436.83</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>897.25</v>
+        <v>5272.83</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>1113.65</v>
+        <v>5339</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>1176.6</v>
+        <v>5305.5</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>KANANIIND</t>
+          <t>DSKULKARNI</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -2204,22 +2204,22 @@
         </is>
       </c>
       <c r="D60" s="3" t="n">
-        <v>1.59</v>
+        <v>19.04</v>
       </c>
       <c r="E60" s="3" t="n">
-        <v>1.5</v>
+        <v>19.04</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>1.53</v>
+        <v>19.42</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>1.54</v>
+        <v>19.42</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>KHAITANLTD</t>
+          <t>ECLERX</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -2233,22 +2233,22 @@
         </is>
       </c>
       <c r="D61" s="3" t="n">
-        <v>153</v>
+        <v>2022.6</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>139.05</v>
+        <v>1917.37</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>160.8</v>
+        <v>1971.7</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>165</v>
+        <v>1969</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>KIRLOSENG</t>
+          <t>EIMCOELECO</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -2262,22 +2262,22 @@
         </is>
       </c>
       <c r="D62" s="3" t="n">
-        <v>2148.33</v>
+        <v>2260.27</v>
       </c>
       <c r="E62" s="3" t="n">
-        <v>2075.33</v>
+        <v>2172.4</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>2160.9</v>
+        <v>2280.4</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>2172</v>
+        <v>2279</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>KRONOX</t>
+          <t>ELANTAS</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -2291,22 +2291,22 @@
         </is>
       </c>
       <c r="D63" s="3" t="n">
-        <v>185.28</v>
+        <v>12071.33</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>172.24</v>
+        <v>11481.33</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>189.68</v>
+        <v>12114</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>189.98</v>
+        <v>12171</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>KRYSTAL</t>
+          <t>EPACKPEB</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -2320,22 +2320,22 @@
         </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>667.1799999999999</v>
+        <v>228.92</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>628.4299999999999</v>
+        <v>221.13</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>667</v>
+        <v>227.3</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>668.75</v>
+        <v>226.99</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>LAHOTIOV</t>
+          <t>FERMENTA</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -2349,22 +2349,22 @@
         </is>
       </c>
       <c r="D65" s="3" t="n">
-        <v>42.27</v>
+        <v>525.8200000000001</v>
       </c>
       <c r="E65" s="3" t="n">
-        <v>40.39</v>
+        <v>484.33</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>41.98</v>
+        <v>502.3</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>41.99</v>
+        <v>500</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDADD</t>
+          <t>FOODSIN</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -2378,22 +2378,22 @@
         </is>
       </c>
       <c r="D66" s="3" t="n">
-        <v>1142.87</v>
+        <v>55.75</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>1142.83</v>
+        <v>53.4</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>1142.98</v>
+        <v>56.06</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>1143</v>
+        <v>56</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDBETA</t>
+          <t>GALAPREC</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -2407,22 +2407,22 @@
         </is>
       </c>
       <c r="D67" s="3" t="n">
-        <v>1006.47</v>
+        <v>1049.1</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>1006.45</v>
+        <v>1007.37</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>1006.57</v>
+        <v>1026.2</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>1006.57</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDBETF</t>
+          <t>GCSL</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -2436,22 +2436,22 @@
         </is>
       </c>
       <c r="D68" s="3" t="n">
-        <v>1097.03</v>
+        <v>577.3200000000001</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>1097</v>
+        <v>560.83</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>1097.15</v>
+        <v>586.7</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>1097.15</v>
+        <v>590.3</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDCASE</t>
+          <t>GFLLIMITED</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -2465,22 +2465,22 @@
         </is>
       </c>
       <c r="D69" s="3" t="n">
-        <v>115.74</v>
+        <v>59.05</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>115.72</v>
+        <v>55.44</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>115.74</v>
+        <v>58.65</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>115.74</v>
+        <v>58.6</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDPLUS</t>
+          <t>GIPCL</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -2494,22 +2494,22 @@
         </is>
       </c>
       <c r="D70" s="3" t="n">
-        <v>1101.38</v>
+        <v>207.05</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>1101.27</v>
+        <v>199.6</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>1101.5</v>
+        <v>208.04</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>1101.51</v>
+        <v>207.51</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDSHRI</t>
+          <t>GKSL</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -2523,22 +2523,22 @@
         </is>
       </c>
       <c r="D71" s="3" t="n">
-        <v>1119.72</v>
+        <v>172.05</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>1119.7</v>
+        <v>162.46</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>1119.83</v>
+        <v>171.51</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>1119.83</v>
+        <v>171.99</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>MALLCOM</t>
+          <t>GKWLIMITED</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -2552,22 +2552,22 @@
         </is>
       </c>
       <c r="D72" s="3" t="n">
-        <v>1033.33</v>
+        <v>1591.6</v>
       </c>
       <c r="E72" s="3" t="n">
-        <v>974.23</v>
+        <v>1525.2</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>1021.15</v>
+        <v>1600</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>1020</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>MARINE</t>
+          <t>GLOBAL</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -2581,22 +2581,22 @@
         </is>
       </c>
       <c r="D73" s="3" t="n">
-        <v>425.83</v>
+        <v>118.09</v>
       </c>
       <c r="E73" s="3" t="n">
-        <v>401.1</v>
+        <v>110.07</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>431.5</v>
+        <v>116.27</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>433.3</v>
+        <v>115.4</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>MMFL</t>
+          <t>GODAVARIB</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -2610,22 +2610,22 @@
         </is>
       </c>
       <c r="D74" s="3" t="n">
-        <v>665.75</v>
+        <v>241.97</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>634.8200000000001</v>
+        <v>233.3</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>648.05</v>
+        <v>245.25</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>654</v>
+        <v>247.76</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>MODISONLTD</t>
+          <t>GRADIENTE</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -2639,22 +2639,22 @@
         </is>
       </c>
       <c r="D75" s="3" t="n">
-        <v>499.83</v>
+        <v>2.67</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>464.62</v>
+        <v>2.62</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>520.65</v>
+        <v>2.67</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>521</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>MOOILGAS</t>
+          <t>GROWWLIQID</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -2668,22 +2668,22 @@
         </is>
       </c>
       <c r="D76" s="3" t="n">
-        <v>11.36</v>
+        <v>110.6</v>
       </c>
       <c r="E76" s="3" t="n">
-        <v>11.05</v>
+        <v>110.59</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>11.18</v>
+        <v>110.6</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>11.18</v>
+        <v>110.61</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>NIFMID150</t>
+          <t>GUJENERGY</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -2697,22 +2697,22 @@
         </is>
       </c>
       <c r="D77" s="3" t="n">
-        <v>224.68</v>
+        <v>262.43</v>
       </c>
       <c r="E77" s="3" t="n">
-        <v>222.19</v>
+        <v>255.22</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>224.96</v>
+        <v>264.1</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>225.54</v>
+        <v>264.11</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>NIRAJISPAT</t>
+          <t>GYFTR</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -2726,22 +2726,22 @@
         </is>
       </c>
       <c r="D78" s="3" t="n">
-        <v>391.78</v>
+        <v>190.36</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>391.03</v>
+        <v>173.57</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>429.65</v>
+        <v>180.23</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>429.65</v>
+        <v>180</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>NLCINDIA</t>
+          <t>HALDYNGL</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -2755,22 +2755,22 @@
         </is>
       </c>
       <c r="D79" s="3" t="n">
-        <v>275.72</v>
+        <v>144</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>268.35</v>
+        <v>138</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>275.5</v>
+        <v>144.65</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>275.6</v>
+        <v>144.13</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>HOMEFIRST</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -2784,22 +2784,22 @@
         </is>
       </c>
       <c r="D80" s="3" t="n">
-        <v>236.92</v>
+        <v>1201.97</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>233.28</v>
+        <v>1164.57</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>237.5</v>
+        <v>1201.4</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>237.5</v>
+        <v>1208.8</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>PANAMAPET</t>
+          <t>ICDSLTD</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -2813,22 +2813,22 @@
         </is>
       </c>
       <c r="D81" s="3" t="n">
-        <v>490.2</v>
+        <v>57.75</v>
       </c>
       <c r="E81" s="3" t="n">
-        <v>469.35</v>
+        <v>51.37</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>489.75</v>
+        <v>64.95999999999999</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>489.7</v>
+        <v>64.95999999999999</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>PAR</t>
+          <t>IFCI</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -2842,22 +2842,22 @@
         </is>
       </c>
       <c r="D82" s="3" t="n">
-        <v>143.18</v>
+        <v>97.11</v>
       </c>
       <c r="E82" s="3" t="n">
-        <v>121.59</v>
+        <v>89.25</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>168.25</v>
+        <v>95.91</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>168.72</v>
+        <v>95.7</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>PARSVNATH</t>
+          <t>INDIQUBE</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -2871,22 +2871,22 @@
         </is>
       </c>
       <c r="D83" s="3" t="n">
-        <v>1.49</v>
+        <v>195.42</v>
       </c>
       <c r="E83" s="3" t="n">
-        <v>1.49</v>
+        <v>187.88</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>1.51</v>
+        <v>193.09</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>1.51</v>
+        <v>193.01</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>PASUPTAC</t>
+          <t>INFIBEAM</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -2900,22 +2900,22 @@
         </is>
       </c>
       <c r="D84" s="3" t="n">
-        <v>63.65</v>
+        <v>16.54</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>60.85</v>
+        <v>15.65</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>64.64</v>
+        <v>16.9</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>64.8</v>
+        <v>16.84</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>PATINTLOG</t>
+          <t>INNOVACAP</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -2929,22 +2929,22 @@
         </is>
       </c>
       <c r="D85" s="3" t="n">
-        <v>13.32</v>
+        <v>1134.57</v>
       </c>
       <c r="E85" s="3" t="n">
-        <v>12.65</v>
+        <v>1070.7</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>13.3</v>
+        <v>1125.4</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>13.4</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>PLAZACABLE</t>
+          <t>IONEXCHANG</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -2958,22 +2958,22 @@
         </is>
       </c>
       <c r="D86" s="3" t="n">
-        <v>59.26</v>
+        <v>383.77</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>55.15</v>
+        <v>367.92</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>61.8</v>
+        <v>382.2</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>61.74</v>
+        <v>384.6</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>PRAENG</t>
+          <t>IRB</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -2987,22 +2987,22 @@
         </is>
       </c>
       <c r="D87" s="3" t="n">
-        <v>24.36</v>
+        <v>19.74</v>
       </c>
       <c r="E87" s="3" t="n">
-        <v>21.78</v>
+        <v>19.13</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>24.86</v>
+        <v>19.67</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>24.95</v>
+        <v>19.73</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>PROZONER</t>
+          <t>JAYKAY</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -3016,22 +3016,22 @@
         </is>
       </c>
       <c r="D88" s="3" t="n">
-        <v>46.25</v>
+        <v>169.69</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>43.97</v>
+        <v>156.64</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>46.49</v>
+        <v>166.46</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>46</v>
+        <v>165.1</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>PTCIL</t>
+          <t>JBMA</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -3045,22 +3045,22 @@
         </is>
       </c>
       <c r="D89" s="3" t="n">
-        <v>22906.67</v>
+        <v>634.45</v>
       </c>
       <c r="E89" s="3" t="n">
-        <v>21906.67</v>
+        <v>614.1</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>22715</v>
+        <v>629.1</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>22865</v>
+        <v>626.5</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>RELIANCE</t>
+          <t>JINDRILL</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -3074,22 +3074,22 @@
         </is>
       </c>
       <c r="D90" s="3" t="n">
-        <v>1310.43</v>
+        <v>645.42</v>
       </c>
       <c r="E90" s="3" t="n">
-        <v>1281.37</v>
+        <v>618.83</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>1313.1</v>
+        <v>649.9</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>1313.1</v>
+        <v>651</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>REPL</t>
+          <t>JUNIPER</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -3103,22 +3103,22 @@
         </is>
       </c>
       <c r="D91" s="3" t="n">
-        <v>67.2</v>
+        <v>220.03</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>61.98</v>
+        <v>213.03</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>64.3</v>
+        <v>217.69</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>64.3</v>
+        <v>218</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>RNBDENIMS</t>
+          <t>KEEPLEARN</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -3132,22 +3132,22 @@
         </is>
       </c>
       <c r="D92" s="3" t="n">
-        <v>10.84</v>
+        <v>1.97</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>10.84</v>
+        <v>1.82</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>11.37</v>
+        <v>1.9</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>11.37</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>ROSSTECH</t>
+          <t>KERNEX</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -3161,22 +3161,22 @@
         </is>
       </c>
       <c r="D93" s="3" t="n">
-        <v>1152.45</v>
+        <v>1747.67</v>
       </c>
       <c r="E93" s="3" t="n">
-        <v>1102.33</v>
+        <v>1636.23</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>1134</v>
+        <v>1709.6</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>1134</v>
+        <v>1702.5</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>RVHL</t>
+          <t>KHAITANLTD</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -3190,22 +3190,22 @@
         </is>
       </c>
       <c r="D94" s="3" t="n">
-        <v>40.52</v>
+        <v>164.67</v>
       </c>
       <c r="E94" s="3" t="n">
-        <v>37.67</v>
+        <v>146.45</v>
       </c>
       <c r="F94" s="3" t="n">
-        <v>39.28</v>
+        <v>162.41</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>39</v>
+        <v>165</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>SABEVENTS</t>
+          <t>KIRLOSENG</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -3219,22 +3219,22 @@
         </is>
       </c>
       <c r="D95" s="3" t="n">
-        <v>6.4</v>
+        <v>2204.67</v>
       </c>
       <c r="E95" s="3" t="n">
-        <v>6.2</v>
+        <v>2094.7</v>
       </c>
       <c r="F95" s="3" t="n">
-        <v>6.63</v>
+        <v>2267.6</v>
       </c>
       <c r="G95" s="3" t="n">
-        <v>6.63</v>
+        <v>2260.4</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>SAHLIBHFI</t>
+          <t>KIRLPNU</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -3248,22 +3248,22 @@
         </is>
       </c>
       <c r="D96" s="3" t="n">
-        <v>84.26000000000001</v>
+        <v>753.28</v>
       </c>
       <c r="E96" s="3" t="n">
-        <v>76.59999999999999</v>
+        <v>725.42</v>
       </c>
       <c r="F96" s="3" t="n">
-        <v>86.36</v>
+        <v>759.8</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>85.90000000000001</v>
+        <v>760</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>SAILIFE</t>
+          <t>KRBL</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -3277,22 +3277,22 @@
         </is>
       </c>
       <c r="D97" s="3" t="n">
-        <v>1550.5</v>
+        <v>429.08</v>
       </c>
       <c r="E97" s="3" t="n">
-        <v>1474.1</v>
+        <v>419.58</v>
       </c>
       <c r="F97" s="3" t="n">
-        <v>1587</v>
+        <v>424.9</v>
       </c>
       <c r="G97" s="3" t="n">
-        <v>1580</v>
+        <v>424.95</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>SAKAR</t>
+          <t>KRONOX</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -3306,22 +3306,22 @@
         </is>
       </c>
       <c r="D98" s="3" t="n">
-        <v>968.8200000000001</v>
+        <v>189.35</v>
       </c>
       <c r="E98" s="3" t="n">
-        <v>898.6</v>
+        <v>176.04</v>
       </c>
       <c r="F98" s="3" t="n">
-        <v>985.8</v>
+        <v>183.37</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>990</v>
+        <v>184.01</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>SASTASUNDR</t>
+          <t>LAHOTIOV</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -3335,22 +3335,22 @@
         </is>
       </c>
       <c r="D99" s="3" t="n">
-        <v>283.13</v>
+        <v>43.98</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>269.72</v>
+        <v>40.69</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>282.6</v>
+        <v>45.08</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>284.65</v>
+        <v>44.5</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>SBILIQETF</t>
+          <t>LENSKART</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
@@ -3364,22 +3364,22 @@
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>1054.19</v>
+        <v>677.02</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>1054.17</v>
+        <v>658.92</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>1054.3</v>
+        <v>672.45</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>1054.32</v>
+        <v>671.9</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>SFL</t>
+          <t>LIQUIDADD</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
@@ -3393,22 +3393,22 @@
         </is>
       </c>
       <c r="D101" s="3" t="n">
-        <v>651.8200000000001</v>
+        <v>1143.01</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>631.53</v>
+        <v>1142.98</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>646.85</v>
+        <v>1143.13</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>645.45</v>
+        <v>1143.14</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>SICAGEN</t>
+          <t>LIQUIDBETA</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
@@ -3422,22 +3422,22 @@
         </is>
       </c>
       <c r="D102" s="3" t="n">
-        <v>56.35</v>
+        <v>1006.59</v>
       </c>
       <c r="E102" s="3" t="n">
-        <v>54.18</v>
+        <v>1006.57</v>
       </c>
       <c r="F102" s="3" t="n">
-        <v>57.93</v>
+        <v>1006.7</v>
       </c>
       <c r="G102" s="3" t="n">
-        <v>57.94</v>
+        <v>1006.7</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>SILVERETF</t>
+          <t>LIQUIDBETF</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
@@ -3451,22 +3451,22 @@
         </is>
       </c>
       <c r="D103" s="3" t="n">
-        <v>201.81</v>
+        <v>1097.16</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>198.28</v>
+        <v>1097.13</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>203.98</v>
+        <v>1097.27</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>204</v>
+        <v>1097.27</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>SKFINDUS</t>
+          <t>LIQUIDCASE</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
@@ -3480,22 +3480,22 @@
         </is>
       </c>
       <c r="D104" s="3" t="n">
-        <v>3069.03</v>
+        <v>115.75</v>
       </c>
       <c r="E104" s="3" t="n">
-        <v>2906.4</v>
+        <v>115.73</v>
       </c>
       <c r="F104" s="3" t="n">
-        <v>3039.2</v>
+        <v>115.76</v>
       </c>
       <c r="G104" s="3" t="n">
-        <v>3020</v>
+        <v>115.77</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>SMLMAH</t>
+          <t>LIQUIDPLUS</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
@@ -3509,22 +3509,22 @@
         </is>
       </c>
       <c r="D105" s="3" t="n">
-        <v>5447.67</v>
+        <v>1101.51</v>
       </c>
       <c r="E105" s="3" t="n">
-        <v>5182.67</v>
+        <v>1101.44</v>
       </c>
       <c r="F105" s="3" t="n">
-        <v>5318.5</v>
+        <v>1101.63</v>
       </c>
       <c r="G105" s="3" t="n">
-        <v>5308</v>
+        <v>1101.62</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>SOMATEX</t>
+          <t>LIQUIDSHRI</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
@@ -3538,22 +3538,22 @@
         </is>
       </c>
       <c r="D106" s="3" t="n">
-        <v>84.45999999999999</v>
+        <v>1119.85</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>82.67</v>
+        <v>1119.83</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>88.34</v>
+        <v>1119.96</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>88.34</v>
+        <v>1119.97</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>SOTL</t>
+          <t>MAHSEAMLES</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
@@ -3567,22 +3567,22 @@
         </is>
       </c>
       <c r="D107" s="3" t="n">
-        <v>761.62</v>
+        <v>673.58</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>699.83</v>
+        <v>646.25</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>752.6</v>
+        <v>653.5</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>743</v>
+        <v>650.15</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>SREEL</t>
+          <t>MANAKSTEEL</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
@@ -3596,22 +3596,22 @@
         </is>
       </c>
       <c r="D108" s="3" t="n">
-        <v>256.43</v>
+        <v>109.52</v>
       </c>
       <c r="E108" s="3" t="n">
-        <v>245.52</v>
+        <v>101.61</v>
       </c>
       <c r="F108" s="3" t="n">
-        <v>253.7</v>
+        <v>111.91</v>
       </c>
       <c r="G108" s="3" t="n">
-        <v>255.99</v>
+        <v>110</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>SUDEEPPHRM</t>
+          <t>MARATHON</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
@@ -3625,22 +3625,22 @@
         </is>
       </c>
       <c r="D109" s="3" t="n">
-        <v>1255.03</v>
+        <v>443.77</v>
       </c>
       <c r="E109" s="3" t="n">
-        <v>1187.25</v>
+        <v>420.05</v>
       </c>
       <c r="F109" s="3" t="n">
-        <v>1234</v>
+        <v>434.95</v>
       </c>
       <c r="G109" s="3" t="n">
-        <v>1239.6</v>
+        <v>432.5</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>SUPERSPIN</t>
+          <t>MARINE</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
@@ -3654,22 +3654,22 @@
         </is>
       </c>
       <c r="D110" s="3" t="n">
-        <v>6.66</v>
+        <v>440.33</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>6.27</v>
+        <v>416.08</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>6.51</v>
+        <v>430.4</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>6.5</v>
+        <v>429.5</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>TBZ</t>
+          <t>MARKSANS</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
@@ -3683,22 +3683,22 @@
         </is>
       </c>
       <c r="D111" s="3" t="n">
-        <v>368.88</v>
+        <v>334.45</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>328.27</v>
+        <v>321.75</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>418.25</v>
+        <v>332.2</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>414</v>
+        <v>332.55</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>TCC</t>
+          <t>MAWANASUG</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
@@ -3712,22 +3712,22 @@
         </is>
       </c>
       <c r="D112" s="3" t="n">
-        <v>232.88</v>
+        <v>153.05</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>222.1</v>
+        <v>142.82</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>233.31</v>
+        <v>146.27</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>232.85</v>
+        <v>146.5</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>TECILCHEM</t>
+          <t>MEESHO</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
@@ -3741,22 +3741,22 @@
         </is>
       </c>
       <c r="D113" s="3" t="n">
-        <v>10.39</v>
+        <v>212.96</v>
       </c>
       <c r="E113" s="3" t="n">
-        <v>9.35</v>
+        <v>204.4</v>
       </c>
       <c r="F113" s="3" t="n">
-        <v>9.890000000000001</v>
+        <v>209.74</v>
       </c>
       <c r="G113" s="3" t="n">
-        <v>9.85</v>
+        <v>209.7</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>TIJARIA</t>
+          <t>MERCANTILE</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
@@ -3770,22 +3770,22 @@
         </is>
       </c>
       <c r="D114" s="3" t="n">
-        <v>7.24</v>
+        <v>27.47</v>
       </c>
       <c r="E114" s="3" t="n">
-        <v>6.13</v>
+        <v>23.5</v>
       </c>
       <c r="F114" s="3" t="n">
-        <v>7.58</v>
+        <v>25.55</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>7.69</v>
+        <v>25.06</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>TNPETRO</t>
+          <t>MOLDTECH</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
@@ -3799,22 +3799,22 @@
         </is>
       </c>
       <c r="D115" s="3" t="n">
-        <v>133.77</v>
+        <v>204.1</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>121.48</v>
+        <v>192.73</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>133.73</v>
+        <v>207.31</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>135.5</v>
+        <v>210</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>TOP10ADD</t>
+          <t>MONTECARLO</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
@@ -3828,22 +3828,22 @@
         </is>
       </c>
       <c r="D116" s="3" t="n">
-        <v>89.06999999999999</v>
+        <v>553.7</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>87.02</v>
+        <v>536.33</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>87.87</v>
+        <v>564.45</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>87.98</v>
+        <v>563.5</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>TPHQ</t>
+          <t>MOREPENLAB</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
@@ -3857,22 +3857,22 @@
         </is>
       </c>
       <c r="D117" s="3" t="n">
-        <v>0.57</v>
+        <v>114.35</v>
       </c>
       <c r="E117" s="3" t="n">
-        <v>0.55</v>
+        <v>104.42</v>
       </c>
       <c r="F117" s="3" t="n">
-        <v>0.57</v>
+        <v>117.45</v>
       </c>
       <c r="G117" s="3" t="n">
-        <v>0.58</v>
+        <v>117.4</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>UDS</t>
+          <t>MSPL</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
@@ -3886,22 +3886,22 @@
         </is>
       </c>
       <c r="D118" s="3" t="n">
-        <v>230.14</v>
+        <v>36.51</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>222.66</v>
+        <v>34.44</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>231.44</v>
+        <v>35.34</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>233.3</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>UFLEX</t>
+          <t>MWL</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
@@ -3915,22 +3915,22 @@
         </is>
       </c>
       <c r="D119" s="3" t="n">
-        <v>678.73</v>
+        <v>39.3</v>
       </c>
       <c r="E119" s="3" t="n">
-        <v>632.97</v>
+        <v>37.34</v>
       </c>
       <c r="F119" s="3" t="n">
-        <v>701.8</v>
+        <v>39.08</v>
       </c>
       <c r="G119" s="3" t="n">
-        <v>696.6</v>
+        <v>39.25</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>UNIDT</t>
+          <t>NATCAPSUQ</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
@@ -3944,22 +3944,22 @@
         </is>
       </c>
       <c r="D120" s="3" t="n">
-        <v>223.43</v>
+        <v>220.92</v>
       </c>
       <c r="E120" s="3" t="n">
-        <v>211.07</v>
+        <v>201.7</v>
       </c>
       <c r="F120" s="3" t="n">
-        <v>221.27</v>
+        <v>226.98</v>
       </c>
       <c r="G120" s="3" t="n">
-        <v>221.86</v>
+        <v>226.98</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>URAVIDEF</t>
+          <t>NCLIND</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
@@ -3973,22 +3973,22 @@
         </is>
       </c>
       <c r="D121" s="3" t="n">
-        <v>119.06</v>
+        <v>176.63</v>
       </c>
       <c r="E121" s="3" t="n">
-        <v>114.26</v>
+        <v>173.15</v>
       </c>
       <c r="F121" s="3" t="n">
-        <v>124.05</v>
+        <v>177.36</v>
       </c>
       <c r="G121" s="3" t="n">
-        <v>124</v>
+        <v>176.75</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>UTISENSETF</t>
+          <t>NIFMID150</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
@@ -4002,22 +4002,22 @@
         </is>
       </c>
       <c r="D122" s="3" t="n">
-        <v>941.63</v>
+        <v>224.68</v>
       </c>
       <c r="E122" s="3" t="n">
-        <v>933.52</v>
+        <v>222.19</v>
       </c>
       <c r="F122" s="3" t="n">
-        <v>939.25</v>
+        <v>224.96</v>
       </c>
       <c r="G122" s="3" t="n">
-        <v>938.3200000000001</v>
+        <v>225.54</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>VIJIFIN</t>
+          <t>NLCINDIA</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
@@ -4031,22 +4031,22 @@
         </is>
       </c>
       <c r="D123" s="3" t="n">
-        <v>15.64</v>
+        <v>278.75</v>
       </c>
       <c r="E123" s="3" t="n">
-        <v>15.64</v>
+        <v>270.87</v>
       </c>
       <c r="F123" s="3" t="n">
-        <v>15.95</v>
+        <v>274.9</v>
       </c>
       <c r="G123" s="3" t="n">
-        <v>15.95</v>
+        <v>275.5</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>WAKEFIT</t>
+          <t>NUVOCO</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
@@ -4060,22 +4060,22 @@
         </is>
       </c>
       <c r="D124" s="3" t="n">
-        <v>153.87</v>
+        <v>332.22</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>146.58</v>
+        <v>318.53</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>152.47</v>
+        <v>338.1</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>152.45</v>
+        <v>337.5</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>WELCORP</t>
+          <t>ONESOURCE</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
@@ -4089,45 +4089,1814 @@
         </is>
       </c>
       <c r="D125" s="3" t="n">
-        <v>2530.67</v>
+        <v>1565.2</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>2407.67</v>
+        <v>1519.7</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>2523.5</v>
+        <v>1575.7</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>2524</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
+          <t>PAISALO</t>
+        </is>
+      </c>
+      <c r="B126" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C126" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D126" s="3" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="E126" s="3" t="n">
+        <v>65.72</v>
+      </c>
+      <c r="F126" s="3" t="n">
+        <v>70.28</v>
+      </c>
+      <c r="G126" s="3" t="n">
+        <v>70.8</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>PAR</t>
+        </is>
+      </c>
+      <c r="B127" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C127" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D127" s="3" t="n">
+        <v>163.18</v>
+      </c>
+      <c r="E127" s="3" t="n">
+        <v>139.87</v>
+      </c>
+      <c r="F127" s="3" t="n">
+        <v>164.95</v>
+      </c>
+      <c r="G127" s="3" t="n">
+        <v>163.3</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>PARSVNATH</t>
+        </is>
+      </c>
+      <c r="B128" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C128" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D128" s="3" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="E128" s="3" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="F128" s="3" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="G128" s="3" t="n">
+        <v>1.54</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>PASUPTAC</t>
+        </is>
+      </c>
+      <c r="B129" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C129" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D129" s="3" t="n">
+        <v>65.17</v>
+      </c>
+      <c r="E129" s="3" t="n">
+        <v>62.19</v>
+      </c>
+      <c r="F129" s="3" t="n">
+        <v>66.79000000000001</v>
+      </c>
+      <c r="G129" s="3" t="n">
+        <v>66.8</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>PATINTLOG</t>
+        </is>
+      </c>
+      <c r="B130" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C130" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D130" s="3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="E130" s="3" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="F130" s="3" t="n">
+        <v>13.41</v>
+      </c>
+      <c r="G130" s="3" t="n">
+        <v>13.54</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>PHOENIXLTD</t>
+        </is>
+      </c>
+      <c r="B131" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C131" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D131" s="3" t="n">
+        <v>1929.2</v>
+      </c>
+      <c r="E131" s="3" t="n">
+        <v>1886.3</v>
+      </c>
+      <c r="F131" s="3" t="n">
+        <v>1960</v>
+      </c>
+      <c r="G131" s="3" t="n">
+        <v>1960</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>PLAZACABLE</t>
+        </is>
+      </c>
+      <c r="B132" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C132" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D132" s="3" t="n">
+        <v>61.91</v>
+      </c>
+      <c r="E132" s="3" t="n">
+        <v>57.18</v>
+      </c>
+      <c r="F132" s="3" t="n">
+        <v>62.62</v>
+      </c>
+      <c r="G132" s="3" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>POWERGRID</t>
+        </is>
+      </c>
+      <c r="B133" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C133" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D133" s="3" t="n">
+        <v>267.88</v>
+      </c>
+      <c r="E133" s="3" t="n">
+        <v>263.23</v>
+      </c>
+      <c r="F133" s="3" t="n">
+        <v>265.6</v>
+      </c>
+      <c r="G133" s="3" t="n">
+        <v>265.6</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>PRABHA</t>
+        </is>
+      </c>
+      <c r="B134" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C134" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D134" s="3" t="n">
+        <v>222.87</v>
+      </c>
+      <c r="E134" s="3" t="n">
+        <v>208.23</v>
+      </c>
+      <c r="F134" s="3" t="n">
+        <v>220.97</v>
+      </c>
+      <c r="G134" s="3" t="n">
+        <v>220.5</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>PRAENG</t>
+        </is>
+      </c>
+      <c r="B135" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C135" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D135" s="3" t="n">
+        <v>26.02</v>
+      </c>
+      <c r="E135" s="3" t="n">
+        <v>23.45</v>
+      </c>
+      <c r="F135" s="3" t="n">
+        <v>25.75</v>
+      </c>
+      <c r="G135" s="3" t="n">
+        <v>25.84</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>PROZONER</t>
+        </is>
+      </c>
+      <c r="B136" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C136" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D136" s="3" t="n">
+        <v>47.08</v>
+      </c>
+      <c r="E136" s="3" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="F136" s="3" t="n">
+        <v>46.42</v>
+      </c>
+      <c r="G136" s="3" t="n">
+        <v>46.89</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>PTCIL</t>
+        </is>
+      </c>
+      <c r="B137" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C137" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D137" s="3" t="n">
+        <v>23308.33</v>
+      </c>
+      <c r="E137" s="3" t="n">
+        <v>22240</v>
+      </c>
+      <c r="F137" s="3" t="n">
+        <v>23820</v>
+      </c>
+      <c r="G137" s="3" t="n">
+        <v>23635</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>RAJESHEXPO</t>
+        </is>
+      </c>
+      <c r="B138" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C138" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D138" s="3" t="n">
+        <v>79.98</v>
+      </c>
+      <c r="E138" s="3" t="n">
+        <v>77.43000000000001</v>
+      </c>
+      <c r="F138" s="3" t="n">
+        <v>83.45999999999999</v>
+      </c>
+      <c r="G138" s="3" t="n">
+        <v>83.45999999999999</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>RHETAN</t>
+        </is>
+      </c>
+      <c r="B139" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C139" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D139" s="3" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="E139" s="3" t="n">
+        <v>21.08</v>
+      </c>
+      <c r="F139" s="3" t="n">
+        <v>23.11</v>
+      </c>
+      <c r="G139" s="3" t="n">
+        <v>23.12</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>RKSWAMY</t>
+        </is>
+      </c>
+      <c r="B140" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C140" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D140" s="3" t="n">
+        <v>93.47</v>
+      </c>
+      <c r="E140" s="3" t="n">
+        <v>90.56</v>
+      </c>
+      <c r="F140" s="3" t="n">
+        <v>92</v>
+      </c>
+      <c r="G140" s="3" t="n">
+        <v>91.20999999999999</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>RUBYMILLS</t>
+        </is>
+      </c>
+      <c r="B141" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C141" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D141" s="3" t="n">
+        <v>403.33</v>
+      </c>
+      <c r="E141" s="3" t="n">
+        <v>380.7</v>
+      </c>
+      <c r="F141" s="3" t="n">
+        <v>409.05</v>
+      </c>
+      <c r="G141" s="3" t="n">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>SABEVENTS</t>
+        </is>
+      </c>
+      <c r="B142" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C142" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D142" s="3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="E142" s="3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="F142" s="3" t="n">
+        <v>6.63</v>
+      </c>
+      <c r="G142" s="3" t="n">
+        <v>6.63</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>SAHLIBHFI</t>
+        </is>
+      </c>
+      <c r="B143" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C143" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D143" s="3" t="n">
+        <v>88.28</v>
+      </c>
+      <c r="E143" s="3" t="n">
+        <v>79.67</v>
+      </c>
+      <c r="F143" s="3" t="n">
+        <v>89.12</v>
+      </c>
+      <c r="G143" s="3" t="n">
+        <v>90.98999999999999</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>SAILIFE</t>
+        </is>
+      </c>
+      <c r="B144" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C144" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D144" s="3" t="n">
+        <v>1595</v>
+      </c>
+      <c r="E144" s="3" t="n">
+        <v>1509.67</v>
+      </c>
+      <c r="F144" s="3" t="n">
+        <v>1574.8</v>
+      </c>
+      <c r="G144" s="3" t="n">
+        <v>1579</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>SASTASUNDR</t>
+        </is>
+      </c>
+      <c r="B145" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C145" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D145" s="3" t="n">
+        <v>283.13</v>
+      </c>
+      <c r="E145" s="3" t="n">
+        <v>269.72</v>
+      </c>
+      <c r="F145" s="3" t="n">
+        <v>282.6</v>
+      </c>
+      <c r="G145" s="3" t="n">
+        <v>284.65</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>SBC</t>
+        </is>
+      </c>
+      <c r="B146" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C146" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D146" s="3" t="n">
+        <v>43.13</v>
+      </c>
+      <c r="E146" s="3" t="n">
+        <v>42.18</v>
+      </c>
+      <c r="F146" s="3" t="n">
+        <v>43.25</v>
+      </c>
+      <c r="G146" s="3" t="n">
+        <v>43.14</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>SBIETFPB</t>
+        </is>
+      </c>
+      <c r="B147" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C147" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D147" s="3" t="n">
+        <v>286.45</v>
+      </c>
+      <c r="E147" s="3" t="n">
+        <v>280.19</v>
+      </c>
+      <c r="F147" s="3" t="n">
+        <v>285.51</v>
+      </c>
+      <c r="G147" s="3" t="n">
+        <v>285.87</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>SBILIQETF</t>
+        </is>
+      </c>
+      <c r="B148" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C148" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D148" s="3" t="n">
+        <v>1054.32</v>
+      </c>
+      <c r="E148" s="3" t="n">
+        <v>1054.3</v>
+      </c>
+      <c r="F148" s="3" t="n">
+        <v>1054.43</v>
+      </c>
+      <c r="G148" s="3" t="n">
+        <v>1054.43</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>SCODATUBES</t>
+        </is>
+      </c>
+      <c r="B149" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C149" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D149" s="3" t="n">
+        <v>133.59</v>
+      </c>
+      <c r="E149" s="3" t="n">
+        <v>127.69</v>
+      </c>
+      <c r="F149" s="3" t="n">
+        <v>134.95</v>
+      </c>
+      <c r="G149" s="3" t="n">
+        <v>134.99</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>SEAMECLTD</t>
+        </is>
+      </c>
+      <c r="B150" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C150" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D150" s="3" t="n">
+        <v>1747.93</v>
+      </c>
+      <c r="E150" s="3" t="n">
+        <v>1675.33</v>
+      </c>
+      <c r="F150" s="3" t="n">
+        <v>1786.6</v>
+      </c>
+      <c r="G150" s="3" t="n">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>SGL</t>
+        </is>
+      </c>
+      <c r="B151" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C151" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D151" s="3" t="n">
+        <v>10.81</v>
+      </c>
+      <c r="E151" s="3" t="n">
+        <v>10.09</v>
+      </c>
+      <c r="F151" s="3" t="n">
+        <v>10.26</v>
+      </c>
+      <c r="G151" s="3" t="n">
+        <v>10.31</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>SHREEJISPG</t>
+        </is>
+      </c>
+      <c r="B152" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C152" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D152" s="3" t="n">
+        <v>659.08</v>
+      </c>
+      <c r="E152" s="3" t="n">
+        <v>634.9299999999999</v>
+      </c>
+      <c r="F152" s="3" t="n">
+        <v>664.25</v>
+      </c>
+      <c r="G152" s="3" t="n">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>SHREEPUSHK</t>
+        </is>
+      </c>
+      <c r="B153" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C153" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D153" s="3" t="n">
+        <v>478.82</v>
+      </c>
+      <c r="E153" s="3" t="n">
+        <v>456.62</v>
+      </c>
+      <c r="F153" s="3" t="n">
+        <v>477.45</v>
+      </c>
+      <c r="G153" s="3" t="n">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>SICAGEN</t>
+        </is>
+      </c>
+      <c r="B154" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C154" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D154" s="3" t="n">
+        <v>57.85</v>
+      </c>
+      <c r="E154" s="3" t="n">
+        <v>55.66</v>
+      </c>
+      <c r="F154" s="3" t="n">
+        <v>58.65</v>
+      </c>
+      <c r="G154" s="3" t="n">
+        <v>58.45</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>SILVERETF</t>
+        </is>
+      </c>
+      <c r="B155" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C155" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D155" s="3" t="n">
+        <v>201.81</v>
+      </c>
+      <c r="E155" s="3" t="n">
+        <v>198.28</v>
+      </c>
+      <c r="F155" s="3" t="n">
+        <v>203.98</v>
+      </c>
+      <c r="G155" s="3" t="n">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>SKFINDUS</t>
+        </is>
+      </c>
+      <c r="B156" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C156" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D156" s="3" t="n">
+        <v>3096.07</v>
+      </c>
+      <c r="E156" s="3" t="n">
+        <v>2956.87</v>
+      </c>
+      <c r="F156" s="3" t="n">
+        <v>3062.8</v>
+      </c>
+      <c r="G156" s="3" t="n">
+        <v>3055</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>SOMATEX</t>
+        </is>
+      </c>
+      <c r="B157" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C157" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D157" s="3" t="n">
+        <v>88.41</v>
+      </c>
+      <c r="E157" s="3" t="n">
+        <v>86.29000000000001</v>
+      </c>
+      <c r="F157" s="3" t="n">
+        <v>92.75</v>
+      </c>
+      <c r="G157" s="3" t="n">
+        <v>92.75</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>SPAL</t>
+        </is>
+      </c>
+      <c r="B158" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C158" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D158" s="3" t="n">
+        <v>1079.83</v>
+      </c>
+      <c r="E158" s="3" t="n">
+        <v>1023.3</v>
+      </c>
+      <c r="F158" s="3" t="n">
+        <v>1062.8</v>
+      </c>
+      <c r="G158" s="3" t="n">
+        <v>1064.7</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>SPECTRUM</t>
+        </is>
+      </c>
+      <c r="B159" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C159" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D159" s="3" t="n">
+        <v>2203.53</v>
+      </c>
+      <c r="E159" s="3" t="n">
+        <v>2075.73</v>
+      </c>
+      <c r="F159" s="3" t="n">
+        <v>2255.7</v>
+      </c>
+      <c r="G159" s="3" t="n">
+        <v>2255.7</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>SUDARCOLOR</t>
+        </is>
+      </c>
+      <c r="B160" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C160" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D160" s="3" t="n">
+        <v>394.67</v>
+      </c>
+      <c r="E160" s="3" t="n">
+        <v>380.85</v>
+      </c>
+      <c r="F160" s="3" t="n">
+        <v>388</v>
+      </c>
+      <c r="G160" s="3" t="n">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>SUDEEPPHRM</t>
+        </is>
+      </c>
+      <c r="B161" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C161" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D161" s="3" t="n">
+        <v>1283.7</v>
+      </c>
+      <c r="E161" s="3" t="n">
+        <v>1218.7</v>
+      </c>
+      <c r="F161" s="3" t="n">
+        <v>1292.8</v>
+      </c>
+      <c r="G161" s="3" t="n">
+        <v>1292</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>SUNDARMFIN</t>
+        </is>
+      </c>
+      <c r="B162" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C162" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D162" s="3" t="n">
+        <v>4599.1</v>
+      </c>
+      <c r="E162" s="3" t="n">
+        <v>4526.53</v>
+      </c>
+      <c r="F162" s="3" t="n">
+        <v>4578</v>
+      </c>
+      <c r="G162" s="3" t="n">
+        <v>4597</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>SUPRIYA</t>
+        </is>
+      </c>
+      <c r="B163" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C163" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D163" s="3" t="n">
+        <v>837.13</v>
+      </c>
+      <c r="E163" s="3" t="n">
+        <v>809.83</v>
+      </c>
+      <c r="F163" s="3" t="n">
+        <v>842.7</v>
+      </c>
+      <c r="G163" s="3" t="n">
+        <v>843.15</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>SURYALA</t>
+        </is>
+      </c>
+      <c r="B164" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C164" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D164" s="3" t="n">
+        <v>412.88</v>
+      </c>
+      <c r="E164" s="3" t="n">
+        <v>388.87</v>
+      </c>
+      <c r="F164" s="3" t="n">
+        <v>407.7</v>
+      </c>
+      <c r="G164" s="3" t="n">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>SYNCOMF</t>
+        </is>
+      </c>
+      <c r="B165" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C165" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D165" s="3" t="n">
+        <v>21.48</v>
+      </c>
+      <c r="E165" s="3" t="n">
+        <v>19.69</v>
+      </c>
+      <c r="F165" s="3" t="n">
+        <v>21.36</v>
+      </c>
+      <c r="G165" s="3" t="n">
+        <v>21.29</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>TBZ</t>
+        </is>
+      </c>
+      <c r="B166" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C166" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D166" s="3" t="n">
+        <v>417.98</v>
+      </c>
+      <c r="E166" s="3" t="n">
+        <v>364.82</v>
+      </c>
+      <c r="F166" s="3" t="n">
+        <v>437.15</v>
+      </c>
+      <c r="G166" s="3" t="n">
+        <v>443.95</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>TEXINFRA</t>
+        </is>
+      </c>
+      <c r="B167" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C167" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D167" s="3" t="n">
+        <v>116.24</v>
+      </c>
+      <c r="E167" s="3" t="n">
+        <v>112.77</v>
+      </c>
+      <c r="F167" s="3" t="n">
+        <v>116.7</v>
+      </c>
+      <c r="G167" s="3" t="n">
+        <v>115.37</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>TIJARIA</t>
+        </is>
+      </c>
+      <c r="B168" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C168" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D168" s="3" t="n">
+        <v>8.109999999999999</v>
+      </c>
+      <c r="E168" s="3" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="F168" s="3" t="n">
+        <v>9.09</v>
+      </c>
+      <c r="G168" s="3" t="n">
+        <v>9.09</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>TNPETRO</t>
+        </is>
+      </c>
+      <c r="B169" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C169" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D169" s="3" t="n">
+        <v>138.17</v>
+      </c>
+      <c r="E169" s="3" t="n">
+        <v>128.71</v>
+      </c>
+      <c r="F169" s="3" t="n">
+        <v>137.81</v>
+      </c>
+      <c r="G169" s="3" t="n">
+        <v>136.5</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>TORNTPOWER</t>
+        </is>
+      </c>
+      <c r="B170" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C170" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D170" s="3" t="n">
+        <v>1272.7</v>
+      </c>
+      <c r="E170" s="3" t="n">
+        <v>1231.8</v>
+      </c>
+      <c r="F170" s="3" t="n">
+        <v>1289.3</v>
+      </c>
+      <c r="G170" s="3" t="n">
+        <v>1287</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B171" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C171" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D171" s="3" t="n">
+        <v>70.62</v>
+      </c>
+      <c r="E171" s="3" t="n">
+        <v>67.40000000000001</v>
+      </c>
+      <c r="F171" s="3" t="n">
+        <v>70.31</v>
+      </c>
+      <c r="G171" s="3" t="n">
+        <v>70.98999999999999</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>UDS</t>
+        </is>
+      </c>
+      <c r="B172" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C172" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D172" s="3" t="n">
+        <v>233.83</v>
+      </c>
+      <c r="E172" s="3" t="n">
+        <v>225.78</v>
+      </c>
+      <c r="F172" s="3" t="n">
+        <v>236.61</v>
+      </c>
+      <c r="G172" s="3" t="n">
+        <v>238.71</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>UNIVPHOTO</t>
+        </is>
+      </c>
+      <c r="B173" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C173" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D173" s="3" t="n">
+        <v>453.95</v>
+      </c>
+      <c r="E173" s="3" t="n">
+        <v>444.35</v>
+      </c>
+      <c r="F173" s="3" t="n">
+        <v>467.25</v>
+      </c>
+      <c r="G173" s="3" t="n">
+        <v>467.25</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>URBANCO</t>
+        </is>
+      </c>
+      <c r="B174" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C174" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D174" s="3" t="n">
+        <v>175.01</v>
+      </c>
+      <c r="E174" s="3" t="n">
+        <v>167.59</v>
+      </c>
+      <c r="F174" s="3" t="n">
+        <v>177.46</v>
+      </c>
+      <c r="G174" s="3" t="n">
+        <v>177.6</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>UTISENSETF</t>
+        </is>
+      </c>
+      <c r="B175" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C175" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D175" s="3" t="n">
+        <v>941.63</v>
+      </c>
+      <c r="E175" s="3" t="n">
+        <v>933.52</v>
+      </c>
+      <c r="F175" s="3" t="n">
+        <v>939.25</v>
+      </c>
+      <c r="G175" s="3" t="n">
+        <v>938.3200000000001</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>VALIANTORG</t>
+        </is>
+      </c>
+      <c r="B176" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C176" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D176" s="3" t="n">
+        <v>303.72</v>
+      </c>
+      <c r="E176" s="3" t="n">
+        <v>290.5</v>
+      </c>
+      <c r="F176" s="3" t="n">
+        <v>316.15</v>
+      </c>
+      <c r="G176" s="3" t="n">
+        <v>316.15</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>VELJAN</t>
+        </is>
+      </c>
+      <c r="B177" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C177" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D177" s="3" t="n">
+        <v>1839</v>
+      </c>
+      <c r="E177" s="3" t="n">
+        <v>1788.67</v>
+      </c>
+      <c r="F177" s="3" t="n">
+        <v>1848.4</v>
+      </c>
+      <c r="G177" s="3" t="n">
+        <v>1850</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>VIJIFIN</t>
+        </is>
+      </c>
+      <c r="B178" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C178" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D178" s="3" t="n">
+        <v>15.95</v>
+      </c>
+      <c r="E178" s="3" t="n">
+        <v>15.95</v>
+      </c>
+      <c r="F178" s="3" t="n">
+        <v>16.26</v>
+      </c>
+      <c r="G178" s="3" t="n">
+        <v>16.26</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>VIMTALABS</t>
+        </is>
+      </c>
+      <c r="B179" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C179" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D179" s="3" t="n">
+        <v>668.22</v>
+      </c>
+      <c r="E179" s="3" t="n">
+        <v>643.1799999999999</v>
+      </c>
+      <c r="F179" s="3" t="n">
+        <v>652.25</v>
+      </c>
+      <c r="G179" s="3" t="n">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>VINDHYATEL</t>
+        </is>
+      </c>
+      <c r="B180" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C180" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D180" s="3" t="n">
+        <v>2750.63</v>
+      </c>
+      <c r="E180" s="3" t="n">
+        <v>2559.03</v>
+      </c>
+      <c r="F180" s="3" t="n">
+        <v>2736.2</v>
+      </c>
+      <c r="G180" s="3" t="n">
+        <v>2742</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>WELCORP</t>
+        </is>
+      </c>
+      <c r="B181" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C181" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D181" s="3" t="n">
+        <v>2614.33</v>
+      </c>
+      <c r="E181" s="3" t="n">
+        <v>2482.87</v>
+      </c>
+      <c r="F181" s="3" t="n">
+        <v>2641.6</v>
+      </c>
+      <c r="G181" s="3" t="n">
+        <v>2631.1</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
           <t>WELENT</t>
         </is>
       </c>
-      <c r="B126" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C126" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D126" s="3" t="n">
-        <v>717.83</v>
-      </c>
-      <c r="E126" s="3" t="n">
-        <v>679.3</v>
-      </c>
-      <c r="F126" s="3" t="n">
-        <v>741.7</v>
-      </c>
-      <c r="G126" s="3" t="n">
-        <v>744</v>
+      <c r="B182" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C182" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D182" s="3" t="n">
+        <v>741.83</v>
+      </c>
+      <c r="E182" s="3" t="n">
+        <v>701.92</v>
+      </c>
+      <c r="F182" s="3" t="n">
+        <v>764.75</v>
+      </c>
+      <c r="G182" s="3" t="n">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>WHIRLPOOL</t>
+        </is>
+      </c>
+      <c r="B183" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C183" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D183" s="3" t="n">
+        <v>807.7</v>
+      </c>
+      <c r="E183" s="3" t="n">
+        <v>787.67</v>
+      </c>
+      <c r="F183" s="3" t="n">
+        <v>804.4</v>
+      </c>
+      <c r="G183" s="3" t="n">
+        <v>805.65</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>WINDLAS</t>
+        </is>
+      </c>
+      <c r="B184" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C184" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D184" s="3" t="n">
+        <v>1091.32</v>
+      </c>
+      <c r="E184" s="3" t="n">
+        <v>1026.38</v>
+      </c>
+      <c r="F184" s="3" t="n">
+        <v>1127.1</v>
+      </c>
+      <c r="G184" s="3" t="n">
+        <v>1123</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>WOCKPHARMA</t>
+        </is>
+      </c>
+      <c r="B185" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C185" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D185" s="3" t="n">
+        <v>1926.93</v>
+      </c>
+      <c r="E185" s="3" t="n">
+        <v>1854.23</v>
+      </c>
+      <c r="F185" s="3" t="n">
+        <v>1950.6</v>
+      </c>
+      <c r="G185" s="3" t="n">
+        <v>1950</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>ZENTEC</t>
+        </is>
+      </c>
+      <c r="B186" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C186" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D186" s="3" t="n">
+        <v>1832.63</v>
+      </c>
+      <c r="E186" s="3" t="n">
+        <v>1760.2</v>
+      </c>
+      <c r="F186" s="3" t="n">
+        <v>1810.3</v>
+      </c>
+      <c r="G186" s="3" t="n">
+        <v>1813.3</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>ZYDUSWELL</t>
+        </is>
+      </c>
+      <c r="B187" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C187" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D187" s="3" t="n">
+        <v>537.17</v>
+      </c>
+      <c r="E187" s="3" t="n">
+        <v>525.48</v>
+      </c>
+      <c r="F187" s="3" t="n">
+        <v>538.2</v>
+      </c>
+      <c r="G187" s="3" t="n">
+        <v>536.95</v>
       </c>
     </row>
   </sheetData>

--- a/data/uptrend_output.xlsx
+++ b/data/uptrend_output.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G257"/>
+  <dimension ref="A1:G275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -508,7 +508,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>21STCENMGM</t>
+          <t>AARTECH</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -522,22 +522,22 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>38.96</v>
+        <v>52.1</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>37.71</v>
+        <v>49.91</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>38.8</v>
+        <v>52.07</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>38.8</v>
+        <v>52.52</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>AAREYDRUGS</t>
+          <t>AARTIIND</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -551,22 +551,22 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>98.63</v>
+        <v>503.8</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>95.22</v>
+        <v>492.43</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>99.98</v>
+        <v>504.05</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>99.20999999999999</v>
+        <v>505.25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>ACSTECH</t>
+          <t>ACUTAAS</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -580,22 +580,22 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>55.47</v>
+        <v>3315.57</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>53.3</v>
+        <v>3187.17</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>59.99</v>
+        <v>3451.4</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>59.99</v>
+        <v>3459.6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>ADVENZYMES</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -609,22 +609,22 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>1425.73</v>
+        <v>304.13</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>1387</v>
+        <v>295.67</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>1423.3</v>
+        <v>303.35</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>1423.3</v>
+        <v>302.2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>ADANIGREEN</t>
+          <t>AEGISLOG</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -638,22 +638,22 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1318</v>
+        <v>1340.8</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1284.4</v>
+        <v>1269.2</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1315</v>
+        <v>1307.6</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>1315</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>ADROITINFO</t>
+          <t>AEGISVOPAK</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -667,22 +667,22 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>10.91</v>
+        <v>295.7</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>10.24</v>
+        <v>285.87</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>10.98</v>
+        <v>291.85</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>11.05</v>
+        <v>292</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>AEROFLEX</t>
+          <t>AEROPLANE</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -696,22 +696,22 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>562.6799999999999</v>
+        <v>205.15</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>539.12</v>
+        <v>196.66</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>561.15</v>
+        <v>206.9</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>561.2</v>
+        <v>207.23</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>AIRAN</t>
+          <t>AHCL</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -725,22 +725,22 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>16.72</v>
+        <v>16.84</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>15.77</v>
+        <v>15.69</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>17.66</v>
+        <v>17.54</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>17.6</v>
+        <v>17.78</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AKSHOPTFBR</t>
+          <t>AKG</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -754,22 +754,22 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>7.94</v>
+        <v>10.37</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>7.76</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>8.59</v>
+        <v>10.73</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>8.59</v>
+        <v>10.73</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>ALKALI</t>
+          <t>AMIRCHAND</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -783,22 +783,22 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>79.56999999999999</v>
+        <v>181.7</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>72.08</v>
+        <v>171.51</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>85.20999999999999</v>
+        <v>185.11</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>84.05</v>
+        <v>184.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ALLCARGO</t>
+          <t>ANMOL</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -812,22 +812,22 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>12.95</v>
+        <v>13.56</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>12.32</v>
+        <v>11.2</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>12.75</v>
+        <v>15.34</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>12.86</v>
+        <v>15.46</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>ALMONDZ</t>
+          <t>AONELIQUID</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -841,22 +841,22 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>19.28</v>
+        <v>1076.03</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>18.14</v>
+        <v>1076.01</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>19</v>
+        <v>1076.19</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>19.07</v>
+        <v>1076.19</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>AMANTA</t>
+          <t>AONESILVER</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -870,22 +870,22 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>199.28</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>199.28</v>
+        <v>8.81</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>205.89</v>
+        <v>8.91</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>205.89</v>
+        <v>8.949999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>AMIRCHAND</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -899,22 +899,22 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>181.7</v>
+        <v>8946.33</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>171.51</v>
+        <v>8776.17</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>185.11</v>
+        <v>8900</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>184.5</v>
+        <v>8900</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>ANMOL</t>
+          <t>APOLSINHOT</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -928,22 +928,22 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>11.78</v>
+        <v>1225.87</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>10.25</v>
+        <v>1206.77</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>13.63</v>
+        <v>1228.9</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>13.65</v>
+        <v>1216.7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>ANUHPHR</t>
+          <t>ARMANFIN</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -957,22 +957,22 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>91.22</v>
+        <v>2075.97</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>85.90000000000001</v>
+        <v>2009.37</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>96.73999999999999</v>
+        <v>2036.5</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>96.95</v>
+        <v>2039</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>AONELIQUID</t>
+          <t>ARTEMISMED</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -986,22 +986,22 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1075.87</v>
+        <v>354.17</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1075.84</v>
+        <v>337.18</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1076.06</v>
+        <v>348.55</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>1076.06</v>
+        <v>347</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>APOLLO</t>
+          <t>ASAHIINDIA</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1015,22 +1015,22 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>409.43</v>
+        <v>979.5</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>396.3</v>
+        <v>955.65</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>422.45</v>
+        <v>976.2</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>420.5</v>
+        <v>980</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>AUGMONT</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1044,22 +1044,22 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>8851.67</v>
+        <v>928.72</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>8698.17</v>
+        <v>886.37</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>8967</v>
+        <v>917.5</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>8967</v>
+        <v>917</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>ARTEMISMED</t>
+          <t>AVANTEL</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>346.6</v>
+        <v>161.8</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>328.95</v>
+        <v>156.28</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>354.3</v>
+        <v>159.07</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>352.2</v>
+        <v>159</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>AUROPHARMA</t>
+          <t>AVG</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -1102,22 +1102,22 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>1677.83</v>
+        <v>174.46</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>1646.87</v>
+        <v>166.09</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>1698.9</v>
+        <v>182.49</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>1698.9</v>
+        <v>182.49</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>AVL</t>
+          <t>AVONMORE</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -1131,22 +1131,22 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>613.88</v>
+        <v>14.38</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>597.25</v>
+        <v>13.49</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>623.1</v>
+        <v>14.19</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>617.05</v>
+        <v>14.32</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>AVONMORE</t>
+          <t>AVTNPL</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1160,16 +1160,16 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>14.07</v>
+        <v>92.76000000000001</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>13.18</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>13.99</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>14.03</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="25">
@@ -1204,7 +1204,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>AXISCADES</t>
+          <t>AXISCETF</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -1218,22 +1218,22 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>1829.67</v>
+        <v>120.57</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>1754.43</v>
+        <v>118.88</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>1875.7</v>
+        <v>121.12</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>1882.8</v>
+        <v>120.8</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>AXISCETF</t>
+          <t>BALPHARMA</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -1247,22 +1247,22 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>120.57</v>
+        <v>111.35</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>118.88</v>
+        <v>95.38</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>121.12</v>
+        <v>106.21</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>120.8</v>
+        <v>105.5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>BAFNAPH</t>
+          <t>BECTORFOOD</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1276,22 +1276,22 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>300.48</v>
+        <v>242.13</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>299.48</v>
+        <v>229.05</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>301.6</v>
+        <v>245.44</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>301.6</v>
+        <v>246</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>BAIDFIN</t>
+          <t>BHAGYANGR</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -1305,22 +1305,22 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>11.47</v>
+        <v>407.28</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>10.64</v>
+        <v>390.1</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>12.03</v>
+        <v>432.2</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>12</v>
+        <v>432.2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>BAJAJHCARE</t>
+          <t>BIL</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -1334,22 +1334,22 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>334.7</v>
+        <v>1076.4</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>323.73</v>
+        <v>959.05</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>333.7</v>
+        <v>1081.7</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>333</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>BANCOINDIA</t>
+          <t>BIMETAL</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -1363,22 +1363,22 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>636.37</v>
+        <v>649.83</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>620.28</v>
+        <v>606.8</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>635.15</v>
+        <v>645</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>634.1</v>
+        <v>645</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>BCG</t>
+          <t>BSLGOLDETF</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -1392,22 +1392,22 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>9.93</v>
+        <v>134.87</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>9.359999999999999</v>
+        <v>133.36</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>10.23</v>
+        <v>134.33</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>10.31</v>
+        <v>134.45</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>BGRENERGY</t>
+          <t>CAMLINFINE</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -1421,22 +1421,22 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>255.45</v>
+        <v>105.07</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>240.57</v>
+        <v>102.35</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>248.87</v>
+        <v>103.57</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>248.4</v>
+        <v>103.71</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>BHARTIHEXA</t>
+          <t>CARYSIL</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -1450,22 +1450,22 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>1538.93</v>
+        <v>1188.3</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>1504.7</v>
+        <v>1143.8</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>1544.8</v>
+        <v>1178.5</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>1543</v>
+        <v>1176.1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>BIL</t>
+          <t>CASHIETF</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -1479,22 +1479,22 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>1001.07</v>
+        <v>1078.71</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>907.37</v>
+        <v>1078.31</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>1108.2</v>
+        <v>1078.88</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>1107.05</v>
+        <v>1078.88</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>BILVYAPAR</t>
+          <t>CEIGALL</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -1508,22 +1508,22 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>4.19</v>
+        <v>380.82</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>3.96</v>
+        <v>364.57</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>4.05</v>
+        <v>379.1</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>4.05</v>
+        <v>379.5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>BLISSGVS</t>
+          <t>CENTEXT</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -1537,22 +1537,22 @@
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>700.28</v>
+        <v>21.99</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>652.67</v>
+        <v>21.12</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>692.85</v>
+        <v>22.8</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>705</v>
+        <v>22.84</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>BODALCHEM</t>
+          <t>CEWATER</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -1566,22 +1566,22 @@
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>173.62</v>
+        <v>281.07</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>161.34</v>
+        <v>266.35</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>174.85</v>
+        <v>279.9</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>174.85</v>
+        <v>281.5</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>CEIGALL</t>
+          <t>CFEL</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -1595,22 +1595,22 @@
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>371.02</v>
+        <v>39.26</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>358.38</v>
+        <v>34.62</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>376.4</v>
+        <v>44.92</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>376.3</v>
+        <v>44.7</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>CENTUM</t>
+          <t>CHEMFAB</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -1624,22 +1624,22 @@
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>4223.33</v>
+        <v>387.85</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>3904.07</v>
+        <v>357.2</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>4250.5</v>
+        <v>384.5</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>4225.5</v>
+        <v>386.45</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>CGPOWER</t>
+          <t>CHENNPETRO</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -1653,22 +1653,22 @@
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>914.13</v>
+        <v>1581.23</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>897.4299999999999</v>
+        <v>1483.97</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>926.95</v>
+        <v>1626.4</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>926.95</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>CLEANMAX</t>
+          <t>CHOLAHLDNG</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -1682,16 +1682,16 @@
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>1403.57</v>
+        <v>1536.5</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>1336.93</v>
+        <v>1508.1</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>1397.6</v>
+        <v>1532</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>1400</v>
+        <v>1528.4</v>
       </c>
     </row>
     <row r="43">
@@ -1711,22 +1711,22 @@
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>424.55</v>
+        <v>430.65</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>415.22</v>
+        <v>421.03</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>COMPUSOFT</t>
+          <t>COCHINSHIP</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -1740,22 +1740,22 @@
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>13.25</v>
+        <v>1551.4</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>12.91</v>
+        <v>1504.2</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>13.21</v>
+        <v>1520.4</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>13.27</v>
+        <v>1520.4</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>CONCORDBIO</t>
+          <t>CPSEETF</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -1769,22 +1769,22 @@
         </is>
       </c>
       <c r="D45" s="3" t="n">
-        <v>1462.1</v>
+        <v>95.29000000000001</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>1425.4</v>
+        <v>93.65000000000001</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>1464.5</v>
+        <v>94.78</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>1473.5</v>
+        <v>94.79000000000001</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>CPL</t>
+          <t>CRIZAC</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -1798,22 +1798,22 @@
         </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>66.59</v>
+        <v>174.59</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>63.32</v>
+        <v>167.55</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>67.81</v>
+        <v>179.7</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>67.5</v>
+        <v>180</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>CRIZAC</t>
+          <t>CUMMINSIND</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -1827,22 +1827,22 @@
         </is>
       </c>
       <c r="D47" s="3" t="n">
-        <v>168.85</v>
+        <v>5163.83</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>162.82</v>
+        <v>5024.83</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>176.04</v>
+        <v>5155</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>176.02</v>
+        <v>5155</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>DEEDEV</t>
+          <t>DCMSIL</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -1856,22 +1856,22 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>691.05</v>
+        <v>72.2</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>654.3</v>
+        <v>68.27</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>674.75</v>
+        <v>72.36</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>670</v>
+        <v>72</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>DEEP</t>
+          <t>DECNGOLD</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -1885,22 +1885,22 @@
         </is>
       </c>
       <c r="D49" s="3" t="n">
-        <v>36.68</v>
+        <v>225.13</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>34.99</v>
+        <v>216.09</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>36.89</v>
+        <v>225.88</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>36.51</v>
+        <v>226</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>DEEPINDS</t>
+          <t>DEEP</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -1914,22 +1914,22 @@
         </is>
       </c>
       <c r="D50" s="3" t="n">
-        <v>806.0700000000001</v>
+        <v>39.08</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>765.13</v>
+        <v>35.77</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>792.7</v>
+        <v>40.98</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>794.7</v>
+        <v>41.4</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>DENTA</t>
+          <t>DIACABS</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -1943,22 +1943,22 @@
         </is>
       </c>
       <c r="D51" s="3" t="n">
-        <v>285.53</v>
+        <v>343.97</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>274.42</v>
+        <v>329.13</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>283.2</v>
+        <v>351.5</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>283.55</v>
+        <v>351.5</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>DHOOTTRANS</t>
+          <t>DIAMINESQ</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -1972,22 +1972,22 @@
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>1600.83</v>
+        <v>253.26</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>1542.73</v>
+        <v>244.99</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>1596.5</v>
+        <v>258.09</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>1593</v>
+        <v>259</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>DIACABS</t>
+          <t>DIGJAMLMTD</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -2001,22 +2001,22 @@
         </is>
       </c>
       <c r="D53" s="3" t="n">
-        <v>339.8</v>
+        <v>55.43</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>323.97</v>
+        <v>50.94</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>334.8</v>
+        <v>61.84</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>334.6</v>
+        <v>61.84</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>DIVISLAB</t>
+          <t>DJML</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -2030,22 +2030,22 @@
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>9399.67</v>
+        <v>81.61</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>9209.83</v>
+        <v>75.95999999999999</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>9488</v>
+        <v>81.75</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>9488</v>
+        <v>83</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>DJML</t>
+          <t>DSKULKARNI</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -2059,22 +2059,22 @@
         </is>
       </c>
       <c r="D55" s="3" t="n">
-        <v>78.93000000000001</v>
+        <v>19.94</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>72.95999999999999</v>
+        <v>19.94</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>82.03</v>
+        <v>20.59</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>82.90000000000001</v>
+        <v>20.59</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>DSKULKARNI</t>
+          <t>DYNPRO</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -2088,22 +2088,22 @@
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>19.42</v>
+        <v>241.17</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>19.42</v>
+        <v>230.81</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>19.8</v>
+        <v>237.05</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>19.8</v>
+        <v>236</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>EBGNG</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -2117,16 +2117,16 @@
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>7726.33</v>
+        <v>672.47</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>7623.17</v>
+        <v>640.85</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>7734.5</v>
+        <v>677.95</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>7734.5</v>
+        <v>682</v>
       </c>
     </row>
     <row r="58">
@@ -2146,22 +2146,22 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>207.13</v>
+        <v>211.81</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>198.88</v>
+        <v>203.33</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>206.06</v>
+        <v>211.65</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>204.3</v>
+        <v>211.9</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>EMIL</t>
+          <t>ELLEN</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -2175,22 +2175,22 @@
         </is>
       </c>
       <c r="D59" s="3" t="n">
-        <v>182.49</v>
+        <v>356.27</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>173.2</v>
+        <v>329.9</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>182.65</v>
+        <v>373.5</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>181.41</v>
+        <v>377</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>EMPOWER</t>
+          <t>EMETAL</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -2204,22 +2204,22 @@
         </is>
       </c>
       <c r="D60" s="3" t="n">
-        <v>1.98</v>
+        <v>13.44</v>
       </c>
       <c r="E60" s="3" t="n">
-        <v>1.9</v>
+        <v>13.17</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>2.1</v>
+        <v>13.49</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>2.11</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>EQUIPPP</t>
+          <t>EMMVEE</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -2233,22 +2233,22 @@
         </is>
       </c>
       <c r="D61" s="3" t="n">
-        <v>23.45</v>
+        <v>339.2</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>22.44</v>
+        <v>325.6</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>23.83</v>
+        <v>342.65</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>24</v>
+        <v>343.5</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>ESDS</t>
+          <t>EMPOWER</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -2262,22 +2262,22 @@
         </is>
       </c>
       <c r="D62" s="3" t="n">
-        <v>1278.98</v>
+        <v>2.08</v>
       </c>
       <c r="E62" s="3" t="n">
-        <v>1223.17</v>
+        <v>2.03</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>1438.85</v>
+        <v>2.19</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>1438.85</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>FCL</t>
+          <t>EMULTIMQ</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -2291,22 +2291,22 @@
         </is>
       </c>
       <c r="D63" s="3" t="n">
-        <v>57.05</v>
+        <v>42.4</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>52.82</v>
+        <v>41.85</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>58.43</v>
+        <v>42.1</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>58.2</v>
+        <v>42.02</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>GABRIEL</t>
+          <t>ESILVER</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -2320,22 +2320,22 @@
         </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>1376.33</v>
+        <v>233.81</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>1330.43</v>
+        <v>229.52</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>1360.8</v>
+        <v>233.29</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>1360</v>
+        <v>234.16</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>GANDHAR</t>
+          <t>EVEREADY</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -2349,22 +2349,22 @@
         </is>
       </c>
       <c r="D65" s="3" t="n">
-        <v>271.43</v>
+        <v>350.67</v>
       </c>
       <c r="E65" s="3" t="n">
-        <v>261.93</v>
+        <v>335.28</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>265.85</v>
+        <v>366.2</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>265.5</v>
+        <v>365</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>GANESHBE</t>
+          <t>EXCELSOFT</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -2378,22 +2378,22 @@
         </is>
       </c>
       <c r="D66" s="3" t="n">
-        <v>129.3</v>
+        <v>77.53</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>123.4</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>128.19</v>
+        <v>80.08</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>129</v>
+        <v>80.7</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>GAYAPROJ</t>
+          <t>FEDERALBNK</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -2407,22 +2407,22 @@
         </is>
       </c>
       <c r="D67" s="3" t="n">
-        <v>23.11</v>
+        <v>345.02</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>22.14</v>
+        <v>340.95</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>23.64</v>
+        <v>346</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>23.45</v>
+        <v>346</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>GENESYS</t>
+          <t>FINCABLES</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -2436,22 +2436,22 @@
         </is>
       </c>
       <c r="D68" s="3" t="n">
-        <v>257.77</v>
+        <v>1352.33</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>240.25</v>
+        <v>1281.07</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>274.31</v>
+        <v>1418.4</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>272.06</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>GESHIP</t>
+          <t>FLUOROCHEM</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -2465,22 +2465,22 @@
         </is>
       </c>
       <c r="D69" s="3" t="n">
-        <v>1389.87</v>
+        <v>4753.87</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>1357.73</v>
+        <v>4620.2</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>1393.4</v>
+        <v>4786.3</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>1391.5</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>GMMPFAUDLR</t>
+          <t>FREDUN</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -2494,22 +2494,22 @@
         </is>
       </c>
       <c r="D70" s="3" t="n">
-        <v>1260.33</v>
+        <v>1457.33</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>1168.7</v>
+        <v>1362.1</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>1305.4</v>
+        <v>1461.2</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>1305</v>
+        <v>1440.2</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>GOACARBON</t>
+          <t>GAJA</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -2523,22 +2523,22 @@
         </is>
       </c>
       <c r="D71" s="3" t="n">
-        <v>410.5</v>
+        <v>160.37</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>381.63</v>
+        <v>152.8</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>463.5</v>
+        <v>155.33</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>463.5</v>
+        <v>155.2</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>GOCLCORP</t>
+          <t>GANDHAR</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -2552,22 +2552,22 @@
         </is>
       </c>
       <c r="D72" s="3" t="n">
-        <v>436.8</v>
+        <v>274.42</v>
       </c>
       <c r="E72" s="3" t="n">
-        <v>426.43</v>
+        <v>264.6</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>431.7</v>
+        <v>271.3</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>433</v>
+        <v>271</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>GODREJAGRO</t>
+          <t>GANECOS</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -2581,22 +2581,22 @@
         </is>
       </c>
       <c r="D73" s="3" t="n">
-        <v>671.95</v>
+        <v>1034.43</v>
       </c>
       <c r="E73" s="3" t="n">
-        <v>646.28</v>
+        <v>994.67</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>674.65</v>
+        <v>1048.6</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>673.5</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>GPIL</t>
+          <t>GANESHBE</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -2610,22 +2610,22 @@
         </is>
       </c>
       <c r="D74" s="3" t="n">
-        <v>248.02</v>
+        <v>132.46</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>240.77</v>
+        <v>125.23</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>253.04</v>
+        <v>133.35</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>252.5</v>
+        <v>133.15</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>GPTHEALTH</t>
+          <t>GEMAROMA</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -2639,22 +2639,22 @@
         </is>
       </c>
       <c r="D75" s="3" t="n">
-        <v>161.42</v>
+        <v>169.1</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>156.46</v>
+        <v>160.43</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>162.63</v>
+        <v>165.09</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>163</v>
+        <v>163.5</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>GRANULES</t>
+          <t>GESHIP</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -2668,22 +2668,22 @@
         </is>
       </c>
       <c r="D76" s="3" t="n">
-        <v>879.75</v>
+        <v>1406.17</v>
       </c>
       <c r="E76" s="3" t="n">
-        <v>852.97</v>
+        <v>1375.4</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>884.8</v>
+        <v>1400.2</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>880.5</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>GROWWDEFNC</t>
+          <t>GMDCLTD</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -2697,22 +2697,22 @@
         </is>
       </c>
       <c r="D77" s="3" t="n">
-        <v>99.05</v>
+        <v>583.55</v>
       </c>
       <c r="E77" s="3" t="n">
-        <v>97.25</v>
+        <v>567.92</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>99.25</v>
+        <v>580.4</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>99.28</v>
+        <v>577.05</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>GUJTHEM</t>
+          <t>GOACARBON</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -2726,22 +2726,22 @@
         </is>
       </c>
       <c r="D78" s="3" t="n">
-        <v>445.07</v>
+        <v>444.83</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>414.87</v>
+        <v>402.18</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>430.75</v>
+        <v>440.25</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>430.8</v>
+        <v>435</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>HAZOOR</t>
+          <t>GODREJAGRO</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -2755,22 +2755,22 @@
         </is>
       </c>
       <c r="D79" s="3" t="n">
-        <v>20.24</v>
+        <v>677.95</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>19.55</v>
+        <v>654.65</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>19.88</v>
+        <v>673.05</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>19.75</v>
+        <v>673.35</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>GOLD1</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -2784,22 +2784,22 @@
         </is>
       </c>
       <c r="D80" s="3" t="n">
-        <v>242.82</v>
+        <v>127.72</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>234.42</v>
+        <v>126.5</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>245.43</v>
+        <v>127.4</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>246</v>
+        <v>127.42</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>HINDOILEXP</t>
+          <t>GOLD360</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -2813,22 +2813,22 @@
         </is>
       </c>
       <c r="D81" s="3" t="n">
-        <v>194.48</v>
+        <v>149.22</v>
       </c>
       <c r="E81" s="3" t="n">
-        <v>186.17</v>
+        <v>147.58</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>195.83</v>
+        <v>149.15</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>195.9</v>
+        <v>148.75</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>ICIL</t>
+          <t>GOLDAXIS</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -2842,22 +2842,22 @@
         </is>
       </c>
       <c r="D82" s="3" t="n">
-        <v>460.17</v>
+        <v>127.32</v>
       </c>
       <c r="E82" s="3" t="n">
-        <v>440.97</v>
+        <v>126.18</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>445.55</v>
+        <v>127.19</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>445.1</v>
+        <v>127.28</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>IDEA</t>
+          <t>GOLDBEES</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -2871,22 +2871,22 @@
         </is>
       </c>
       <c r="D83" s="3" t="n">
-        <v>15.54</v>
+        <v>126.39</v>
       </c>
       <c r="E83" s="3" t="n">
-        <v>14.92</v>
+        <v>125.32</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>15.52</v>
+        <v>126.2</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>15.52</v>
+        <v>126.26</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>INDIAGLYCO</t>
+          <t>GOLDBETA</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -2900,22 +2900,22 @@
         </is>
       </c>
       <c r="D84" s="3" t="n">
-        <v>278.37</v>
+        <v>128.68</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>277.47</v>
+        <v>127.47</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>301.3</v>
+        <v>128.5</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>301.3</v>
+        <v>128.65</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>INDOMIM</t>
+          <t>GPTHEALTH</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -2929,22 +2929,22 @@
         </is>
       </c>
       <c r="D85" s="3" t="n">
-        <v>987.98</v>
+        <v>163.55</v>
       </c>
       <c r="E85" s="3" t="n">
-        <v>944.42</v>
+        <v>159.18</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>984.55</v>
+        <v>161.29</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>994</v>
+        <v>161.06</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>INDORAMA</t>
+          <t>GRAUWEIL</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -2958,22 +2958,22 @@
         </is>
       </c>
       <c r="D86" s="3" t="n">
-        <v>80.15000000000001</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>71.37</v>
+        <v>71.26000000000001</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>86.13</v>
+        <v>76.48</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>85</v>
+        <v>76.68000000000001</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>INDOUS</t>
+          <t>GROWWHOSPI</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -2987,22 +2987,22 @@
         </is>
       </c>
       <c r="D87" s="3" t="n">
-        <v>80.34999999999999</v>
+        <v>53.03</v>
       </c>
       <c r="E87" s="3" t="n">
-        <v>74.65000000000001</v>
+        <v>52.01</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>80.25</v>
+        <v>52.65</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>80.5</v>
+        <v>52.73</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>INDSWFTLAB</t>
+          <t>GROWWSLVR</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -3016,22 +3016,22 @@
         </is>
       </c>
       <c r="D88" s="3" t="n">
-        <v>383.52</v>
+        <v>22.93</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>360.78</v>
+        <v>22.67</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>388.55</v>
+        <v>22.92</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>385.95</v>
+        <v>22.96</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>INFIBEAM</t>
+          <t>GUJRAFFIA</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -3045,22 +3045,22 @@
         </is>
       </c>
       <c r="D89" s="3" t="n">
-        <v>16.54</v>
+        <v>41.95</v>
       </c>
       <c r="E89" s="3" t="n">
-        <v>15.65</v>
+        <v>40.26</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>16.9</v>
+        <v>41.17</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>16.84</v>
+        <v>40.75</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>INVPRECQ</t>
+          <t>GVKPIL</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -3074,22 +3074,22 @@
         </is>
       </c>
       <c r="D90" s="3" t="n">
-        <v>1308.43</v>
+        <v>2.17</v>
       </c>
       <c r="E90" s="3" t="n">
-        <v>1306.1</v>
+        <v>2.14</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>1351.3</v>
+        <v>2.21</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>1351.3</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>IVP</t>
+          <t>HCG</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -3103,22 +3103,22 @@
         </is>
       </c>
       <c r="D91" s="3" t="n">
-        <v>215.16</v>
+        <v>715.5700000000001</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>205.1</v>
+        <v>688.75</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>220.26</v>
+        <v>700.9</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>218.01</v>
+        <v>703.5</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>JAINREC</t>
+          <t>HCL-INSYS</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -3132,22 +3132,22 @@
         </is>
       </c>
       <c r="D92" s="3" t="n">
-        <v>291.82</v>
+        <v>10.27</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>282.68</v>
+        <v>10.02</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>295.85</v>
+        <v>10.12</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>296.15</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>JASH</t>
+          <t>HDFCGOLD</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -3161,22 +3161,22 @@
         </is>
       </c>
       <c r="D93" s="3" t="n">
-        <v>510.65</v>
+        <v>130.7</v>
       </c>
       <c r="E93" s="3" t="n">
-        <v>491.43</v>
+        <v>129.52</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>518.75</v>
+        <v>130.49</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>519.15</v>
+        <v>130.6</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>JINDRILL</t>
+          <t>HDFCNIMEG</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -3190,22 +3190,22 @@
         </is>
       </c>
       <c r="D94" s="3" t="n">
-        <v>683.97</v>
+        <v>134.77</v>
       </c>
       <c r="E94" s="3" t="n">
-        <v>655.6</v>
+        <v>131.9</v>
       </c>
       <c r="F94" s="3" t="n">
-        <v>673.75</v>
+        <v>133.04</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>672.5</v>
+        <v>133.2</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>JUBLPHARMA</t>
+          <t>HDFCSILVER</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -3219,22 +3219,22 @@
         </is>
       </c>
       <c r="D95" s="3" t="n">
-        <v>969.23</v>
+        <v>223.93</v>
       </c>
       <c r="E95" s="3" t="n">
-        <v>936.08</v>
+        <v>220.81</v>
       </c>
       <c r="F95" s="3" t="n">
-        <v>1019</v>
+        <v>223.54</v>
       </c>
       <c r="G95" s="3" t="n">
-        <v>1019.95</v>
+        <v>223.9</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>JYOTISTRUC</t>
+          <t>HERANBA</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -3248,22 +3248,22 @@
         </is>
       </c>
       <c r="D96" s="3" t="n">
-        <v>10.32</v>
+        <v>174.99</v>
       </c>
       <c r="E96" s="3" t="n">
-        <v>9.81</v>
+        <v>170.13</v>
       </c>
       <c r="F96" s="3" t="n">
-        <v>10.08</v>
+        <v>172.3</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>10.13</v>
+        <v>173.25</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>KABRAEXTRU</t>
+          <t>HLEGLAS</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -3277,22 +3277,22 @@
         </is>
       </c>
       <c r="D97" s="3" t="n">
-        <v>634.97</v>
+        <v>368.85</v>
       </c>
       <c r="E97" s="3" t="n">
-        <v>594.5</v>
+        <v>342.52</v>
       </c>
       <c r="F97" s="3" t="n">
-        <v>662.95</v>
+        <v>367.6</v>
       </c>
       <c r="G97" s="3" t="n">
-        <v>659</v>
+        <v>368</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>KAMATHOTEL</t>
+          <t>HONASA</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -3306,22 +3306,22 @@
         </is>
       </c>
       <c r="D98" s="3" t="n">
-        <v>229.96</v>
+        <v>479.78</v>
       </c>
       <c r="E98" s="3" t="n">
-        <v>220.32</v>
+        <v>466.62</v>
       </c>
       <c r="F98" s="3" t="n">
-        <v>226.46</v>
+        <v>475.65</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>227.95</v>
+        <v>474.8</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>KAYA</t>
+          <t>HTEL</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -3335,22 +3335,22 @@
         </is>
       </c>
       <c r="D99" s="3" t="n">
-        <v>356.82</v>
+        <v>78.09</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>346.03</v>
+        <v>75.68000000000001</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>350</v>
+        <v>81.53</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>350</v>
+        <v>81.53</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>KESORAMIND</t>
+          <t>HUHTAMAKI</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
@@ -3364,22 +3364,22 @@
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>11.24</v>
+        <v>268.33</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>11.19</v>
+        <v>251.37</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>11.55</v>
+        <v>262.05</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>11.55</v>
+        <v>261.9</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>KILITCH</t>
+          <t>IITL</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
@@ -3393,22 +3393,22 @@
         </is>
       </c>
       <c r="D101" s="3" t="n">
-        <v>186.38</v>
+        <v>151.03</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>178.77</v>
+        <v>142.69</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>188.45</v>
+        <v>147.23</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>187</v>
+        <v>154.5</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>KISSHT</t>
+          <t>IKIO</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
@@ -3422,22 +3422,22 @@
         </is>
       </c>
       <c r="D102" s="3" t="n">
-        <v>325.47</v>
+        <v>225.37</v>
       </c>
       <c r="E102" s="3" t="n">
-        <v>311.1</v>
+        <v>213.34</v>
       </c>
       <c r="F102" s="3" t="n">
-        <v>322.85</v>
+        <v>231.73</v>
       </c>
       <c r="G102" s="3" t="n">
-        <v>324</v>
+        <v>231.5</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>KOTHARIPET</t>
+          <t>INA</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
@@ -3451,22 +3451,22 @@
         </is>
       </c>
       <c r="D103" s="3" t="n">
-        <v>139.42</v>
+        <v>94.23</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>134.09</v>
+        <v>89.78</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>148.9</v>
+        <v>93</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>148.2</v>
+        <v>92.94</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>KPL</t>
+          <t>INDIQUBE</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
@@ -3480,22 +3480,22 @@
         </is>
       </c>
       <c r="D104" s="3" t="n">
-        <v>3549.63</v>
+        <v>207.15</v>
       </c>
       <c r="E104" s="3" t="n">
-        <v>3349.73</v>
+        <v>195.56</v>
       </c>
       <c r="F104" s="3" t="n">
-        <v>3577</v>
+        <v>205.56</v>
       </c>
       <c r="G104" s="3" t="n">
-        <v>3569.9</v>
+        <v>205</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>KRBL</t>
+          <t>INDOMIM</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
@@ -3509,22 +3509,22 @@
         </is>
       </c>
       <c r="D105" s="3" t="n">
-        <v>438.02</v>
+        <v>1005.17</v>
       </c>
       <c r="E105" s="3" t="n">
-        <v>422.33</v>
+        <v>962.5</v>
       </c>
       <c r="F105" s="3" t="n">
-        <v>434.45</v>
+        <v>1006.55</v>
       </c>
       <c r="G105" s="3" t="n">
-        <v>433.3</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>KRISHNADEF</t>
+          <t>INDORAMA</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
@@ -3538,22 +3538,22 @@
         </is>
       </c>
       <c r="D106" s="3" t="n">
-        <v>1082.4</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>1033</v>
+        <v>75.44</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>1087.2</v>
+        <v>82.93000000000001</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>1080</v>
+        <v>83.2</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>KRITI</t>
+          <t>INDOTHAI</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
@@ -3567,22 +3567,22 @@
         </is>
       </c>
       <c r="D107" s="3" t="n">
-        <v>63.78</v>
+        <v>40.78</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>60.03</v>
+        <v>39.59</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>60.95</v>
+        <v>43.43</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>60.93</v>
+        <v>43.43</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>KRN</t>
+          <t>INDRAMEDCO</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
@@ -3596,22 +3596,22 @@
         </is>
       </c>
       <c r="D108" s="3" t="n">
-        <v>1640.67</v>
+        <v>359.48</v>
       </c>
       <c r="E108" s="3" t="n">
-        <v>1560.7</v>
+        <v>353.05</v>
       </c>
       <c r="F108" s="3" t="n">
-        <v>1597.3</v>
+        <v>360</v>
       </c>
       <c r="G108" s="3" t="n">
-        <v>1599</v>
+        <v>360.5</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>KSHINTL</t>
+          <t>INFIBEAM</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
@@ -3625,22 +3625,22 @@
         </is>
       </c>
       <c r="D109" s="3" t="n">
-        <v>1140.63</v>
+        <v>16.54</v>
       </c>
       <c r="E109" s="3" t="n">
-        <v>1084</v>
+        <v>15.65</v>
       </c>
       <c r="F109" s="3" t="n">
-        <v>1152.05</v>
+        <v>16.9</v>
       </c>
       <c r="G109" s="3" t="n">
-        <v>1149</v>
+        <v>16.84</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>KSHITIJ-RE</t>
+          <t>INOXGREEN</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
@@ -3654,22 +3654,22 @@
         </is>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>177.07</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>170.88</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>0.08</v>
+        <v>178.12</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>0.08</v>
+        <v>179</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>KSR</t>
+          <t>INOXWIND</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
@@ -3683,22 +3683,22 @@
         </is>
       </c>
       <c r="D111" s="3" t="n">
-        <v>36.28</v>
+        <v>77.15000000000001</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>33.81</v>
+        <v>74.98999999999999</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>39.19</v>
+        <v>76.02</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>39.19</v>
+        <v>76.02</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>LINC</t>
+          <t>INVPRECQ</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
@@ -3712,22 +3712,22 @@
         </is>
       </c>
       <c r="D112" s="3" t="n">
-        <v>98.5</v>
+        <v>1342.87</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>95.09</v>
+        <v>1342.87</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>98.09999999999999</v>
+        <v>1378.3</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>98.79000000000001</v>
+        <v>1378.3</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDADD</t>
+          <t>JAMNAAUTO</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
@@ -3741,22 +3741,22 @@
         </is>
       </c>
       <c r="D113" s="3" t="n">
-        <v>1143.8</v>
+        <v>130.72</v>
       </c>
       <c r="E113" s="3" t="n">
-        <v>1143.67</v>
+        <v>124.82</v>
       </c>
       <c r="F113" s="3" t="n">
-        <v>1143.91</v>
+        <v>131.86</v>
       </c>
       <c r="G113" s="3" t="n">
-        <v>1143.9</v>
+        <v>132.18</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDBETF</t>
+          <t>JUBLPHARMA</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
@@ -3770,22 +3770,22 @@
         </is>
       </c>
       <c r="D114" s="3" t="n">
-        <v>1097.82</v>
+        <v>1001.62</v>
       </c>
       <c r="E114" s="3" t="n">
-        <v>1097.8</v>
+        <v>971.65</v>
       </c>
       <c r="F114" s="3" t="n">
-        <v>1098.02</v>
+        <v>1025.65</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>1098.02</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDCASE</t>
+          <t>KABRAEXTRU</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
@@ -3799,22 +3799,22 @@
         </is>
       </c>
       <c r="D115" s="3" t="n">
-        <v>115.83</v>
+        <v>679.3200000000001</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>115.81</v>
+        <v>626.05</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>115.83</v>
+        <v>707.55</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>115.84</v>
+        <v>707</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDPLUS</t>
+          <t>KALYANKJIL</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
@@ -3828,22 +3828,22 @@
         </is>
       </c>
       <c r="D116" s="3" t="n">
-        <v>1102.51</v>
+        <v>613.67</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>1102.11</v>
+        <v>598.9299999999999</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>1102.39</v>
+        <v>615.2</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>1102.39</v>
+        <v>615.2</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDSHRI</t>
+          <t>KANORICHEM</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
@@ -3857,22 +3857,22 @@
         </is>
       </c>
       <c r="D117" s="3" t="n">
-        <v>1120.48</v>
+        <v>166.49</v>
       </c>
       <c r="E117" s="3" t="n">
-        <v>1120.46</v>
+        <v>161.2</v>
       </c>
       <c r="F117" s="3" t="n">
-        <v>1120.66</v>
+        <v>175.14</v>
       </c>
       <c r="G117" s="3" t="n">
-        <v>1120.66</v>
+        <v>175.14</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>LTFOODS</t>
+          <t>KESORAMIND</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
@@ -3886,22 +3886,22 @@
         </is>
       </c>
       <c r="D118" s="3" t="n">
-        <v>454.12</v>
+        <v>11.48</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>442.72</v>
+        <v>11.48</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>453.55</v>
+        <v>11.78</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>452.6</v>
+        <v>11.78</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>LYKALABS</t>
+          <t>KINGFA</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
@@ -3915,22 +3915,22 @@
         </is>
       </c>
       <c r="D119" s="3" t="n">
-        <v>80.47</v>
+        <v>6210.83</v>
       </c>
       <c r="E119" s="3" t="n">
-        <v>80.47</v>
+        <v>5994</v>
       </c>
       <c r="F119" s="3" t="n">
-        <v>83.14</v>
+        <v>6227.5</v>
       </c>
       <c r="G119" s="3" t="n">
-        <v>83.14</v>
+        <v>6185.5</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>MAFANG</t>
+          <t>KMCSHIL</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
@@ -3944,22 +3944,22 @@
         </is>
       </c>
       <c r="D120" s="3" t="n">
-        <v>230.01</v>
+        <v>139.26</v>
       </c>
       <c r="E120" s="3" t="n">
-        <v>213.67</v>
+        <v>135.37</v>
       </c>
       <c r="F120" s="3" t="n">
-        <v>228.06</v>
+        <v>137.45</v>
       </c>
       <c r="G120" s="3" t="n">
-        <v>231.4</v>
+        <v>137.8</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>MAJESAUT</t>
+          <t>KOTIC</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
@@ -3973,22 +3973,22 @@
         </is>
       </c>
       <c r="D121" s="3" t="n">
-        <v>358.9</v>
+        <v>145.29</v>
       </c>
       <c r="E121" s="3" t="n">
-        <v>348.8</v>
+        <v>133.05</v>
       </c>
       <c r="F121" s="3" t="n">
-        <v>360.5</v>
+        <v>151.21</v>
       </c>
       <c r="G121" s="3" t="n">
-        <v>360.5</v>
+        <v>147</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>MALUPAPER</t>
+          <t>KOVAI</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
@@ -4002,22 +4002,22 @@
         </is>
       </c>
       <c r="D122" s="3" t="n">
-        <v>34.34</v>
+        <v>6252.33</v>
       </c>
       <c r="E122" s="3" t="n">
-        <v>32.31</v>
+        <v>6072.33</v>
       </c>
       <c r="F122" s="3" t="n">
-        <v>34.81</v>
+        <v>6292</v>
       </c>
       <c r="G122" s="3" t="n">
-        <v>34.92</v>
+        <v>6350</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>MAMATA</t>
+          <t>KROSS</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
@@ -4031,22 +4031,22 @@
         </is>
       </c>
       <c r="D123" s="3" t="n">
-        <v>427.2</v>
+        <v>224.9</v>
       </c>
       <c r="E123" s="3" t="n">
-        <v>407.08</v>
+        <v>212.34</v>
       </c>
       <c r="F123" s="3" t="n">
-        <v>419.4</v>
+        <v>231.54</v>
       </c>
       <c r="G123" s="3" t="n">
-        <v>418.9</v>
+        <v>233</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>MANAKCOAT</t>
+          <t>KSHITIJ-RE</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
@@ -4060,22 +4060,22 @@
         </is>
       </c>
       <c r="D124" s="3" t="n">
-        <v>124.48</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>121.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>126.42</v>
+        <v>0.08</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>127.79</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>MANAKSIA</t>
+          <t>KSR</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
@@ -4089,22 +4089,22 @@
         </is>
       </c>
       <c r="D125" s="3" t="n">
-        <v>67.06</v>
+        <v>38.43</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>62.61</v>
+        <v>36.18</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>66.20999999999999</v>
+        <v>40.93</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>66.06</v>
+        <v>41.14</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>MANORAMA</t>
+          <t>LADDERUP</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
@@ -4118,22 +4118,22 @@
         </is>
       </c>
       <c r="D126" s="3" t="n">
-        <v>2060.37</v>
+        <v>55.38</v>
       </c>
       <c r="E126" s="3" t="n">
-        <v>1995.83</v>
+        <v>47.95</v>
       </c>
       <c r="F126" s="3" t="n">
-        <v>2093.3</v>
+        <v>61.93</v>
       </c>
       <c r="G126" s="3" t="n">
-        <v>2085.2</v>
+        <v>61.93</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>MARKSANS</t>
+          <t>LALITHAA</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
@@ -4147,22 +4147,22 @@
         </is>
       </c>
       <c r="D127" s="3" t="n">
-        <v>338.15</v>
+        <v>335.42</v>
       </c>
       <c r="E127" s="3" t="n">
-        <v>326.28</v>
+        <v>320.45</v>
       </c>
       <c r="F127" s="3" t="n">
-        <v>330.15</v>
+        <v>337.6</v>
       </c>
       <c r="G127" s="3" t="n">
-        <v>329.2</v>
+        <v>338.65</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>MASPTOP50</t>
+          <t>LATTEYS</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
@@ -4176,22 +4176,22 @@
         </is>
       </c>
       <c r="D128" s="3" t="n">
-        <v>93.06</v>
+        <v>21.69</v>
       </c>
       <c r="E128" s="3" t="n">
-        <v>85.72</v>
+        <v>20.77</v>
       </c>
       <c r="F128" s="3" t="n">
-        <v>100.76</v>
+        <v>21.53</v>
       </c>
       <c r="G128" s="3" t="n">
-        <v>101.5</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>MAXESTATES</t>
+          <t>LIQUIDADD</t>
         </is>
       </c>
       <c r="B129" s="3" t="inlineStr">
@@ -4205,22 +4205,22 @@
         </is>
       </c>
       <c r="D129" s="3" t="n">
-        <v>549.55</v>
+        <v>1143.94</v>
       </c>
       <c r="E129" s="3" t="n">
-        <v>529.83</v>
+        <v>1143.85</v>
       </c>
       <c r="F129" s="3" t="n">
-        <v>546.1</v>
+        <v>1144.03</v>
       </c>
       <c r="G129" s="3" t="n">
-        <v>548.4</v>
+        <v>1144.04</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>MBECL</t>
+          <t>LIQUIDBETF</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
@@ -4234,22 +4234,22 @@
         </is>
       </c>
       <c r="D130" s="3" t="n">
-        <v>285.65</v>
+        <v>1097.99</v>
       </c>
       <c r="E130" s="3" t="n">
-        <v>285.65</v>
+        <v>1097.97</v>
       </c>
       <c r="F130" s="3" t="n">
-        <v>299.69</v>
+        <v>1098.14</v>
       </c>
       <c r="G130" s="3" t="n">
-        <v>299.69</v>
+        <v>1098.13</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>MCX</t>
+          <t>LIQUIDCASE</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
@@ -4263,22 +4263,22 @@
         </is>
       </c>
       <c r="D131" s="3" t="n">
-        <v>3353.27</v>
+        <v>115.84</v>
       </c>
       <c r="E131" s="3" t="n">
-        <v>3255.33</v>
+        <v>115.82</v>
       </c>
       <c r="F131" s="3" t="n">
-        <v>3350</v>
+        <v>115.84</v>
       </c>
       <c r="G131" s="3" t="n">
-        <v>3350</v>
+        <v>115.85</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>MEDICAMEQ</t>
+          <t>LIQUIDSHRI</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
@@ -4292,22 +4292,22 @@
         </is>
       </c>
       <c r="D132" s="3" t="n">
-        <v>294.05</v>
+        <v>1120.64</v>
       </c>
       <c r="E132" s="3" t="n">
-        <v>269.23</v>
+        <v>1120.62</v>
       </c>
       <c r="F132" s="3" t="n">
-        <v>312.9</v>
+        <v>1120.8</v>
       </c>
       <c r="G132" s="3" t="n">
-        <v>314.9</v>
+        <v>1120.81</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>MEDICAPQ</t>
+          <t>LYKALABS</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
@@ -4321,22 +4321,22 @@
         </is>
       </c>
       <c r="D133" s="3" t="n">
-        <v>28.53</v>
+        <v>82.62</v>
       </c>
       <c r="E133" s="3" t="n">
-        <v>25.33</v>
+        <v>82.09</v>
       </c>
       <c r="F133" s="3" t="n">
-        <v>30.74</v>
+        <v>84.2</v>
       </c>
       <c r="G133" s="3" t="n">
-        <v>30.74</v>
+        <v>84.2</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>MENNPIS</t>
+          <t>MADHAV</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
@@ -4350,22 +4350,22 @@
         </is>
       </c>
       <c r="D134" s="3" t="n">
-        <v>82.81999999999999</v>
+        <v>36.42</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>77.33</v>
+        <v>34.86</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>80.43000000000001</v>
+        <v>36.89</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>80.48</v>
+        <v>36.89</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>METROBRAND</t>
+          <t>MANAKCOAT</t>
         </is>
       </c>
       <c r="B135" s="3" t="inlineStr">
@@ -4379,22 +4379,22 @@
         </is>
       </c>
       <c r="D135" s="3" t="n">
-        <v>946.42</v>
+        <v>128.06</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>922.48</v>
+        <v>122.35</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>959</v>
+        <v>124.37</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>956.8</v>
+        <v>123.91</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>MIDHANI</t>
+          <t>MANAKSIA</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
@@ -4408,22 +4408,22 @@
         </is>
       </c>
       <c r="D136" s="3" t="n">
-        <v>444.22</v>
+        <v>70.13</v>
       </c>
       <c r="E136" s="3" t="n">
-        <v>429.82</v>
+        <v>65.16</v>
       </c>
       <c r="F136" s="3" t="n">
-        <v>463.8</v>
+        <v>70.51000000000001</v>
       </c>
       <c r="G136" s="3" t="n">
-        <v>463.7</v>
+        <v>70.40000000000001</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>MMP</t>
+          <t>MANIPALHOS</t>
         </is>
       </c>
       <c r="B137" s="3" t="inlineStr">
@@ -4437,22 +4437,22 @@
         </is>
       </c>
       <c r="D137" s="3" t="n">
-        <v>447.85</v>
+        <v>739.23</v>
       </c>
       <c r="E137" s="3" t="n">
-        <v>413.62</v>
+        <v>719.28</v>
       </c>
       <c r="F137" s="3" t="n">
-        <v>460.25</v>
+        <v>733.25</v>
       </c>
       <c r="G137" s="3" t="n">
-        <v>466</v>
+        <v>731.4</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>MODEFENCE</t>
+          <t>MAXESTATES</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
@@ -4466,22 +4466,22 @@
         </is>
       </c>
       <c r="D138" s="3" t="n">
-        <v>109.01</v>
+        <v>554.8200000000001</v>
       </c>
       <c r="E138" s="3" t="n">
-        <v>107.23</v>
+        <v>532.6799999999999</v>
       </c>
       <c r="F138" s="3" t="n">
-        <v>108.87</v>
+        <v>559.75</v>
       </c>
       <c r="G138" s="3" t="n">
-        <v>109</v>
+        <v>559.5</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>MODINATUR</t>
+          <t>MAYURUNIQ</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
@@ -4495,22 +4495,22 @@
         </is>
       </c>
       <c r="D139" s="3" t="n">
-        <v>351.92</v>
+        <v>752.48</v>
       </c>
       <c r="E139" s="3" t="n">
-        <v>337.35</v>
+        <v>722.7</v>
       </c>
       <c r="F139" s="3" t="n">
-        <v>349.1</v>
+        <v>756.55</v>
       </c>
       <c r="G139" s="3" t="n">
-        <v>346.05</v>
+        <v>755</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>MOLDTECH</t>
+          <t>MBECL</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
@@ -4524,22 +4524,22 @@
         </is>
       </c>
       <c r="D140" s="3" t="n">
-        <v>219.6</v>
+        <v>299.93</v>
       </c>
       <c r="E140" s="3" t="n">
-        <v>206.5</v>
+        <v>299.93</v>
       </c>
       <c r="F140" s="3" t="n">
-        <v>212.51</v>
+        <v>314.67</v>
       </c>
       <c r="G140" s="3" t="n">
-        <v>213</v>
+        <v>314.67</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>MOM30IETF</t>
+          <t>MEDANTA</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
@@ -4553,22 +4553,22 @@
         </is>
       </c>
       <c r="D141" s="3" t="n">
-        <v>31.72</v>
+        <v>1485.5</v>
       </c>
       <c r="E141" s="3" t="n">
-        <v>30.98</v>
+        <v>1432.4</v>
       </c>
       <c r="F141" s="3" t="n">
-        <v>31.54</v>
+        <v>1459.6</v>
       </c>
       <c r="G141" s="3" t="n">
-        <v>31.5</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>MOMENTUM50</t>
+          <t>MEDICAMEQ</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
@@ -4582,22 +4582,22 @@
         </is>
       </c>
       <c r="D142" s="3" t="n">
-        <v>54.91</v>
+        <v>310.73</v>
       </c>
       <c r="E142" s="3" t="n">
-        <v>54.21</v>
+        <v>282.8</v>
       </c>
       <c r="F142" s="3" t="n">
-        <v>54.96</v>
+        <v>307.5</v>
       </c>
       <c r="G142" s="3" t="n">
-        <v>54.85</v>
+        <v>302</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>MOMMIDCAP</t>
+          <t>MEDICAPQ</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
@@ -4611,22 +4611,22 @@
         </is>
       </c>
       <c r="D143" s="3" t="n">
-        <v>13.11</v>
+        <v>31.81</v>
       </c>
       <c r="E143" s="3" t="n">
-        <v>12.99</v>
+        <v>27.32</v>
       </c>
       <c r="F143" s="3" t="n">
-        <v>13.12</v>
+        <v>35.22</v>
       </c>
       <c r="G143" s="3" t="n">
-        <v>13.14</v>
+        <v>34.94</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>MON100</t>
+          <t>MEESHO</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
@@ -4640,22 +4640,22 @@
         </is>
       </c>
       <c r="D144" s="3" t="n">
-        <v>339.85</v>
+        <v>216.61</v>
       </c>
       <c r="E144" s="3" t="n">
-        <v>329.22</v>
+        <v>209.59</v>
       </c>
       <c r="F144" s="3" t="n">
-        <v>340.57</v>
+        <v>217.91</v>
       </c>
       <c r="G144" s="3" t="n">
-        <v>342</v>
+        <v>217.55</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>MONQ50</t>
+          <t>MERCURYEV</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
@@ -4669,22 +4669,22 @@
         </is>
       </c>
       <c r="D145" s="3" t="n">
-        <v>182.39</v>
+        <v>39.52</v>
       </c>
       <c r="E145" s="3" t="n">
-        <v>160.05</v>
+        <v>36.24</v>
       </c>
       <c r="F145" s="3" t="n">
-        <v>213.01</v>
+        <v>41.61</v>
       </c>
       <c r="G145" s="3" t="n">
-        <v>214.08</v>
+        <v>41.61</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>MTARTECH</t>
+          <t>METROGLOBL</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
@@ -4698,22 +4698,22 @@
         </is>
       </c>
       <c r="D146" s="3" t="n">
-        <v>7541.67</v>
+        <v>142.65</v>
       </c>
       <c r="E146" s="3" t="n">
-        <v>7143.33</v>
+        <v>135.08</v>
       </c>
       <c r="F146" s="3" t="n">
-        <v>7501</v>
+        <v>140.97</v>
       </c>
       <c r="G146" s="3" t="n">
-        <v>7501</v>
+        <v>143</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>MUKANDLTD</t>
+          <t>METROPOLIS</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
@@ -4727,22 +4727,22 @@
         </is>
       </c>
       <c r="D147" s="3" t="n">
-        <v>138.26</v>
+        <v>600.4</v>
       </c>
       <c r="E147" s="3" t="n">
-        <v>133.81</v>
+        <v>581.9</v>
       </c>
       <c r="F147" s="3" t="n">
-        <v>139.69</v>
+        <v>595.65</v>
       </c>
       <c r="G147" s="3" t="n">
-        <v>140.9</v>
+        <v>595</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>MVELECTRO</t>
+          <t>MIDHANI</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
@@ -4756,22 +4756,22 @@
         </is>
       </c>
       <c r="D148" s="3" t="n">
-        <v>902.3</v>
+        <v>461.95</v>
       </c>
       <c r="E148" s="3" t="n">
-        <v>806.73</v>
+        <v>444.52</v>
       </c>
       <c r="F148" s="3" t="n">
-        <v>917.5</v>
+        <v>463.35</v>
       </c>
       <c r="G148" s="3" t="n">
-        <v>912</v>
+        <v>464.3</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>MVGJL</t>
+          <t>MOALPHA50</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
@@ -4785,22 +4785,22 @@
         </is>
       </c>
       <c r="D149" s="3" t="n">
-        <v>209.34</v>
+        <v>56.93</v>
       </c>
       <c r="E149" s="3" t="n">
-        <v>184.9</v>
+        <v>56.08</v>
       </c>
       <c r="F149" s="3" t="n">
-        <v>214.64</v>
+        <v>56.43</v>
       </c>
       <c r="G149" s="3" t="n">
-        <v>215</v>
+        <v>56.35</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>MYSORPETRO</t>
+          <t>MOLBIO</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
@@ -4814,22 +4814,22 @@
         </is>
       </c>
       <c r="D150" s="3" t="n">
-        <v>140.22</v>
+        <v>1319.3</v>
       </c>
       <c r="E150" s="3" t="n">
-        <v>134.65</v>
+        <v>1164.23</v>
       </c>
       <c r="F150" s="3" t="n">
-        <v>147.09</v>
+        <v>1509.4</v>
       </c>
       <c r="G150" s="3" t="n">
-        <v>147.09</v>
+        <v>1509.4</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>NECCLTD</t>
+          <t>MOSILVER</t>
         </is>
       </c>
       <c r="B151" s="3" t="inlineStr">
@@ -4843,22 +4843,22 @@
         </is>
       </c>
       <c r="D151" s="3" t="n">
-        <v>19.25</v>
+        <v>231.24</v>
       </c>
       <c r="E151" s="3" t="n">
-        <v>18.63</v>
+        <v>228.59</v>
       </c>
       <c r="F151" s="3" t="n">
-        <v>19.59</v>
+        <v>230.84</v>
       </c>
       <c r="G151" s="3" t="n">
-        <v>19.4</v>
+        <v>231.05</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>NELCO</t>
+          <t>MRPL</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
@@ -4872,22 +4872,22 @@
         </is>
       </c>
       <c r="D152" s="3" t="n">
-        <v>959.22</v>
+        <v>185.26</v>
       </c>
       <c r="E152" s="3" t="n">
-        <v>923.4299999999999</v>
+        <v>173.82</v>
       </c>
       <c r="F152" s="3" t="n">
-        <v>958.3</v>
+        <v>181.32</v>
       </c>
       <c r="G152" s="3" t="n">
-        <v>958</v>
+        <v>181</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>NEOGEN</t>
+          <t>MUKANDLTD</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
@@ -4901,22 +4901,22 @@
         </is>
       </c>
       <c r="D153" s="3" t="n">
-        <v>2251.07</v>
+        <v>142.13</v>
       </c>
       <c r="E153" s="3" t="n">
-        <v>2155.5</v>
+        <v>136.1</v>
       </c>
       <c r="F153" s="3" t="n">
-        <v>2255.2</v>
+        <v>142.57</v>
       </c>
       <c r="G153" s="3" t="n">
-        <v>2247.7</v>
+        <v>141.6</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>NESCO</t>
+          <t>MYSORPETRO</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
@@ -4930,22 +4930,22 @@
         </is>
       </c>
       <c r="D154" s="3" t="n">
-        <v>1095</v>
+        <v>147.21</v>
       </c>
       <c r="E154" s="3" t="n">
-        <v>1058.2</v>
+        <v>140.73</v>
       </c>
       <c r="F154" s="3" t="n">
-        <v>1096.9</v>
+        <v>148.52</v>
       </c>
       <c r="G154" s="3" t="n">
-        <v>1096.5</v>
+        <v>148.5</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>NATIONSTD</t>
         </is>
       </c>
       <c r="B155" s="3" t="inlineStr">
@@ -4959,22 +4959,22 @@
         </is>
       </c>
       <c r="D155" s="3" t="n">
-        <v>1913.13</v>
+        <v>114.81</v>
       </c>
       <c r="E155" s="3" t="n">
-        <v>1863.43</v>
+        <v>108.07</v>
       </c>
       <c r="F155" s="3" t="n">
-        <v>1890.6</v>
+        <v>115.89</v>
       </c>
       <c r="G155" s="3" t="n">
-        <v>1887.2</v>
+        <v>113.04</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>NIFMID150</t>
+          <t>NAZARA</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
@@ -4988,22 +4988,22 @@
         </is>
       </c>
       <c r="D156" s="3" t="n">
-        <v>224.68</v>
+        <v>377.47</v>
       </c>
       <c r="E156" s="3" t="n">
-        <v>222.19</v>
+        <v>364.9</v>
       </c>
       <c r="F156" s="3" t="n">
-        <v>224.96</v>
+        <v>374.65</v>
       </c>
       <c r="G156" s="3" t="n">
-        <v>225.54</v>
+        <v>374.55</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>NOCIL</t>
+          <t>NEOGEN</t>
         </is>
       </c>
       <c r="B157" s="3" t="inlineStr">
@@ -5017,22 +5017,22 @@
         </is>
       </c>
       <c r="D157" s="3" t="n">
-        <v>179.95</v>
+        <v>2326.87</v>
       </c>
       <c r="E157" s="3" t="n">
-        <v>173.85</v>
+        <v>2191.5</v>
       </c>
       <c r="F157" s="3" t="n">
-        <v>188.28</v>
+        <v>2388.9</v>
       </c>
       <c r="G157" s="3" t="n">
-        <v>188.41</v>
+        <v>2388</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>NRAIL</t>
+          <t>NEUEON</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
@@ -5046,22 +5046,22 @@
         </is>
       </c>
       <c r="D158" s="3" t="n">
-        <v>625.42</v>
+        <v>12.22</v>
       </c>
       <c r="E158" s="3" t="n">
-        <v>561.67</v>
+        <v>11.37</v>
       </c>
       <c r="F158" s="3" t="n">
-        <v>611.2</v>
+        <v>12.05</v>
       </c>
       <c r="G158" s="3" t="n">
-        <v>613.05</v>
+        <v>12.19</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>NRBBEARING</t>
+          <t>NEXTMEDIA</t>
         </is>
       </c>
       <c r="B159" s="3" t="inlineStr">
@@ -5075,22 +5075,22 @@
         </is>
       </c>
       <c r="D159" s="3" t="n">
-        <v>478.08</v>
+        <v>3.98</v>
       </c>
       <c r="E159" s="3" t="n">
-        <v>457.75</v>
+        <v>3.74</v>
       </c>
       <c r="F159" s="3" t="n">
-        <v>484.55</v>
+        <v>3.89</v>
       </c>
       <c r="G159" s="3" t="n">
-        <v>488</v>
+        <v>3.81</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>ONIXSOLAR</t>
+          <t>NIFMID150</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
@@ -5104,22 +5104,22 @@
         </is>
       </c>
       <c r="D160" s="3" t="n">
-        <v>443.5</v>
+        <v>224.68</v>
       </c>
       <c r="E160" s="3" t="n">
-        <v>418.02</v>
+        <v>222.19</v>
       </c>
       <c r="F160" s="3" t="n">
-        <v>455.3</v>
+        <v>224.96</v>
       </c>
       <c r="G160" s="3" t="n">
-        <v>453</v>
+        <v>225.54</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>ORTINGLOBE</t>
+          <t>NOCIL</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
@@ -5133,22 +5133,22 @@
         </is>
       </c>
       <c r="D161" s="3" t="n">
-        <v>15.98</v>
+        <v>188.61</v>
       </c>
       <c r="E161" s="3" t="n">
-        <v>15.33</v>
+        <v>179.56</v>
       </c>
       <c r="F161" s="3" t="n">
-        <v>15.53</v>
+        <v>195.31</v>
       </c>
       <c r="G161" s="3" t="n">
-        <v>15.53</v>
+        <v>194.49</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>PAISALO</t>
+          <t>NORTHARC</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
@@ -5162,22 +5162,22 @@
         </is>
       </c>
       <c r="D162" s="3" t="n">
-        <v>78.23</v>
+        <v>312.75</v>
       </c>
       <c r="E162" s="3" t="n">
-        <v>73.8</v>
+        <v>303.22</v>
       </c>
       <c r="F162" s="3" t="n">
-        <v>79.92</v>
+        <v>309.15</v>
       </c>
       <c r="G162" s="3" t="n">
-        <v>79.98</v>
+        <v>310</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>PAKKA</t>
+          <t>NOVARTIND</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
@@ -5191,22 +5191,22 @@
         </is>
       </c>
       <c r="D163" s="3" t="n">
-        <v>77.95999999999999</v>
+        <v>2158.07</v>
       </c>
       <c r="E163" s="3" t="n">
-        <v>74.17</v>
+        <v>1895.2</v>
       </c>
       <c r="F163" s="3" t="n">
-        <v>78.13</v>
+        <v>2428.2</v>
       </c>
       <c r="G163" s="3" t="n">
-        <v>78.01000000000001</v>
+        <v>2420.8</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>PANAMAPET</t>
+          <t>NRBBEARING</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
@@ -5220,22 +5220,22 @@
         </is>
       </c>
       <c r="D164" s="3" t="n">
-        <v>502.58</v>
+        <v>499.45</v>
       </c>
       <c r="E164" s="3" t="n">
-        <v>480.07</v>
+        <v>470.22</v>
       </c>
       <c r="F164" s="3" t="n">
-        <v>498.4</v>
+        <v>515.95</v>
       </c>
       <c r="G164" s="3" t="n">
-        <v>498.5</v>
+        <v>516.5</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>PARADEEP</t>
+          <t>NURECA</t>
         </is>
       </c>
       <c r="B165" s="3" t="inlineStr">
@@ -5249,22 +5249,22 @@
         </is>
       </c>
       <c r="D165" s="3" t="n">
-        <v>159.11</v>
+        <v>336.57</v>
       </c>
       <c r="E165" s="3" t="n">
-        <v>155.22</v>
+        <v>321.55</v>
       </c>
       <c r="F165" s="3" t="n">
-        <v>157.92</v>
+        <v>343.55</v>
       </c>
       <c r="G165" s="3" t="n">
-        <v>157.8</v>
+        <v>342.5</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>PARAS</t>
+          <t>NYKAA</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
@@ -5278,22 +5278,22 @@
         </is>
       </c>
       <c r="D166" s="3" t="n">
-        <v>1494</v>
+        <v>342.72</v>
       </c>
       <c r="E166" s="3" t="n">
-        <v>1427.8</v>
+        <v>335.82</v>
       </c>
       <c r="F166" s="3" t="n">
-        <v>1470</v>
+        <v>341.95</v>
       </c>
       <c r="G166" s="3" t="n">
-        <v>1471</v>
+        <v>341.95</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>PARSVNATH</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="B167" s="3" t="inlineStr">
@@ -5307,22 +5307,22 @@
         </is>
       </c>
       <c r="D167" s="3" t="n">
-        <v>1.61</v>
+        <v>504.03</v>
       </c>
       <c r="E167" s="3" t="n">
-        <v>1.61</v>
+        <v>491.73</v>
       </c>
       <c r="F167" s="3" t="n">
-        <v>1.66</v>
+        <v>500.3</v>
       </c>
       <c r="G167" s="3" t="n">
-        <v>1.66</v>
+        <v>500.3</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>PENIND</t>
+          <t>OMNI</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
@@ -5336,22 +5336,22 @@
         </is>
       </c>
       <c r="D168" s="3" t="n">
-        <v>177.03</v>
+        <v>552.35</v>
       </c>
       <c r="E168" s="3" t="n">
-        <v>170.91</v>
+        <v>522.9</v>
       </c>
       <c r="F168" s="3" t="n">
-        <v>178.08</v>
+        <v>563.35</v>
       </c>
       <c r="G168" s="3" t="n">
-        <v>177.74</v>
+        <v>560</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>PFOCUS</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="B169" s="3" t="inlineStr">
@@ -5365,22 +5365,22 @@
         </is>
       </c>
       <c r="D169" s="3" t="n">
-        <v>315.43</v>
+        <v>238.35</v>
       </c>
       <c r="E169" s="3" t="n">
-        <v>300.4</v>
+        <v>234.13</v>
       </c>
       <c r="F169" s="3" t="n">
-        <v>316.3</v>
+        <v>237.27</v>
       </c>
       <c r="G169" s="3" t="n">
-        <v>316.3</v>
+        <v>237.27</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>PINELABS</t>
+          <t>ONWARDTEC</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
@@ -5394,22 +5394,22 @@
         </is>
       </c>
       <c r="D170" s="3" t="n">
-        <v>171.13</v>
+        <v>291.48</v>
       </c>
       <c r="E170" s="3" t="n">
-        <v>162.31</v>
+        <v>280.82</v>
       </c>
       <c r="F170" s="3" t="n">
-        <v>175.08</v>
+        <v>288.65</v>
       </c>
       <c r="G170" s="3" t="n">
-        <v>175.05</v>
+        <v>287</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>PIRAMALFIN</t>
+          <t>OSWALSEEDS</t>
         </is>
       </c>
       <c r="B171" s="3" t="inlineStr">
@@ -5423,22 +5423,22 @@
         </is>
       </c>
       <c r="D171" s="3" t="n">
-        <v>2291.83</v>
+        <v>13.83</v>
       </c>
       <c r="E171" s="3" t="n">
-        <v>2229.87</v>
+        <v>12.17</v>
       </c>
       <c r="F171" s="3" t="n">
-        <v>2310.5</v>
+        <v>14.75</v>
       </c>
       <c r="G171" s="3" t="n">
-        <v>2312.5</v>
+        <v>14.64</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>PKTEA</t>
+          <t>PAISALO</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
@@ -5452,22 +5452,22 @@
         </is>
       </c>
       <c r="D172" s="3" t="n">
-        <v>977.72</v>
+        <v>81.33</v>
       </c>
       <c r="E172" s="3" t="n">
-        <v>809.35</v>
+        <v>76.84999999999999</v>
       </c>
       <c r="F172" s="3" t="n">
-        <v>1136.3</v>
+        <v>83.05</v>
       </c>
       <c r="G172" s="3" t="n">
-        <v>1155</v>
+        <v>82.7</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>PODDARMENT</t>
+          <t>PARASPETRO</t>
         </is>
       </c>
       <c r="B173" s="3" t="inlineStr">
@@ -5481,22 +5481,22 @@
         </is>
       </c>
       <c r="D173" s="3" t="n">
-        <v>286.67</v>
+        <v>2.22</v>
       </c>
       <c r="E173" s="3" t="n">
-        <v>267.73</v>
+        <v>2.12</v>
       </c>
       <c r="F173" s="3" t="n">
-        <v>295.85</v>
+        <v>2.15</v>
       </c>
       <c r="G173" s="3" t="n">
-        <v>295.1</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>PPL</t>
+          <t>PARSVNATH</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
@@ -5510,22 +5510,22 @@
         </is>
       </c>
       <c r="D174" s="3" t="n">
-        <v>275.15</v>
+        <v>1.65</v>
       </c>
       <c r="E174" s="3" t="n">
-        <v>262.87</v>
+        <v>1.65</v>
       </c>
       <c r="F174" s="3" t="n">
-        <v>287.55</v>
+        <v>1.69</v>
       </c>
       <c r="G174" s="3" t="n">
-        <v>287.75</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>PPLPHARMA</t>
+          <t>PCBL</t>
         </is>
       </c>
       <c r="B175" s="3" t="inlineStr">
@@ -5539,22 +5539,22 @@
         </is>
       </c>
       <c r="D175" s="3" t="n">
-        <v>222.18</v>
+        <v>336.77</v>
       </c>
       <c r="E175" s="3" t="n">
-        <v>213.58</v>
+        <v>324.2</v>
       </c>
       <c r="F175" s="3" t="n">
-        <v>218</v>
+        <v>334.8</v>
       </c>
       <c r="G175" s="3" t="n">
-        <v>218.45</v>
+        <v>335.4</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>PRISMX</t>
+          <t>PKTEA</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
@@ -5568,22 +5568,22 @@
         </is>
       </c>
       <c r="D176" s="3" t="n">
-        <v>0.57</v>
+        <v>1097.38</v>
       </c>
       <c r="E176" s="3" t="n">
-        <v>0.54</v>
+        <v>920.13</v>
       </c>
       <c r="F176" s="3" t="n">
-        <v>0.57</v>
+        <v>1094.2</v>
       </c>
       <c r="G176" s="3" t="n">
-        <v>0.58</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>RAJOOENG</t>
+          <t>POWERGRID</t>
         </is>
       </c>
       <c r="B177" s="3" t="inlineStr">
@@ -5597,22 +5597,22 @@
         </is>
       </c>
       <c r="D177" s="3" t="n">
-        <v>54.03</v>
+        <v>269.93</v>
       </c>
       <c r="E177" s="3" t="n">
-        <v>51.02</v>
+        <v>264.68</v>
       </c>
       <c r="F177" s="3" t="n">
-        <v>55.9</v>
+        <v>271.75</v>
       </c>
       <c r="G177" s="3" t="n">
-        <v>56</v>
+        <v>271.75</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>RAYMOND</t>
+          <t>POWERICA</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
@@ -5626,22 +5626,22 @@
         </is>
       </c>
       <c r="D178" s="3" t="n">
-        <v>793.63</v>
+        <v>555.72</v>
       </c>
       <c r="E178" s="3" t="n">
-        <v>747.62</v>
+        <v>528.1</v>
       </c>
       <c r="F178" s="3" t="n">
-        <v>808.45</v>
+        <v>575.85</v>
       </c>
       <c r="G178" s="3" t="n">
-        <v>811.45</v>
+        <v>578.45</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>RBLBANK</t>
+          <t>PPL</t>
         </is>
       </c>
       <c r="B179" s="3" t="inlineStr">
@@ -5655,22 +5655,22 @@
         </is>
       </c>
       <c r="D179" s="3" t="n">
-        <v>418.57</v>
+        <v>285.78</v>
       </c>
       <c r="E179" s="3" t="n">
-        <v>409.75</v>
+        <v>271.17</v>
       </c>
       <c r="F179" s="3" t="n">
-        <v>416</v>
+        <v>290.9</v>
       </c>
       <c r="G179" s="3" t="n">
-        <v>416</v>
+        <v>291</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>RCOM</t>
+          <t>PRISMX</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
@@ -5684,22 +5684,22 @@
         </is>
       </c>
       <c r="D180" s="3" t="n">
-        <v>0.87</v>
+        <v>0.59</v>
       </c>
       <c r="E180" s="3" t="n">
-        <v>0.84</v>
+        <v>0.55</v>
       </c>
       <c r="F180" s="3" t="n">
-        <v>0.93</v>
+        <v>0.59</v>
       </c>
       <c r="G180" s="3" t="n">
-        <v>0.93</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>REDINGTON</t>
+          <t>PRSMJOHNSN</t>
         </is>
       </c>
       <c r="B181" s="3" t="inlineStr">
@@ -5713,22 +5713,22 @@
         </is>
       </c>
       <c r="D181" s="3" t="n">
-        <v>381.03</v>
+        <v>114.63</v>
       </c>
       <c r="E181" s="3" t="n">
-        <v>370.42</v>
+        <v>111.55</v>
       </c>
       <c r="F181" s="3" t="n">
-        <v>378.05</v>
+        <v>115.22</v>
       </c>
       <c r="G181" s="3" t="n">
-        <v>378.5</v>
+        <v>115.35</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>RISHABH</t>
+          <t>RAJOOENG</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
@@ -5742,22 +5742,22 @@
         </is>
       </c>
       <c r="D182" s="3" t="n">
-        <v>805.67</v>
+        <v>55.84</v>
       </c>
       <c r="E182" s="3" t="n">
-        <v>752.1799999999999</v>
+        <v>52.73</v>
       </c>
       <c r="F182" s="3" t="n">
-        <v>815.9</v>
+        <v>54.89</v>
       </c>
       <c r="G182" s="3" t="n">
-        <v>816.85</v>
+        <v>54.94</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>RKSWAMY</t>
+          <t>RAJRATAN</t>
         </is>
       </c>
       <c r="B183" s="3" t="inlineStr">
@@ -5771,22 +5771,22 @@
         </is>
       </c>
       <c r="D183" s="3" t="n">
-        <v>95.16</v>
+        <v>524.35</v>
       </c>
       <c r="E183" s="3" t="n">
-        <v>92.36</v>
+        <v>493.95</v>
       </c>
       <c r="F183" s="3" t="n">
-        <v>93.04000000000001</v>
+        <v>509.65</v>
       </c>
       <c r="G183" s="3" t="n">
-        <v>93</v>
+        <v>510</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>RMDRIP</t>
+          <t>RATNAMANI</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
@@ -5800,22 +5800,22 @@
         </is>
       </c>
       <c r="D184" s="3" t="n">
-        <v>22.61</v>
+        <v>2834.63</v>
       </c>
       <c r="E184" s="3" t="n">
-        <v>21.66</v>
+        <v>2712.8</v>
       </c>
       <c r="F184" s="3" t="n">
-        <v>23.89</v>
+        <v>2823</v>
       </c>
       <c r="G184" s="3" t="n">
-        <v>24.02</v>
+        <v>2802</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>ROLLT</t>
+          <t>RAYMOND</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">
@@ -5829,22 +5829,22 @@
         </is>
       </c>
       <c r="D185" s="3" t="n">
-        <v>4.63</v>
+        <v>827.83</v>
       </c>
       <c r="E185" s="3" t="n">
-        <v>4.35</v>
+        <v>773.42</v>
       </c>
       <c r="F185" s="3" t="n">
-        <v>4.7</v>
+        <v>853.85</v>
       </c>
       <c r="G185" s="3" t="n">
-        <v>4.75</v>
+        <v>849.9</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>ROSSTECH</t>
+          <t>RCOM</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
@@ -5858,22 +5858,22 @@
         </is>
       </c>
       <c r="D186" s="3" t="n">
-        <v>1193.9</v>
+        <v>0.92</v>
       </c>
       <c r="E186" s="3" t="n">
-        <v>1147.13</v>
+        <v>0.89</v>
       </c>
       <c r="F186" s="3" t="n">
-        <v>1193.7</v>
+        <v>0.97</v>
       </c>
       <c r="G186" s="3" t="n">
-        <v>1185.5</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>RPGLIFE</t>
+          <t>REDINGTON</t>
         </is>
       </c>
       <c r="B187" s="3" t="inlineStr">
@@ -5887,22 +5887,22 @@
         </is>
       </c>
       <c r="D187" s="3" t="n">
-        <v>2827.33</v>
+        <v>389.18</v>
       </c>
       <c r="E187" s="3" t="n">
-        <v>2695.33</v>
+        <v>374.78</v>
       </c>
       <c r="F187" s="3" t="n">
-        <v>2812</v>
+        <v>392</v>
       </c>
       <c r="G187" s="3" t="n">
-        <v>2796.1</v>
+        <v>395</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>RSL</t>
+          <t>RKFORGE</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
@@ -5916,22 +5916,22 @@
         </is>
       </c>
       <c r="D188" s="3" t="n">
-        <v>188.69</v>
+        <v>725.87</v>
       </c>
       <c r="E188" s="3" t="n">
-        <v>183.3</v>
+        <v>702.15</v>
       </c>
       <c r="F188" s="3" t="n">
-        <v>190.09</v>
+        <v>727.05</v>
       </c>
       <c r="G188" s="3" t="n">
-        <v>190.95</v>
+        <v>728</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>RUCHIRA</t>
+          <t>RMDRIP</t>
         </is>
       </c>
       <c r="B189" s="3" t="inlineStr">
@@ -5945,22 +5945,22 @@
         </is>
       </c>
       <c r="D189" s="3" t="n">
-        <v>110.72</v>
+        <v>23.6</v>
       </c>
       <c r="E189" s="3" t="n">
-        <v>106.7</v>
+        <v>22.33</v>
       </c>
       <c r="F189" s="3" t="n">
-        <v>109.8</v>
+        <v>23.33</v>
       </c>
       <c r="G189" s="3" t="n">
-        <v>110.15</v>
+        <v>23.99</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>RVHL</t>
+          <t>SABEVENTS</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
@@ -5974,22 +5974,22 @@
         </is>
       </c>
       <c r="D190" s="3" t="n">
-        <v>41.33</v>
+        <v>6.4</v>
       </c>
       <c r="E190" s="3" t="n">
-        <v>39.05</v>
+        <v>6.2</v>
       </c>
       <c r="F190" s="3" t="n">
-        <v>40.23</v>
+        <v>6.63</v>
       </c>
       <c r="G190" s="3" t="n">
-        <v>40.77</v>
+        <v>6.63</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>S&amp;SPOWER</t>
+          <t>SANATHAN</t>
         </is>
       </c>
       <c r="B191" s="3" t="inlineStr">
@@ -6003,22 +6003,22 @@
         </is>
       </c>
       <c r="D191" s="3" t="n">
-        <v>341.7</v>
+        <v>485.78</v>
       </c>
       <c r="E191" s="3" t="n">
-        <v>323.15</v>
+        <v>468.18</v>
       </c>
       <c r="F191" s="3" t="n">
-        <v>342.05</v>
+        <v>483.1</v>
       </c>
       <c r="G191" s="3" t="n">
-        <v>341</v>
+        <v>486.5</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>SABEVENTS</t>
+          <t>SANDHAR</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
@@ -6032,22 +6032,22 @@
         </is>
       </c>
       <c r="D192" s="3" t="n">
-        <v>6.4</v>
+        <v>637.1799999999999</v>
       </c>
       <c r="E192" s="3" t="n">
-        <v>6.2</v>
+        <v>620.3</v>
       </c>
       <c r="F192" s="3" t="n">
-        <v>6.63</v>
+        <v>627.25</v>
       </c>
       <c r="G192" s="3" t="n">
-        <v>6.63</v>
+        <v>625.05</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>SADHNANIQ</t>
+          <t>SANGINITA</t>
         </is>
       </c>
       <c r="B193" s="3" t="inlineStr">
@@ -6061,22 +6061,22 @@
         </is>
       </c>
       <c r="D193" s="3" t="n">
-        <v>2.77</v>
+        <v>62.74</v>
       </c>
       <c r="E193" s="3" t="n">
-        <v>2.75</v>
+        <v>62.74</v>
       </c>
       <c r="F193" s="3" t="n">
-        <v>2.81</v>
+        <v>64.39</v>
       </c>
       <c r="G193" s="3" t="n">
-        <v>2.81</v>
+        <v>64.39</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>SAKAR</t>
+          <t>SARDAEN</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
@@ -6090,22 +6090,22 @@
         </is>
       </c>
       <c r="D194" s="3" t="n">
-        <v>1107.32</v>
+        <v>541.7</v>
       </c>
       <c r="E194" s="3" t="n">
-        <v>1040.3</v>
+        <v>519.3</v>
       </c>
       <c r="F194" s="3" t="n">
-        <v>1152.35</v>
+        <v>537.25</v>
       </c>
       <c r="G194" s="3" t="n">
-        <v>1142</v>
+        <v>536.7</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>SANATHAN</t>
+          <t>SASTASUNDR</t>
         </is>
       </c>
       <c r="B195" s="3" t="inlineStr">
@@ -6119,22 +6119,22 @@
         </is>
       </c>
       <c r="D195" s="3" t="n">
-        <v>479.87</v>
+        <v>283.13</v>
       </c>
       <c r="E195" s="3" t="n">
-        <v>456.02</v>
+        <v>269.72</v>
       </c>
       <c r="F195" s="3" t="n">
-        <v>480.35</v>
+        <v>282.6</v>
       </c>
       <c r="G195" s="3" t="n">
-        <v>478.55</v>
+        <v>284.65</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>SANGINITA</t>
+          <t>SBC</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
@@ -6148,22 +6148,22 @@
         </is>
       </c>
       <c r="D196" s="3" t="n">
-        <v>61.11</v>
+        <v>48.73</v>
       </c>
       <c r="E196" s="3" t="n">
-        <v>61.11</v>
+        <v>46.92</v>
       </c>
       <c r="F196" s="3" t="n">
-        <v>63.13</v>
+        <v>48.05</v>
       </c>
       <c r="G196" s="3" t="n">
-        <v>63.13</v>
+        <v>48.09</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>SANSERA</t>
+          <t>SBILIQETF</t>
         </is>
       </c>
       <c r="B197" s="3" t="inlineStr">
@@ -6177,22 +6177,22 @@
         </is>
       </c>
       <c r="D197" s="3" t="n">
-        <v>3974.93</v>
+        <v>1055.13</v>
       </c>
       <c r="E197" s="3" t="n">
-        <v>3823.77</v>
+        <v>1055.11</v>
       </c>
       <c r="F197" s="3" t="n">
-        <v>4135.9</v>
+        <v>1055.27</v>
       </c>
       <c r="G197" s="3" t="n">
-        <v>4110</v>
+        <v>1055.29</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>SARLAPOLY</t>
+          <t>SBISILVER</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
@@ -6206,22 +6206,22 @@
         </is>
       </c>
       <c r="D198" s="3" t="n">
-        <v>103.16</v>
+        <v>229.39</v>
       </c>
       <c r="E198" s="3" t="n">
-        <v>99.19</v>
+        <v>226.54</v>
       </c>
       <c r="F198" s="3" t="n">
-        <v>101.46</v>
+        <v>229.15</v>
       </c>
       <c r="G198" s="3" t="n">
-        <v>102.5</v>
+        <v>229.2</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>SARVESHWAR</t>
+          <t>SECMARK</t>
         </is>
       </c>
       <c r="B199" s="3" t="inlineStr">
@@ -6235,22 +6235,22 @@
         </is>
       </c>
       <c r="D199" s="3" t="n">
-        <v>3.76</v>
+        <v>151.48</v>
       </c>
       <c r="E199" s="3" t="n">
-        <v>3.49</v>
+        <v>139.63</v>
       </c>
       <c r="F199" s="3" t="n">
-        <v>3.78</v>
+        <v>149.16</v>
       </c>
       <c r="G199" s="3" t="n">
-        <v>3.78</v>
+        <v>146.98</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>SASTASUNDR</t>
+          <t>SETFGOLD</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
@@ -6264,22 +6264,22 @@
         </is>
       </c>
       <c r="D200" s="3" t="n">
-        <v>283.13</v>
+        <v>130.37</v>
       </c>
       <c r="E200" s="3" t="n">
-        <v>269.72</v>
+        <v>129.19</v>
       </c>
       <c r="F200" s="3" t="n">
-        <v>282.6</v>
+        <v>130.26</v>
       </c>
       <c r="G200" s="3" t="n">
-        <v>284.65</v>
+        <v>130.36</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>SBC</t>
+          <t>SETL</t>
         </is>
       </c>
       <c r="B201" s="3" t="inlineStr">
@@ -6293,22 +6293,22 @@
         </is>
       </c>
       <c r="D201" s="3" t="n">
-        <v>47.9</v>
+        <v>427.8</v>
       </c>
       <c r="E201" s="3" t="n">
-        <v>45.4</v>
+        <v>410</v>
       </c>
       <c r="F201" s="3" t="n">
-        <v>48.68</v>
+        <v>445.9</v>
       </c>
       <c r="G201" s="3" t="n">
-        <v>48.7</v>
+        <v>445.9</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>SBILIQETF</t>
+          <t>SHAKTIPUMP</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr">
@@ -6322,22 +6322,22 @@
         </is>
       </c>
       <c r="D202" s="3" t="n">
-        <v>1054.97</v>
+        <v>492.28</v>
       </c>
       <c r="E202" s="3" t="n">
-        <v>1054.95</v>
+        <v>474.7</v>
       </c>
       <c r="F202" s="3" t="n">
-        <v>1055.16</v>
+        <v>503.2</v>
       </c>
       <c r="G202" s="3" t="n">
-        <v>1055.16</v>
+        <v>504</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>SHAILY</t>
+          <t>SHANTIGEAR</t>
         </is>
       </c>
       <c r="B203" s="3" t="inlineStr">
@@ -6351,22 +6351,22 @@
         </is>
       </c>
       <c r="D203" s="3" t="n">
-        <v>3397.23</v>
+        <v>711.35</v>
       </c>
       <c r="E203" s="3" t="n">
-        <v>3294.73</v>
+        <v>660.87</v>
       </c>
       <c r="F203" s="3" t="n">
-        <v>3455</v>
+        <v>725.45</v>
       </c>
       <c r="G203" s="3" t="n">
-        <v>3425.2</v>
+        <v>733</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>SHANTIGEAR</t>
+          <t>SHARDAMOTR</t>
         </is>
       </c>
       <c r="B204" s="3" t="inlineStr">
@@ -6380,22 +6380,22 @@
         </is>
       </c>
       <c r="D204" s="3" t="n">
-        <v>676.17</v>
+        <v>926.53</v>
       </c>
       <c r="E204" s="3" t="n">
-        <v>626.78</v>
+        <v>888.45</v>
       </c>
       <c r="F204" s="3" t="n">
-        <v>707.75</v>
+        <v>946.25</v>
       </c>
       <c r="G204" s="3" t="n">
-        <v>694</v>
+        <v>942.5</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>SHARDAMOTR</t>
+          <t>SHEKHAWATI</t>
         </is>
       </c>
       <c r="B205" s="3" t="inlineStr">
@@ -6409,22 +6409,22 @@
         </is>
       </c>
       <c r="D205" s="3" t="n">
-        <v>902.02</v>
+        <v>17.46</v>
       </c>
       <c r="E205" s="3" t="n">
-        <v>879.28</v>
+        <v>16.39</v>
       </c>
       <c r="F205" s="3" t="n">
-        <v>909.3</v>
+        <v>18.45</v>
       </c>
       <c r="G205" s="3" t="n">
-        <v>905</v>
+        <v>18.45</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>SHEKHAWATI</t>
+          <t>SHIVALIK</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr">
@@ -6438,22 +6438,22 @@
         </is>
       </c>
       <c r="D206" s="3" t="n">
-        <v>16.55</v>
+        <v>380.23</v>
       </c>
       <c r="E206" s="3" t="n">
-        <v>15.36</v>
+        <v>331.02</v>
       </c>
       <c r="F206" s="3" t="n">
-        <v>17.58</v>
+        <v>366.8</v>
       </c>
       <c r="G206" s="3" t="n">
-        <v>17.65</v>
+        <v>362.75</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>SHIVAUM</t>
+          <t>SHREEJISPG</t>
         </is>
       </c>
       <c r="B207" s="3" t="inlineStr">
@@ -6467,22 +6467,22 @@
         </is>
       </c>
       <c r="D207" s="3" t="n">
-        <v>459.8</v>
+        <v>713.58</v>
       </c>
       <c r="E207" s="3" t="n">
-        <v>453.02</v>
+        <v>692.03</v>
       </c>
       <c r="F207" s="3" t="n">
-        <v>464.35</v>
+        <v>713.1</v>
       </c>
       <c r="G207" s="3" t="n">
-        <v>465</v>
+        <v>713</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>SHREEJISPG</t>
+          <t>SIGACHI</t>
         </is>
       </c>
       <c r="B208" s="3" t="inlineStr">
@@ -6496,22 +6496,22 @@
         </is>
       </c>
       <c r="D208" s="3" t="n">
-        <v>701.08</v>
+        <v>36.63</v>
       </c>
       <c r="E208" s="3" t="n">
-        <v>676.4299999999999</v>
+        <v>34.5</v>
       </c>
       <c r="F208" s="3" t="n">
-        <v>713.1</v>
+        <v>37.56</v>
       </c>
       <c r="G208" s="3" t="n">
-        <v>714.9</v>
+        <v>37.6</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>SHUKRAPHAR</t>
+          <t>SIGMAADV</t>
         </is>
       </c>
       <c r="B209" s="3" t="inlineStr">
@@ -6525,22 +6525,22 @@
         </is>
       </c>
       <c r="D209" s="3" t="n">
-        <v>55.68</v>
+        <v>782.5</v>
       </c>
       <c r="E209" s="3" t="n">
-        <v>52.77</v>
+        <v>754</v>
       </c>
       <c r="F209" s="3" t="n">
-        <v>56.1</v>
+        <v>792.85</v>
       </c>
       <c r="G209" s="3" t="n">
-        <v>56.69</v>
+        <v>792.85</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>SIKKO</t>
+          <t>SIKA</t>
         </is>
       </c>
       <c r="B210" s="3" t="inlineStr">
@@ -6554,22 +6554,22 @@
         </is>
       </c>
       <c r="D210" s="3" t="n">
-        <v>5.57</v>
+        <v>1027.83</v>
       </c>
       <c r="E210" s="3" t="n">
-        <v>5.24</v>
+        <v>985.95</v>
       </c>
       <c r="F210" s="3" t="n">
-        <v>5.58</v>
+        <v>1024.85</v>
       </c>
       <c r="G210" s="3" t="n">
-        <v>5.62</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>SILVERETF</t>
+          <t>SIKKO</t>
         </is>
       </c>
       <c r="B211" s="3" t="inlineStr">
@@ -6583,22 +6583,22 @@
         </is>
       </c>
       <c r="D211" s="3" t="n">
-        <v>201.81</v>
+        <v>5.66</v>
       </c>
       <c r="E211" s="3" t="n">
-        <v>198.28</v>
+        <v>5.3</v>
       </c>
       <c r="F211" s="3" t="n">
-        <v>203.98</v>
+        <v>5.56</v>
       </c>
       <c r="G211" s="3" t="n">
-        <v>204</v>
+        <v>5.61</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>SKYGOLD</t>
+          <t>SILVER</t>
         </is>
       </c>
       <c r="B212" s="3" t="inlineStr">
@@ -6612,22 +6612,22 @@
         </is>
       </c>
       <c r="D212" s="3" t="n">
-        <v>809.02</v>
+        <v>233.81</v>
       </c>
       <c r="E212" s="3" t="n">
-        <v>770.03</v>
+        <v>231.01</v>
       </c>
       <c r="F212" s="3" t="n">
-        <v>832.2</v>
+        <v>233.49</v>
       </c>
       <c r="G212" s="3" t="n">
-        <v>831.9</v>
+        <v>233.89</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>SMALLCAP</t>
+          <t>SILVER1</t>
         </is>
       </c>
       <c r="B213" s="3" t="inlineStr">
@@ -6641,22 +6641,22 @@
         </is>
       </c>
       <c r="D213" s="3" t="n">
-        <v>49.48</v>
+        <v>22.73</v>
       </c>
       <c r="E213" s="3" t="n">
-        <v>48.62</v>
+        <v>22.45</v>
       </c>
       <c r="F213" s="3" t="n">
-        <v>49.35</v>
+        <v>22.71</v>
       </c>
       <c r="G213" s="3" t="n">
-        <v>49.3</v>
+        <v>22.72</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>SMCGLOBAL</t>
+          <t>SILVER360</t>
         </is>
       </c>
       <c r="B214" s="3" t="inlineStr">
@@ -6670,22 +6670,22 @@
         </is>
       </c>
       <c r="D214" s="3" t="n">
-        <v>84.26000000000001</v>
+        <v>230.42</v>
       </c>
       <c r="E214" s="3" t="n">
-        <v>80.41</v>
+        <v>226.75</v>
       </c>
       <c r="F214" s="3" t="n">
-        <v>83.93000000000001</v>
+        <v>230.33</v>
       </c>
       <c r="G214" s="3" t="n">
-        <v>84</v>
+        <v>230.5</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>SMLMAH</t>
+          <t>SILVERADD</t>
         </is>
       </c>
       <c r="B215" s="3" t="inlineStr">
@@ -6699,22 +6699,22 @@
         </is>
       </c>
       <c r="D215" s="3" t="n">
-        <v>6458.83</v>
+        <v>22.59</v>
       </c>
       <c r="E215" s="3" t="n">
-        <v>6050.83</v>
+        <v>22.29</v>
       </c>
       <c r="F215" s="3" t="n">
-        <v>6570</v>
+        <v>22.55</v>
       </c>
       <c r="G215" s="3" t="n">
-        <v>6529.5</v>
+        <v>22.55</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>SOFTTECH</t>
+          <t>SILVERAG</t>
         </is>
       </c>
       <c r="B216" s="3" t="inlineStr">
@@ -6728,22 +6728,22 @@
         </is>
       </c>
       <c r="D216" s="3" t="n">
-        <v>437.98</v>
+        <v>228.07</v>
       </c>
       <c r="E216" s="3" t="n">
-        <v>422.52</v>
+        <v>224.25</v>
       </c>
       <c r="F216" s="3" t="n">
-        <v>441.65</v>
+        <v>227.93</v>
       </c>
       <c r="G216" s="3" t="n">
-        <v>442</v>
+        <v>228.1</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>SOLARINDS</t>
+          <t>SILVERAXIS</t>
         </is>
       </c>
       <c r="B217" s="3" t="inlineStr">
@@ -6757,22 +6757,22 @@
         </is>
       </c>
       <c r="D217" s="3" t="n">
-        <v>22173.33</v>
+        <v>232.59</v>
       </c>
       <c r="E217" s="3" t="n">
-        <v>21675</v>
+        <v>229.84</v>
       </c>
       <c r="F217" s="3" t="n">
-        <v>22355</v>
+        <v>232.4</v>
       </c>
       <c r="G217" s="3" t="n">
-        <v>22355</v>
+        <v>232.89</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>SPCENET</t>
+          <t>SILVERBEES</t>
         </is>
       </c>
       <c r="B218" s="3" t="inlineStr">
@@ -6786,22 +6786,22 @@
         </is>
       </c>
       <c r="D218" s="3" t="n">
-        <v>3.6</v>
+        <v>223.6</v>
       </c>
       <c r="E218" s="3" t="n">
-        <v>3.43</v>
+        <v>221.12</v>
       </c>
       <c r="F218" s="3" t="n">
-        <v>3.57</v>
+        <v>223.53</v>
       </c>
       <c r="G218" s="3" t="n">
-        <v>3.59</v>
+        <v>223.83</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>SPECTRUM</t>
+          <t>SILVERBETA</t>
         </is>
       </c>
       <c r="B219" s="3" t="inlineStr">
@@ -6815,22 +6815,22 @@
         </is>
       </c>
       <c r="D219" s="3" t="n">
-        <v>2532.27</v>
+        <v>225.97</v>
       </c>
       <c r="E219" s="3" t="n">
-        <v>2398.67</v>
+        <v>222.52</v>
       </c>
       <c r="F219" s="3" t="n">
-        <v>2741.6</v>
+        <v>225.65</v>
       </c>
       <c r="G219" s="3" t="n">
-        <v>2741.6</v>
+        <v>226.02</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>SPLPETRO</t>
+          <t>SILVERBND</t>
         </is>
       </c>
       <c r="B220" s="3" t="inlineStr">
@@ -6844,22 +6844,22 @@
         </is>
       </c>
       <c r="D220" s="3" t="n">
-        <v>808.53</v>
+        <v>234.95</v>
       </c>
       <c r="E220" s="3" t="n">
-        <v>768.67</v>
+        <v>231.52</v>
       </c>
       <c r="F220" s="3" t="n">
-        <v>813.55</v>
+        <v>233.85</v>
       </c>
       <c r="G220" s="3" t="n">
-        <v>816</v>
+        <v>233.69</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>SREEL</t>
+          <t>SILVERCASE</t>
         </is>
       </c>
       <c r="B221" s="3" t="inlineStr">
@@ -6873,22 +6873,22 @@
         </is>
       </c>
       <c r="D221" s="3" t="n">
-        <v>299.94</v>
+        <v>23.71</v>
       </c>
       <c r="E221" s="3" t="n">
-        <v>269.83</v>
+        <v>23.41</v>
       </c>
       <c r="F221" s="3" t="n">
-        <v>345.01</v>
+        <v>23.72</v>
       </c>
       <c r="G221" s="3" t="n">
-        <v>345.01</v>
+        <v>23.74</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>STAR</t>
+          <t>SILVERETF</t>
         </is>
       </c>
       <c r="B222" s="3" t="inlineStr">
@@ -6902,22 +6902,22 @@
         </is>
       </c>
       <c r="D222" s="3" t="n">
-        <v>1157.03</v>
+        <v>201.81</v>
       </c>
       <c r="E222" s="3" t="n">
-        <v>1088.77</v>
+        <v>198.28</v>
       </c>
       <c r="F222" s="3" t="n">
-        <v>1195.7</v>
+        <v>203.98</v>
       </c>
       <c r="G222" s="3" t="n">
-        <v>1190</v>
+        <v>204</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>STLNETWORK</t>
+          <t>SILVERIETF</t>
         </is>
       </c>
       <c r="B223" s="3" t="inlineStr">
@@ -6931,22 +6931,22 @@
         </is>
       </c>
       <c r="D223" s="3" t="n">
-        <v>30.79</v>
+        <v>233.45</v>
       </c>
       <c r="E223" s="3" t="n">
-        <v>29.33</v>
+        <v>230.81</v>
       </c>
       <c r="F223" s="3" t="n">
-        <v>33.2</v>
+        <v>233.48</v>
       </c>
       <c r="G223" s="3" t="n">
-        <v>33.2</v>
+        <v>233.77</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>STLTECH</t>
+          <t>SKYGOLD</t>
         </is>
       </c>
       <c r="B224" s="3" t="inlineStr">
@@ -6960,22 +6960,22 @@
         </is>
       </c>
       <c r="D224" s="3" t="n">
-        <v>800.37</v>
+        <v>827.65</v>
       </c>
       <c r="E224" s="3" t="n">
-        <v>777.08</v>
+        <v>799.03</v>
       </c>
       <c r="F224" s="3" t="n">
-        <v>865.9</v>
+        <v>830.3</v>
       </c>
       <c r="G224" s="3" t="n">
-        <v>865.9</v>
+        <v>827</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>STYRENIX</t>
+          <t>SPECTRUM</t>
         </is>
       </c>
       <c r="B225" s="3" t="inlineStr">
@@ -6989,22 +6989,22 @@
         </is>
       </c>
       <c r="D225" s="3" t="n">
-        <v>2108</v>
+        <v>2702.33</v>
       </c>
       <c r="E225" s="3" t="n">
-        <v>2044.87</v>
+        <v>2606</v>
       </c>
       <c r="F225" s="3" t="n">
-        <v>2146.5</v>
+        <v>2878.6</v>
       </c>
       <c r="G225" s="3" t="n">
-        <v>2154</v>
+        <v>2878.6</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>SUKHJITS</t>
+          <t>SPLPETRO</t>
         </is>
       </c>
       <c r="B226" s="3" t="inlineStr">
@@ -7018,22 +7018,22 @@
         </is>
       </c>
       <c r="D226" s="3" t="n">
-        <v>162.87</v>
+        <v>828.8</v>
       </c>
       <c r="E226" s="3" t="n">
-        <v>157.69</v>
+        <v>797.0700000000001</v>
       </c>
       <c r="F226" s="3" t="n">
-        <v>160.03</v>
+        <v>828.15</v>
       </c>
       <c r="G226" s="3" t="n">
-        <v>160.03</v>
+        <v>830</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>SUNDARMFIN</t>
+          <t>SREEL</t>
         </is>
       </c>
       <c r="B227" s="3" t="inlineStr">
@@ -7047,22 +7047,22 @@
         </is>
       </c>
       <c r="D227" s="3" t="n">
-        <v>4709.9</v>
+        <v>343.67</v>
       </c>
       <c r="E227" s="3" t="n">
-        <v>4610.4</v>
+        <v>300.33</v>
       </c>
       <c r="F227" s="3" t="n">
-        <v>4728</v>
+        <v>370.3</v>
       </c>
       <c r="G227" s="3" t="n">
-        <v>4722.1</v>
+        <v>367.5</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>SUNDRMFAST</t>
+          <t>STALLION</t>
         </is>
       </c>
       <c r="B228" s="3" t="inlineStr">
@@ -7076,22 +7076,22 @@
         </is>
       </c>
       <c r="D228" s="3" t="n">
-        <v>1235.6</v>
+        <v>222.32</v>
       </c>
       <c r="E228" s="3" t="n">
-        <v>1201.4</v>
+        <v>214.03</v>
       </c>
       <c r="F228" s="3" t="n">
-        <v>1219.4</v>
+        <v>234.26</v>
       </c>
       <c r="G228" s="3" t="n">
-        <v>1216</v>
+        <v>234.57</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>SUNSHINE</t>
+          <t>STARHEALTH</t>
         </is>
       </c>
       <c r="B229" s="3" t="inlineStr">
@@ -7105,22 +7105,22 @@
         </is>
       </c>
       <c r="D229" s="3" t="n">
-        <v>495.8</v>
+        <v>578.2</v>
       </c>
       <c r="E229" s="3" t="n">
-        <v>464.25</v>
+        <v>558.08</v>
       </c>
       <c r="F229" s="3" t="n">
-        <v>481.2</v>
+        <v>576.25</v>
       </c>
       <c r="G229" s="3" t="n">
-        <v>479</v>
+        <v>578.9</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>SUPRIYA</t>
+          <t>STEELXIND</t>
         </is>
       </c>
       <c r="B230" s="3" t="inlineStr">
@@ -7134,22 +7134,22 @@
         </is>
       </c>
       <c r="D230" s="3" t="n">
-        <v>905.33</v>
+        <v>12.4</v>
       </c>
       <c r="E230" s="3" t="n">
-        <v>867.22</v>
+        <v>11.52</v>
       </c>
       <c r="F230" s="3" t="n">
-        <v>911.4</v>
+        <v>12.17</v>
       </c>
       <c r="G230" s="3" t="n">
-        <v>909</v>
+        <v>12.23</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>SWARNSAR</t>
+          <t>STLNETWORK</t>
         </is>
       </c>
       <c r="B231" s="3" t="inlineStr">
@@ -7163,22 +7163,22 @@
         </is>
       </c>
       <c r="D231" s="3" t="n">
-        <v>43.11</v>
+        <v>32.79</v>
       </c>
       <c r="E231" s="3" t="n">
-        <v>37.44</v>
+        <v>31.28</v>
       </c>
       <c r="F231" s="3" t="n">
-        <v>40.78</v>
+        <v>34.86</v>
       </c>
       <c r="G231" s="3" t="n">
-        <v>40.99</v>
+        <v>34.86</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>STLTECH</t>
         </is>
       </c>
       <c r="B232" s="3" t="inlineStr">
@@ -7192,22 +7192,22 @@
         </is>
       </c>
       <c r="D232" s="3" t="n">
-        <v>1591.67</v>
+        <v>849.83</v>
       </c>
       <c r="E232" s="3" t="n">
-        <v>1508.23</v>
+        <v>807.45</v>
       </c>
       <c r="F232" s="3" t="n">
-        <v>1622.4</v>
+        <v>854.75</v>
       </c>
       <c r="G232" s="3" t="n">
-        <v>1616</v>
+        <v>858</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>SYSTMTXC</t>
+          <t>STYRENIX</t>
         </is>
       </c>
       <c r="B233" s="3" t="inlineStr">
@@ -7221,22 +7221,22 @@
         </is>
       </c>
       <c r="D233" s="3" t="n">
-        <v>64.40000000000001</v>
+        <v>2138.67</v>
       </c>
       <c r="E233" s="3" t="n">
-        <v>62.71</v>
+        <v>2087.33</v>
       </c>
       <c r="F233" s="3" t="n">
-        <v>69.72</v>
+        <v>2142.9</v>
       </c>
       <c r="G233" s="3" t="n">
-        <v>69.72</v>
+        <v>2135</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>TAKE</t>
+          <t>SUNDARMFIN</t>
         </is>
       </c>
       <c r="B234" s="3" t="inlineStr">
@@ -7250,22 +7250,22 @@
         </is>
       </c>
       <c r="D234" s="3" t="n">
-        <v>14.77</v>
+        <v>4741.13</v>
       </c>
       <c r="E234" s="3" t="n">
-        <v>14.18</v>
+        <v>4640.5</v>
       </c>
       <c r="F234" s="3" t="n">
-        <v>15.99</v>
+        <v>4703</v>
       </c>
       <c r="G234" s="3" t="n">
-        <v>15.99</v>
+        <v>4693.9</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>TAMBOLIIN</t>
+          <t>SUNDRMFAST</t>
         </is>
       </c>
       <c r="B235" s="3" t="inlineStr">
@@ -7279,22 +7279,22 @@
         </is>
       </c>
       <c r="D235" s="3" t="n">
-        <v>270.77</v>
+        <v>1279</v>
       </c>
       <c r="E235" s="3" t="n">
-        <v>259.88</v>
+        <v>1211.93</v>
       </c>
       <c r="F235" s="3" t="n">
-        <v>285.7</v>
+        <v>1256.1</v>
       </c>
       <c r="G235" s="3" t="n">
-        <v>285.7</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>TDPOWERSYS</t>
+          <t>SUNSHINE</t>
         </is>
       </c>
       <c r="B236" s="3" t="inlineStr">
@@ -7308,22 +7308,22 @@
         </is>
       </c>
       <c r="D236" s="3" t="n">
-        <v>761.7</v>
+        <v>505.5</v>
       </c>
       <c r="E236" s="3" t="n">
-        <v>732.6799999999999</v>
+        <v>477.17</v>
       </c>
       <c r="F236" s="3" t="n">
-        <v>755.1</v>
+        <v>509.7</v>
       </c>
       <c r="G236" s="3" t="n">
-        <v>756</v>
+        <v>511</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>TECHNOCRAF</t>
+          <t>SUPRIYA</t>
         </is>
       </c>
       <c r="B237" s="3" t="inlineStr">
@@ -7337,22 +7337,22 @@
         </is>
       </c>
       <c r="D237" s="3" t="n">
-        <v>406.95</v>
+        <v>927.05</v>
       </c>
       <c r="E237" s="3" t="n">
-        <v>384.4</v>
+        <v>888.63</v>
       </c>
       <c r="F237" s="3" t="n">
-        <v>409</v>
+        <v>917.45</v>
       </c>
       <c r="G237" s="3" t="n">
-        <v>408.1</v>
+        <v>919.4</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>TEGA</t>
+          <t>SWANDEF</t>
         </is>
       </c>
       <c r="B238" s="3" t="inlineStr">
@@ -7366,22 +7366,22 @@
         </is>
       </c>
       <c r="D238" s="3" t="n">
-        <v>1646.43</v>
+        <v>2607.4</v>
       </c>
       <c r="E238" s="3" t="n">
-        <v>1567.1</v>
+        <v>2476.07</v>
       </c>
       <c r="F238" s="3" t="n">
-        <v>1678.3</v>
+        <v>2662.8</v>
       </c>
       <c r="G238" s="3" t="n">
-        <v>1680</v>
+        <v>2700</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>TEXMOPIPES</t>
+          <t>SYMBIOTEC</t>
         </is>
       </c>
       <c r="B239" s="3" t="inlineStr">
@@ -7395,22 +7395,22 @@
         </is>
       </c>
       <c r="D239" s="3" t="n">
-        <v>53.71</v>
+        <v>1154.65</v>
       </c>
       <c r="E239" s="3" t="n">
-        <v>47.96</v>
+        <v>1087.55</v>
       </c>
       <c r="F239" s="3" t="n">
-        <v>57.59</v>
+        <v>1138.95</v>
       </c>
       <c r="G239" s="3" t="n">
-        <v>58.25</v>
+        <v>1135.95</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>TITAGARH</t>
+          <t>SYSTMTXC</t>
         </is>
       </c>
       <c r="B240" s="3" t="inlineStr">
@@ -7424,22 +7424,22 @@
         </is>
       </c>
       <c r="D240" s="3" t="n">
-        <v>901.45</v>
+        <v>68.02</v>
       </c>
       <c r="E240" s="3" t="n">
-        <v>861.38</v>
+        <v>67.73999999999999</v>
       </c>
       <c r="F240" s="3" t="n">
-        <v>876.35</v>
+        <v>71.11</v>
       </c>
       <c r="G240" s="3" t="n">
-        <v>876.3</v>
+        <v>71.11</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>UDAYJEW</t>
+          <t>TAALTECH</t>
         </is>
       </c>
       <c r="B241" s="3" t="inlineStr">
@@ -7453,22 +7453,22 @@
         </is>
       </c>
       <c r="D241" s="3" t="n">
-        <v>174.72</v>
+        <v>4927.93</v>
       </c>
       <c r="E241" s="3" t="n">
-        <v>156.75</v>
+        <v>4594.67</v>
       </c>
       <c r="F241" s="3" t="n">
-        <v>174.55</v>
+        <v>5198.7</v>
       </c>
       <c r="G241" s="3" t="n">
-        <v>174.2</v>
+        <v>5232</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>UNIDT</t>
+          <t>TAKE</t>
         </is>
       </c>
       <c r="B242" s="3" t="inlineStr">
@@ -7482,22 +7482,22 @@
         </is>
       </c>
       <c r="D242" s="3" t="n">
-        <v>234.99</v>
+        <v>15.76</v>
       </c>
       <c r="E242" s="3" t="n">
-        <v>221.35</v>
+        <v>15.6</v>
       </c>
       <c r="F242" s="3" t="n">
-        <v>230.36</v>
+        <v>16.78</v>
       </c>
       <c r="G242" s="3" t="n">
-        <v>231.51</v>
+        <v>16.78</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>UNIMECH</t>
+          <t>TAMBOLIIN</t>
         </is>
       </c>
       <c r="B243" s="3" t="inlineStr">
@@ -7511,22 +7511,22 @@
         </is>
       </c>
       <c r="D243" s="3" t="n">
-        <v>1565.93</v>
+        <v>283.58</v>
       </c>
       <c r="E243" s="3" t="n">
-        <v>1499.8</v>
+        <v>271.88</v>
       </c>
       <c r="F243" s="3" t="n">
-        <v>1586.4</v>
+        <v>299.95</v>
       </c>
       <c r="G243" s="3" t="n">
-        <v>1587</v>
+        <v>299.95</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>UNIPARTS</t>
+          <t>TATSILV</t>
         </is>
       </c>
       <c r="B244" s="3" t="inlineStr">
@@ -7540,22 +7540,22 @@
         </is>
       </c>
       <c r="D244" s="3" t="n">
-        <v>905.23</v>
+        <v>22.75</v>
       </c>
       <c r="E244" s="3" t="n">
-        <v>868.02</v>
+        <v>22.43</v>
       </c>
       <c r="F244" s="3" t="n">
-        <v>894.05</v>
+        <v>22.69</v>
       </c>
       <c r="G244" s="3" t="n">
-        <v>892.25</v>
+        <v>22.73</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>UNIVPHOTO</t>
+          <t>TCC</t>
         </is>
       </c>
       <c r="B245" s="3" t="inlineStr">
@@ -7569,22 +7569,22 @@
         </is>
       </c>
       <c r="D245" s="3" t="n">
-        <v>524.37</v>
+        <v>54.11</v>
       </c>
       <c r="E245" s="3" t="n">
-        <v>495.83</v>
+        <v>45.97</v>
       </c>
       <c r="F245" s="3" t="n">
-        <v>566.25</v>
+        <v>53.62</v>
       </c>
       <c r="G245" s="3" t="n">
-        <v>567</v>
+        <v>55.73</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>UTIAMC</t>
+          <t>TECHNOCRAF</t>
         </is>
       </c>
       <c r="B246" s="3" t="inlineStr">
@@ -7598,22 +7598,22 @@
         </is>
       </c>
       <c r="D246" s="3" t="n">
-        <v>893.7</v>
+        <v>425.48</v>
       </c>
       <c r="E246" s="3" t="n">
-        <v>884.38</v>
+        <v>400.03</v>
       </c>
       <c r="F246" s="3" t="n">
-        <v>900.9</v>
+        <v>439.4</v>
       </c>
       <c r="G246" s="3" t="n">
-        <v>901.1</v>
+        <v>438.7</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>UTISENSETF</t>
+          <t>TECHNOE</t>
         </is>
       </c>
       <c r="B247" s="3" t="inlineStr">
@@ -7627,22 +7627,22 @@
         </is>
       </c>
       <c r="D247" s="3" t="n">
-        <v>941.63</v>
+        <v>996.15</v>
       </c>
       <c r="E247" s="3" t="n">
-        <v>933.52</v>
+        <v>964.12</v>
       </c>
       <c r="F247" s="3" t="n">
-        <v>939.25</v>
+        <v>977.85</v>
       </c>
       <c r="G247" s="3" t="n">
-        <v>938.3200000000001</v>
+        <v>975.15</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>VALIANTORG</t>
+          <t>TEGA</t>
         </is>
       </c>
       <c r="B248" s="3" t="inlineStr">
@@ -7656,22 +7656,22 @@
         </is>
       </c>
       <c r="D248" s="3" t="n">
-        <v>340.83</v>
+        <v>1720.63</v>
       </c>
       <c r="E248" s="3" t="n">
-        <v>328.35</v>
+        <v>1619.1</v>
       </c>
       <c r="F248" s="3" t="n">
-        <v>359.5</v>
+        <v>1721.6</v>
       </c>
       <c r="G248" s="3" t="n">
-        <v>359.5</v>
+        <v>1729.5</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>VENUSPIPES</t>
+          <t>TEXMOPIPES</t>
         </is>
       </c>
       <c r="B249" s="3" t="inlineStr">
@@ -7685,22 +7685,22 @@
         </is>
       </c>
       <c r="D249" s="3" t="n">
-        <v>1821.33</v>
+        <v>58.86</v>
       </c>
       <c r="E249" s="3" t="n">
-        <v>1714.27</v>
+        <v>51.45</v>
       </c>
       <c r="F249" s="3" t="n">
-        <v>1930.1</v>
+        <v>56.44</v>
       </c>
       <c r="G249" s="3" t="n">
-        <v>1942</v>
+        <v>57.36</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>VHLTD-RE1</t>
+          <t>THERMAX</t>
         </is>
       </c>
       <c r="B250" s="3" t="inlineStr">
@@ -7714,22 +7714,22 @@
         </is>
       </c>
       <c r="D250" s="3" t="n">
-        <v>0.51</v>
+        <v>3697.27</v>
       </c>
       <c r="E250" s="3" t="n">
-        <v>0.44</v>
+        <v>3610.93</v>
       </c>
       <c r="F250" s="3" t="n">
-        <v>0.68</v>
+        <v>3645.4</v>
       </c>
       <c r="G250" s="3" t="n">
-        <v>0.68</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>VSTL</t>
+          <t>TIMKEN</t>
         </is>
       </c>
       <c r="B251" s="3" t="inlineStr">
@@ -7743,22 +7743,22 @@
         </is>
       </c>
       <c r="D251" s="3" t="n">
-        <v>122.5</v>
+        <v>3226.33</v>
       </c>
       <c r="E251" s="3" t="n">
-        <v>118.17</v>
+        <v>3097.4</v>
       </c>
       <c r="F251" s="3" t="n">
-        <v>123.41</v>
+        <v>3297.2</v>
       </c>
       <c r="G251" s="3" t="n">
-        <v>123.5</v>
+        <v>3296.8</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>WEALTH</t>
+          <t>TIRUMALCHM</t>
         </is>
       </c>
       <c r="B252" s="3" t="inlineStr">
@@ -7772,22 +7772,22 @@
         </is>
       </c>
       <c r="D252" s="3" t="n">
-        <v>852.23</v>
+        <v>161.23</v>
       </c>
       <c r="E252" s="3" t="n">
-        <v>834.72</v>
+        <v>156.01</v>
       </c>
       <c r="F252" s="3" t="n">
-        <v>848.35</v>
+        <v>157.52</v>
       </c>
       <c r="G252" s="3" t="n">
-        <v>848.85</v>
+        <v>157.5</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>WHEELS</t>
+          <t>TSFINV</t>
         </is>
       </c>
       <c r="B253" s="3" t="inlineStr">
@@ -7801,22 +7801,22 @@
         </is>
       </c>
       <c r="D253" s="3" t="n">
-        <v>2009.53</v>
+        <v>428.4</v>
       </c>
       <c r="E253" s="3" t="n">
-        <v>1822.77</v>
+        <v>412.37</v>
       </c>
       <c r="F253" s="3" t="n">
-        <v>2400.6</v>
+        <v>441.15</v>
       </c>
       <c r="G253" s="3" t="n">
-        <v>2450</v>
+        <v>441</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>WOCKPHARMA</t>
+          <t>UDAYJEW</t>
         </is>
       </c>
       <c r="B254" s="3" t="inlineStr">
@@ -7830,22 +7830,22 @@
         </is>
       </c>
       <c r="D254" s="3" t="n">
-        <v>2205.8</v>
+        <v>177.81</v>
       </c>
       <c r="E254" s="3" t="n">
-        <v>2082.77</v>
+        <v>165.75</v>
       </c>
       <c r="F254" s="3" t="n">
-        <v>2248.8</v>
+        <v>175.12</v>
       </c>
       <c r="G254" s="3" t="n">
-        <v>2240</v>
+        <v>175</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>XCHANGING</t>
+          <t>UNIINFO</t>
         </is>
       </c>
       <c r="B255" s="3" t="inlineStr">
@@ -7859,22 +7859,22 @@
         </is>
       </c>
       <c r="D255" s="3" t="n">
-        <v>63.78</v>
+        <v>11.33</v>
       </c>
       <c r="E255" s="3" t="n">
-        <v>60.97</v>
+        <v>10.78</v>
       </c>
       <c r="F255" s="3" t="n">
-        <v>63.28</v>
+        <v>11.27</v>
       </c>
       <c r="G255" s="3" t="n">
-        <v>64.73</v>
+        <v>11.49</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>XTRANET</t>
+          <t>UNIPARTS</t>
         </is>
       </c>
       <c r="B256" s="3" t="inlineStr">
@@ -7888,45 +7888,567 @@
         </is>
       </c>
       <c r="D256" s="3" t="n">
-        <v>288.81</v>
+        <v>908.6</v>
       </c>
       <c r="E256" s="3" t="n">
-        <v>255.22</v>
+        <v>881.33</v>
       </c>
       <c r="F256" s="3" t="n">
-        <v>293.37</v>
+        <v>893.85</v>
       </c>
       <c r="G256" s="3" t="n">
-        <v>293.37</v>
+        <v>895</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
         <is>
+          <t>UNIVPHOTO</t>
+        </is>
+      </c>
+      <c r="B257" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C257" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D257" s="3" t="n">
+        <v>554.17</v>
+      </c>
+      <c r="E257" s="3" t="n">
+        <v>523.6799999999999</v>
+      </c>
+      <c r="F257" s="3" t="n">
+        <v>540.5</v>
+      </c>
+      <c r="G257" s="3" t="n">
+        <v>540.5</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="inlineStr">
+        <is>
+          <t>UTISENSETF</t>
+        </is>
+      </c>
+      <c r="B258" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C258" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D258" s="3" t="n">
+        <v>941.63</v>
+      </c>
+      <c r="E258" s="3" t="n">
+        <v>933.52</v>
+      </c>
+      <c r="F258" s="3" t="n">
+        <v>939.25</v>
+      </c>
+      <c r="G258" s="3" t="n">
+        <v>938.3200000000001</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="inlineStr">
+        <is>
+          <t>UTLSOLAR</t>
+        </is>
+      </c>
+      <c r="B259" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C259" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D259" s="3" t="n">
+        <v>449.1</v>
+      </c>
+      <c r="E259" s="3" t="n">
+        <v>428.42</v>
+      </c>
+      <c r="F259" s="3" t="n">
+        <v>441.25</v>
+      </c>
+      <c r="G259" s="3" t="n">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="inlineStr">
+        <is>
+          <t>VALIANTLAB</t>
+        </is>
+      </c>
+      <c r="B260" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C260" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D260" s="3" t="n">
+        <v>118.85</v>
+      </c>
+      <c r="E260" s="3" t="n">
+        <v>113.46</v>
+      </c>
+      <c r="F260" s="3" t="n">
+        <v>124.8</v>
+      </c>
+      <c r="G260" s="3" t="n">
+        <v>124.98</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="inlineStr">
+        <is>
+          <t>VARDHACRLC</t>
+        </is>
+      </c>
+      <c r="B261" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C261" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D261" s="3" t="n">
+        <v>44.55</v>
+      </c>
+      <c r="E261" s="3" t="n">
+        <v>43.39</v>
+      </c>
+      <c r="F261" s="3" t="n">
+        <v>44.25</v>
+      </c>
+      <c r="G261" s="3" t="n">
+        <v>44.28</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="inlineStr">
+        <is>
+          <t>VARDMNPOLY</t>
+        </is>
+      </c>
+      <c r="B262" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C262" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D262" s="3" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="E262" s="3" t="n">
+        <v>5.84</v>
+      </c>
+      <c r="F262" s="3" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="G262" s="3" t="n">
+        <v>5.91</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="inlineStr">
+        <is>
+          <t>VARROC</t>
+        </is>
+      </c>
+      <c r="B263" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C263" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D263" s="3" t="n">
+        <v>861.38</v>
+      </c>
+      <c r="E263" s="3" t="n">
+        <v>829.37</v>
+      </c>
+      <c r="F263" s="3" t="n">
+        <v>884.4</v>
+      </c>
+      <c r="G263" s="3" t="n">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="inlineStr">
+        <is>
+          <t>VCL</t>
+        </is>
+      </c>
+      <c r="B264" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C264" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D264" s="3" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="E264" s="3" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="F264" s="3" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="G264" s="3" t="n">
+        <v>1.73</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="inlineStr">
+        <is>
+          <t>VENKEYS</t>
+        </is>
+      </c>
+      <c r="B265" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C265" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D265" s="3" t="n">
+        <v>1712.9</v>
+      </c>
+      <c r="E265" s="3" t="n">
+        <v>1664.57</v>
+      </c>
+      <c r="F265" s="3" t="n">
+        <v>1706.7</v>
+      </c>
+      <c r="G265" s="3" t="n">
+        <v>1704</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="inlineStr">
+        <is>
+          <t>VHLTD-RE1</t>
+        </is>
+      </c>
+      <c r="B266" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C266" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D266" s="3" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="E266" s="3" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="F266" s="3" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G266" s="3" t="n">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="inlineStr">
+        <is>
+          <t>VIPCLOTHNG</t>
+        </is>
+      </c>
+      <c r="B267" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C267" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D267" s="3" t="n">
+        <v>21.71</v>
+      </c>
+      <c r="E267" s="3" t="n">
+        <v>20.42</v>
+      </c>
+      <c r="F267" s="3" t="n">
+        <v>21.26</v>
+      </c>
+      <c r="G267" s="3" t="n">
+        <v>21.25</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="inlineStr">
+        <is>
+          <t>WABAG</t>
+        </is>
+      </c>
+      <c r="B268" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C268" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D268" s="3" t="n">
+        <v>2159.03</v>
+      </c>
+      <c r="E268" s="3" t="n">
+        <v>2037.8</v>
+      </c>
+      <c r="F268" s="3" t="n">
+        <v>2211.8</v>
+      </c>
+      <c r="G268" s="3" t="n">
+        <v>2207</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="inlineStr">
+        <is>
+          <t>WEBELSOLAR</t>
+        </is>
+      </c>
+      <c r="B269" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C269" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D269" s="3" t="n">
+        <v>77.97</v>
+      </c>
+      <c r="E269" s="3" t="n">
+        <v>74.67</v>
+      </c>
+      <c r="F269" s="3" t="n">
+        <v>75.39</v>
+      </c>
+      <c r="G269" s="3" t="n">
+        <v>75.73999999999999</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="inlineStr">
+        <is>
+          <t>WENDT</t>
+        </is>
+      </c>
+      <c r="B270" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C270" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D270" s="3" t="n">
+        <v>8603</v>
+      </c>
+      <c r="E270" s="3" t="n">
+        <v>8179.5</v>
+      </c>
+      <c r="F270" s="3" t="n">
+        <v>8669.5</v>
+      </c>
+      <c r="G270" s="3" t="n">
+        <v>8705</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="2" t="inlineStr">
+        <is>
+          <t>WHEELS</t>
+        </is>
+      </c>
+      <c r="B271" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C271" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D271" s="3" t="n">
+        <v>2249.3</v>
+      </c>
+      <c r="E271" s="3" t="n">
+        <v>1999.7</v>
+      </c>
+      <c r="F271" s="3" t="n">
+        <v>2313</v>
+      </c>
+      <c r="G271" s="3" t="n">
+        <v>2267</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="2" t="inlineStr">
+        <is>
+          <t>XTRANET</t>
+        </is>
+      </c>
+      <c r="B272" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C272" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D272" s="3" t="n">
+        <v>296.72</v>
+      </c>
+      <c r="E272" s="3" t="n">
+        <v>269.13</v>
+      </c>
+      <c r="F272" s="3" t="n">
+        <v>285.59</v>
+      </c>
+      <c r="G272" s="3" t="n">
+        <v>280.3</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="2" t="inlineStr">
+        <is>
+          <t>YUKEN</t>
+        </is>
+      </c>
+      <c r="B273" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C273" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D273" s="3" t="n">
+        <v>1080.92</v>
+      </c>
+      <c r="E273" s="3" t="n">
+        <v>1018.57</v>
+      </c>
+      <c r="F273" s="3" t="n">
+        <v>1085.7</v>
+      </c>
+      <c r="G273" s="3" t="n">
+        <v>1089.95</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="inlineStr">
+        <is>
+          <t>ZFSTEERING</t>
+        </is>
+      </c>
+      <c r="B274" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C274" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D274" s="3" t="n">
+        <v>718.3</v>
+      </c>
+      <c r="E274" s="3" t="n">
+        <v>668.15</v>
+      </c>
+      <c r="F274" s="3" t="n">
+        <v>743.4</v>
+      </c>
+      <c r="G274" s="3" t="n">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="2" t="inlineStr">
+        <is>
           <t>ZIMLAB</t>
         </is>
       </c>
-      <c r="B257" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C257" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D257" s="3" t="n">
-        <v>132.03</v>
-      </c>
-      <c r="E257" s="3" t="n">
-        <v>125.97</v>
-      </c>
-      <c r="F257" s="3" t="n">
-        <v>133.35</v>
-      </c>
-      <c r="G257" s="3" t="n">
-        <v>135</v>
+      <c r="B275" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C275" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D275" s="3" t="n">
+        <v>137.2</v>
+      </c>
+      <c r="E275" s="3" t="n">
+        <v>128.67</v>
+      </c>
+      <c r="F275" s="3" t="n">
+        <v>136.43</v>
+      </c>
+      <c r="G275" s="3" t="n">
+        <v>137.2</v>
       </c>
     </row>
   </sheetData>
